--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9D2A75-D6C5-4596-A8E7-FDCAEBD8B0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA016C5-42DB-42FF-A23B-1772A447A0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$L$125</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="263">
   <si>
     <t>TOTAL</t>
   </si>
@@ -578,9 +578,6 @@
     <t>Sra. Abogada Lorena Ferreiro - Honorarios</t>
   </si>
   <si>
-    <t>Ingreso efectivo - Cuota 3/24 - Plan de pagos 3A</t>
-  </si>
-  <si>
     <t>Abono ascensor - Lema Ascensores - Mantenimiento</t>
   </si>
   <si>
@@ -733,9 +730,6 @@
     <t>Russo Ruben Alberto - 2 Cabos de madera</t>
   </si>
   <si>
-    <t>Acuerdo de deuda 4G - Plan de pago</t>
-  </si>
-  <si>
     <t>Doartero Julio - Inspeccion de gas</t>
   </si>
   <si>
@@ -812,6 +806,39 @@
   </si>
   <si>
     <t>Fernando daniel Minxxo / Jeremy Naguel</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados 5F</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado del mes de Diciembre 5F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan de pago de 4G: Consta de 7 cuotas de $170.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t>Acuerdo de deuda 4G - Plan de pago (Abonado por UF)</t>
+  </si>
+  <si>
+    <t>Acuerdo de deuda 11C - Plan de pago (Abonado por UF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan de pago de 11C: Consta de 11 cuotas de 250.000 + expensas en curso </t>
+  </si>
+  <si>
+    <t>Adelanto de plan de pagos 4G</t>
+  </si>
+  <si>
+    <t>Adelanto de plan de pagos 11C</t>
+  </si>
+  <si>
+    <t>Adelanto plan de pagos 6B</t>
+  </si>
+  <si>
+    <t>Acuerdo de deuda 6B - Plan de pago (Abonado por UF)</t>
+  </si>
+  <si>
+    <t>Ingreso efectivo - Cuota 4/24 - Plan de pagos 3A</t>
   </si>
 </sst>
 </file>
@@ -828,7 +855,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1009,15 +1036,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1093,12 +1113,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1466,7 +1480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1755,12 +1769,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="14" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="8" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1771,8 +1779,22 @@
     <xf numFmtId="8" fontId="14" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="11" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="15" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="15" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="15" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="15" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1784,11 +1806,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="20" fillId="16" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="16" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="19" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="19" fillId="16" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="16" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="12" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="12" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="12" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="12" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="16" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1807,6 +1847,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1825,12 +1868,78 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1846,97 +1955,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="17" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="19" fillId="17" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="17" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="17" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2300,7 +2325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2318,12 +2343,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="223" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="207"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="224"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -2336,12 +2361,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="225" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="209"/>
+      <c r="C3" s="225"/>
+      <c r="D3" s="225"/>
+      <c r="E3" s="226"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -2359,7 +2384,7 @@
         <v>156</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2379,49 +2404,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="210" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="210"/>
+      <c r="B8" s="227" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="227"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="210"/>
-      <c r="C9" s="210"/>
+      <c r="B9" s="227"/>
+      <c r="C9" s="227"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="210"/>
-      <c r="C10" s="210"/>
+      <c r="B10" s="227"/>
+      <c r="C10" s="227"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="211" t="s">
+      <c r="A13" s="228" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="211"/>
-      <c r="C13" s="211"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="211"/>
+      <c r="B13" s="228"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="211"/>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
+      <c r="A14" s="228"/>
+      <c r="B14" s="228"/>
+      <c r="C14" s="228"/>
+      <c r="D14" s="228"/>
+      <c r="E14" s="228"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="211"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
+      <c r="A15" s="228"/>
+      <c r="B15" s="228"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="228"/>
+      <c r="E15" s="228"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="211"/>
-      <c r="B16" s="211"/>
-      <c r="C16" s="211"/>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
+      <c r="A16" s="228"/>
+      <c r="B16" s="228"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="228"/>
+      <c r="E16" s="228"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2447,48 +2472,48 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="200" t="s">
+      <c r="A22" s="216" t="s">
         <v>177</v>
       </c>
-      <c r="B22" s="201"/>
+      <c r="B22" s="217"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="186">
+      <c r="D22" s="184">
         <v>2182238</v>
       </c>
       <c r="E22" s="48"/>
       <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="200" t="s">
+      <c r="A23" s="216" t="s">
         <v>178</v>
       </c>
-      <c r="B23" s="201"/>
+      <c r="B23" s="217"/>
       <c r="C23" s="22"/>
-      <c r="D23" s="186">
+      <c r="D23" s="184">
         <v>-474636.76</v>
       </c>
       <c r="E23" s="24"/>
       <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="200" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="201"/>
+      <c r="A24" s="216" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="217"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="187">
+      <c r="D24" s="185">
         <v>1381383</v>
       </c>
       <c r="E24" s="24"/>
       <c r="H24" s="23"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="200" t="s">
+      <c r="A25" s="216" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="201"/>
+      <c r="B25" s="217"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="187">
+      <c r="D25" s="185">
         <v>0.76</v>
       </c>
       <c r="E25" s="24"/>
@@ -2508,7 +2533,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -2517,7 +2542,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -2549,7 +2574,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B31" s="122"/>
       <c r="C31" s="122"/>
@@ -2557,7 +2582,7 @@
         <v>13757.84</v>
       </c>
       <c r="E31" s="132" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -2570,7 +2595,7 @@
         <v>1235711.01</v>
       </c>
       <c r="E32" s="132" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2583,7 +2608,7 @@
         <v>225490.24</v>
       </c>
       <c r="E33" s="132" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,29 +2670,29 @@
       <c r="E38" s="29"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="203" t="s">
+      <c r="A39" s="219" t="s">
         <v>150</v>
       </c>
-      <c r="B39" s="204"/>
+      <c r="B39" s="220"/>
       <c r="C39" s="32"/>
-      <c r="D39" s="185">
+      <c r="D39" s="183">
         <v>313739</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="203" t="s">
+      <c r="A40" s="219" t="s">
         <v>151</v>
       </c>
-      <c r="B40" s="204"/>
+      <c r="B40" s="220"/>
       <c r="C40" s="32"/>
       <c r="D40" s="178">
         <v>5204</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2696,14 +2721,14 @@
         <v>113</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C43" s="37"/>
       <c r="D43" s="39">
         <v>542686.9</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2711,7 +2736,7 @@
         <v>113</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="39">
@@ -2724,7 +2749,7 @@
         <v>113</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="39">
@@ -2742,20 +2767,20 @@
         <v>10111.620000000001</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="203" t="s">
+      <c r="A47" s="219" t="s">
         <v>115</v>
       </c>
-      <c r="B47" s="204"/>
+      <c r="B47" s="220"/>
       <c r="C47" s="37"/>
       <c r="D47" s="39">
         <v>4813938.26</v>
       </c>
       <c r="E47" s="177" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2787,89 +2812,89 @@
       <c r="E50" s="44"/>
     </row>
     <row r="51" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="200" t="s">
-        <v>181</v>
-      </c>
-      <c r="B51" s="201"/>
+      <c r="A51" s="216" t="s">
+        <v>180</v>
+      </c>
+      <c r="B51" s="217"/>
       <c r="C51" s="37"/>
       <c r="D51" s="39">
         <v>225000</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="200" t="s">
-        <v>206</v>
-      </c>
-      <c r="B52" s="201"/>
+      <c r="A52" s="216" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" s="217"/>
       <c r="C52" s="37"/>
       <c r="D52" s="39">
         <v>500000</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="200" t="s">
-        <v>210</v>
-      </c>
-      <c r="B53" s="201"/>
+      <c r="A53" s="216" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="217"/>
       <c r="C53" s="37"/>
       <c r="D53" s="39">
         <v>1520000</v>
       </c>
       <c r="E53" s="170" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="200" t="s">
-        <v>241</v>
-      </c>
-      <c r="B54" s="201"/>
+      <c r="A54" s="216" t="s">
+        <v>239</v>
+      </c>
+      <c r="B54" s="217"/>
       <c r="C54" s="37"/>
       <c r="D54" s="39">
         <f>272252*2</f>
         <v>544504</v>
       </c>
       <c r="E54" s="170" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="200" t="s">
-        <v>225</v>
-      </c>
-      <c r="B55" s="201"/>
+      <c r="A55" s="216" t="s">
+        <v>224</v>
+      </c>
+      <c r="B55" s="217"/>
       <c r="C55" s="37"/>
       <c r="D55" s="39">
         <v>85000</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F55" s="64"/>
     </row>
     <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="200" t="s">
-        <v>247</v>
-      </c>
-      <c r="B56" s="201"/>
+      <c r="A56" s="216" t="s">
+        <v>245</v>
+      </c>
+      <c r="B56" s="217"/>
       <c r="C56" s="37"/>
       <c r="D56" s="39">
         <v>120000</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F56" s="64"/>
     </row>
     <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="37"/>
@@ -2877,41 +2902,41 @@
         <v>35000</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F57" s="64"/>
     </row>
     <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="200" t="s">
-        <v>226</v>
-      </c>
-      <c r="B58" s="201"/>
+      <c r="A58" s="216" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" s="217"/>
       <c r="C58" s="37"/>
       <c r="D58" s="39">
         <v>6000</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F58" s="64"/>
     </row>
     <row r="59" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="200" t="s">
-        <v>230</v>
-      </c>
-      <c r="B59" s="201"/>
+      <c r="A59" s="216" t="s">
+        <v>228</v>
+      </c>
+      <c r="B59" s="217"/>
       <c r="C59" s="37"/>
       <c r="D59" s="39">
         <v>7000000</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F59" s="64"/>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="37"/>
@@ -2925,7 +2950,7 @@
     </row>
     <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="140" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="37"/>
@@ -2933,13 +2958,13 @@
         <v>150800</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F61" s="64"/>
     </row>
     <row r="62" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="180" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B62" s="181"/>
       <c r="C62" s="37"/>
@@ -2947,27 +2972,27 @@
         <v>910000</v>
       </c>
       <c r="E62" s="48" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F62" s="64"/>
     </row>
     <row r="63" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="200" t="s">
-        <v>223</v>
-      </c>
-      <c r="B63" s="201"/>
+      <c r="A63" s="216" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="217"/>
       <c r="C63" s="37"/>
       <c r="D63" s="39">
         <v>250000</v>
       </c>
       <c r="E63" s="48" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F63" s="64"/>
     </row>
     <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="140" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B64" s="21"/>
       <c r="C64" s="37"/>
@@ -2975,35 +3000,35 @@
         <v>133300</v>
       </c>
       <c r="E64" s="48" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F64" s="64"/>
     </row>
     <row r="65" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="200" t="s">
-        <v>216</v>
-      </c>
-      <c r="B65" s="201"/>
+      <c r="A65" s="216" t="s">
+        <v>215</v>
+      </c>
+      <c r="B65" s="217"/>
       <c r="C65" s="37"/>
       <c r="D65" s="39">
         <v>105602.65</v>
       </c>
       <c r="E65" s="48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F65" s="64"/>
     </row>
     <row r="66" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="200" t="s">
-        <v>200</v>
-      </c>
-      <c r="B66" s="201"/>
+      <c r="A66" s="216" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="217"/>
       <c r="C66" s="37"/>
       <c r="D66" s="39">
         <v>2022800</v>
       </c>
       <c r="E66" s="48" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3028,12 +3053,12 @@
       <c r="E68" s="19"/>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="200" t="s">
-        <v>208</v>
-      </c>
-      <c r="B69" s="201"/>
+      <c r="A69" s="216" t="s">
+        <v>207</v>
+      </c>
+      <c r="B69" s="217"/>
       <c r="C69" s="22"/>
-      <c r="D69" s="184">
+      <c r="D69" s="182">
         <v>650000</v>
       </c>
       <c r="E69" s="48"/>
@@ -3048,25 +3073,25 @@
         <v>125000</v>
       </c>
       <c r="E70" s="48" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="200" t="s">
-        <v>240</v>
-      </c>
-      <c r="B71" s="201"/>
+      <c r="A71" s="216" t="s">
+        <v>238</v>
+      </c>
+      <c r="B71" s="217"/>
       <c r="C71" s="22"/>
       <c r="D71" s="139">
         <v>62500</v>
       </c>
       <c r="E71" s="48" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="140" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="22"/>
@@ -3074,7 +3099,7 @@
         <v>45000</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3217,8 +3242,8 @@
       <c r="E87" s="74"/>
     </row>
     <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="200"/>
-      <c r="B88" s="201"/>
+      <c r="A88" s="216"/>
+      <c r="B88" s="217"/>
       <c r="C88" s="37"/>
       <c r="D88" s="46"/>
       <c r="E88" s="74"/>
@@ -3276,8 +3301,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="79" t="s">
         <v>125</v>
       </c>
@@ -3286,7 +3311,7 @@
         <v>25293837.280000001</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="79" t="s">
         <v>126</v>
       </c>
@@ -3295,7 +3320,7 @@
         <v>25293837.280000001</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="79" t="s">
         <v>127</v>
       </c>
@@ -3304,7 +3329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="79" t="s">
         <v>128</v>
       </c>
@@ -3313,189 +3338,275 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="205" t="s">
-        <v>183</v>
-      </c>
-      <c r="B103" s="205"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="205"/>
-      <c r="B104" s="205"/>
-    </row>
-    <row r="105" spans="1:6" s="83" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-      <c r="B105" s="81"/>
-      <c r="C105" s="82"/>
-    </row>
-    <row r="106" spans="1:6" s="83" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="137" t="s">
+    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="222" t="s">
+        <v>254</v>
+      </c>
+      <c r="B104" s="222"/>
+    </row>
+    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="222"/>
+      <c r="B105" s="222"/>
+    </row>
+    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="222"/>
+      <c r="B106" s="222"/>
+    </row>
+    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="222" t="s">
+        <v>257</v>
+      </c>
+      <c r="B108" s="222"/>
+    </row>
+    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="222"/>
+      <c r="B109" s="222"/>
+    </row>
+    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="222"/>
+      <c r="B110" s="222"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="221" t="s">
+        <v>182</v>
+      </c>
+      <c r="B113" s="221"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="221"/>
+      <c r="B114" s="221"/>
+    </row>
+    <row r="115" spans="1:6" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115"/>
+      <c r="B115" s="81"/>
+      <c r="C115" s="82"/>
+    </row>
+    <row r="116" spans="1:6" s="83" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="137" t="s">
         <v>175</v>
       </c>
-      <c r="B106" s="84">
-        <v>15946414.27</v>
-      </c>
-      <c r="C106" s="82"/>
-      <c r="D106" s="85"/>
-      <c r="E106" s="85"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="32" t="s">
+      <c r="B116" s="84">
+        <v>10597369.743745035</v>
+      </c>
+      <c r="C116" s="82"/>
+      <c r="D116" s="85"/>
+      <c r="E116" s="85"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="B107" s="86">
+      <c r="B117" s="86">
         <f>-B99-B100</f>
         <v>-25293837.280000001</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="32" t="s">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="B108" s="86">
-        <f>B124</f>
+      <c r="B118" s="86">
+        <f>B140</f>
         <v>195940.3</v>
       </c>
-      <c r="F108" s="81"/>
-    </row>
-    <row r="109" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="B109" s="157">
+      <c r="F118" s="81"/>
+    </row>
+    <row r="119" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B119" s="157">
         <v>-239116.53</v>
       </c>
-      <c r="F109" s="81"/>
-    </row>
-    <row r="110" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="B110" s="158">
+      <c r="F119" s="81"/>
+    </row>
+    <row r="120" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="B120" s="158">
         <f>-119452</f>
         <v>-119452</v>
       </c>
-      <c r="F110" s="81"/>
-    </row>
-    <row r="111" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A111" s="32" t="s">
-        <v>250</v>
-      </c>
-      <c r="B111" s="158">
+      <c r="F120" s="81"/>
+    </row>
+    <row r="121" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A121" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="B121" s="158">
         <v>-123612</v>
       </c>
-      <c r="F111" s="81"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="B112" s="158">
+      <c r="F121" s="81"/>
+    </row>
+    <row r="122" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="B122" s="158">
+        <v>-168836.39</v>
+      </c>
+      <c r="F122" s="81"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="B123" s="158">
+        <v>-20871</v>
+      </c>
+      <c r="F123" s="81"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="B124" s="158">
         <v>-3820</v>
       </c>
-      <c r="F112" s="81"/>
-    </row>
-    <row r="113" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="B113" s="158">
+      <c r="F124" s="81"/>
+    </row>
+    <row r="125" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="B125" s="158">
         <v>-7274</v>
       </c>
-      <c r="F113" s="81"/>
-    </row>
-    <row r="114" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="B114" s="156">
+      <c r="F125" s="81"/>
+    </row>
+    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="B126" s="156">
         <v>-7528</v>
       </c>
-      <c r="F114" s="81"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="32" t="s">
+      <c r="F126" s="81"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B115" s="87">
+      <c r="B127" s="87">
         <f>PRORRATEO!F117</f>
-        <v>13512038.039999999</v>
-      </c>
-      <c r="F115" s="81"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="B116" s="183">
-        <v>-132000</v>
-      </c>
-      <c r="F116" s="81"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="32"/>
-      <c r="B117" s="182"/>
-      <c r="F117" s="81"/>
-    </row>
-    <row r="118" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="88" t="s">
-        <v>180</v>
-      </c>
-      <c r="B118" s="171">
-        <v>122500</v>
-      </c>
-      <c r="F118" s="81"/>
-    </row>
-    <row r="119" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="89" t="s">
+        <v>13927009.310000001</v>
+      </c>
+      <c r="F127" s="81"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="B128" s="87">
+        <v>300000</v>
+      </c>
+      <c r="F128" s="81"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="B129" s="87">
+        <v>250000</v>
+      </c>
+      <c r="F129" s="81"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="B130" s="87">
+        <v>200000.42</v>
+      </c>
+      <c r="F130" s="81"/>
+    </row>
+    <row r="131" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="B131" s="214">
+        <v>-130000</v>
+      </c>
+      <c r="F131" s="81"/>
+    </row>
+    <row r="132" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A132" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="B132" s="214">
+        <v>-130000</v>
+      </c>
+      <c r="F132" s="81"/>
+    </row>
+    <row r="133" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="B133" s="214">
+        <v>-130000</v>
+      </c>
+      <c r="F133" s="81"/>
+    </row>
+    <row r="134" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A134" s="88" t="s">
+        <v>262</v>
+      </c>
+      <c r="B134" s="171">
+        <v>123300</v>
+      </c>
+      <c r="F134" s="81"/>
+    </row>
+    <row r="135" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="B119" s="90">
-        <f>SUM(B106:C118)</f>
-        <v>3850252.7999999989</v>
-      </c>
-      <c r="D119" s="81"/>
-      <c r="E119" s="64"/>
-      <c r="F119" s="64"/>
-    </row>
-    <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="202" t="s">
+      <c r="B135" s="90">
+        <f>SUM(B116:C134)</f>
+        <v>-780727.42625496525</v>
+      </c>
+      <c r="D135" s="81"/>
+      <c r="E135" s="64"/>
+      <c r="F135" s="64"/>
+    </row>
+    <row r="136" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="218" t="s">
         <v>130</v>
       </c>
-      <c r="B121" s="202"/>
-      <c r="C121" s="202"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="202"/>
-      <c r="B122" s="202"/>
-      <c r="C122" s="202"/>
-    </row>
-    <row r="123" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="91" t="s">
-        <v>249</v>
-      </c>
-      <c r="B123" s="169">
+      <c r="B137" s="218"/>
+      <c r="C137" s="218"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="218"/>
+      <c r="B138" s="218"/>
+      <c r="C138" s="218"/>
+    </row>
+    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="91" t="s">
+        <v>247</v>
+      </c>
+      <c r="B139" s="169">
         <v>195940.3</v>
       </c>
-      <c r="C123" s="92"/>
-      <c r="D123" s="70"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="B124" s="94">
-        <f>SUM(B123:B123)</f>
+      <c r="C139" s="92"/>
+      <c r="D139" s="70"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="94">
+        <f>SUM(B139:B139)</f>
         <v>195940.3</v>
       </c>
-      <c r="C124" s="95"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M125" s="96"/>
+      <c r="C140" s="95"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M141" s="96"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="29">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="B1:E1"/>
@@ -3511,9 +3622,9 @@
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A121:C122"/>
+    <mergeCell ref="A137:C138"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A103:B104"/>
+    <mergeCell ref="A113:B114"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A88:B88"/>
@@ -3523,6 +3634,8 @@
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A104:B106"/>
+    <mergeCell ref="A108:B110"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3556,14 +3669,14 @@
       <c r="A1" s="141"/>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
       <c r="L1" s="143"/>
     </row>
     <row r="2" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3573,10 +3686,10 @@
       <c r="D2" s="146" t="s">
         <v>131</v>
       </c>
-      <c r="E2" s="240">
+      <c r="E2" s="252">
         <v>3000000</v>
       </c>
-      <c r="F2" s="240"/>
+      <c r="F2" s="252"/>
       <c r="G2" s="146"/>
       <c r="H2" s="146"/>
       <c r="I2" s="146" t="s">
@@ -3605,167 +3718,167 @@
       <c r="M3" s="97"/>
     </row>
     <row r="4" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="220" t="s">
+      <c r="A4" s="230" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="221"/>
-      <c r="C4" s="221"/>
-      <c r="D4" s="221"/>
-      <c r="E4" s="221"/>
-      <c r="F4" s="221"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="221"/>
-      <c r="J4" s="221"/>
-      <c r="K4" s="221"/>
-      <c r="L4" s="222"/>
+      <c r="B4" s="231"/>
+      <c r="C4" s="231"/>
+      <c r="D4" s="231"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="231"/>
+      <c r="G4" s="231"/>
+      <c r="H4" s="231"/>
+      <c r="I4" s="231"/>
+      <c r="J4" s="231"/>
+      <c r="K4" s="231"/>
+      <c r="L4" s="232"/>
       <c r="M4" s="97"/>
     </row>
     <row r="5" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="223"/>
-      <c r="B5" s="224"/>
-      <c r="C5" s="224"/>
-      <c r="D5" s="224"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="224"/>
-      <c r="G5" s="224"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="224"/>
-      <c r="K5" s="224"/>
-      <c r="L5" s="225"/>
+      <c r="A5" s="233"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="234"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="234"/>
+      <c r="G5" s="234"/>
+      <c r="H5" s="234"/>
+      <c r="I5" s="234"/>
+      <c r="J5" s="234"/>
+      <c r="K5" s="234"/>
+      <c r="L5" s="235"/>
       <c r="M5" s="97"/>
     </row>
     <row r="6" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="223"/>
-      <c r="B6" s="224"/>
-      <c r="C6" s="224"/>
-      <c r="D6" s="224"/>
-      <c r="E6" s="224"/>
-      <c r="F6" s="224"/>
-      <c r="G6" s="224"/>
-      <c r="H6" s="224"/>
-      <c r="I6" s="224"/>
-      <c r="J6" s="224"/>
-      <c r="K6" s="224"/>
-      <c r="L6" s="225"/>
+      <c r="A6" s="233"/>
+      <c r="B6" s="234"/>
+      <c r="C6" s="234"/>
+      <c r="D6" s="234"/>
+      <c r="E6" s="234"/>
+      <c r="F6" s="234"/>
+      <c r="G6" s="234"/>
+      <c r="H6" s="234"/>
+      <c r="I6" s="234"/>
+      <c r="J6" s="234"/>
+      <c r="K6" s="234"/>
+      <c r="L6" s="235"/>
       <c r="M6" s="97"/>
     </row>
     <row r="7" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="223"/>
-      <c r="B7" s="224"/>
-      <c r="C7" s="224"/>
-      <c r="D7" s="224"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="224"/>
-      <c r="G7" s="224"/>
-      <c r="H7" s="224"/>
-      <c r="I7" s="224"/>
-      <c r="J7" s="224"/>
-      <c r="K7" s="224"/>
-      <c r="L7" s="225"/>
+      <c r="A7" s="233"/>
+      <c r="B7" s="234"/>
+      <c r="C7" s="234"/>
+      <c r="D7" s="234"/>
+      <c r="E7" s="234"/>
+      <c r="F7" s="234"/>
+      <c r="G7" s="234"/>
+      <c r="H7" s="234"/>
+      <c r="I7" s="234"/>
+      <c r="J7" s="234"/>
+      <c r="K7" s="234"/>
+      <c r="L7" s="235"/>
       <c r="M7" s="97"/>
     </row>
     <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="226"/>
-      <c r="B8" s="227"/>
-      <c r="C8" s="227"/>
-      <c r="D8" s="227"/>
-      <c r="E8" s="227"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="227"/>
-      <c r="H8" s="227"/>
-      <c r="I8" s="227"/>
-      <c r="J8" s="227"/>
-      <c r="K8" s="227"/>
-      <c r="L8" s="228"/>
+      <c r="A8" s="236"/>
+      <c r="B8" s="237"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="237"/>
+      <c r="J8" s="237"/>
+      <c r="K8" s="237"/>
+      <c r="L8" s="238"/>
     </row>
     <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="234" t="s">
+      <c r="A9" s="246" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="235"/>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="236"/>
+      <c r="B9" s="247"/>
+      <c r="C9" s="247"/>
+      <c r="D9" s="247"/>
+      <c r="E9" s="247"/>
+      <c r="F9" s="247"/>
+      <c r="G9" s="247"/>
+      <c r="H9" s="247"/>
+      <c r="I9" s="247"/>
+      <c r="J9" s="247"/>
+      <c r="K9" s="247"/>
+      <c r="L9" s="248"/>
     </row>
     <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="237" t="s">
+      <c r="A10" s="249" t="s">
         <v>172</v>
       </c>
-      <c r="B10" s="238"/>
-      <c r="C10" s="238"/>
-      <c r="D10" s="238"/>
-      <c r="E10" s="238"/>
-      <c r="F10" s="238"/>
-      <c r="G10" s="238"/>
-      <c r="H10" s="238"/>
-      <c r="I10" s="238"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="238"/>
-      <c r="L10" s="239"/>
+      <c r="B10" s="250"/>
+      <c r="C10" s="250"/>
+      <c r="D10" s="250"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="250"/>
+      <c r="I10" s="250"/>
+      <c r="J10" s="250"/>
+      <c r="K10" s="250"/>
+      <c r="L10" s="251"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="229" t="s">
+      <c r="A11" s="239" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="229" t="s">
+      <c r="B11" s="239" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="229" t="s">
+      <c r="C11" s="239" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="229" t="s">
+      <c r="D11" s="239" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="212" t="s">
+      <c r="E11" s="242" t="s">
         <v>137</v>
       </c>
-      <c r="F11" s="229" t="s">
+      <c r="F11" s="239" t="s">
         <v>138</v>
       </c>
-      <c r="G11" s="232" t="s">
+      <c r="G11" s="244" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="212" t="s">
+      <c r="H11" s="242" t="s">
         <v>140</v>
       </c>
-      <c r="I11" s="212" t="s">
+      <c r="I11" s="242" t="s">
         <v>132</v>
       </c>
-      <c r="J11" s="214" t="s">
+      <c r="J11" s="253" t="s">
         <v>131</v>
       </c>
       <c r="K11" s="98" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="216" t="s">
+      <c r="L11" s="255" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="230"/>
-      <c r="B12" s="230"/>
-      <c r="C12" s="231"/>
-      <c r="D12" s="230"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="230"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="213"/>
-      <c r="I12" s="213"/>
-      <c r="J12" s="215"/>
+      <c r="A12" s="240"/>
+      <c r="B12" s="240"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="240"/>
+      <c r="E12" s="243"/>
+      <c r="F12" s="240"/>
+      <c r="G12" s="245"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="254"/>
       <c r="K12" s="99" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="L12" s="217"/>
+      <c r="L12" s="256"/>
     </row>
     <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100">
@@ -3781,7 +3894,7 @@
       <c r="E13" s="102">
         <v>206522.01</v>
       </c>
-      <c r="F13" s="188">
+      <c r="F13" s="103">
         <f>E13</f>
         <v>206522.01</v>
       </c>
@@ -3827,7 +3940,7 @@
       <c r="E14" s="102">
         <v>2512429.02</v>
       </c>
-      <c r="F14" s="188">
+      <c r="F14" s="103">
         <v>30000</v>
       </c>
       <c r="G14" s="104">
@@ -3859,7 +3972,7 @@
         <v>0.02</v>
       </c>
       <c r="N14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3876,7 +3989,7 @@
       <c r="E15" s="102">
         <v>111552.03</v>
       </c>
-      <c r="F15" s="188">
+      <c r="F15" s="103">
         <f>E15</f>
         <v>111552.03</v>
       </c>
@@ -3910,43 +4023,46 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="100">
+      <c r="A16" s="260">
         <v>4</v>
       </c>
-      <c r="B16" s="100" t="s">
+      <c r="B16" s="260" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="101">
+      <c r="C16" s="136"/>
+      <c r="D16" s="127">
         <v>1.47</v>
       </c>
-      <c r="E16" s="102">
+      <c r="E16" s="128">
         <v>214949.04</v>
       </c>
-      <c r="F16" s="103"/>
-      <c r="G16" s="104">
+      <c r="F16" s="128">
+        <f>E16</f>
+        <v>214949.04</v>
+      </c>
+      <c r="G16" s="129">
         <f t="shared" si="0"/>
-        <v>214949.04</v>
-      </c>
-      <c r="H16" s="104">
+        <v>0</v>
+      </c>
+      <c r="H16" s="129">
         <f t="shared" si="5"/>
-        <v>6448.4712</v>
-      </c>
-      <c r="I16" s="105">
+        <v>0</v>
+      </c>
+      <c r="I16" s="126">
         <f t="shared" si="1"/>
         <v>177496.98749999999</v>
       </c>
-      <c r="J16" s="105">
+      <c r="J16" s="126">
         <f t="shared" si="2"/>
         <v>44100</v>
       </c>
-      <c r="K16" s="106">
+      <c r="K16" s="130">
         <f t="shared" si="3"/>
-        <v>442994.04</v>
-      </c>
-      <c r="L16" s="107">
+        <v>221597.04</v>
+      </c>
+      <c r="L16" s="131">
         <f t="shared" si="4"/>
-        <v>456284.04</v>
+        <v>228245.04</v>
       </c>
       <c r="M16" s="64">
         <f t="shared" si="6"/>
@@ -3967,7 +4083,7 @@
       <c r="E17" s="102">
         <v>163771.04999999999</v>
       </c>
-      <c r="F17" s="188">
+      <c r="F17" s="103">
         <v>168684.05</v>
       </c>
       <c r="G17" s="104">
@@ -4013,7 +4129,7 @@
       <c r="E18" s="102">
         <v>203507.06</v>
       </c>
-      <c r="F18" s="188">
+      <c r="F18" s="103">
         <f>E18</f>
         <v>203507.06</v>
       </c>
@@ -4060,7 +4176,7 @@
       <c r="E19" s="102">
         <v>168836.07</v>
       </c>
-      <c r="F19" s="188">
+      <c r="F19" s="103">
         <f>E19</f>
         <v>168836.07</v>
       </c>
@@ -4107,7 +4223,7 @@
       <c r="E20" s="102">
         <v>123612.08</v>
       </c>
-      <c r="F20" s="188">
+      <c r="F20" s="103">
         <f>E20</f>
         <v>123612.08</v>
       </c>
@@ -4154,7 +4270,7 @@
       <c r="E21" s="102">
         <v>119904.09</v>
       </c>
-      <c r="F21" s="188">
+      <c r="F21" s="103">
         <v>123501.09</v>
       </c>
       <c r="G21" s="104">
@@ -4244,7 +4360,7 @@
       <c r="E23" s="102">
         <v>168836.11</v>
       </c>
-      <c r="F23" s="188">
+      <c r="F23" s="103">
         <f>E23</f>
         <v>168836.11</v>
       </c>
@@ -4337,7 +4453,7 @@
       <c r="E25" s="102">
         <v>206752.13</v>
       </c>
-      <c r="F25" s="188">
+      <c r="F25" s="103">
         <f>E25</f>
         <v>206752.13</v>
       </c>
@@ -4428,7 +4544,7 @@
       <c r="E27" s="103">
         <v>382072.15</v>
       </c>
-      <c r="F27" s="188">
+      <c r="F27" s="103">
         <f>123612.15+250932+7528</f>
         <v>382072.15</v>
       </c>
@@ -4475,7 +4591,7 @@
       <c r="E28" s="102">
         <v>758530.16</v>
       </c>
-      <c r="F28" s="188">
+      <c r="F28" s="103">
         <v>400000.16</v>
       </c>
       <c r="G28" s="104">
@@ -4521,7 +4637,7 @@
       <c r="E29" s="102">
         <v>202000.17</v>
       </c>
-      <c r="F29" s="188">
+      <c r="F29" s="103">
         <f>E29</f>
         <v>202000.17</v>
       </c>
@@ -4568,7 +4684,7 @@
       <c r="E30" s="103">
         <v>168836.18</v>
       </c>
-      <c r="F30" s="188">
+      <c r="F30" s="103">
         <v>173901.18</v>
       </c>
       <c r="G30" s="162">
@@ -4614,7 +4730,7 @@
       <c r="E31" s="102">
         <v>176373.19</v>
       </c>
-      <c r="F31" s="188">
+      <c r="F31" s="103">
         <f>191448.19-F112</f>
         <v>176372.19</v>
       </c>
@@ -4651,41 +4767,41 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="166">
+      <c r="A32" s="205">
         <v>20</v>
       </c>
-      <c r="B32" s="159" t="s">
+      <c r="B32" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="167"/>
-      <c r="D32" s="161">
+      <c r="C32" s="207"/>
+      <c r="D32" s="208">
         <v>1.35</v>
       </c>
-      <c r="E32" s="103">
+      <c r="E32" s="209">
         <v>203507.20000000001</v>
       </c>
-      <c r="F32" s="103"/>
-      <c r="G32" s="162">
+      <c r="F32" s="209"/>
+      <c r="G32" s="210">
         <f t="shared" si="0"/>
         <v>203507.20000000001</v>
       </c>
-      <c r="H32" s="162">
+      <c r="H32" s="210">
         <f t="shared" si="5"/>
         <v>6105.2160000000003</v>
       </c>
-      <c r="I32" s="163">
+      <c r="I32" s="211">
         <f t="shared" si="1"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J32" s="163">
+      <c r="J32" s="211">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K32" s="164">
+      <c r="K32" s="212">
         <f t="shared" si="3"/>
         <v>413120.2</v>
       </c>
-      <c r="L32" s="165">
+      <c r="L32" s="213">
         <f t="shared" si="4"/>
         <v>425514.2</v>
       </c>
@@ -4711,7 +4827,7 @@
       <c r="E33" s="103">
         <v>168836.21</v>
       </c>
-      <c r="F33" s="188">
+      <c r="F33" s="103">
         <f>E33</f>
         <v>168836.21</v>
       </c>
@@ -4759,7 +4875,7 @@
       <c r="E34" s="102">
         <v>123612.22</v>
       </c>
-      <c r="F34" s="188">
+      <c r="F34" s="103">
         <v>127320.22</v>
       </c>
       <c r="G34" s="104">
@@ -4806,7 +4922,7 @@
       <c r="E35" s="102">
         <v>119904.23</v>
       </c>
-      <c r="F35" s="188">
+      <c r="F35" s="103">
         <f>E35</f>
         <v>119904.23</v>
       </c>
@@ -4942,16 +5058,19 @@
         <v>1.17</v>
       </c>
       <c r="E38" s="102">
-        <v>364334.26</v>
-      </c>
-      <c r="F38" s="103"/>
+        <v>375264.26</v>
+      </c>
+      <c r="F38" s="103">
+        <f>E38</f>
+        <v>375264.26</v>
+      </c>
       <c r="G38" s="104">
         <f t="shared" si="0"/>
-        <v>364334.26</v>
+        <v>0</v>
       </c>
       <c r="H38" s="104">
         <f t="shared" si="5"/>
-        <v>10930.0278</v>
+        <v>0</v>
       </c>
       <c r="I38" s="105">
         <f t="shared" si="1"/>
@@ -4963,11 +5082,11 @@
       </c>
       <c r="K38" s="106">
         <f t="shared" si="3"/>
-        <v>551637.26</v>
+        <v>176373.26</v>
       </c>
       <c r="L38" s="107">
         <f t="shared" si="8"/>
-        <v>568186.26</v>
+        <v>181664.26</v>
       </c>
       <c r="M38" s="64">
         <f t="shared" si="7"/>
@@ -4989,7 +5108,7 @@
       <c r="E39" s="102">
         <v>197402.27</v>
       </c>
-      <c r="F39" s="188">
+      <c r="F39" s="103">
         <f>E39</f>
         <v>197402.27</v>
       </c>
@@ -5037,7 +5156,7 @@
       <c r="E40" s="102">
         <v>163771.28</v>
       </c>
-      <c r="F40" s="188">
+      <c r="F40" s="103">
         <v>168684.28</v>
       </c>
       <c r="G40" s="104">
@@ -5132,7 +5251,7 @@
       <c r="E42" s="102">
         <v>120677.3</v>
       </c>
-      <c r="F42" s="188">
+      <c r="F42" s="103">
         <v>125000</v>
       </c>
       <c r="G42" s="104">
@@ -5179,7 +5298,7 @@
       <c r="E43" s="102">
         <v>202000.31</v>
       </c>
-      <c r="F43" s="188">
+      <c r="F43" s="103">
         <v>208060.31</v>
       </c>
       <c r="G43" s="104">
@@ -5257,46 +5376,44 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="190">
+      <c r="A45" s="186">
         <f t="shared" si="9"/>
         <v>33</v>
       </c>
-      <c r="B45" s="191" t="s">
+      <c r="B45" s="187" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="192"/>
-      <c r="D45" s="193">
+      <c r="C45" s="188"/>
+      <c r="D45" s="189">
         <v>1.17</v>
       </c>
-      <c r="E45" s="194">
-        <v>1112030.33</v>
-      </c>
-      <c r="F45" s="195">
-        <v>300000</v>
-      </c>
-      <c r="G45" s="196">
+      <c r="E45" s="190">
+        <v>176373.11249999999</v>
+      </c>
+      <c r="F45" s="190"/>
+      <c r="G45" s="191">
         <f t="shared" si="0"/>
-        <v>812030.33000000007</v>
-      </c>
-      <c r="H45" s="196">
+        <v>176373.11249999999</v>
+      </c>
+      <c r="H45" s="191">
         <f t="shared" si="5"/>
-        <v>24360.909900000002</v>
-      </c>
-      <c r="I45" s="197">
+        <v>5291.1933749999998</v>
+      </c>
+      <c r="I45" s="192">
         <f t="shared" ref="I45:I76" si="10">J$2*D45/100</f>
         <v>141273.11249999999</v>
       </c>
-      <c r="J45" s="197">
+      <c r="J45" s="192">
         <f t="shared" ref="J45:J76" si="11">E$2*D45/100</f>
         <v>35100</v>
       </c>
-      <c r="K45" s="198">
+      <c r="K45" s="193">
         <f t="shared" ref="K45:K76" si="12">ROUND(SUM(G45:J45),0) + M45</f>
-        <v>1012764.33</v>
-      </c>
-      <c r="L45" s="199">
+        <v>358037.33</v>
+      </c>
+      <c r="L45" s="194">
         <f t="shared" si="8"/>
-        <v>1043147.33</v>
+        <v>368778.33</v>
       </c>
       <c r="M45" s="64">
         <f t="shared" si="7"/>
@@ -5318,7 +5435,7 @@
       <c r="E46" s="102">
         <v>203507.34</v>
       </c>
-      <c r="F46" s="188">
+      <c r="F46" s="103">
         <f>E46</f>
         <v>203507.34</v>
       </c>
@@ -5366,7 +5483,7 @@
       <c r="E47" s="128">
         <v>341763.35</v>
       </c>
-      <c r="F47" s="189">
+      <c r="F47" s="128">
         <v>200000</v>
       </c>
       <c r="G47" s="129">
@@ -5416,7 +5533,7 @@
       <c r="E48" s="102">
         <v>119904.36</v>
       </c>
-      <c r="F48" s="188">
+      <c r="F48" s="103">
         <f>E48</f>
         <v>119904.36</v>
       </c>
@@ -5467,7 +5584,7 @@
       <c r="E49" s="103">
         <v>258461.37</v>
       </c>
-      <c r="F49" s="188">
+      <c r="F49" s="103">
         <f>E49</f>
         <v>258461.37</v>
       </c>
@@ -5560,16 +5677,17 @@
       <c r="E51" s="102">
         <v>358543.39</v>
       </c>
-      <c r="F51" s="188">
-        <v>168836.39</v>
+      <c r="F51" s="103">
+        <f>168836.39*2+20871</f>
+        <v>358543.78</v>
       </c>
       <c r="G51" s="104">
         <f t="shared" si="0"/>
-        <v>189707</v>
+        <v>-0.39000000001396984</v>
       </c>
       <c r="H51" s="104">
         <f t="shared" si="5"/>
-        <v>5691.21</v>
+        <v>0</v>
       </c>
       <c r="I51" s="105">
         <f t="shared" si="10"/>
@@ -5581,11 +5699,11 @@
       </c>
       <c r="K51" s="106">
         <f t="shared" si="12"/>
-        <v>364234.39</v>
+        <v>168835.39</v>
       </c>
       <c r="L51" s="107">
         <f t="shared" si="8"/>
-        <v>375161.39</v>
+        <v>173900.39</v>
       </c>
       <c r="M51" s="64">
         <f t="shared" si="7"/>
@@ -5652,7 +5770,7 @@
       <c r="E53" s="102">
         <v>203507.41</v>
       </c>
-      <c r="F53" s="188">
+      <c r="F53" s="103">
         <v>209612.41</v>
       </c>
       <c r="G53" s="104">
@@ -5685,46 +5803,44 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="109">
+      <c r="A54" s="186">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
-      <c r="B54" s="110" t="s">
+      <c r="B54" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="108"/>
-      <c r="D54" s="101">
+      <c r="C54" s="188"/>
+      <c r="D54" s="189">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E54" s="102">
+      <c r="E54" s="190">
         <v>818744.42</v>
       </c>
-      <c r="F54" s="188">
-        <v>214949.42</v>
-      </c>
-      <c r="G54" s="104">
+      <c r="F54" s="190"/>
+      <c r="G54" s="191">
         <f t="shared" si="0"/>
-        <v>603795</v>
-      </c>
-      <c r="H54" s="104">
+        <v>818744.42</v>
+      </c>
+      <c r="H54" s="191">
         <f t="shared" si="5"/>
-        <v>18113.849999999999</v>
-      </c>
-      <c r="I54" s="105">
+        <v>24562.332600000002</v>
+      </c>
+      <c r="I54" s="192">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J54" s="105">
+      <c r="J54" s="192">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K54" s="106">
+      <c r="K54" s="193">
         <f t="shared" si="12"/>
-        <v>790745.42</v>
-      </c>
-      <c r="L54" s="107">
+        <v>1012143.42</v>
+      </c>
+      <c r="L54" s="194">
         <f t="shared" si="8"/>
-        <v>814467.42</v>
+        <v>1042507.42</v>
       </c>
       <c r="M54" s="64">
         <f t="shared" si="7"/>
@@ -5838,7 +5954,7 @@
       <c r="E57" s="102">
         <v>202000.45</v>
       </c>
-      <c r="F57" s="188">
+      <c r="F57" s="103">
         <f>E57</f>
         <v>202000.45</v>
       </c>
@@ -5886,14 +6002,16 @@
       <c r="E58" s="102">
         <v>191258.46</v>
       </c>
-      <c r="F58" s="103"/>
+      <c r="F58" s="103">
+        <v>150000</v>
+      </c>
       <c r="G58" s="104">
         <f t="shared" si="0"/>
-        <v>191258.46</v>
+        <v>41258.459999999992</v>
       </c>
       <c r="H58" s="104">
         <f t="shared" si="5"/>
-        <v>5737.7537999999995</v>
+        <v>1237.7537999999997</v>
       </c>
       <c r="I58" s="105">
         <f t="shared" si="10"/>
@@ -5905,11 +6023,11 @@
       </c>
       <c r="K58" s="106">
         <f t="shared" si="12"/>
-        <v>365832.46</v>
+        <v>211332.46</v>
       </c>
       <c r="L58" s="107">
         <f t="shared" si="8"/>
-        <v>376807.46</v>
+        <v>217672.46</v>
       </c>
       <c r="M58" s="64">
         <f t="shared" si="7"/>
@@ -5934,7 +6052,7 @@
       <c r="E59" s="128">
         <v>581351.47</v>
       </c>
-      <c r="F59" s="189">
+      <c r="F59" s="128">
         <v>173374.17</v>
       </c>
       <c r="G59" s="129">
@@ -5966,7 +6084,7 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="N59" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -5984,7 +6102,7 @@
       <c r="E60" s="103">
         <v>209612.48</v>
       </c>
-      <c r="F60" s="188">
+      <c r="F60" s="103">
         <f>E60</f>
         <v>209612.48</v>
       </c>
@@ -6035,7 +6153,7 @@
       <c r="E61" s="102">
         <v>163771.49</v>
       </c>
-      <c r="F61" s="188">
+      <c r="F61" s="103">
         <v>168684.49</v>
       </c>
       <c r="G61" s="104">
@@ -6082,7 +6200,7 @@
       <c r="E62" s="102">
         <v>250933.5</v>
       </c>
-      <c r="F62" s="188">
+      <c r="F62" s="103">
         <f>E62</f>
         <v>250933.5</v>
       </c>
@@ -6130,7 +6248,7 @@
       <c r="E63" s="102">
         <v>233265.51</v>
       </c>
-      <c r="F63" s="188">
+      <c r="F63" s="103">
         <v>106459.51</v>
       </c>
       <c r="G63" s="104">
@@ -6177,7 +6295,7 @@
       <c r="E64" s="102">
         <v>202000.52</v>
       </c>
-      <c r="F64" s="188">
+      <c r="F64" s="103">
         <f>E64</f>
         <v>202000.52</v>
       </c>
@@ -6225,7 +6343,7 @@
       <c r="E65" s="103">
         <v>300737.53000000003</v>
       </c>
-      <c r="F65" s="188">
+      <c r="F65" s="103">
         <v>98556.53</v>
       </c>
       <c r="G65" s="104">
@@ -6272,7 +6390,7 @@
       <c r="E66" s="102">
         <v>171082.54</v>
       </c>
-      <c r="F66" s="188">
+      <c r="F66" s="103">
         <v>176214.54</v>
       </c>
       <c r="G66" s="104">
@@ -6319,7 +6437,7 @@
       <c r="E67" s="102">
         <v>197402.55</v>
       </c>
-      <c r="F67" s="188">
+      <c r="F67" s="103">
         <v>203324.55</v>
       </c>
       <c r="G67" s="104">
@@ -6366,7 +6484,7 @@
       <c r="E68" s="102">
         <v>168836.56</v>
       </c>
-      <c r="F68" s="188">
+      <c r="F68" s="103">
         <v>173901.56</v>
       </c>
       <c r="G68" s="104">
@@ -6413,7 +6531,7 @@
       <c r="E69" s="102">
         <v>119898.57</v>
       </c>
-      <c r="F69" s="188">
+      <c r="F69" s="103">
         <v>120000</v>
       </c>
       <c r="G69" s="104">
@@ -6460,7 +6578,7 @@
       <c r="E70" s="102">
         <v>123612.58</v>
       </c>
-      <c r="F70" s="188">
+      <c r="F70" s="103">
         <f t="shared" ref="F70" si="13">E70</f>
         <v>123612.58</v>
       </c>
@@ -6508,7 +6626,7 @@
       <c r="E71" s="103">
         <v>410061.59</v>
       </c>
-      <c r="F71" s="188">
+      <c r="F71" s="103">
         <f>239116.53-PRORRATEO!F105-PRORRATEO!F113+194996.59+6100</f>
         <v>410061.18</v>
       </c>
@@ -6556,7 +6674,7 @@
       <c r="E72" s="102">
         <v>163771.6</v>
       </c>
-      <c r="F72" s="188">
+      <c r="F72" s="103">
         <v>168684.6</v>
       </c>
       <c r="G72" s="104">
@@ -6603,7 +6721,7 @@
       <c r="E73" s="102">
         <v>176373.61</v>
       </c>
-      <c r="F73" s="188">
+      <c r="F73" s="103">
         <f t="shared" ref="F73:F75" si="14">E73</f>
         <v>176373.61</v>
       </c>
@@ -6651,7 +6769,7 @@
       <c r="E74" s="102">
         <v>197402.62</v>
       </c>
-      <c r="F74" s="188">
+      <c r="F74" s="103">
         <v>203325.62</v>
       </c>
       <c r="G74" s="104">
@@ -6698,7 +6816,7 @@
       <c r="E75" s="102">
         <v>168836.63</v>
       </c>
-      <c r="F75" s="188">
+      <c r="F75" s="103">
         <f t="shared" si="14"/>
         <v>168836.63</v>
       </c>
@@ -6746,7 +6864,7 @@
       <c r="E76" s="102">
         <v>254752.64000000001</v>
       </c>
-      <c r="F76" s="188">
+      <c r="F76" s="103">
         <f>127320.64+123612+3820</f>
         <v>254752.64000000001</v>
       </c>
@@ -6780,44 +6898,44 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="244">
+      <c r="A77" s="196">
         <f t="shared" si="9"/>
         <v>65</v>
       </c>
-      <c r="B77" s="245" t="s">
+      <c r="B77" s="197" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="246"/>
-      <c r="D77" s="247">
+      <c r="C77" s="198"/>
+      <c r="D77" s="199">
         <v>0.82</v>
       </c>
-      <c r="E77" s="248">
+      <c r="E77" s="200">
         <v>880370.65</v>
       </c>
-      <c r="F77" s="253">
+      <c r="F77" s="215">
         <v>99011.93</v>
       </c>
-      <c r="G77" s="249">
+      <c r="G77" s="201">
         <f t="shared" ref="G77:G115" si="15">E77-F77</f>
         <v>781358.72</v>
       </c>
-      <c r="H77" s="249">
+      <c r="H77" s="201">
         <f t="shared" si="5"/>
         <v>23440.761599999998</v>
       </c>
-      <c r="I77" s="250">
+      <c r="I77" s="202">
         <f t="shared" ref="I77:I108" si="16">J$2*D77/100</f>
         <v>99011.925000000003</v>
       </c>
-      <c r="J77" s="250">
+      <c r="J77" s="202">
         <f t="shared" ref="J77:J108" si="17">E$2*D77/100</f>
         <v>24600</v>
       </c>
-      <c r="K77" s="251">
+      <c r="K77" s="203">
         <f t="shared" ref="K77:K108" si="18">ROUND(SUM(G77:J77),0) + M77</f>
         <v>928411.65</v>
       </c>
-      <c r="L77" s="252">
+      <c r="L77" s="204">
         <f t="shared" si="8"/>
         <v>956263.65</v>
       </c>
@@ -6826,7 +6944,7 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="N77" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -6844,7 +6962,7 @@
       <c r="E78" s="102">
         <v>195940.66</v>
       </c>
-      <c r="F78" s="188">
+      <c r="F78" s="103">
         <v>201818.66</v>
       </c>
       <c r="G78" s="104">
@@ -6891,7 +7009,7 @@
       <c r="E79" s="102">
         <v>347955.67</v>
       </c>
-      <c r="F79" s="188">
+      <c r="F79" s="103">
         <v>180000.67</v>
       </c>
       <c r="G79" s="104">
@@ -6985,7 +7103,7 @@
       <c r="E81" s="102">
         <v>197402.69</v>
       </c>
-      <c r="F81" s="188">
+      <c r="F81" s="103">
         <v>203324.69</v>
       </c>
       <c r="G81" s="104">
@@ -7062,7 +7180,7 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="N82" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -7080,7 +7198,7 @@
       <c r="E83" s="102">
         <v>250338.71</v>
       </c>
-      <c r="F83" s="188">
+      <c r="F83" s="103">
         <f>119452+123612.71+7274</f>
         <v>250338.71000000002</v>
       </c>
@@ -7128,7 +7246,7 @@
       <c r="E84" s="102">
         <v>123612.72</v>
       </c>
-      <c r="F84" s="188">
+      <c r="F84" s="103">
         <f>E84</f>
         <v>123612.72</v>
       </c>
@@ -7266,7 +7384,7 @@
       <c r="E87" s="102">
         <v>176373.75</v>
       </c>
-      <c r="F87" s="188">
+      <c r="F87" s="103">
         <f>E87</f>
         <v>176373.75</v>
       </c>
@@ -7314,7 +7432,7 @@
       <c r="E88" s="102">
         <v>209612.76</v>
       </c>
-      <c r="F88" s="188">
+      <c r="F88" s="103">
         <f>E88</f>
         <v>209612.76</v>
       </c>
@@ -7362,7 +7480,7 @@
       <c r="E89" s="102">
         <v>163771.76999999999</v>
       </c>
-      <c r="F89" s="188">
+      <c r="F89" s="103">
         <v>168684.77</v>
       </c>
       <c r="G89" s="104">
@@ -7395,46 +7513,44 @@
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A90" s="109">
+      <c r="A90" s="186">
         <f t="shared" si="9"/>
         <v>78</v>
       </c>
-      <c r="B90" s="110" t="s">
+      <c r="B90" s="187" t="s">
         <v>79</v>
       </c>
-      <c r="C90" s="108"/>
-      <c r="D90" s="101">
+      <c r="C90" s="188"/>
+      <c r="D90" s="189">
         <v>0.82</v>
       </c>
-      <c r="E90" s="102">
-        <v>1569769.78</v>
-      </c>
-      <c r="F90" s="103">
-        <v>0</v>
-      </c>
-      <c r="G90" s="104">
+      <c r="E90" s="190">
+        <v>123611.925</v>
+      </c>
+      <c r="F90" s="190"/>
+      <c r="G90" s="191">
         <f t="shared" si="15"/>
-        <v>1569769.78</v>
-      </c>
-      <c r="H90" s="104">
+        <v>123611.925</v>
+      </c>
+      <c r="H90" s="191">
         <f t="shared" si="19"/>
-        <v>47093.093399999998</v>
-      </c>
-      <c r="I90" s="105">
+        <v>3708.3577500000001</v>
+      </c>
+      <c r="I90" s="192">
         <f t="shared" si="16"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J90" s="105">
+      <c r="J90" s="192">
         <f t="shared" si="17"/>
         <v>24600</v>
       </c>
-      <c r="K90" s="106">
+      <c r="K90" s="193">
         <f t="shared" si="18"/>
-        <v>1740475.78</v>
-      </c>
-      <c r="L90" s="107">
+        <v>250932.78</v>
+      </c>
+      <c r="L90" s="194">
         <f t="shared" si="8"/>
-        <v>1792689.78</v>
+        <v>258460.78</v>
       </c>
       <c r="M90" s="64">
         <f t="shared" si="7"/>
@@ -7456,7 +7572,7 @@
       <c r="E91" s="102">
         <v>123612.79</v>
       </c>
-      <c r="F91" s="188">
+      <c r="F91" s="103">
         <f>E91</f>
         <v>123612.79</v>
       </c>
@@ -7504,7 +7620,7 @@
       <c r="E92" s="102">
         <v>410061.8</v>
       </c>
-      <c r="F92" s="188">
+      <c r="F92" s="103">
         <v>220400.8</v>
       </c>
       <c r="G92" s="104">
@@ -7551,7 +7667,7 @@
       <c r="E93" s="128">
         <v>638725.81000000006</v>
       </c>
-      <c r="F93" s="189">
+      <c r="F93" s="128">
         <v>250000</v>
       </c>
       <c r="G93" s="129">
@@ -7583,7 +7699,7 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="N93" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -7601,7 +7717,7 @@
       <c r="E94" s="102">
         <v>181664.82</v>
       </c>
-      <c r="F94" s="188">
+      <c r="F94" s="103">
         <f>E94</f>
         <v>181664.82</v>
       </c>
@@ -7649,7 +7765,7 @@
       <c r="E95" s="103">
         <v>191113.83</v>
       </c>
-      <c r="F95" s="188">
+      <c r="F95" s="103">
         <f>RESUMEN!D54/2+196846.93</f>
         <v>469098.93</v>
       </c>
@@ -7697,7 +7813,7 @@
       <c r="E96" s="103">
         <v>449255.84</v>
       </c>
-      <c r="F96" s="188">
+      <c r="F96" s="103">
         <f>RESUMEN!D54/2+168836.84</f>
         <v>441088.83999999997</v>
       </c>
@@ -7745,7 +7861,7 @@
       <c r="E97" s="102">
         <v>123612.85</v>
       </c>
-      <c r="F97" s="188">
+      <c r="F97" s="103">
         <f t="shared" ref="F97:F112" si="21">E97</f>
         <v>123612.85</v>
       </c>
@@ -7793,7 +7909,7 @@
       <c r="E98" s="102">
         <v>123612.86</v>
       </c>
-      <c r="F98" s="188">
+      <c r="F98" s="103">
         <f t="shared" si="21"/>
         <v>123612.86</v>
       </c>
@@ -7841,7 +7957,7 @@
       <c r="E99" s="102">
         <v>195940.87</v>
       </c>
-      <c r="F99" s="188">
+      <c r="F99" s="103">
         <v>201818.87</v>
       </c>
       <c r="G99" s="104">
@@ -7888,7 +8004,7 @@
       <c r="E100" s="102">
         <v>163771.88</v>
       </c>
-      <c r="F100" s="188">
+      <c r="F100" s="103">
         <f>E100</f>
         <v>163771.88</v>
       </c>
@@ -7936,7 +8052,7 @@
       <c r="E101" s="102">
         <v>176373.89</v>
       </c>
-      <c r="F101" s="188">
+      <c r="F101" s="103">
         <f t="shared" si="21"/>
         <v>176373.89</v>
       </c>
@@ -7984,7 +8100,7 @@
       <c r="E102" s="102">
         <v>14623.9</v>
       </c>
-      <c r="F102" s="188">
+      <c r="F102" s="103">
         <v>15062.9</v>
       </c>
       <c r="G102" s="104">
@@ -8031,7 +8147,7 @@
       <c r="E103" s="102">
         <v>31068.91</v>
       </c>
-      <c r="F103" s="188">
+      <c r="F103" s="103">
         <v>15528.91</v>
       </c>
       <c r="G103" s="104">
@@ -8078,7 +8194,7 @@
       <c r="E104" s="102">
         <v>15527.92</v>
       </c>
-      <c r="F104" s="188">
+      <c r="F104" s="103">
         <f t="shared" si="21"/>
         <v>15527.92</v>
       </c>
@@ -8126,7 +8242,7 @@
       <c r="E105" s="103">
         <v>15075.93</v>
       </c>
-      <c r="F105" s="188">
+      <c r="F105" s="103">
         <f>E105</f>
         <v>15075.93</v>
       </c>
@@ -8174,7 +8290,7 @@
       <c r="E106" s="103">
         <v>15075.94</v>
       </c>
-      <c r="F106" s="188">
+      <c r="F106" s="103">
         <f>E106</f>
         <v>15075.94</v>
       </c>
@@ -8213,7 +8329,7 @@
         <v>95</v>
       </c>
       <c r="B107" s="168" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C107" s="167"/>
       <c r="D107" s="161">
@@ -8222,7 +8338,7 @@
       <c r="E107" s="103">
         <v>15075.95</v>
       </c>
-      <c r="F107" s="188">
+      <c r="F107" s="103">
         <v>15527.95</v>
       </c>
       <c r="G107" s="162">
@@ -8269,7 +8385,7 @@
       <c r="E108" s="103">
         <v>15075.96</v>
       </c>
-      <c r="F108" s="188">
+      <c r="F108" s="103">
         <f t="shared" si="21"/>
         <v>15075.96</v>
       </c>
@@ -8320,7 +8436,7 @@
       <c r="E109" s="103">
         <v>15075.97</v>
       </c>
-      <c r="F109" s="188">
+      <c r="F109" s="103">
         <f t="shared" si="21"/>
         <v>15075.97</v>
       </c>
@@ -8368,7 +8484,7 @@
       <c r="E110" s="103">
         <v>15075.98</v>
       </c>
-      <c r="F110" s="188">
+      <c r="F110" s="103">
         <f t="shared" si="21"/>
         <v>15075.98</v>
       </c>
@@ -8416,7 +8532,7 @@
       <c r="E111" s="103">
         <v>14623.99</v>
       </c>
-      <c r="F111" s="188">
+      <c r="F111" s="103">
         <v>15062.9</v>
       </c>
       <c r="G111" s="162">
@@ -8463,7 +8579,7 @@
       <c r="E112" s="103">
         <v>15076</v>
       </c>
-      <c r="F112" s="188">
+      <c r="F112" s="103">
         <f t="shared" si="21"/>
         <v>15076</v>
       </c>
@@ -8511,7 +8627,7 @@
       <c r="E113" s="103">
         <v>15076.01</v>
       </c>
-      <c r="F113" s="188">
+      <c r="F113" s="103">
         <f>E113</f>
         <v>15076.01</v>
       </c>
@@ -8549,7 +8665,7 @@
         <f t="shared" si="23"/>
         <v>102</v>
       </c>
-      <c r="B114" s="243" t="s">
+      <c r="B114" s="195" t="s">
         <v>101</v>
       </c>
       <c r="C114" s="167"/>
@@ -8595,7 +8711,7 @@
         <v>103</v>
       </c>
       <c r="B115" s="168" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C115" s="167"/>
       <c r="D115" s="161">
@@ -8604,7 +8720,7 @@
       <c r="E115" s="103">
         <v>14624.03</v>
       </c>
-      <c r="F115" s="188">
+      <c r="F115" s="103">
         <f>E115</f>
         <v>14624.03</v>
       </c>
@@ -8639,7 +8755,7 @@
     </row>
     <row r="116" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="166"/>
-      <c r="B116" s="243"/>
+      <c r="B116" s="195"/>
       <c r="C116" s="167"/>
       <c r="D116" s="161"/>
       <c r="E116" s="111"/>
@@ -8662,19 +8778,19 @@
       </c>
       <c r="E117" s="115">
         <f t="shared" si="27"/>
-        <v>35218775.560000002</v>
+        <v>32847890.487500001</v>
       </c>
       <c r="F117" s="116">
         <f>SUM(F13:F116)</f>
-        <v>13512038.039999999</v>
+        <v>13927009.310000001</v>
       </c>
       <c r="G117" s="116">
         <f t="shared" si="27"/>
-        <v>21706737.519999996</v>
+        <v>18920881.177499998</v>
       </c>
       <c r="H117" s="116">
         <f t="shared" si="27"/>
-        <v>662378.89980000013</v>
+        <v>578803.22122499999</v>
       </c>
       <c r="I117" s="117">
         <f t="shared" si="27"/>
@@ -8686,11 +8802,11 @@
       </c>
       <c r="K117" s="118">
         <f t="shared" si="27"/>
-        <v>37467915.560000002</v>
+        <v>34598483.560000002</v>
       </c>
       <c r="L117" s="118">
         <f t="shared" si="27"/>
-        <v>38591947.560000002</v>
+        <v>35636432.56000001</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8699,85 +8815,81 @@
     </row>
     <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="218" t="s">
+      <c r="B120" s="257" t="s">
         <v>107</v>
       </c>
-      <c r="C120" s="218"/>
-      <c r="D120" s="218"/>
-      <c r="E120" s="218"/>
-      <c r="F120" s="218"/>
-      <c r="G120" s="218"/>
-      <c r="H120" s="218"/>
-      <c r="I120" s="218"/>
-      <c r="J120" s="218"/>
-      <c r="K120" s="218"/>
+      <c r="C120" s="257"/>
+      <c r="D120" s="257"/>
+      <c r="E120" s="257"/>
+      <c r="F120" s="257"/>
+      <c r="G120" s="257"/>
+      <c r="H120" s="257"/>
+      <c r="I120" s="257"/>
+      <c r="J120" s="257"/>
+      <c r="K120" s="257"/>
     </row>
     <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="218"/>
-      <c r="C121" s="218"/>
-      <c r="D121" s="218"/>
-      <c r="E121" s="218"/>
-      <c r="F121" s="218"/>
-      <c r="G121" s="218"/>
-      <c r="H121" s="218"/>
-      <c r="I121" s="218"/>
-      <c r="J121" s="218"/>
-      <c r="K121" s="218"/>
+      <c r="B121" s="257"/>
+      <c r="C121" s="257"/>
+      <c r="D121" s="257"/>
+      <c r="E121" s="257"/>
+      <c r="F121" s="257"/>
+      <c r="G121" s="257"/>
+      <c r="H121" s="257"/>
+      <c r="I121" s="257"/>
+      <c r="J121" s="257"/>
+      <c r="K121" s="257"/>
     </row>
     <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="218"/>
-      <c r="C122" s="218"/>
-      <c r="D122" s="218"/>
-      <c r="E122" s="218"/>
-      <c r="F122" s="218"/>
-      <c r="G122" s="218"/>
-      <c r="H122" s="218"/>
-      <c r="I122" s="218"/>
-      <c r="J122" s="218"/>
-      <c r="K122" s="218"/>
+      <c r="B122" s="257"/>
+      <c r="C122" s="257"/>
+      <c r="D122" s="257"/>
+      <c r="E122" s="257"/>
+      <c r="F122" s="257"/>
+      <c r="G122" s="257"/>
+      <c r="H122" s="257"/>
+      <c r="I122" s="257"/>
+      <c r="J122" s="257"/>
+      <c r="K122" s="257"/>
     </row>
     <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="218"/>
-      <c r="C123" s="218"/>
-      <c r="D123" s="218"/>
-      <c r="E123" s="218"/>
-      <c r="F123" s="218"/>
-      <c r="G123" s="218"/>
-      <c r="H123" s="218"/>
-      <c r="I123" s="218"/>
-      <c r="J123" s="218"/>
-      <c r="K123" s="218"/>
+      <c r="B123" s="257"/>
+      <c r="C123" s="257"/>
+      <c r="D123" s="257"/>
+      <c r="E123" s="257"/>
+      <c r="F123" s="257"/>
+      <c r="G123" s="257"/>
+      <c r="H123" s="257"/>
+      <c r="I123" s="257"/>
+      <c r="J123" s="257"/>
+      <c r="K123" s="257"/>
     </row>
     <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="218"/>
-      <c r="C124" s="218"/>
-      <c r="D124" s="218"/>
-      <c r="E124" s="218"/>
-      <c r="F124" s="218"/>
-      <c r="G124" s="218"/>
-      <c r="H124" s="218"/>
-      <c r="I124" s="218"/>
-      <c r="J124" s="218"/>
-      <c r="K124" s="218"/>
+      <c r="B124" s="257"/>
+      <c r="C124" s="257"/>
+      <c r="D124" s="257"/>
+      <c r="E124" s="257"/>
+      <c r="F124" s="257"/>
+      <c r="G124" s="257"/>
+      <c r="H124" s="257"/>
+      <c r="I124" s="257"/>
+      <c r="J124" s="257"/>
+      <c r="K124" s="257"/>
     </row>
     <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="218"/>
-      <c r="C125" s="218"/>
-      <c r="D125" s="218"/>
-      <c r="E125" s="218"/>
-      <c r="F125" s="218"/>
-      <c r="G125" s="218"/>
-      <c r="H125" s="218"/>
-      <c r="I125" s="218"/>
-      <c r="J125" s="218"/>
-      <c r="K125" s="218"/>
+      <c r="B125" s="257"/>
+      <c r="C125" s="257"/>
+      <c r="D125" s="257"/>
+      <c r="E125" s="257"/>
+      <c r="F125" s="257"/>
+      <c r="G125" s="257"/>
+      <c r="H125" s="257"/>
+      <c r="I125" s="257"/>
+      <c r="J125" s="257"/>
+      <c r="K125" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="L11:L12"/>
     <mergeCell ref="B120:K125"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="A4:L8"/>
@@ -8791,6 +8903,10 @@
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A10:L10"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="L11:L12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -8806,22 +8922,22 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="241" t="s">
+      <c r="B5" s="258" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="258"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="L5" s="83" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="241"/>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="L5" s="83" t="s">
-        <v>190</v>
-      </c>
       <c r="M5" s="83" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
@@ -8848,7 +8964,7 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -8883,7 +8999,7 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="172" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C12" s="172"/>
       <c r="D12" s="172"/>
@@ -8900,7 +9016,7 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="172" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C13" s="173">
         <v>194996.59</v>
@@ -8919,7 +9035,7 @@
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="172" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" s="173">
         <v>15075.93</v>
@@ -8938,7 +9054,7 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="172" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C15" s="173">
         <v>15076.01</v>
@@ -8972,34 +9088,34 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="174" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="174"/>
+    </row>
+    <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="259" t="s">
         <v>197</v>
       </c>
-      <c r="C22" s="174"/>
-    </row>
-    <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="242" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="242"/>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
-      <c r="F25" s="242"/>
-      <c r="G25" s="242"/>
-      <c r="H25" s="242"/>
-      <c r="I25" s="242"/>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242"/>
-      <c r="M25" s="242"/>
-      <c r="N25" s="242"/>
-      <c r="O25" s="242"/>
-      <c r="P25" s="242"/>
-      <c r="Q25" s="242"/>
+      <c r="C25" s="259"/>
+      <c r="D25" s="259"/>
+      <c r="E25" s="259"/>
+      <c r="F25" s="259"/>
+      <c r="G25" s="259"/>
+      <c r="H25" s="259"/>
+      <c r="I25" s="259"/>
+      <c r="J25" s="259"/>
+      <c r="K25" s="259"/>
+      <c r="L25" s="259"/>
+      <c r="M25" s="259"/>
+      <c r="N25" s="259"/>
+      <c r="O25" s="259"/>
+      <c r="P25" s="259"/>
+      <c r="Q25" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\ITALIA\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA016C5-42DB-42FF-A23B-1772A447A0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92C6BA-2604-48AA-8334-2FB5C60DF8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -346,9 +346,6 @@
     <t>HORARIOS DE ATENCION: LUNES A VIERNES</t>
   </si>
   <si>
-    <t>10 A 16HS - EMERGENCIAS 24HS</t>
-  </si>
-  <si>
     <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</t>
   </si>
   <si>
@@ -839,6 +836,9 @@
   </si>
   <si>
     <t>Ingreso efectivo - Cuota 4/24 - Plan de pagos 3A</t>
+  </si>
+  <si>
+    <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
 </sst>
 </file>
@@ -1829,43 +1829,47 @@
     <xf numFmtId="44" fontId="20" fillId="16" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1952,16 +1956,12 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2326,49 +2326,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M141"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="223" t="s">
-        <v>154</v>
-      </c>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="224"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="221" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="222"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="225" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="225"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="226"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="223" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="224"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>103</v>
       </c>
@@ -2379,12 +2379,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2392,90 +2392,90 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="120" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="225" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="225"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="225"/>
+      <c r="C9" s="225"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="225"/>
+      <c r="C10" s="225"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="226" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="227" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="227"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="227"/>
-      <c r="C9" s="227"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="227"/>
-      <c r="C10" s="227"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="228" t="s">
+      <c r="B13" s="226"/>
+      <c r="C13" s="226"/>
+      <c r="D13" s="226"/>
+      <c r="E13" s="226"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="226"/>
+      <c r="B14" s="226"/>
+      <c r="C14" s="226"/>
+      <c r="D14" s="226"/>
+      <c r="E14" s="226"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="226"/>
+      <c r="B15" s="226"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="226"/>
+      <c r="E15" s="226"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="226"/>
+      <c r="B16" s="226"/>
+      <c r="C16" s="226"/>
+      <c r="D16" s="226"/>
+      <c r="E16" s="226"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>107</v>
-      </c>
-      <c r="B13" s="228"/>
-      <c r="C13" s="228"/>
-      <c r="D13" s="228"/>
-      <c r="E13" s="228"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="228"/>
-      <c r="B14" s="228"/>
-      <c r="C14" s="228"/>
-      <c r="D14" s="228"/>
-      <c r="E14" s="228"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="228"/>
-      <c r="B15" s="228"/>
-      <c r="C15" s="228"/>
-      <c r="D15" s="228"/>
-      <c r="E15" s="228"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="228"/>
-      <c r="B16" s="228"/>
-      <c r="C16" s="228"/>
-      <c r="D16" s="228"/>
-      <c r="E16" s="228"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>108</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="176"/>
       <c r="E21" s="19"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="216" t="s">
-        <v>177</v>
-      </c>
-      <c r="B22" s="217"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="217" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="218"/>
       <c r="C22" s="22"/>
       <c r="D22" s="184">
         <v>2182238</v>
@@ -2483,11 +2483,11 @@
       <c r="E22" s="48"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="216" t="s">
-        <v>178</v>
-      </c>
-      <c r="B23" s="217"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="217" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="218"/>
       <c r="C23" s="22"/>
       <c r="D23" s="184">
         <v>-474636.76</v>
@@ -2495,11 +2495,11 @@
       <c r="E23" s="24"/>
       <c r="H23" s="23"/>
     </row>
-    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="216" t="s">
-        <v>187</v>
-      </c>
-      <c r="B24" s="217"/>
+    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="217" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" s="218"/>
       <c r="C24" s="22"/>
       <c r="D24" s="185">
         <v>1381383</v>
@@ -2507,11 +2507,11 @@
       <c r="E24" s="24"/>
       <c r="H24" s="23"/>
     </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="216" t="s">
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="217" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="217"/>
+      <c r="B25" s="218"/>
       <c r="C25" s="22"/>
       <c r="D25" s="185">
         <v>0.76</v>
@@ -2519,9 +2519,9 @@
       <c r="E25" s="24"/>
       <c r="H25" s="23"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -2531,18 +2531,18 @@
         <v>3088985</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
       <c r="D27" s="26"/>
       <c r="E27" s="121"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -2551,9 +2551,9 @@
       </c>
       <c r="E28" s="123"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -2563,18 +2563,18 @@
         <v>148000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="26"/>
       <c r="E30" s="121"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B31" s="122"/>
       <c r="C31" s="122"/>
@@ -2582,12 +2582,12 @@
         <v>13757.84</v>
       </c>
       <c r="E31" s="132" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B32" s="122"/>
       <c r="C32" s="122"/>
@@ -2595,12 +2595,12 @@
         <v>1235711.01</v>
       </c>
       <c r="E32" s="132" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B33" s="122"/>
       <c r="C33" s="122"/>
@@ -2608,12 +2608,12 @@
         <v>225490.24</v>
       </c>
       <c r="E33" s="132" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -2625,9 +2625,9 @@
         <v>Debito 16/02</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -2639,18 +2639,18 @@
         <v>Debito 16/02</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B36" s="122"/>
       <c r="C36" s="122"/>
       <c r="D36" s="46"/>
       <c r="E36" s="132"/>
     </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -2660,18 +2660,18 @@
         <v>1584070.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
       <c r="D38" s="28"/>
       <c r="E38" s="29"/>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="219" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B39" s="220"/>
       <c r="C39" s="32"/>
@@ -2679,12 +2679,12 @@
         <v>313739</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="219" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="220"/>
       <c r="C40" s="32"/>
@@ -2692,12 +2692,12 @@
         <v>5204</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -2707,36 +2707,36 @@
         <v>318943</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B42" s="34"/>
       <c r="C42" s="34"/>
       <c r="D42" s="35"/>
       <c r="E42" s="36"/>
     </row>
-    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C43" s="37"/>
       <c r="D43" s="39">
         <v>542686.9</v>
       </c>
       <c r="E43" s="24" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="37" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B44" s="37" t="s">
-        <v>237</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="39">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="E44" s="24"/>
     </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="39">
@@ -2757,9 +2757,9 @@
       </c>
       <c r="E45" s="24"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B46" s="40"/>
       <c r="C46" s="37"/>
@@ -2767,12 +2767,12 @@
         <v>10111.620000000001</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="219" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B47" s="220"/>
       <c r="C47" s="37"/>
@@ -2780,21 +2780,21 @@
         <v>4813938.26</v>
       </c>
       <c r="E47" s="177" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B48" s="31"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38"/>
       <c r="E48" s="24"/>
     </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -2804,97 +2804,97 @@
         <v>5366736.7799999993</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="17"/>
       <c r="B50" s="25"/>
       <c r="C50" s="25"/>
       <c r="D50" s="26"/>
       <c r="E50" s="44"/>
     </row>
-    <row r="51" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="216" t="s">
-        <v>180</v>
-      </c>
-      <c r="B51" s="217"/>
+    <row r="51" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="217" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" s="218"/>
       <c r="C51" s="37"/>
       <c r="D51" s="39">
         <v>225000</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="216" t="s">
-        <v>205</v>
-      </c>
-      <c r="B52" s="217"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="217" t="s">
+        <v>204</v>
+      </c>
+      <c r="B52" s="218"/>
       <c r="C52" s="37"/>
       <c r="D52" s="39">
         <v>500000</v>
       </c>
       <c r="E52" s="45" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="216" t="s">
-        <v>209</v>
-      </c>
-      <c r="B53" s="217"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="217" t="s">
+        <v>208</v>
+      </c>
+      <c r="B53" s="218"/>
       <c r="C53" s="37"/>
       <c r="D53" s="39">
         <v>1520000</v>
       </c>
       <c r="E53" s="170" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="216" t="s">
-        <v>239</v>
-      </c>
-      <c r="B54" s="217"/>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="217" t="s">
+        <v>238</v>
+      </c>
+      <c r="B54" s="218"/>
       <c r="C54" s="37"/>
       <c r="D54" s="39">
         <f>272252*2</f>
         <v>544504</v>
       </c>
       <c r="E54" s="170" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="216" t="s">
-        <v>224</v>
-      </c>
-      <c r="B55" s="217"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="B55" s="218"/>
       <c r="C55" s="37"/>
       <c r="D55" s="39">
         <v>85000</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F55" s="64"/>
     </row>
-    <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="216" t="s">
-        <v>245</v>
-      </c>
-      <c r="B56" s="217"/>
+    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="217" t="s">
+        <v>244</v>
+      </c>
+      <c r="B56" s="218"/>
       <c r="C56" s="37"/>
       <c r="D56" s="39">
         <v>120000</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F56" s="64"/>
     </row>
-    <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="37"/>
@@ -2902,41 +2902,41 @@
         <v>35000</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F57" s="64"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="216" t="s">
-        <v>225</v>
-      </c>
-      <c r="B58" s="217"/>
+    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="217" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" s="218"/>
       <c r="C58" s="37"/>
       <c r="D58" s="39">
         <v>6000</v>
       </c>
       <c r="E58" s="45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F58" s="64"/>
     </row>
-    <row r="59" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="216" t="s">
-        <v>228</v>
-      </c>
-      <c r="B59" s="217"/>
+    <row r="59" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="217" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="218"/>
       <c r="C59" s="37"/>
       <c r="D59" s="39">
         <v>7000000</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F59" s="64"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="37"/>
@@ -2944,13 +2944,13 @@
         <v>28000</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F60" s="64"/>
     </row>
-    <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="140" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="37"/>
@@ -2958,13 +2958,13 @@
         <v>150800</v>
       </c>
       <c r="E61" s="45" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F61" s="64"/>
     </row>
-    <row r="62" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="180" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B62" s="181"/>
       <c r="C62" s="37"/>
@@ -2972,27 +2972,27 @@
         <v>910000</v>
       </c>
       <c r="E62" s="48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F62" s="64"/>
     </row>
-    <row r="63" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="216" t="s">
-        <v>222</v>
-      </c>
-      <c r="B63" s="217"/>
+    <row r="63" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="217" t="s">
+        <v>221</v>
+      </c>
+      <c r="B63" s="218"/>
       <c r="C63" s="37"/>
       <c r="D63" s="39">
         <v>250000</v>
       </c>
       <c r="E63" s="48" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F63" s="64"/>
     </row>
-    <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="140" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B64" s="21"/>
       <c r="C64" s="37"/>
@@ -3000,38 +3000,38 @@
         <v>133300</v>
       </c>
       <c r="E64" s="48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F64" s="64"/>
     </row>
-    <row r="65" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="216" t="s">
-        <v>215</v>
-      </c>
-      <c r="B65" s="217"/>
+    <row r="65" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="217" t="s">
+        <v>214</v>
+      </c>
+      <c r="B65" s="218"/>
       <c r="C65" s="37"/>
       <c r="D65" s="39">
         <v>105602.65</v>
       </c>
       <c r="E65" s="48" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F65" s="64"/>
     </row>
-    <row r="66" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="216" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" s="217"/>
+    <row r="66" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="217" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66" s="218"/>
       <c r="C66" s="37"/>
       <c r="D66" s="39">
         <v>2022800</v>
       </c>
       <c r="E66" s="48" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="25" t="s">
         <v>0</v>
       </c>
@@ -3043,29 +3043,29 @@
         <v>13636006.65</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
       <c r="D68" s="18"/>
       <c r="E68" s="19"/>
     </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="216" t="s">
-        <v>207</v>
-      </c>
-      <c r="B69" s="217"/>
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="217" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" s="218"/>
       <c r="C69" s="22"/>
       <c r="D69" s="182">
         <v>650000</v>
       </c>
       <c r="E69" s="48"/>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B70" s="21"/>
       <c r="C70" s="22"/>
@@ -3073,25 +3073,25 @@
         <v>125000</v>
       </c>
       <c r="E70" s="48" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="216" t="s">
-        <v>238</v>
-      </c>
-      <c r="B71" s="217"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="217" t="s">
+        <v>237</v>
+      </c>
+      <c r="B71" s="218"/>
       <c r="C71" s="22"/>
       <c r="D71" s="139">
         <v>62500</v>
       </c>
       <c r="E71" s="48" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="22"/>
@@ -3099,12 +3099,12 @@
         <v>45000</v>
       </c>
       <c r="E72" s="48" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -3114,18 +3114,18 @@
         <v>882500</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B74" s="49"/>
       <c r="C74" s="25"/>
       <c r="D74" s="50"/>
       <c r="E74" s="33"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B75" s="37"/>
       <c r="C75" s="37"/>
@@ -3134,9 +3134,9 @@
       </c>
       <c r="E75" s="51"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B76" s="37"/>
       <c r="C76" s="37"/>
@@ -3146,9 +3146,9 @@
       </c>
       <c r="E76" s="52"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B77" s="125"/>
       <c r="C77" s="125"/>
@@ -3157,9 +3157,9 @@
       </c>
       <c r="E77" s="52"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B78" s="125"/>
       <c r="C78" s="125"/>
@@ -3168,9 +3168,9 @@
       </c>
       <c r="E78" s="52"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B79" s="53"/>
       <c r="C79" s="53"/>
@@ -3180,31 +3180,31 @@
         <v>268594.86</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="37"/>
       <c r="B80" s="37"/>
       <c r="C80" s="37"/>
       <c r="D80" s="56"/>
       <c r="E80" s="57"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B81" s="58"/>
       <c r="C81" s="58"/>
       <c r="D81" s="59"/>
       <c r="E81" s="60"/>
     </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="61"/>
       <c r="D82" s="62"/>
       <c r="E82" s="63"/>
       <c r="F82" s="64"/>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B83" s="66"/>
       <c r="C83" s="67"/>
@@ -3216,52 +3216,52 @@
       <c r="F83" s="70"/>
       <c r="G83" s="64"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D84" s="62"/>
       <c r="E84" s="62"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D85" s="62"/>
       <c r="E85" s="62"/>
       <c r="H85" s="71"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B86" s="13"/>
       <c r="C86" s="14"/>
       <c r="D86" s="72"/>
       <c r="E86" s="73"/>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="30"/>
       <c r="B87" s="31"/>
       <c r="C87" s="37"/>
       <c r="D87" s="46"/>
       <c r="E87" s="74"/>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="216"/>
-      <c r="B88" s="217"/>
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="217"/>
+      <c r="B88" s="218"/>
       <c r="C88" s="37"/>
       <c r="D88" s="46"/>
       <c r="E88" s="74"/>
     </row>
-    <row r="89" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D89" s="56"/>
       <c r="E89" s="37"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="30"/>
       <c r="B90" s="75"/>
       <c r="C90" s="37"/>
       <c r="D90" s="46"/>
       <c r="E90" s="74"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B91" s="77"/>
       <c r="C91" s="77"/>
@@ -3271,27 +3271,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D92" s="62"/>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="D93" s="62"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B94" s="58"/>
       <c r="C94" s="58"/>
       <c r="D94" s="59"/>
       <c r="E94" s="133"/>
     </row>
-    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D95" s="62"/>
     </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B96" s="66"/>
       <c r="C96" s="67"/>
@@ -3301,89 +3301,89 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="98" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B98" s="80">
         <f>E83</f>
         <v>25293837.280000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="79" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B99" s="80">
         <f>E83-E81</f>
         <v>25293837.280000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B100" s="80">
         <f>E96-E94</f>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B101" s="80">
         <f>E96</f>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="222" t="s">
-        <v>254</v>
-      </c>
-      <c r="B104" s="222"/>
-    </row>
-    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="222"/>
-      <c r="B105" s="222"/>
-    </row>
-    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="222"/>
-      <c r="B106" s="222"/>
-    </row>
-    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="222" t="s">
-        <v>257</v>
-      </c>
-      <c r="B108" s="222"/>
-    </row>
-    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="222"/>
-      <c r="B109" s="222"/>
-    </row>
-    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="222"/>
-      <c r="B110" s="222"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="221" t="s">
-        <v>182</v>
-      </c>
-      <c r="B113" s="221"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="221"/>
-      <c r="B114" s="221"/>
-    </row>
-    <row r="115" spans="1:6" s="83" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="229" t="s">
+        <v>253</v>
+      </c>
+      <c r="B104" s="229"/>
+    </row>
+    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="229"/>
+      <c r="B105" s="229"/>
+    </row>
+    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="229"/>
+      <c r="B106" s="229"/>
+    </row>
+    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="229" t="s">
+        <v>256</v>
+      </c>
+      <c r="B108" s="229"/>
+    </row>
+    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="229"/>
+      <c r="B109" s="229"/>
+    </row>
+    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="229"/>
+      <c r="B110" s="229"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="228" t="s">
+        <v>181</v>
+      </c>
+      <c r="B113" s="228"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="228"/>
+      <c r="B114" s="228"/>
+    </row>
+    <row r="115" spans="1:6" s="83" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115"/>
       <c r="B115" s="81"/>
       <c r="C115" s="82"/>
     </row>
-    <row r="116" spans="1:6" s="83" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" s="83" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B116" s="84">
         <v>10597369.743745035</v>
@@ -3392,18 +3392,18 @@
       <c r="D116" s="85"/>
       <c r="E116" s="85"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B117" s="86">
         <f>-B99-B100</f>
         <v>-25293837.280000001</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B118" s="86">
         <f>B140</f>
@@ -3411,18 +3411,18 @@
       </c>
       <c r="F118" s="81"/>
     </row>
-    <row r="119" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="32" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B119" s="157">
         <v>-239116.53</v>
       </c>
       <c r="F119" s="81"/>
     </row>
-    <row r="120" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B120" s="158">
         <f>-119452</f>
@@ -3430,61 +3430,61 @@
       </c>
       <c r="F120" s="81"/>
     </row>
-    <row r="121" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B121" s="158">
         <v>-123612</v>
       </c>
       <c r="F121" s="81"/>
     </row>
-    <row r="122" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B122" s="158">
         <v>-168836.39</v>
       </c>
       <c r="F122" s="81"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B123" s="158">
         <v>-20871</v>
       </c>
       <c r="F123" s="81"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="32" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B124" s="158">
         <v>-3820</v>
       </c>
       <c r="F124" s="81"/>
     </row>
-    <row r="125" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B125" s="158">
         <v>-7274</v>
       </c>
       <c r="F125" s="81"/>
     </row>
-    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B126" s="156">
         <v>-7528</v>
       </c>
       <c r="F126" s="81"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="32" t="s">
         <v>2</v>
       </c>
@@ -3494,72 +3494,72 @@
       </c>
       <c r="F127" s="81"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B128" s="87">
         <v>300000</v>
       </c>
       <c r="F128" s="81"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B129" s="87">
         <v>250000</v>
       </c>
       <c r="F129" s="81"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B130" s="87">
         <v>200000.42</v>
       </c>
       <c r="F130" s="81"/>
     </row>
-    <row r="131" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B131" s="214">
         <v>-130000</v>
       </c>
       <c r="F131" s="81"/>
     </row>
-    <row r="132" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A132" s="32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B132" s="214">
         <v>-130000</v>
       </c>
       <c r="F132" s="81"/>
     </row>
-    <row r="133" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B133" s="214">
         <v>-130000</v>
       </c>
       <c r="F133" s="81"/>
     </row>
-    <row r="134" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="88" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B134" s="171">
         <v>123300</v>
       </c>
       <c r="F134" s="81"/>
     </row>
-    <row r="135" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B135" s="90">
         <f>SUM(B116:C134)</f>
@@ -3569,22 +3569,22 @@
       <c r="E135" s="64"/>
       <c r="F135" s="64"/>
     </row>
-    <row r="136" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="218" t="s">
-        <v>130</v>
-      </c>
-      <c r="B137" s="218"/>
-      <c r="C137" s="218"/>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A138" s="218"/>
-      <c r="B138" s="218"/>
-      <c r="C138" s="218"/>
-    </row>
-    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="227" t="s">
+        <v>129</v>
+      </c>
+      <c r="B137" s="227"/>
+      <c r="C137" s="227"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A138" s="227"/>
+      <c r="B138" s="227"/>
+      <c r="C138" s="227"/>
+    </row>
+    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="91" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B139" s="169">
         <v>195940.3</v>
@@ -3592,7 +3592,7 @@
       <c r="C139" s="92"/>
       <c r="D139" s="70"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="93" t="s">
         <v>0</v>
       </c>
@@ -3602,24 +3602,11 @@
       </c>
       <c r="C140" s="95"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M141" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A56:B56"/>
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A137:C138"/>
@@ -3636,6 +3623,19 @@
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A104:B106"/>
     <mergeCell ref="A108:B110"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A56:B56"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3646,54 +3646,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:N125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="141"/>
       <c r="B1" s="142"/>
       <c r="C1" s="142"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="229"/>
-      <c r="F1" s="229"/>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
+      <c r="D1" s="231"/>
+      <c r="E1" s="231"/>
+      <c r="F1" s="231"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
       <c r="L1" s="143"/>
     </row>
-    <row r="2" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="144"/>
       <c r="B2" s="145"/>
       <c r="C2" s="146"/>
       <c r="D2" s="146" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" s="252">
+        <v>130</v>
+      </c>
+      <c r="E2" s="254">
         <v>3000000</v>
       </c>
-      <c r="F2" s="252"/>
+      <c r="F2" s="254"/>
       <c r="G2" s="146"/>
       <c r="H2" s="146"/>
       <c r="I2" s="146" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J2" s="147">
         <v>12074625</v>
@@ -3702,7 +3702,7 @@
       <c r="L2" s="149"/>
       <c r="M2" s="97"/>
     </row>
-    <row r="3" spans="1:14" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="150"/>
       <c r="B3" s="151"/>
       <c r="C3" s="151"/>
@@ -3717,170 +3717,170 @@
       <c r="L3" s="154"/>
       <c r="M3" s="97"/>
     </row>
-    <row r="4" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="230" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="231"/>
-      <c r="C4" s="231"/>
-      <c r="D4" s="231"/>
-      <c r="E4" s="231"/>
-      <c r="F4" s="231"/>
-      <c r="G4" s="231"/>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="231"/>
-      <c r="K4" s="231"/>
-      <c r="L4" s="232"/>
+    <row r="4" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="232" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="233"/>
+      <c r="C4" s="233"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="234"/>
       <c r="M4" s="97"/>
     </row>
-    <row r="5" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="233"/>
-      <c r="B5" s="234"/>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="234"/>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="234"/>
-      <c r="K5" s="234"/>
-      <c r="L5" s="235"/>
+    <row r="5" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="235"/>
+      <c r="B5" s="236"/>
+      <c r="C5" s="236"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="236"/>
+      <c r="G5" s="236"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="236"/>
+      <c r="K5" s="236"/>
+      <c r="L5" s="237"/>
       <c r="M5" s="97"/>
     </row>
-    <row r="6" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="233"/>
-      <c r="B6" s="234"/>
-      <c r="C6" s="234"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="234"/>
-      <c r="F6" s="234"/>
-      <c r="G6" s="234"/>
-      <c r="H6" s="234"/>
-      <c r="I6" s="234"/>
-      <c r="J6" s="234"/>
-      <c r="K6" s="234"/>
-      <c r="L6" s="235"/>
+    <row r="6" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="235"/>
+      <c r="B6" s="236"/>
+      <c r="C6" s="236"/>
+      <c r="D6" s="236"/>
+      <c r="E6" s="236"/>
+      <c r="F6" s="236"/>
+      <c r="G6" s="236"/>
+      <c r="H6" s="236"/>
+      <c r="I6" s="236"/>
+      <c r="J6" s="236"/>
+      <c r="K6" s="236"/>
+      <c r="L6" s="237"/>
       <c r="M6" s="97"/>
     </row>
-    <row r="7" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="233"/>
-      <c r="B7" s="234"/>
-      <c r="C7" s="234"/>
-      <c r="D7" s="234"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="234"/>
-      <c r="H7" s="234"/>
-      <c r="I7" s="234"/>
-      <c r="J7" s="234"/>
-      <c r="K7" s="234"/>
-      <c r="L7" s="235"/>
+    <row r="7" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="235"/>
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="237"/>
       <c r="M7" s="97"/>
     </row>
-    <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="236"/>
-      <c r="B8" s="237"/>
-      <c r="C8" s="237"/>
-      <c r="D8" s="237"/>
-      <c r="E8" s="237"/>
-      <c r="F8" s="237"/>
-      <c r="G8" s="237"/>
-      <c r="H8" s="237"/>
-      <c r="I8" s="237"/>
-      <c r="J8" s="237"/>
-      <c r="K8" s="237"/>
-      <c r="L8" s="238"/>
-    </row>
-    <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="246" t="s">
+    <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="238"/>
+      <c r="B8" s="239"/>
+      <c r="C8" s="239"/>
+      <c r="D8" s="239"/>
+      <c r="E8" s="239"/>
+      <c r="F8" s="239"/>
+      <c r="G8" s="239"/>
+      <c r="H8" s="239"/>
+      <c r="I8" s="239"/>
+      <c r="J8" s="239"/>
+      <c r="K8" s="239"/>
+      <c r="L8" s="240"/>
+    </row>
+    <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="248" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="249"/>
+      <c r="C9" s="249"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="250"/>
+    </row>
+    <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="251" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="247"/>
-      <c r="C9" s="247"/>
-      <c r="D9" s="247"/>
-      <c r="E9" s="247"/>
-      <c r="F9" s="247"/>
-      <c r="G9" s="247"/>
-      <c r="H9" s="247"/>
-      <c r="I9" s="247"/>
-      <c r="J9" s="247"/>
-      <c r="K9" s="247"/>
-      <c r="L9" s="248"/>
-    </row>
-    <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="249" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" s="250"/>
-      <c r="C10" s="250"/>
-      <c r="D10" s="250"/>
-      <c r="E10" s="250"/>
-      <c r="F10" s="250"/>
-      <c r="G10" s="250"/>
-      <c r="H10" s="250"/>
-      <c r="I10" s="250"/>
-      <c r="J10" s="250"/>
-      <c r="K10" s="250"/>
-      <c r="L10" s="251"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="239" t="s">
+      <c r="B10" s="252"/>
+      <c r="C10" s="252"/>
+      <c r="D10" s="252"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="252"/>
+      <c r="G10" s="252"/>
+      <c r="H10" s="252"/>
+      <c r="I10" s="252"/>
+      <c r="J10" s="252"/>
+      <c r="K10" s="252"/>
+      <c r="L10" s="253"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="241" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="241" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="239" t="s">
+      <c r="C11" s="241" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="239" t="s">
+      <c r="D11" s="241" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="239" t="s">
+      <c r="E11" s="244" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="242" t="s">
+      <c r="F11" s="241" t="s">
         <v>137</v>
       </c>
-      <c r="F11" s="239" t="s">
+      <c r="G11" s="246" t="s">
         <v>138</v>
       </c>
-      <c r="G11" s="244" t="s">
+      <c r="H11" s="244" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="242" t="s">
+      <c r="I11" s="244" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" s="255" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" s="98" t="s">
         <v>140</v>
       </c>
-      <c r="I11" s="242" t="s">
-        <v>132</v>
-      </c>
-      <c r="J11" s="253" t="s">
-        <v>131</v>
-      </c>
-      <c r="K11" s="98" t="s">
+      <c r="L11" s="257" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="255" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="240"/>
-      <c r="B12" s="240"/>
-      <c r="C12" s="241"/>
-      <c r="D12" s="240"/>
-      <c r="E12" s="243"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="245"/>
-      <c r="H12" s="243"/>
-      <c r="I12" s="243"/>
-      <c r="J12" s="254"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="242"/>
+      <c r="B12" s="242"/>
+      <c r="C12" s="243"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="245"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="247"/>
+      <c r="H12" s="245"/>
+      <c r="I12" s="245"/>
+      <c r="J12" s="256"/>
       <c r="K12" s="99" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="L12" s="256"/>
-    </row>
-    <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="258"/>
+    </row>
+    <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="100">
         <v>1</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="100">
         <v>2</v>
       </c>
@@ -3972,10 +3972,10 @@
         <v>0.02</v>
       </c>
       <c r="N14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="100">
         <v>3</v>
       </c>
@@ -4022,11 +4022,11 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="260">
+    <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="216">
         <v>4</v>
       </c>
-      <c r="B16" s="260" t="s">
+      <c r="B16" s="216" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="136"/>
@@ -4069,7 +4069,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="100">
         <v>5</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="100">
         <v>6</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="100">
         <v>7</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="100">
         <v>8</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="100">
         <v>9</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="100">
         <v>10</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="100">
         <v>11</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="100">
         <v>12</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="100">
         <v>13</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="100">
         <v>14</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="159">
         <v>15</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="100">
         <v>16</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="100">
         <v>17</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="159">
         <v>18</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="100">
         <v>19</v>
       </c>
@@ -4763,10 +4763,10 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="N31" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="205">
         <v>20</v>
       </c>
@@ -4810,10 +4810,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="N32" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="166">
         <v>21</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="109">
         <f>A33+1</f>
         <v>22</v>
@@ -4907,7 +4907,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="109">
         <f t="shared" ref="A35:A98" si="9">A34+1</f>
         <v>23</v>
@@ -4955,7 +4955,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="109">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -5000,7 +5000,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="109">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -5045,7 +5045,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="109">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -5093,7 +5093,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="109">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -5141,7 +5141,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="109">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -5188,7 +5188,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="134">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -5233,10 +5233,10 @@
         <v>0.29000000000000009</v>
       </c>
       <c r="N41" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="166">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -5283,7 +5283,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="109">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -5330,7 +5330,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="109">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -5375,7 +5375,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="186">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -5420,7 +5420,7 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="109">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -5468,7 +5468,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="134">
         <f t="shared" si="9"/>
         <v>35</v>
@@ -5515,10 +5515,10 @@
         <v>0.35000000000000014</v>
       </c>
       <c r="N47" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="109">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -5566,10 +5566,10 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="N48" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="109">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -5617,7 +5617,7 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="109">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -5662,7 +5662,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="109">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -5710,7 +5710,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="109">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -5755,7 +5755,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="109">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -5802,7 +5802,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="186">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -5847,7 +5847,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="109">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -5894,7 +5894,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="109">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -5939,7 +5939,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="109">
         <f t="shared" si="9"/>
         <v>45</v>
@@ -5987,7 +5987,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="109">
         <f t="shared" si="9"/>
         <v>46</v>
@@ -6034,10 +6034,10 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="N58" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="134">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -6084,10 +6084,10 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="N59" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="166">
         <f t="shared" si="9"/>
         <v>48</v>
@@ -6135,10 +6135,10 @@
         <v>0.48000000000000026</v>
       </c>
       <c r="N60" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="109">
         <f t="shared" si="9"/>
         <v>49</v>
@@ -6185,7 +6185,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="109">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6233,7 +6233,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="109">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6280,7 +6280,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="109">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6328,7 +6328,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="166">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6375,7 +6375,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="109">
         <f t="shared" si="9"/>
         <v>54</v>
@@ -6422,7 +6422,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="109">
         <f t="shared" si="9"/>
         <v>55</v>
@@ -6469,7 +6469,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="109">
         <f t="shared" si="9"/>
         <v>56</v>
@@ -6516,7 +6516,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="166">
         <f t="shared" si="9"/>
         <v>57</v>
@@ -6563,7 +6563,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="109">
         <f t="shared" si="9"/>
         <v>58</v>
@@ -6611,7 +6611,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="166">
         <f t="shared" si="9"/>
         <v>59</v>
@@ -6659,7 +6659,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="109">
         <f t="shared" si="9"/>
         <v>60</v>
@@ -6706,7 +6706,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="109">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -6754,7 +6754,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="109">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -6801,7 +6801,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="109">
         <f t="shared" si="9"/>
         <v>63</v>
@@ -6849,7 +6849,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="109">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -6897,7 +6897,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="196">
         <f t="shared" si="9"/>
         <v>65</v>
@@ -6944,10 +6944,10 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="N77" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="109">
         <f t="shared" si="9"/>
         <v>66</v>
@@ -6994,7 +6994,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="109">
         <f t="shared" si="9"/>
         <v>67</v>
@@ -7041,7 +7041,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="109">
         <f t="shared" si="9"/>
         <v>68</v>
@@ -7088,7 +7088,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="109">
         <f t="shared" si="9"/>
         <v>69</v>
@@ -7135,7 +7135,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="134">
         <f t="shared" si="9"/>
         <v>70</v>
@@ -7180,10 +7180,10 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="N82" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="166">
         <f t="shared" si="9"/>
         <v>71</v>
@@ -7231,7 +7231,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="109">
         <f t="shared" si="9"/>
         <v>72</v>
@@ -7279,7 +7279,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="109">
         <f t="shared" si="9"/>
         <v>73</v>
@@ -7324,7 +7324,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="109">
         <f t="shared" si="9"/>
         <v>74</v>
@@ -7369,7 +7369,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="109">
         <f t="shared" si="9"/>
         <v>75</v>
@@ -7417,7 +7417,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="109">
         <f t="shared" si="9"/>
         <v>76</v>
@@ -7465,7 +7465,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="109">
         <f t="shared" si="9"/>
         <v>77</v>
@@ -7512,7 +7512,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="186">
         <f t="shared" si="9"/>
         <v>78</v>
@@ -7557,7 +7557,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="109">
         <f t="shared" si="9"/>
         <v>79</v>
@@ -7605,7 +7605,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="109">
         <f t="shared" si="9"/>
         <v>80</v>
@@ -7652,7 +7652,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="134">
         <f t="shared" si="9"/>
         <v>81</v>
@@ -7699,10 +7699,10 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="N93" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="109">
         <f t="shared" si="9"/>
         <v>82</v>
@@ -7750,7 +7750,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="166">
         <f t="shared" si="9"/>
         <v>83</v>
@@ -7798,7 +7798,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="166">
         <f t="shared" si="9"/>
         <v>84</v>
@@ -7846,7 +7846,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="109">
         <f t="shared" si="9"/>
         <v>85</v>
@@ -7894,7 +7894,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="109">
         <f t="shared" si="9"/>
         <v>86</v>
@@ -7942,7 +7942,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="109">
         <f t="shared" ref="A99:A115" si="23">A98+1</f>
         <v>87</v>
@@ -7989,7 +7989,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="109">
         <f t="shared" si="23"/>
         <v>88</v>
@@ -8037,7 +8037,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="109">
         <f t="shared" si="23"/>
         <v>89</v>
@@ -8085,7 +8085,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="109">
         <f t="shared" si="23"/>
         <v>90</v>
@@ -8132,7 +8132,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="109">
         <f t="shared" si="23"/>
         <v>91</v>
@@ -8179,7 +8179,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="109">
         <f t="shared" si="23"/>
         <v>92</v>
@@ -8227,7 +8227,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="166">
         <f t="shared" si="23"/>
         <v>93</v>
@@ -8275,7 +8275,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="166">
         <f t="shared" si="23"/>
         <v>94</v>
@@ -8323,13 +8323,13 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="166">
         <f t="shared" si="23"/>
         <v>95</v>
       </c>
       <c r="B107" s="168" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C107" s="167"/>
       <c r="D107" s="161">
@@ -8370,7 +8370,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="166">
         <f t="shared" si="23"/>
         <v>96</v>
@@ -8418,10 +8418,10 @@
         <v>0.96000000000000063</v>
       </c>
       <c r="N108" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="166">
         <f t="shared" si="23"/>
         <v>97</v>
@@ -8469,7 +8469,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="166">
         <f t="shared" si="23"/>
         <v>98</v>
@@ -8517,7 +8517,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="166">
         <f t="shared" si="23"/>
         <v>99</v>
@@ -8564,7 +8564,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="166">
         <f t="shared" si="23"/>
         <v>100</v>
@@ -8612,7 +8612,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="166">
         <f t="shared" si="23"/>
         <v>101</v>
@@ -8660,7 +8660,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="166">
         <f t="shared" si="23"/>
         <v>102</v>
@@ -8705,13 +8705,13 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="166">
         <f t="shared" si="23"/>
         <v>103</v>
       </c>
       <c r="B115" s="168" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C115" s="167"/>
       <c r="D115" s="161">
@@ -8753,7 +8753,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="166"/>
       <c r="B116" s="195"/>
       <c r="C116" s="167"/>
@@ -8768,7 +8768,7 @@
       <c r="L116" s="165"/>
       <c r="M116" s="64"/>
     </row>
-    <row r="117" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="112"/>
       <c r="B117" s="113"/>
       <c r="C117" s="113"/>
@@ -8809,87 +8809,88 @@
         <v>35636432.56000001</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="119"/>
       <c r="C118" s="119"/>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="257" t="s">
-        <v>107</v>
-      </c>
-      <c r="C120" s="257"/>
-      <c r="D120" s="257"/>
-      <c r="E120" s="257"/>
-      <c r="F120" s="257"/>
-      <c r="G120" s="257"/>
-      <c r="H120" s="257"/>
-      <c r="I120" s="257"/>
-      <c r="J120" s="257"/>
-      <c r="K120" s="257"/>
-    </row>
-    <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="257"/>
-      <c r="C121" s="257"/>
-      <c r="D121" s="257"/>
-      <c r="E121" s="257"/>
-      <c r="F121" s="257"/>
-      <c r="G121" s="257"/>
-      <c r="H121" s="257"/>
-      <c r="I121" s="257"/>
-      <c r="J121" s="257"/>
-      <c r="K121" s="257"/>
-    </row>
-    <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="257"/>
-      <c r="C122" s="257"/>
-      <c r="D122" s="257"/>
-      <c r="E122" s="257"/>
-      <c r="F122" s="257"/>
-      <c r="G122" s="257"/>
-      <c r="H122" s="257"/>
-      <c r="I122" s="257"/>
-      <c r="J122" s="257"/>
-      <c r="K122" s="257"/>
-    </row>
-    <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="257"/>
-      <c r="C123" s="257"/>
-      <c r="D123" s="257"/>
-      <c r="E123" s="257"/>
-      <c r="F123" s="257"/>
-      <c r="G123" s="257"/>
-      <c r="H123" s="257"/>
-      <c r="I123" s="257"/>
-      <c r="J123" s="257"/>
-      <c r="K123" s="257"/>
-    </row>
-    <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="257"/>
-      <c r="C124" s="257"/>
-      <c r="D124" s="257"/>
-      <c r="E124" s="257"/>
-      <c r="F124" s="257"/>
-      <c r="G124" s="257"/>
-      <c r="H124" s="257"/>
-      <c r="I124" s="257"/>
-      <c r="J124" s="257"/>
-      <c r="K124" s="257"/>
-    </row>
-    <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="257"/>
-      <c r="C125" s="257"/>
-      <c r="D125" s="257"/>
-      <c r="E125" s="257"/>
-      <c r="F125" s="257"/>
-      <c r="G125" s="257"/>
-      <c r="H125" s="257"/>
-      <c r="I125" s="257"/>
-      <c r="J125" s="257"/>
-      <c r="K125" s="257"/>
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="230" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" s="230"/>
+      <c r="D120" s="230"/>
+      <c r="E120" s="230"/>
+      <c r="F120" s="230"/>
+      <c r="G120" s="230"/>
+      <c r="H120" s="230"/>
+      <c r="I120" s="230"/>
+      <c r="J120" s="230"/>
+      <c r="K120" s="230"/>
+    </row>
+    <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="230"/>
+      <c r="C121" s="230"/>
+      <c r="D121" s="230"/>
+      <c r="E121" s="230"/>
+      <c r="F121" s="230"/>
+      <c r="G121" s="230"/>
+      <c r="H121" s="230"/>
+      <c r="I121" s="230"/>
+      <c r="J121" s="230"/>
+      <c r="K121" s="230"/>
+    </row>
+    <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="230"/>
+      <c r="C122" s="230"/>
+      <c r="D122" s="230"/>
+      <c r="E122" s="230"/>
+      <c r="F122" s="230"/>
+      <c r="G122" s="230"/>
+      <c r="H122" s="230"/>
+      <c r="I122" s="230"/>
+      <c r="J122" s="230"/>
+      <c r="K122" s="230"/>
+    </row>
+    <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="230"/>
+      <c r="C123" s="230"/>
+      <c r="D123" s="230"/>
+      <c r="E123" s="230"/>
+      <c r="F123" s="230"/>
+      <c r="G123" s="230"/>
+      <c r="H123" s="230"/>
+      <c r="I123" s="230"/>
+      <c r="J123" s="230"/>
+      <c r="K123" s="230"/>
+    </row>
+    <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="230"/>
+      <c r="C124" s="230"/>
+      <c r="D124" s="230"/>
+      <c r="E124" s="230"/>
+      <c r="F124" s="230"/>
+      <c r="G124" s="230"/>
+      <c r="H124" s="230"/>
+      <c r="I124" s="230"/>
+      <c r="J124" s="230"/>
+      <c r="K124" s="230"/>
+    </row>
+    <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="230"/>
+      <c r="C125" s="230"/>
+      <c r="D125" s="230"/>
+      <c r="E125" s="230"/>
+      <c r="F125" s="230"/>
+      <c r="G125" s="230"/>
+      <c r="H125" s="230"/>
+      <c r="I125" s="230"/>
+      <c r="J125" s="230"/>
+      <c r="K125" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L11:L12"/>
     <mergeCell ref="B120:K125"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="A4:L8"/>
@@ -8906,7 +8907,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="L11:L12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -8916,31 +8916,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="B5:Q25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="258" t="s">
+    <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="259" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="259"/>
+      <c r="D5" s="259"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="259"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="259"/>
+      <c r="L5" s="83" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="258"/>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="L5" s="83" t="s">
-        <v>189</v>
-      </c>
       <c r="M5" s="83" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
@@ -8951,7 +8951,7 @@
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -8962,9 +8962,9 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -8975,7 +8975,7 @@
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -8986,7 +8986,7 @@
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -8997,9 +8997,9 @@
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="172" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C12" s="172"/>
       <c r="D12" s="172"/>
@@ -9014,9 +9014,9 @@
       <c r="M12" s="172"/>
       <c r="N12" s="172"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="172" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C13" s="173">
         <v>194996.59</v>
@@ -9033,9 +9033,9 @@
       <c r="M13" s="172"/>
       <c r="N13" s="172"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="172" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C14" s="173">
         <v>15075.93</v>
@@ -9052,9 +9052,9 @@
       <c r="M14" s="172"/>
       <c r="N14" s="172"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="172" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C15" s="173">
         <v>15076.01</v>
@@ -9071,7 +9071,7 @@
       <c r="M15" s="172"/>
       <c r="N15" s="172"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="172"/>
       <c r="C16" s="172"/>
       <c r="D16" s="172"/>
@@ -9086,36 +9086,36 @@
       <c r="M16" s="172"/>
       <c r="N16" s="172"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B22" s="174" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="174" t="s">
+      <c r="C22" s="174"/>
+    </row>
+    <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="260" t="s">
         <v>196</v>
       </c>
-      <c r="C22" s="174"/>
-    </row>
-    <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="259" t="s">
-        <v>197</v>
-      </c>
-      <c r="C25" s="259"/>
-      <c r="D25" s="259"/>
-      <c r="E25" s="259"/>
-      <c r="F25" s="259"/>
-      <c r="G25" s="259"/>
-      <c r="H25" s="259"/>
-      <c r="I25" s="259"/>
-      <c r="J25" s="259"/>
-      <c r="K25" s="259"/>
-      <c r="L25" s="259"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="259"/>
-      <c r="O25" s="259"/>
-      <c r="P25" s="259"/>
-      <c r="Q25" s="259"/>
+      <c r="C25" s="260"/>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="260"/>
+      <c r="G25" s="260"/>
+      <c r="H25" s="260"/>
+      <c r="I25" s="260"/>
+      <c r="J25" s="260"/>
+      <c r="K25" s="260"/>
+      <c r="L25" s="260"/>
+      <c r="M25" s="260"/>
+      <c r="N25" s="260"/>
+      <c r="O25" s="260"/>
+      <c r="P25" s="260"/>
+      <c r="Q25" s="260"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD92C6BA-2604-48AA-8334-2FB5C60DF8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685FB0E0-584B-4F48-9479-37A9B46F2937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$L$125</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$139</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="262">
   <si>
     <t>TOTAL</t>
   </si>
@@ -599,9 +599,6 @@
   </si>
   <si>
     <t>Silvana Valeria Arredondo - Braian Brito</t>
-  </si>
-  <si>
-    <t>Diferencia mes anterior Sueldo Sr. Cesar por atraso en traspaso de cuenta (INCLUYE SAC)</t>
   </si>
   <si>
     <t>EL 12A Y 12 B TIENE GASTOS (QUE PAGARON ELLOS ) PENDIENTES QUE LES PONGAMOS COMO INGRESO DEL ASCENSOR. DEBEMOS AGREGARLE $272.252 A CADA UNO</t>
@@ -1773,12 +1770,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="14" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="14" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1836,12 +1827,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1860,14 +1860,11 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1950,17 +1947,17 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="22" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="22" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2325,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -2343,12 +2340,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="221" t="s">
+      <c r="B1" s="222" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="221"/>
-      <c r="D1" s="221"/>
-      <c r="E1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="223"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2361,12 +2358,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="223" t="s">
+      <c r="B3" s="224" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
-      <c r="E3" s="224"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="225"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2384,7 +2381,7 @@
         <v>155</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2399,54 +2396,54 @@
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="225" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="225"/>
+      <c r="B8" s="226" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="226"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="225"/>
-      <c r="C9" s="225"/>
+      <c r="B9" s="226"/>
+      <c r="C9" s="226"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="225"/>
-      <c r="C10" s="225"/>
+      <c r="B10" s="226"/>
+      <c r="C10" s="226"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="226" t="s">
+      <c r="A13" s="227" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="226"/>
-      <c r="C13" s="226"/>
-      <c r="D13" s="226"/>
-      <c r="E13" s="226"/>
+      <c r="B13" s="227"/>
+      <c r="C13" s="227"/>
+      <c r="D13" s="227"/>
+      <c r="E13" s="227"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="226"/>
-      <c r="B14" s="226"/>
-      <c r="C14" s="226"/>
-      <c r="D14" s="226"/>
-      <c r="E14" s="226"/>
+      <c r="A14" s="227"/>
+      <c r="B14" s="227"/>
+      <c r="C14" s="227"/>
+      <c r="D14" s="227"/>
+      <c r="E14" s="227"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="226"/>
-      <c r="B15" s="226"/>
-      <c r="C15" s="226"/>
-      <c r="D15" s="226"/>
-      <c r="E15" s="226"/>
+      <c r="A15" s="227"/>
+      <c r="B15" s="227"/>
+      <c r="C15" s="227"/>
+      <c r="D15" s="227"/>
+      <c r="E15" s="227"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="226"/>
-      <c r="B16" s="226"/>
-      <c r="C16" s="226"/>
-      <c r="D16" s="226"/>
-      <c r="E16" s="226"/>
+      <c r="A16" s="227"/>
+      <c r="B16" s="227"/>
+      <c r="C16" s="227"/>
+      <c r="D16" s="227"/>
+      <c r="E16" s="227"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2472,271 +2469,272 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="217" t="s">
+      <c r="A22" s="215" t="s">
         <v>176</v>
       </c>
-      <c r="B22" s="218"/>
+      <c r="B22" s="216"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="184">
-        <v>2182238</v>
+      <c r="D22" s="259">
+        <v>1931623</v>
       </c>
       <c r="E22" s="48"/>
       <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="217" t="s">
+      <c r="A23" s="215" t="s">
         <v>177</v>
       </c>
-      <c r="B23" s="218"/>
+      <c r="B23" s="216"/>
       <c r="C23" s="22"/>
-      <c r="D23" s="184">
-        <v>-474636.76</v>
+      <c r="D23" s="259">
+        <v>-420128</v>
       </c>
       <c r="E23" s="24"/>
       <c r="H23" s="23"/>
     </row>
-    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="217" t="s">
-        <v>186</v>
-      </c>
-      <c r="B24" s="218"/>
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="215" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="216"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="185">
-        <v>1381383</v>
+      <c r="D24" s="260">
+        <v>0</v>
       </c>
       <c r="E24" s="24"/>
       <c r="H24" s="23"/>
     </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="217" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="218"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="185">
-        <v>0.76</v>
-      </c>
-      <c r="E25" s="24"/>
-      <c r="H25" s="23"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="27">
+        <f>SUM(D22:D24)</f>
+        <v>1511495</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="26"/>
-      <c r="E26" s="27">
-        <f>SUM(D22:D25)</f>
-        <v>3088985</v>
-      </c>
+      <c r="E26" s="121"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="121"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="138">
+        <v>148000</v>
+      </c>
+      <c r="E27" s="123"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="138">
+      <c r="A28" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="155"/>
+      <c r="E28" s="29">
+        <f>D27</f>
         <v>148000</v>
       </c>
-      <c r="E28" s="123"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="29">
-        <f>D28</f>
-        <v>148000</v>
-      </c>
+      <c r="A29" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="121"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="121"/>
+      <c r="A30" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" s="122"/>
+      <c r="C30" s="122"/>
+      <c r="D30" s="138">
+        <v>13757.84</v>
+      </c>
+      <c r="E30" s="132" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="B31" s="122"/>
       <c r="C31" s="122"/>
       <c r="D31" s="138">
-        <v>13757.84</v>
+        <v>1235711.01</v>
       </c>
       <c r="E31" s="132" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B32" s="122"/>
       <c r="C32" s="122"/>
       <c r="D32" s="138">
-        <v>1235711.01</v>
+        <v>225490.24</v>
       </c>
       <c r="E32" s="132" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B33" s="122"/>
       <c r="C33" s="122"/>
       <c r="D33" s="138">
-        <v>225490.24</v>
-      </c>
-      <c r="E33" s="132" t="s">
-        <v>213</v>
+        <v>98200.71</v>
+      </c>
+      <c r="E33" s="132" t="str">
+        <f>E32</f>
+        <v>Debito 16/02</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
       <c r="D34" s="138">
-        <v>98200.71</v>
+        <v>10911.19</v>
       </c>
       <c r="E34" s="132" t="str">
-        <f>E33</f>
+        <f>E32</f>
         <v>Debito 16/02</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
-      <c r="D35" s="138">
-        <v>10911.19</v>
-      </c>
-      <c r="E35" s="132" t="str">
-        <f>E33</f>
-        <v>Debito 16/02</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B36" s="122"/>
-      <c r="C36" s="122"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="132"/>
-    </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
+      <c r="D35" s="46"/>
+      <c r="E35" s="132"/>
+    </row>
+    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
         <v>145</v>
+      </c>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="33">
+        <f>SUM(D30:D35)</f>
+        <v>1584070.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="33">
-        <f>SUM(D31:D36)</f>
-        <v>1584070.99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="29"/>
-    </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="219" t="s">
+      <c r="D37" s="28"/>
+      <c r="E37" s="29"/>
+    </row>
+    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="218" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="220"/>
+      <c r="B38" s="219"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="183">
+        <v>313739</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="218" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="219"/>
       <c r="C39" s="32"/>
-      <c r="D39" s="183">
-        <v>313739</v>
+      <c r="D39" s="178">
+        <v>5204</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="219" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" s="220"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="178">
-        <v>5204</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="33">
+        <f>SUM(D38:D39)</f>
+        <v>318943</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="33">
-        <f>SUM(D39:D40)</f>
-        <v>318943</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
+      <c r="A41" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="36"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="36"/>
+    </row>
+    <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="39">
+        <v>542686.9</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
         <v>112</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C43" s="37"/>
       <c r="D43" s="39">
-        <v>542686.9</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>235</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E43" s="24"/>
     </row>
     <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="37" t="s">
         <v>112</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="39">
@@ -2744,725 +2742,721 @@
       </c>
       <c r="E44" s="24"/>
     </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="B45" s="37" t="s">
-        <v>234</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="B45" s="40"/>
       <c r="C45" s="37"/>
       <c r="D45" s="39">
-        <v>0</v>
-      </c>
-      <c r="E45" s="24"/>
+        <v>10111.620000000001</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="40"/>
+      <c r="A46" s="218" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="219"/>
       <c r="C46" s="37"/>
       <c r="D46" s="39">
-        <v>10111.620000000001</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>232</v>
+        <v>4813938.26</v>
+      </c>
+      <c r="E46" s="177" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="219" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="220"/>
+      <c r="A47" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="31"/>
       <c r="C47" s="37"/>
-      <c r="D47" s="39">
-        <v>4813938.26</v>
-      </c>
-      <c r="E47" s="177" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="24"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="25" t="s">
+      <c r="D47" s="38"/>
+      <c r="E47" s="24"/>
+    </row>
+    <row r="48" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="25" t="s">
         <v>116</v>
       </c>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="43">
+        <f>SUM(D42:D47)</f>
+        <v>5366736.7799999993</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="17"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="43">
-        <f>SUM(D43:D48)</f>
-        <v>5366736.7799999993</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="17"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="44"/>
-    </row>
-    <row r="51" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="217" t="s">
+      <c r="D49" s="26"/>
+      <c r="E49" s="44"/>
+    </row>
+    <row r="50" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="215" t="s">
         <v>179</v>
       </c>
-      <c r="B51" s="218"/>
+      <c r="B50" s="216"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="39">
+        <v>225000</v>
+      </c>
+      <c r="E50" s="45" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="215" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" s="216"/>
       <c r="C51" s="37"/>
       <c r="D51" s="39">
-        <v>225000</v>
+        <v>500000</v>
       </c>
       <c r="E51" s="45" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="217" t="s">
-        <v>204</v>
-      </c>
-      <c r="B52" s="218"/>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="215" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="216"/>
       <c r="C52" s="37"/>
       <c r="D52" s="39">
-        <v>500000</v>
-      </c>
-      <c r="E52" s="45" t="s">
+        <v>1520000</v>
+      </c>
+      <c r="E52" s="170" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="217" t="s">
-        <v>208</v>
-      </c>
-      <c r="B53" s="218"/>
+    <row r="53" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="215" t="s">
+        <v>237</v>
+      </c>
+      <c r="B53" s="216"/>
       <c r="C53" s="37"/>
       <c r="D53" s="39">
-        <v>1520000</v>
+        <f>272252*2</f>
+        <v>544504</v>
       </c>
       <c r="E53" s="170" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="217" t="s">
         <v>238</v>
       </c>
-      <c r="B54" s="218"/>
+    </row>
+    <row r="54" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="215" t="s">
+        <v>222</v>
+      </c>
+      <c r="B54" s="216"/>
       <c r="C54" s="37"/>
       <c r="D54" s="39">
-        <f>272252*2</f>
-        <v>544504</v>
-      </c>
-      <c r="E54" s="170" t="s">
-        <v>239</v>
-      </c>
+        <v>85000</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="F54" s="64"/>
     </row>
     <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="217" t="s">
-        <v>223</v>
-      </c>
-      <c r="B55" s="218"/>
+      <c r="A55" s="215" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55" s="216"/>
       <c r="C55" s="37"/>
       <c r="D55" s="39">
-        <v>85000</v>
+        <v>120000</v>
       </c>
       <c r="E55" s="45" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F55" s="64"/>
     </row>
     <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="217" t="s">
-        <v>244</v>
-      </c>
-      <c r="B56" s="218"/>
+      <c r="A56" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B56" s="21"/>
       <c r="C56" s="37"/>
       <c r="D56" s="39">
-        <v>120000</v>
+        <v>35000</v>
       </c>
       <c r="E56" s="45" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F56" s="64"/>
     </row>
-    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="B57" s="21"/>
+    <row r="57" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="215" t="s">
+        <v>223</v>
+      </c>
+      <c r="B57" s="216"/>
       <c r="C57" s="37"/>
       <c r="D57" s="39">
-        <v>35000</v>
+        <v>6000</v>
       </c>
       <c r="E57" s="45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F57" s="64"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="217" t="s">
-        <v>224</v>
-      </c>
-      <c r="B58" s="218"/>
+    <row r="58" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="215" t="s">
+        <v>226</v>
+      </c>
+      <c r="B58" s="216"/>
       <c r="C58" s="37"/>
       <c r="D58" s="39">
-        <v>6000</v>
-      </c>
-      <c r="E58" s="45" t="s">
-        <v>222</v>
+        <v>7000000</v>
+      </c>
+      <c r="E58" s="48" t="s">
+        <v>227</v>
       </c>
       <c r="F58" s="64"/>
     </row>
-    <row r="59" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="217" t="s">
-        <v>227</v>
-      </c>
-      <c r="B59" s="218"/>
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B59" s="21"/>
       <c r="C59" s="37"/>
       <c r="D59" s="39">
-        <v>7000000</v>
-      </c>
-      <c r="E59" s="48" t="s">
-        <v>228</v>
+        <v>28000</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>173</v>
       </c>
       <c r="F59" s="64"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="20" t="s">
-        <v>218</v>
+    <row r="60" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="140" t="s">
+        <v>180</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="37"/>
       <c r="D60" s="39">
-        <v>28000</v>
+        <v>150800</v>
       </c>
       <c r="E60" s="45" t="s">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="F60" s="64"/>
     </row>
     <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="140" t="s">
-        <v>180</v>
-      </c>
-      <c r="B61" s="21"/>
+      <c r="A61" s="180" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" s="181"/>
       <c r="C61" s="37"/>
       <c r="D61" s="39">
-        <v>150800</v>
-      </c>
-      <c r="E61" s="45" t="s">
-        <v>222</v>
+        <v>910000</v>
+      </c>
+      <c r="E61" s="48" t="s">
+        <v>218</v>
       </c>
       <c r="F61" s="64"/>
     </row>
-    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="180" t="s">
-        <v>202</v>
-      </c>
-      <c r="B62" s="181"/>
+    <row r="62" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="215" t="s">
+        <v>220</v>
+      </c>
+      <c r="B62" s="216"/>
       <c r="C62" s="37"/>
       <c r="D62" s="39">
-        <v>910000</v>
+        <v>250000</v>
       </c>
       <c r="E62" s="48" t="s">
         <v>219</v>
       </c>
       <c r="F62" s="64"/>
     </row>
-    <row r="63" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="217" t="s">
-        <v>221</v>
-      </c>
-      <c r="B63" s="218"/>
+    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="140" t="s">
+        <v>199</v>
+      </c>
+      <c r="B63" s="21"/>
       <c r="C63" s="37"/>
       <c r="D63" s="39">
-        <v>250000</v>
+        <v>133300</v>
       </c>
       <c r="E63" s="48" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="F63" s="64"/>
     </row>
     <row r="64" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="140" t="s">
-        <v>200</v>
-      </c>
-      <c r="B64" s="21"/>
+      <c r="A64" s="215" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="216"/>
       <c r="C64" s="37"/>
       <c r="D64" s="39">
-        <v>133300</v>
+        <v>105602.65</v>
       </c>
       <c r="E64" s="48" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F64" s="64"/>
     </row>
-    <row r="65" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="217" t="s">
-        <v>214</v>
-      </c>
-      <c r="B65" s="218"/>
+    <row r="65" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="215" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" s="216"/>
       <c r="C65" s="37"/>
       <c r="D65" s="39">
-        <v>105602.65</v>
+        <v>2022800</v>
       </c>
       <c r="E65" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="F65" s="64"/>
-    </row>
-    <row r="66" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="217" t="s">
         <v>198</v>
       </c>
-      <c r="B66" s="218"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="39">
-        <v>2022800</v>
-      </c>
-      <c r="E66" s="48" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="25" t="s">
-        <v>0</v>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="33">
+        <f>SUM(D50:D65)</f>
+        <v>13636006.65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="17" t="s">
+        <v>117</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="33">
-        <f>SUM(D51:D66)</f>
-        <v>13636006.65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="19"/>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="217" t="s">
-        <v>206</v>
-      </c>
-      <c r="B69" s="218"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="215" t="s">
+        <v>205</v>
+      </c>
+      <c r="B68" s="216"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="182">
+        <v>650000</v>
+      </c>
+      <c r="E68" s="48"/>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="21"/>
       <c r="C69" s="22"/>
-      <c r="D69" s="182">
-        <v>650000</v>
-      </c>
-      <c r="E69" s="48"/>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="B70" s="21"/>
+      <c r="D69" s="139">
+        <v>125000</v>
+      </c>
+      <c r="E69" s="48" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="215" t="s">
+        <v>236</v>
+      </c>
+      <c r="B70" s="216"/>
       <c r="C70" s="22"/>
       <c r="D70" s="139">
-        <v>125000</v>
+        <v>62500</v>
       </c>
       <c r="E70" s="48" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="217" t="s">
-        <v>237</v>
-      </c>
-      <c r="B71" s="218"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="140" t="s">
+        <v>206</v>
+      </c>
+      <c r="B71" s="21"/>
       <c r="C71" s="22"/>
       <c r="D71" s="139">
-        <v>62500</v>
+        <v>45000</v>
       </c>
       <c r="E71" s="48" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="140" t="s">
-        <v>207</v>
-      </c>
-      <c r="B72" s="21"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="139">
-        <v>45000</v>
-      </c>
-      <c r="E72" s="48" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="25"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="27">
+        <f>SUM(D68:D71)</f>
+        <v>882500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B73" s="49"/>
       <c r="C73" s="25"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="27">
-        <f>SUM(D69:D72)</f>
-        <v>882500</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B74" s="49"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="50"/>
-      <c r="E74" s="33"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D73" s="50"/>
+      <c r="E73" s="33"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="39">
+        <v>18681.400000000001</v>
+      </c>
+      <c r="E74" s="51"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B75" s="37"/>
       <c r="C75" s="37"/>
       <c r="D75" s="39">
-        <v>18681.400000000001</v>
-      </c>
-      <c r="E75" s="51"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="39">
         <f>29633.91-18681.4</f>
         <v>10952.509999999998</v>
       </c>
+      <c r="E75" s="52"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" s="125"/>
+      <c r="C76" s="125"/>
+      <c r="D76" s="179">
+        <v>45000</v>
+      </c>
       <c r="E76" s="52"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B77" s="125"/>
       <c r="C77" s="125"/>
       <c r="D77" s="179">
-        <v>45000</v>
+        <v>193960.95</v>
       </c>
       <c r="E77" s="52"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="B78" s="125"/>
-      <c r="C78" s="125"/>
-      <c r="D78" s="179">
-        <v>193960.95</v>
-      </c>
-      <c r="E78" s="52"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="53" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="54"/>
-      <c r="E79" s="55">
-        <f>SUM(D75:D78)</f>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="55">
+        <f>SUM(D74:D77)</f>
         <v>268594.86</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="56"/>
-      <c r="E80" s="57"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="58" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="37"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="57"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="B81" s="58"/>
-      <c r="C81" s="58"/>
-      <c r="D81" s="59"/>
-      <c r="E81" s="60"/>
+      <c r="B80" s="58"/>
+      <c r="C80" s="58"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="60"/>
+    </row>
+    <row r="81" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="61"/>
+      <c r="D81" s="62"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="64"/>
     </row>
     <row r="82" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="61"/>
-      <c r="D82" s="62"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="64"/>
-    </row>
-    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="65" t="s">
+      <c r="A82" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="B83" s="66"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="68"/>
-      <c r="E83" s="69">
-        <f>(SUM(E21:E81))</f>
-        <v>25293837.280000001</v>
-      </c>
-      <c r="F83" s="70"/>
-      <c r="G83" s="64"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B82" s="66"/>
+      <c r="C82" s="67"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="69">
+        <f>(SUM(E21:E80))</f>
+        <v>23716347.280000001</v>
+      </c>
+      <c r="F82" s="70"/>
+      <c r="G82" s="64"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D83" s="62"/>
+      <c r="E83" s="62"/>
+    </row>
+    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D84" s="62"/>
       <c r="E84" s="62"/>
-    </row>
-    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D85" s="62"/>
-      <c r="E85" s="62"/>
-      <c r="H85" s="71"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="12" t="s">
+      <c r="H84" s="71"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="72"/>
-      <c r="E86" s="73"/>
+      <c r="B85" s="13"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="72"/>
+      <c r="E85" s="73"/>
+    </row>
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="30"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="37"/>
+      <c r="D86" s="46"/>
+      <c r="E86" s="74"/>
     </row>
     <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
+      <c r="A87" s="215"/>
+      <c r="B87" s="216"/>
       <c r="C87" s="37"/>
       <c r="D87" s="46"/>
       <c r="E87" s="74"/>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="217"/>
-      <c r="B88" s="218"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="74"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D89" s="56"/>
-      <c r="E89" s="37"/>
+    <row r="88" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D88" s="56"/>
+      <c r="E88" s="37"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="30"/>
+      <c r="B89" s="75"/>
+      <c r="C89" s="37"/>
+      <c r="D89" s="46"/>
+      <c r="E89" s="74"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="30"/>
-      <c r="B90" s="75"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="74"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="76" t="s">
+      <c r="A90" s="76" t="s">
         <v>152</v>
       </c>
-      <c r="B91" s="77"/>
-      <c r="C91" s="77"/>
-      <c r="D91" s="175"/>
-      <c r="E91" s="124">
-        <f>SUM(D87:D90)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="77"/>
+      <c r="C90" s="77"/>
+      <c r="D90" s="175"/>
+      <c r="E90" s="124">
+        <f>SUM(D86:D89)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D91" s="62"/>
+    </row>
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="D92" s="62"/>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="D93" s="62"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="58" t="s">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="B94" s="58"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="59"/>
-      <c r="E94" s="133"/>
+      <c r="B93" s="58"/>
+      <c r="C93" s="58"/>
+      <c r="D93" s="59"/>
+      <c r="E93" s="133"/>
+    </row>
+    <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D94" s="62"/>
     </row>
     <row r="95" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D95" s="62"/>
-    </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="65" t="s">
+      <c r="A95" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="B96" s="66"/>
-      <c r="C96" s="67"/>
-      <c r="D96" s="67"/>
-      <c r="E96" s="78">
-        <f>E91+E94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+      <c r="B95" s="66"/>
+      <c r="C95" s="67"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="78">
+        <f>E90+E93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="97" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="79" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="80">
+        <f>E82</f>
+        <v>23716347.280000001</v>
+      </c>
+    </row>
     <row r="98" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="79" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B98" s="80">
-        <f>E83</f>
-        <v>25293837.280000001</v>
+        <f>E82-E80</f>
+        <v>23716347.280000001</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="79" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B99" s="80">
-        <f>E83-E81</f>
-        <v>25293837.280000001</v>
+        <f>E95-E93</f>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="79" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B100" s="80">
-        <f>E96-E94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="79" t="s">
-        <v>127</v>
-      </c>
-      <c r="B101" s="80">
-        <f>E96</f>
-        <v>0</v>
-      </c>
+        <f>E95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="221" t="s">
+        <v>252</v>
+      </c>
+      <c r="B103" s="221"/>
     </row>
     <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="229" t="s">
-        <v>253</v>
-      </c>
-      <c r="B104" s="229"/>
+      <c r="A104" s="221"/>
+      <c r="B104" s="221"/>
     </row>
     <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="229"/>
-      <c r="B105" s="229"/>
-    </row>
-    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="229"/>
-      <c r="B106" s="229"/>
+      <c r="A105" s="221"/>
+      <c r="B105" s="221"/>
+    </row>
+    <row r="107" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="221" t="s">
+        <v>255</v>
+      </c>
+      <c r="B107" s="221"/>
     </row>
     <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="229" t="s">
-        <v>256</v>
-      </c>
-      <c r="B108" s="229"/>
+      <c r="A108" s="221"/>
+      <c r="B108" s="221"/>
     </row>
     <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="229"/>
-      <c r="B109" s="229"/>
-    </row>
-    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="229"/>
-      <c r="B110" s="229"/>
+      <c r="A109" s="221"/>
+      <c r="B109" s="221"/>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="220" t="s">
+        <v>181</v>
+      </c>
+      <c r="B112" s="220"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="228" t="s">
-        <v>181</v>
-      </c>
-      <c r="B113" s="228"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="228"/>
-      <c r="B114" s="228"/>
-    </row>
-    <row r="115" spans="1:6" s="83" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A115"/>
-      <c r="B115" s="81"/>
+      <c r="A113" s="220"/>
+      <c r="B113" s="220"/>
+    </row>
+    <row r="114" spans="1:6" s="83" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114"/>
+      <c r="B114" s="81"/>
+      <c r="C114" s="82"/>
+    </row>
+    <row r="115" spans="1:6" s="83" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="137" t="s">
+        <v>174</v>
+      </c>
+      <c r="B115" s="84">
+        <v>10597369.743745035</v>
+      </c>
       <c r="C115" s="82"/>
-    </row>
-    <row r="116" spans="1:6" s="83" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="137" t="s">
-        <v>174</v>
-      </c>
-      <c r="B116" s="84">
-        <v>10597369.743745035</v>
-      </c>
-      <c r="C116" s="82"/>
-      <c r="D116" s="85"/>
-      <c r="E116" s="85"/>
+      <c r="D115" s="85"/>
+      <c r="E115" s="85"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="B116" s="86">
+        <f>-B98-B99</f>
+        <v>-23716347.280000001</v>
+      </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="32" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B117" s="86">
-        <f>-B99-B100</f>
-        <v>-25293837.280000001</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+        <f>B139</f>
+        <v>195940.3</v>
+      </c>
+      <c r="F117" s="81"/>
+    </row>
+    <row r="118" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="B118" s="86">
-        <f>B140</f>
-        <v>195940.3</v>
+        <v>239</v>
+      </c>
+      <c r="B118" s="157">
+        <v>-239116.53</v>
       </c>
       <c r="F118" s="81"/>
     </row>
-    <row r="119" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="B119" s="157">
-        <v>-239116.53</v>
-      </c>
-      <c r="F119" s="81"/>
-    </row>
-    <row r="120" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="B120" s="158">
+      <c r="B119" s="158">
         <f>-119452</f>
         <v>-119452</v>
       </c>
+      <c r="F119" s="81"/>
+    </row>
+    <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A120" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="B120" s="158">
+        <v>-123612</v>
+      </c>
       <c r="F120" s="81"/>
     </row>
     <row r="121" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="32" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B121" s="158">
-        <v>-123612</v>
+        <v>-168836.39</v>
       </c>
       <c r="F121" s="81"/>
     </row>
-    <row r="122" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="32" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B122" s="158">
-        <v>-168836.39</v>
+        <v>-20871</v>
       </c>
       <c r="F122" s="81"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="32" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B123" s="158">
-        <v>-20871</v>
+        <v>-3820</v>
       </c>
       <c r="F123" s="81"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="32" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B124" s="158">
-        <v>-3820</v>
+        <v>-7274</v>
       </c>
       <c r="F124" s="81"/>
     </row>
@@ -3470,27 +3464,27 @@
       <c r="A125" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="B125" s="158">
-        <v>-7274</v>
+      <c r="B125" s="156">
+        <v>-7528</v>
       </c>
       <c r="F125" s="81"/>
     </row>
-    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="B126" s="156">
-        <v>-7528</v>
+        <v>2</v>
+      </c>
+      <c r="B126" s="87">
+        <f>PRORRATEO!F117</f>
+        <v>13927009.310000001</v>
       </c>
       <c r="F126" s="81"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="32" t="s">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="B127" s="87">
-        <f>PRORRATEO!F117</f>
-        <v>13927009.310000001</v>
+        <v>300000</v>
       </c>
       <c r="F127" s="81"/>
     </row>
@@ -3499,7 +3493,7 @@
         <v>257</v>
       </c>
       <c r="B128" s="87">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="F128" s="81"/>
     </row>
@@ -3508,134 +3502,124 @@
         <v>258</v>
       </c>
       <c r="B129" s="87">
-        <v>250000</v>
+        <v>200000.42</v>
       </c>
       <c r="F129" s="81"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="B130" s="87">
-        <v>200000.42</v>
+        <v>253</v>
+      </c>
+      <c r="B130" s="212">
+        <v>-130000</v>
       </c>
       <c r="F130" s="81"/>
     </row>
     <row r="131" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="B131" s="212">
+        <v>-130000</v>
+      </c>
+      <c r="F131" s="81"/>
+    </row>
+    <row r="132" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="B131" s="214">
+      <c r="B132" s="212">
         <v>-130000</v>
       </c>
-      <c r="F131" s="81"/>
-    </row>
-    <row r="132" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A132" s="32" t="s">
+      <c r="F132" s="81"/>
+    </row>
+    <row r="133" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A133" s="88" t="s">
         <v>260</v>
       </c>
-      <c r="B132" s="214">
-        <v>-130000</v>
-      </c>
-      <c r="F132" s="81"/>
-    </row>
-    <row r="133" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="B133" s="214">
-        <v>-130000</v>
+      <c r="B133" s="171">
+        <v>123300</v>
       </c>
       <c r="F133" s="81"/>
     </row>
-    <row r="134" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A134" s="88" t="s">
-        <v>261</v>
-      </c>
-      <c r="B134" s="171">
-        <v>123300</v>
-      </c>
-      <c r="F134" s="81"/>
-    </row>
-    <row r="135" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="89" t="s">
+    <row r="134" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="B135" s="90">
-        <f>SUM(B116:C134)</f>
-        <v>-780727.42625496525</v>
-      </c>
-      <c r="D135" s="81"/>
-      <c r="E135" s="64"/>
-      <c r="F135" s="64"/>
-    </row>
-    <row r="136" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="B134" s="90">
+        <f>SUM(B115:C133)</f>
+        <v>796762.57374503464</v>
+      </c>
+      <c r="D134" s="81"/>
+      <c r="E134" s="64"/>
+      <c r="F134" s="64"/>
+    </row>
+    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="217" t="s">
+        <v>129</v>
+      </c>
+      <c r="B136" s="217"/>
+      <c r="C136" s="217"/>
+    </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137" s="227" t="s">
-        <v>129</v>
-      </c>
-      <c r="B137" s="227"/>
-      <c r="C137" s="227"/>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A138" s="227"/>
-      <c r="B138" s="227"/>
-      <c r="C138" s="227"/>
-    </row>
-    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="91" t="s">
-        <v>246</v>
-      </c>
-      <c r="B139" s="169">
+      <c r="A137" s="217"/>
+      <c r="B137" s="217"/>
+      <c r="C137" s="217"/>
+    </row>
+    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="91" t="s">
+        <v>245</v>
+      </c>
+      <c r="B138" s="169">
         <v>195940.3</v>
       </c>
-      <c r="C139" s="92"/>
-      <c r="D139" s="70"/>
+      <c r="C138" s="92"/>
+      <c r="D138" s="70"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B139" s="94">
+        <f>SUM(B138:B138)</f>
+        <v>195940.3</v>
+      </c>
+      <c r="C139" s="95"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="94">
-        <f>SUM(B139:B139)</f>
-        <v>195940.3</v>
-      </c>
-      <c r="C140" s="95"/>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M141" s="96"/>
+      <c r="M140" s="96"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A137:C138"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A113:B114"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A104:B106"/>
-    <mergeCell ref="A108:B110"/>
+  <mergeCells count="28">
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A136:C137"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A103:B105"/>
+    <mergeCell ref="A107:B109"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3859,7 +3843,7 @@
       <c r="K11" s="98" t="s">
         <v>140</v>
       </c>
-      <c r="L11" s="257" t="s">
+      <c r="L11" s="228" t="s">
         <v>141</v>
       </c>
     </row>
@@ -3878,7 +3862,7 @@
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="L12" s="258"/>
+      <c r="L12" s="229"/>
     </row>
     <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="100">
@@ -4023,10 +4007,10 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="216">
+      <c r="A16" s="214">
         <v>4</v>
       </c>
-      <c r="B16" s="216" t="s">
+      <c r="B16" s="214" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="136"/>
@@ -4767,41 +4751,41 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="205">
+      <c r="A32" s="203">
         <v>20</v>
       </c>
-      <c r="B32" s="206" t="s">
+      <c r="B32" s="204" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="207"/>
-      <c r="D32" s="208">
+      <c r="C32" s="205"/>
+      <c r="D32" s="206">
         <v>1.35</v>
       </c>
-      <c r="E32" s="209">
+      <c r="E32" s="207">
         <v>203507.20000000001</v>
       </c>
-      <c r="F32" s="209"/>
-      <c r="G32" s="210">
+      <c r="F32" s="207"/>
+      <c r="G32" s="208">
         <f t="shared" si="0"/>
         <v>203507.20000000001</v>
       </c>
-      <c r="H32" s="210">
+      <c r="H32" s="208">
         <f t="shared" si="5"/>
         <v>6105.2160000000003</v>
       </c>
-      <c r="I32" s="211">
+      <c r="I32" s="209">
         <f t="shared" si="1"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J32" s="211">
+      <c r="J32" s="209">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K32" s="212">
+      <c r="K32" s="210">
         <f t="shared" si="3"/>
         <v>413120.2</v>
       </c>
-      <c r="L32" s="213">
+      <c r="L32" s="211">
         <f t="shared" si="4"/>
         <v>425514.2</v>
       </c>
@@ -5376,42 +5360,42 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="186">
+      <c r="A45" s="184">
         <f t="shared" si="9"/>
         <v>33</v>
       </c>
-      <c r="B45" s="187" t="s">
+      <c r="B45" s="185" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="188"/>
-      <c r="D45" s="189">
+      <c r="C45" s="186"/>
+      <c r="D45" s="187">
         <v>1.17</v>
       </c>
-      <c r="E45" s="190">
+      <c r="E45" s="188">
         <v>176373.11249999999</v>
       </c>
-      <c r="F45" s="190"/>
-      <c r="G45" s="191">
+      <c r="F45" s="188"/>
+      <c r="G45" s="189">
         <f t="shared" si="0"/>
         <v>176373.11249999999</v>
       </c>
-      <c r="H45" s="191">
+      <c r="H45" s="189">
         <f t="shared" si="5"/>
         <v>5291.1933749999998</v>
       </c>
-      <c r="I45" s="192">
+      <c r="I45" s="190">
         <f t="shared" ref="I45:I76" si="10">J$2*D45/100</f>
         <v>141273.11249999999</v>
       </c>
-      <c r="J45" s="192">
+      <c r="J45" s="190">
         <f t="shared" ref="J45:J76" si="11">E$2*D45/100</f>
         <v>35100</v>
       </c>
-      <c r="K45" s="193">
+      <c r="K45" s="191">
         <f t="shared" ref="K45:K76" si="12">ROUND(SUM(G45:J45),0) + M45</f>
         <v>358037.33</v>
       </c>
-      <c r="L45" s="194">
+      <c r="L45" s="192">
         <f t="shared" si="8"/>
         <v>368778.33</v>
       </c>
@@ -5803,42 +5787,42 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="186">
+      <c r="A54" s="184">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
-      <c r="B54" s="187" t="s">
+      <c r="B54" s="185" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="188"/>
-      <c r="D54" s="189">
+      <c r="C54" s="186"/>
+      <c r="D54" s="187">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E54" s="190">
+      <c r="E54" s="188">
         <v>818744.42</v>
       </c>
-      <c r="F54" s="190"/>
-      <c r="G54" s="191">
+      <c r="F54" s="188"/>
+      <c r="G54" s="189">
         <f t="shared" si="0"/>
         <v>818744.42</v>
       </c>
-      <c r="H54" s="191">
+      <c r="H54" s="189">
         <f t="shared" si="5"/>
         <v>24562.332600000002</v>
       </c>
-      <c r="I54" s="192">
+      <c r="I54" s="190">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J54" s="192">
+      <c r="J54" s="190">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K54" s="193">
+      <c r="K54" s="191">
         <f t="shared" si="12"/>
         <v>1012143.42</v>
       </c>
-      <c r="L54" s="194">
+      <c r="L54" s="192">
         <f t="shared" si="8"/>
         <v>1042507.42</v>
       </c>
@@ -6084,7 +6068,7 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="N59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -6898,44 +6882,44 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="196">
+      <c r="A77" s="194">
         <f t="shared" si="9"/>
         <v>65</v>
       </c>
-      <c r="B77" s="197" t="s">
+      <c r="B77" s="195" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="198"/>
-      <c r="D77" s="199">
+      <c r="C77" s="196"/>
+      <c r="D77" s="197">
         <v>0.82</v>
       </c>
-      <c r="E77" s="200">
+      <c r="E77" s="198">
         <v>880370.65</v>
       </c>
-      <c r="F77" s="215">
+      <c r="F77" s="213">
         <v>99011.93</v>
       </c>
-      <c r="G77" s="201">
+      <c r="G77" s="199">
         <f t="shared" ref="G77:G115" si="15">E77-F77</f>
         <v>781358.72</v>
       </c>
-      <c r="H77" s="201">
+      <c r="H77" s="199">
         <f t="shared" si="5"/>
         <v>23440.761599999998</v>
       </c>
-      <c r="I77" s="202">
+      <c r="I77" s="200">
         <f t="shared" ref="I77:I108" si="16">J$2*D77/100</f>
         <v>99011.925000000003</v>
       </c>
-      <c r="J77" s="202">
+      <c r="J77" s="200">
         <f t="shared" ref="J77:J108" si="17">E$2*D77/100</f>
         <v>24600</v>
       </c>
-      <c r="K77" s="203">
+      <c r="K77" s="201">
         <f t="shared" ref="K77:K108" si="18">ROUND(SUM(G77:J77),0) + M77</f>
         <v>928411.65</v>
       </c>
-      <c r="L77" s="204">
+      <c r="L77" s="202">
         <f t="shared" si="8"/>
         <v>956263.65</v>
       </c>
@@ -6944,7 +6928,7 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="N77" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
@@ -7513,42 +7497,42 @@
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A90" s="186">
+      <c r="A90" s="184">
         <f t="shared" si="9"/>
         <v>78</v>
       </c>
-      <c r="B90" s="187" t="s">
+      <c r="B90" s="185" t="s">
         <v>79</v>
       </c>
-      <c r="C90" s="188"/>
-      <c r="D90" s="189">
+      <c r="C90" s="186"/>
+      <c r="D90" s="187">
         <v>0.82</v>
       </c>
-      <c r="E90" s="190">
+      <c r="E90" s="188">
         <v>123611.925</v>
       </c>
-      <c r="F90" s="190"/>
-      <c r="G90" s="191">
+      <c r="F90" s="188"/>
+      <c r="G90" s="189">
         <f t="shared" si="15"/>
         <v>123611.925</v>
       </c>
-      <c r="H90" s="191">
+      <c r="H90" s="189">
         <f t="shared" si="19"/>
         <v>3708.3577500000001</v>
       </c>
-      <c r="I90" s="192">
+      <c r="I90" s="190">
         <f t="shared" si="16"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J90" s="192">
+      <c r="J90" s="190">
         <f t="shared" si="17"/>
         <v>24600</v>
       </c>
-      <c r="K90" s="193">
+      <c r="K90" s="191">
         <f t="shared" si="18"/>
         <v>250932.78</v>
       </c>
-      <c r="L90" s="194">
+      <c r="L90" s="192">
         <f t="shared" si="8"/>
         <v>258460.78</v>
       </c>
@@ -7699,7 +7683,7 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="N93" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
@@ -7766,7 +7750,7 @@
         <v>191113.83</v>
       </c>
       <c r="F95" s="103">
-        <f>RESUMEN!D54/2+196846.93</f>
+        <f>RESUMEN!D53/2+196846.93</f>
         <v>469098.93</v>
       </c>
       <c r="G95" s="104">
@@ -7814,7 +7798,7 @@
         <v>449255.84</v>
       </c>
       <c r="F96" s="103">
-        <f>RESUMEN!D54/2+168836.84</f>
+        <f>RESUMEN!D53/2+168836.84</f>
         <v>441088.83999999997</v>
       </c>
       <c r="G96" s="104">
@@ -8665,7 +8649,7 @@
         <f t="shared" si="23"/>
         <v>102</v>
       </c>
-      <c r="B114" s="195" t="s">
+      <c r="B114" s="193" t="s">
         <v>101</v>
       </c>
       <c r="C114" s="167"/>
@@ -8755,7 +8739,7 @@
     </row>
     <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="166"/>
-      <c r="B116" s="195"/>
+      <c r="B116" s="193"/>
       <c r="C116" s="167"/>
       <c r="D116" s="161"/>
       <c r="E116" s="111"/>
@@ -8890,6 +8874,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="B120:K125"/>
     <mergeCell ref="D1:K1"/>
@@ -8906,7 +8891,6 @@
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -8922,19 +8906,19 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="259" t="s">
+      <c r="B5" s="257" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
+      <c r="H5" s="257"/>
+      <c r="I5" s="257"/>
+      <c r="J5" s="257"/>
+      <c r="L5" s="83" t="s">
         <v>187</v>
-      </c>
-      <c r="C5" s="259"/>
-      <c r="D5" s="259"/>
-      <c r="E5" s="259"/>
-      <c r="F5" s="259"/>
-      <c r="G5" s="259"/>
-      <c r="H5" s="259"/>
-      <c r="I5" s="259"/>
-      <c r="J5" s="259"/>
-      <c r="L5" s="83" t="s">
-        <v>188</v>
       </c>
       <c r="M5" s="83" t="s">
         <v>183</v>
@@ -8964,7 +8948,7 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -8999,7 +8983,7 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="172" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C12" s="172"/>
       <c r="D12" s="172"/>
@@ -9016,7 +9000,7 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="172" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" s="173">
         <v>194996.59</v>
@@ -9035,7 +9019,7 @@
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="172" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C14" s="173">
         <v>15075.93</v>
@@ -9054,7 +9038,7 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="172" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C15" s="173">
         <v>15076.01</v>
@@ -9088,34 +9072,34 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="174" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="174"/>
+    </row>
+    <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="258" t="s">
         <v>195</v>
       </c>
-      <c r="C22" s="174"/>
-    </row>
-    <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="260" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="260"/>
-      <c r="D25" s="260"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="260"/>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="260"/>
-      <c r="J25" s="260"/>
-      <c r="K25" s="260"/>
-      <c r="L25" s="260"/>
-      <c r="M25" s="260"/>
-      <c r="N25" s="260"/>
-      <c r="O25" s="260"/>
-      <c r="P25" s="260"/>
-      <c r="Q25" s="260"/>
+      <c r="C25" s="258"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="258"/>
+      <c r="F25" s="258"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
+      <c r="M25" s="258"/>
+      <c r="N25" s="258"/>
+      <c r="O25" s="258"/>
+      <c r="P25" s="258"/>
+      <c r="Q25" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15178C8-C9E6-4046-BE75-0314A4440489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B937B3D-42EE-4879-AD68-BBFFFDAB0796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$126</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$141</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$142</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="268">
   <si>
     <t>TOTAL</t>
   </si>
@@ -864,6 +864,9 @@
   </si>
   <si>
     <t>LA CUENTA BANCARIA DEL BANCO ROELA HA SIDO CERRADA, TRANSFERENCIAS SOLO AL CREDICOP</t>
+  </si>
+  <si>
+    <t>Seguro Sra. Gisela</t>
   </si>
 </sst>
 </file>
@@ -1944,24 +1947,33 @@
     <xf numFmtId="165" fontId="20" fillId="11" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1974,14 +1986,23 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2064,29 +2085,11 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2451,7 +2454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.54296875" customWidth="1"/>
@@ -2469,12 +2472,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="209" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="205"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="210"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -2487,12 +2490,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="211" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="209"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="212"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
@@ -2530,49 +2533,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="210" t="s">
+      <c r="B8" s="213" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="210"/>
+      <c r="C8" s="213"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="210"/>
-      <c r="C9" s="210"/>
+      <c r="B9" s="213"/>
+      <c r="C9" s="213"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="210"/>
-      <c r="C10" s="210"/>
+      <c r="B10" s="213"/>
+      <c r="C10" s="213"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="211" t="s">
+      <c r="A13" s="214" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="211"/>
-      <c r="C13" s="211"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="211"/>
+      <c r="B13" s="214"/>
+      <c r="C13" s="214"/>
+      <c r="D13" s="214"/>
+      <c r="E13" s="214"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="211"/>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
+      <c r="A14" s="214"/>
+      <c r="B14" s="214"/>
+      <c r="C14" s="214"/>
+      <c r="D14" s="214"/>
+      <c r="E14" s="214"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="211"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
+      <c r="A15" s="214"/>
+      <c r="B15" s="214"/>
+      <c r="C15" s="214"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="214"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="211"/>
-      <c r="B16" s="211"/>
-      <c r="C16" s="211"/>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
+      <c r="A16" s="214"/>
+      <c r="B16" s="214"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="214"/>
+      <c r="E16" s="214"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2598,10 +2601,10 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="206" t="s">
+      <c r="A22" s="202" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="207"/>
+      <c r="B22" s="203"/>
       <c r="C22" s="22"/>
       <c r="D22" s="170">
         <v>1931623</v>
@@ -2610,10 +2613,10 @@
       <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="206" t="s">
+      <c r="A23" s="202" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="207"/>
+      <c r="B23" s="203"/>
       <c r="C23" s="22"/>
       <c r="D23" s="170">
         <v>-420128</v>
@@ -2622,10 +2625,10 @@
       <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="206" t="s">
+      <c r="A24" s="202" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="207"/>
+      <c r="B24" s="203"/>
       <c r="C24" s="22"/>
       <c r="D24" s="171">
         <v>0</v>
@@ -2666,217 +2669,217 @@
       <c r="E27" s="110"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="45">
+        <v>5842.51</v>
+      </c>
+      <c r="E28" s="118" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="29">
-        <f>D27</f>
-        <v>148000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="29">
+        <f>D27+D28</f>
+        <v>153842.51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="108"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="B30" s="109"/>
-      <c r="C30" s="109"/>
-      <c r="D30" s="45">
-        <v>13757.84</v>
-      </c>
-      <c r="E30" s="118" t="s">
-        <v>224</v>
-      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="108"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="B31" s="109"/>
       <c r="C31" s="109"/>
       <c r="D31" s="45">
-        <v>1235711.01</v>
+        <v>13757.84</v>
       </c>
       <c r="E31" s="118" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B32" s="109"/>
       <c r="C32" s="109"/>
       <c r="D32" s="45">
-        <v>225490.24</v>
+        <v>1235711.01</v>
       </c>
       <c r="E32" s="118" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B33" s="109"/>
       <c r="C33" s="109"/>
       <c r="D33" s="45">
-        <v>98200.71</v>
-      </c>
-      <c r="E33" s="118" t="str">
-        <f>E32</f>
-        <v>Debito 16/02</v>
+        <v>225490.24</v>
+      </c>
+      <c r="E33" s="118" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B34" s="109"/>
       <c r="C34" s="109"/>
       <c r="D34" s="45">
-        <v>10911.19</v>
+        <v>98200.71</v>
       </c>
       <c r="E34" s="118" t="str">
-        <f>E32</f>
+        <f>E33</f>
         <v>Debito 16/02</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="22" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="B35" s="109"/>
       <c r="C35" s="109"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="118"/>
-    </row>
-    <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="25" t="s">
+      <c r="D35" s="45">
+        <v>10911.19</v>
+      </c>
+      <c r="E35" s="118" t="str">
+        <f>E33</f>
+        <v>Debito 16/02</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="109"/>
+      <c r="C36" s="109"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="118"/>
+    </row>
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="25" t="s">
         <v>145</v>
-      </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="33">
-        <f>SUM(D30:D35)</f>
-        <v>1584070.99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="17" t="s">
-        <v>109</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="29"/>
-    </row>
-    <row r="38" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="202" t="s">
+      <c r="D37" s="26"/>
+      <c r="E37" s="33">
+        <f>SUM(D31:D36)</f>
+        <v>1584070.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="29"/>
+    </row>
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="205" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="203"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="172">
+      <c r="B39" s="206"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="172">
         <v>313739</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E39" s="24" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="202" t="s">
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="205" t="s">
         <v>264</v>
       </c>
-      <c r="B39" s="203"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="173">
-        <v>214164</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="202" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" s="203"/>
+      <c r="B40" s="206"/>
       <c r="C40" s="32"/>
       <c r="D40" s="173">
+        <v>214164</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="205" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="206"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="173">
         <v>5204</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E41" s="24" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="25" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="33">
-        <f>SUM(D38:D40)</f>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="33">
+        <f>SUM(D39:D41)</f>
         <v>533107</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="17" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="36"/>
-    </row>
-    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="38">
-        <v>542686.9</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>230</v>
-      </c>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="36"/>
     </row>
     <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="37" t="s">
         <v>112</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="38">
-        <v>0</v>
-      </c>
-      <c r="E44" s="24"/>
+        <v>542686.9</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="37" t="s">
         <v>112</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="38">
@@ -2884,895 +2887,908 @@
       </c>
       <c r="E45" s="24"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="39"/>
+        <v>112</v>
+      </c>
+      <c r="B46" s="37" t="s">
+        <v>229</v>
+      </c>
       <c r="C46" s="37"/>
       <c r="D46" s="38">
-        <v>10111.620000000001</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>227</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" s="24"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="202" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="203"/>
+      <c r="A47" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="39"/>
       <c r="C47" s="37"/>
       <c r="D47" s="38">
+        <v>10111.620000000001</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="205" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="206"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="38">
         <v>4813938.26</v>
       </c>
-      <c r="E47" s="158" t="s">
+      <c r="E48" s="158" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="40" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="24"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="25" t="s">
+      <c r="B49" s="31"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="24"/>
+    </row>
+    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="42">
-        <f>SUM(D43:D48)</f>
-        <v>5366736.7799999993</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="17"/>
       <c r="B50" s="25"/>
       <c r="C50" s="25"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="43"/>
-    </row>
-    <row r="51" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="206" t="s">
+      <c r="D50" s="41"/>
+      <c r="E50" s="42">
+        <f>SUM(D44:D49)</f>
+        <v>5366736.7799999993</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="17"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="43"/>
+    </row>
+    <row r="52" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="202" t="s">
         <v>178</v>
       </c>
-      <c r="B51" s="207"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="38">
-        <v>225000</v>
-      </c>
-      <c r="E51" s="44" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="206" t="s">
-        <v>201</v>
-      </c>
-      <c r="B52" s="207"/>
+      <c r="B52" s="203"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38">
-        <v>500000</v>
+        <v>225000</v>
       </c>
       <c r="E52" s="44" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="206" t="s">
-        <v>204</v>
-      </c>
-      <c r="B53" s="207"/>
+    <row r="53" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="202" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="203"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38">
-        <v>1520000</v>
-      </c>
-      <c r="E53" s="151" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="206" t="s">
-        <v>233</v>
-      </c>
-      <c r="B54" s="207"/>
+        <v>500000</v>
+      </c>
+      <c r="E53" s="44" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="202" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" s="203"/>
       <c r="C54" s="37"/>
       <c r="D54" s="38">
+        <v>1520000</v>
+      </c>
+      <c r="E54" s="151" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="202" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="203"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="38">
         <f>272252*2</f>
         <v>544504</v>
       </c>
-      <c r="E54" s="151" t="s">
+      <c r="E55" s="151" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="206" t="s">
+    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="202" t="s">
         <v>219</v>
       </c>
-      <c r="B55" s="207"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="38">
-        <v>85000</v>
-      </c>
-      <c r="E55" s="44" t="s">
-        <v>218</v>
-      </c>
-      <c r="F55" s="63"/>
-    </row>
-    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="206" t="s">
-        <v>238</v>
-      </c>
-      <c r="B56" s="207"/>
+      <c r="B56" s="203"/>
       <c r="C56" s="37"/>
       <c r="D56" s="38">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F56" s="63"/>
     </row>
     <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B57" s="21"/>
+      <c r="A57" s="202" t="s">
+        <v>238</v>
+      </c>
+      <c r="B57" s="203"/>
       <c r="C57" s="37"/>
       <c r="D57" s="38">
-        <v>35000</v>
+        <v>120000</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F57" s="63"/>
     </row>
-    <row r="58" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="206" t="s">
-        <v>220</v>
-      </c>
-      <c r="B58" s="207"/>
+    <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B58" s="21"/>
       <c r="C58" s="37"/>
       <c r="D58" s="38">
-        <v>6000</v>
+        <v>35000</v>
       </c>
       <c r="E58" s="44" t="s">
         <v>218</v>
       </c>
       <c r="F58" s="63"/>
     </row>
-    <row r="59" spans="1:6" ht="86" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="206" t="s">
-        <v>261</v>
-      </c>
-      <c r="B59" s="207"/>
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="202" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" s="203"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38">
-        <v>7000000</v>
-      </c>
-      <c r="E59" s="47" t="s">
-        <v>223</v>
+        <v>6000</v>
+      </c>
+      <c r="E59" s="44" t="s">
+        <v>218</v>
       </c>
       <c r="F59" s="63"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="B60" s="21"/>
+    <row r="60" spans="1:6" ht="86" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="202" t="s">
+        <v>261</v>
+      </c>
+      <c r="B60" s="203"/>
       <c r="C60" s="37"/>
       <c r="D60" s="38">
-        <v>28000</v>
-      </c>
-      <c r="E60" s="44" t="s">
-        <v>172</v>
+        <v>7000000</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>223</v>
       </c>
       <c r="F60" s="63"/>
     </row>
-    <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="123" t="s">
-        <v>179</v>
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="20" t="s">
+        <v>214</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="37"/>
       <c r="D61" s="38">
-        <v>150800</v>
+        <v>28000</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="F61" s="63"/>
     </row>
     <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="159" t="s">
-        <v>199</v>
-      </c>
-      <c r="B62" s="160"/>
+      <c r="A62" s="123" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" s="21"/>
       <c r="C62" s="37"/>
       <c r="D62" s="38">
-        <v>910000</v>
-      </c>
-      <c r="E62" s="47" t="s">
-        <v>215</v>
+        <v>150800</v>
+      </c>
+      <c r="E62" s="44" t="s">
+        <v>218</v>
       </c>
       <c r="F62" s="63"/>
     </row>
-    <row r="63" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="206" t="s">
-        <v>217</v>
-      </c>
-      <c r="B63" s="207"/>
+    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="159" t="s">
+        <v>199</v>
+      </c>
+      <c r="B63" s="160"/>
       <c r="C63" s="37"/>
       <c r="D63" s="38">
-        <v>250000</v>
+        <v>910000</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F63" s="63"/>
     </row>
-    <row r="64" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="123" t="s">
-        <v>197</v>
-      </c>
-      <c r="B64" s="21"/>
+    <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="202" t="s">
+        <v>217</v>
+      </c>
+      <c r="B64" s="203"/>
       <c r="C64" s="37"/>
       <c r="D64" s="38">
-        <v>133300</v>
+        <v>250000</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="F64" s="63"/>
     </row>
     <row r="65" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="206" t="s">
-        <v>210</v>
-      </c>
-      <c r="B65" s="207"/>
+      <c r="A65" s="123" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" s="21"/>
       <c r="C65" s="37"/>
       <c r="D65" s="38">
-        <v>105602.65</v>
+        <v>133300</v>
       </c>
       <c r="E65" s="47" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F65" s="63"/>
     </row>
-    <row r="66" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="206" t="s">
-        <v>195</v>
-      </c>
-      <c r="B66" s="207"/>
+    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="202" t="s">
+        <v>210</v>
+      </c>
+      <c r="B66" s="203"/>
       <c r="C66" s="37"/>
       <c r="D66" s="38">
+        <v>105602.65</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="F66" s="63"/>
+    </row>
+    <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="202" t="s">
+        <v>195</v>
+      </c>
+      <c r="B67" s="203"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="38">
         <v>2022800</v>
       </c>
-      <c r="E66" s="47" t="s">
+      <c r="E67" s="47" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="33">
-        <f>SUM(D51:D66)</f>
-        <v>13636006.65</v>
-      </c>
-    </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="17" t="s">
-        <v>117</v>
+      <c r="A68" s="25" t="s">
+        <v>0</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="19"/>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="206" t="s">
+      <c r="D68" s="46"/>
+      <c r="E68" s="33">
+        <f>SUM(D52:D67)</f>
+        <v>13636006.65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="B69" s="207"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="174">
+      <c r="B70" s="203"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="174">
         <v>650000</v>
       </c>
-      <c r="E69" s="47"/>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="20" t="s">
+      <c r="E70" s="47"/>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="21"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="175">
-        <v>125000</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="206" t="s">
-        <v>232</v>
-      </c>
-      <c r="B71" s="207"/>
+      <c r="B71" s="21"/>
       <c r="C71" s="22"/>
       <c r="D71" s="175">
-        <v>62500</v>
+        <v>125000</v>
       </c>
       <c r="E71" s="47" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="B72" s="21"/>
+      <c r="A72" s="202" t="s">
+        <v>232</v>
+      </c>
+      <c r="B72" s="203"/>
       <c r="C72" s="22"/>
       <c r="D72" s="175">
+        <v>62500</v>
+      </c>
+      <c r="E72" s="47" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="123" t="s">
+        <v>260</v>
+      </c>
+      <c r="B73" s="21"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="175">
         <v>45000</v>
       </c>
-      <c r="E72" s="47" t="s">
+      <c r="E73" s="47" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="25" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="27">
-        <f>SUM(D69:D72)</f>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="27">
+        <f>SUM(D70:D73)</f>
         <v>882500</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="17" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="B74" s="48"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="33"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="38">
-        <v>18681.400000000001</v>
-      </c>
-      <c r="E75" s="50"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="33"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="37" t="s">
-        <v>259</v>
+        <v>157</v>
       </c>
       <c r="B76" s="37"/>
       <c r="C76" s="37"/>
       <c r="D76" s="38">
+        <v>18681.400000000001</v>
+      </c>
+      <c r="E76" s="50"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="38">
         <f>29633.91-18681.4+50000</f>
         <v>60952.509999999995</v>
       </c>
-      <c r="E76" s="51"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="B77" s="112"/>
-      <c r="C77" s="112"/>
-      <c r="D77" s="176">
-        <v>45000</v>
-      </c>
       <c r="E77" s="51"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B78" s="112"/>
       <c r="C78" s="112"/>
       <c r="D78" s="176">
+        <v>45000</v>
+      </c>
+      <c r="E78" s="51"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79" s="112"/>
+      <c r="C79" s="112"/>
+      <c r="D79" s="176">
         <f>9386+1200+193960.95+3629+1284.98</f>
         <v>209460.93000000002</v>
       </c>
-      <c r="E78" s="51"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="52" t="s">
+      <c r="E79" s="51"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="54">
-        <f>SUM(D75:D78)</f>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="54">
+        <f>SUM(D76:D79)</f>
         <v>334094.84000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="37"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="55"/>
-      <c r="E80" s="56"/>
-    </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" s="57" t="s">
+      <c r="A81" s="37"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="56"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="B81" s="57"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="58"/>
-      <c r="E81" s="59"/>
-    </row>
-    <row r="82" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="60"/>
-      <c r="D82" s="61"/>
-      <c r="E82" s="62"/>
-      <c r="F82" s="63"/>
+      <c r="B82" s="57"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="58"/>
+      <c r="E82" s="59"/>
     </row>
     <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="64" t="s">
+      <c r="A83" s="60"/>
+      <c r="D83" s="61"/>
+      <c r="E83" s="62"/>
+      <c r="F83" s="63"/>
+    </row>
+    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="B83" s="65"/>
-      <c r="C83" s="66"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="68">
-        <f>(SUM(E21:E81))</f>
-        <v>23996011.260000002</v>
-      </c>
-      <c r="F83" s="69"/>
-      <c r="G83" s="63"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-    </row>
-    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B84" s="65"/>
+      <c r="C84" s="66"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="68">
+        <f>(SUM(E21:E82))</f>
+        <v>24001853.77</v>
+      </c>
+      <c r="F84" s="69"/>
+      <c r="G84" s="63"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D85" s="61"/>
       <c r="E85" s="61"/>
-      <c r="H85" s="70"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" s="12" t="s">
+    </row>
+    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="H86" s="70"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="71"/>
-      <c r="E86" s="72"/>
-    </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="30"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="45"/>
-      <c r="E87" s="73"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="71"/>
+      <c r="E87" s="72"/>
     </row>
     <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="206"/>
-      <c r="B88" s="207"/>
+      <c r="A88" s="30"/>
+      <c r="B88" s="31"/>
       <c r="C88" s="37"/>
       <c r="D88" s="45"/>
       <c r="E88" s="73"/>
     </row>
-    <row r="89" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D89" s="55"/>
-      <c r="E89" s="37"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="30"/>
-      <c r="B90" s="74"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="73"/>
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="202"/>
+      <c r="B89" s="203"/>
+      <c r="C89" s="37"/>
+      <c r="D89" s="45"/>
+      <c r="E89" s="73"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D90" s="55"/>
+      <c r="E90" s="37"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="75" t="s">
+      <c r="A91" s="30"/>
+      <c r="B91" s="74"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="73"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="B91" s="76"/>
-      <c r="C91" s="76"/>
-      <c r="D91" s="156"/>
-      <c r="E91" s="111">
-        <f>SUM(D87:D90)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D92" s="61"/>
-    </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="76"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="156"/>
+      <c r="E92" s="111">
+        <f>SUM(D88:D91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D93" s="61"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A94" s="57" t="s">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="D94" s="61"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="B94" s="57"/>
-      <c r="C94" s="57"/>
-      <c r="D94" s="58"/>
-      <c r="E94" s="119"/>
-    </row>
-    <row r="95" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D95" s="61"/>
+      <c r="B95" s="57"/>
+      <c r="C95" s="57"/>
+      <c r="D95" s="58"/>
+      <c r="E95" s="119"/>
     </row>
     <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="64" t="s">
+      <c r="D96" s="61"/>
+    </row>
+    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="B96" s="65"/>
-      <c r="C96" s="66"/>
-      <c r="D96" s="66"/>
-      <c r="E96" s="77">
-        <f>E91+E94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="98" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="78" t="s">
+      <c r="B97" s="65"/>
+      <c r="C97" s="66"/>
+      <c r="D97" s="66"/>
+      <c r="E97" s="77">
+        <f>E92+E95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="B98" s="79">
-        <f>E83</f>
-        <v>23996011.260000002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="78" t="s">
+      <c r="B99" s="79">
+        <f>E84</f>
+        <v>24001853.77</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="B99" s="79">
-        <f>E83-E81</f>
-        <v>23996011.260000002</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="78" t="s">
+      <c r="B100" s="79">
+        <f>E84-E82</f>
+        <v>24001853.77</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="B100" s="79">
-        <f>E96-E94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="78" t="s">
+      <c r="B101" s="79">
+        <f>E97-E95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="B101" s="79">
-        <f>E96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="214" t="s">
+      <c r="B102" s="79">
+        <f>E97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="208" t="s">
         <v>247</v>
       </c>
-      <c r="B104" s="214"/>
-    </row>
-    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="214"/>
-      <c r="B105" s="214"/>
-    </row>
-    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="214"/>
-      <c r="B106" s="214"/>
-    </row>
-    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="214" t="s">
+      <c r="B105" s="208"/>
+    </row>
+    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="208"/>
+      <c r="B106" s="208"/>
+    </row>
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="208"/>
+      <c r="B107" s="208"/>
+    </row>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="208" t="s">
         <v>250</v>
       </c>
-      <c r="B108" s="214"/>
-    </row>
-    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="214"/>
-      <c r="B109" s="214"/>
-    </row>
-    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="214"/>
-      <c r="B110" s="214"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="213" t="s">
+      <c r="B109" s="208"/>
+    </row>
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="208"/>
+      <c r="B110" s="208"/>
+    </row>
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="208"/>
+      <c r="B111" s="208"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="207" t="s">
         <v>265</v>
       </c>
-      <c r="B113" s="213"/>
-    </row>
-    <row r="114" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="213"/>
-      <c r="B114" s="213"/>
-    </row>
-    <row r="115" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A115"/>
-      <c r="B115" s="80"/>
-      <c r="C115" s="81"/>
-    </row>
-    <row r="116" spans="1:6" s="82" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="122" t="s">
+      <c r="B114" s="207"/>
+    </row>
+    <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="207"/>
+      <c r="B115" s="207"/>
+    </row>
+    <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A116"/>
+      <c r="B116" s="80"/>
+      <c r="C116" s="81"/>
+    </row>
+    <row r="117" spans="1:6" s="82" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="122" t="s">
         <v>173</v>
       </c>
-      <c r="B116" s="83">
+      <c r="B117" s="83">
         <v>10597369.743745035</v>
       </c>
-      <c r="C116" s="81"/>
-      <c r="D116" s="84"/>
-      <c r="E116" s="84"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="B117" s="85">
-        <f>-B99-B100</f>
-        <v>-23996011.260000002</v>
-      </c>
+      <c r="C117" s="81"/>
+      <c r="D117" s="84"/>
+      <c r="E117" s="84"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="B118" s="85">
+        <f>-B100-B101</f>
+        <v>-24001853.77</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="B118" s="85">
-        <f>B141</f>
+      <c r="B119" s="85">
+        <f>B142</f>
         <v>195940.3</v>
       </c>
-      <c r="F118" s="80"/>
-    </row>
-    <row r="119" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="32" t="s">
+      <c r="F119" s="80"/>
+    </row>
+    <row r="120" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="B119" s="140">
+      <c r="B120" s="140">
         <v>-239116.53</v>
       </c>
-      <c r="F119" s="80"/>
-    </row>
-    <row r="120" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="32" t="s">
+      <c r="F120" s="80"/>
+    </row>
+    <row r="121" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="B120" s="141">
+      <c r="B121" s="141">
         <f>-119452</f>
         <v>-119452</v>
       </c>
-      <c r="F120" s="80"/>
-    </row>
-    <row r="121" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A121" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="B121" s="141">
-        <v>-123612</v>
-      </c>
       <c r="F121" s="80"/>
     </row>
     <row r="122" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B122" s="141">
+        <v>-123612</v>
+      </c>
+      <c r="F122" s="80"/>
+    </row>
+    <row r="123" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A123" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="B122" s="141">
+      <c r="B123" s="141">
         <v>-168836.39</v>
-      </c>
-      <c r="F122" s="80"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="B123" s="141">
-        <v>-20871</v>
       </c>
       <c r="F123" s="80"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="B124" s="141">
+        <v>-20871</v>
+      </c>
+      <c r="F124" s="80"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="B124" s="141">
+      <c r="B125" s="141">
         <v>-3820</v>
-      </c>
-      <c r="F124" s="80"/>
-    </row>
-    <row r="125" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="B125" s="141">
-        <v>-7274</v>
       </c>
       <c r="F125" s="80"/>
     </row>
     <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="B126" s="139">
-        <v>-7528</v>
+        <v>236</v>
+      </c>
+      <c r="B126" s="141">
+        <v>-7274</v>
       </c>
       <c r="F126" s="80"/>
     </row>
     <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="B127" s="139">
+        <v>-7528</v>
+      </c>
+      <c r="F127" s="80"/>
+    </row>
+    <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="B127" s="139">
+      <c r="B128" s="139">
         <v>-50000</v>
       </c>
-      <c r="F127" s="80"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="32" t="s">
+      <c r="F128" s="80"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A129" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B128" s="86">
+      <c r="B129" s="86">
         <f>PRORRATEO!F118</f>
         <v>14531886.810000001</v>
       </c>
-      <c r="F128" s="80"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A129" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="B129" s="86">
-        <v>300000</v>
-      </c>
       <c r="F129" s="80"/>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B130" s="86">
-        <v>250000</v>
+        <v>300000</v>
       </c>
       <c r="F130" s="80"/>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="B131" s="86">
+        <v>250000</v>
+      </c>
+      <c r="F131" s="80"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A132" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="B131" s="86">
+      <c r="B132" s="86">
         <v>200000.42</v>
-      </c>
-      <c r="F131" s="80"/>
-    </row>
-    <row r="132" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A132" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="B132" s="168">
-        <v>-130000</v>
       </c>
       <c r="F132" s="80"/>
     </row>
     <row r="133" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="32" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B133" s="168">
         <v>-130000</v>
       </c>
       <c r="F133" s="80"/>
     </row>
-    <row r="134" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="32" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B134" s="168">
         <v>-130000</v>
       </c>
       <c r="F134" s="80"/>
     </row>
-    <row r="135" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A135" s="87" t="s">
+    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="B135" s="168">
+        <v>-130000</v>
+      </c>
+      <c r="F135" s="80"/>
+    </row>
+    <row r="136" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A136" s="87" t="s">
         <v>255</v>
       </c>
-      <c r="B135" s="152">
+      <c r="B136" s="152">
         <v>123300</v>
       </c>
-      <c r="F135" s="80"/>
-    </row>
-    <row r="136" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="88" t="s">
+      <c r="F136" s="80"/>
+    </row>
+    <row r="137" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="B136" s="89">
-        <f>SUM(B116:C135)</f>
-        <v>1071976.0937450342</v>
-      </c>
-      <c r="D136" s="80"/>
-      <c r="E136" s="63"/>
-      <c r="F136" s="63"/>
-    </row>
-    <row r="137" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A138" s="212" t="s">
+      <c r="B137" s="89">
+        <f>SUM(B117:C136)</f>
+        <v>1066133.5837450363</v>
+      </c>
+      <c r="D137" s="80"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="63"/>
+    </row>
+    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A139" s="204" t="s">
         <v>129</v>
       </c>
-      <c r="B138" s="212"/>
-      <c r="C138" s="212"/>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A139" s="212"/>
-      <c r="B139" s="212"/>
-      <c r="C139" s="212"/>
-    </row>
-    <row r="140" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="90" t="s">
+      <c r="B139" s="204"/>
+      <c r="C139" s="204"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A140" s="204"/>
+      <c r="B140" s="204"/>
+      <c r="C140" s="204"/>
+    </row>
+    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="90" t="s">
         <v>240</v>
       </c>
-      <c r="B140" s="150">
+      <c r="B141" s="150">
         <v>195940.3</v>
       </c>
-      <c r="C140" s="91"/>
-      <c r="D140" s="69"/>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A141" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="B141" s="93">
-        <f>SUM(B140:B140)</f>
+      <c r="C141" s="91"/>
+      <c r="D141" s="69"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A142" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" s="93">
+        <f>SUM(B141:B141)</f>
         <v>195940.3</v>
       </c>
-      <c r="C141" s="94"/>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="M142" s="95"/>
+      <c r="C142" s="94"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M143" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A138:C139"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A113:B114"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A104:B106"/>
-    <mergeCell ref="A108:B110"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A139:C140"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A114:B115"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A89:B89"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A105:B107"/>
+    <mergeCell ref="A109:B111"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3807,15 +3823,15 @@
       <c r="A1" s="124"/>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="215"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
       <c r="M1" s="126"/>
     </row>
     <row r="2" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
@@ -3825,10 +3841,10 @@
       <c r="D2" s="129" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="239">
+      <c r="E2" s="245">
         <v>3000000</v>
       </c>
-      <c r="F2" s="239"/>
+      <c r="F2" s="245"/>
       <c r="G2" s="129"/>
       <c r="H2" s="129"/>
       <c r="I2" s="129" t="s">
@@ -3859,195 +3875,195 @@
       <c r="N3" s="96"/>
     </row>
     <row r="4" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="216" t="s">
+      <c r="A4" s="222" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="217"/>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="217"/>
-      <c r="M4" s="218"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="M4" s="224"/>
       <c r="N4" s="96"/>
     </row>
     <row r="5" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="219"/>
-      <c r="B5" s="220"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="220"/>
-      <c r="E5" s="220"/>
-      <c r="F5" s="220"/>
-      <c r="G5" s="220"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="220"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="220"/>
-      <c r="M5" s="221"/>
+      <c r="A5" s="225"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="227"/>
       <c r="N5" s="96"/>
     </row>
     <row r="6" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="219"/>
-      <c r="B6" s="220"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
-      <c r="F6" s="220"/>
-      <c r="G6" s="220"/>
-      <c r="H6" s="220"/>
-      <c r="I6" s="220"/>
-      <c r="J6" s="220"/>
-      <c r="K6" s="220"/>
-      <c r="L6" s="220"/>
-      <c r="M6" s="221"/>
+      <c r="A6" s="225"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="227"/>
       <c r="N6" s="96"/>
     </row>
     <row r="7" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="219"/>
-      <c r="B7" s="220"/>
-      <c r="C7" s="220"/>
-      <c r="D7" s="220"/>
-      <c r="E7" s="220"/>
-      <c r="F7" s="220"/>
-      <c r="G7" s="220"/>
-      <c r="H7" s="220"/>
-      <c r="I7" s="220"/>
-      <c r="J7" s="220"/>
-      <c r="K7" s="220"/>
-      <c r="L7" s="220"/>
-      <c r="M7" s="221"/>
+      <c r="A7" s="225"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="227"/>
       <c r="N7" s="96"/>
     </row>
     <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="222"/>
-      <c r="B8" s="223"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="223"/>
-      <c r="H8" s="223"/>
-      <c r="I8" s="223"/>
-      <c r="J8" s="223"/>
-      <c r="K8" s="223"/>
-      <c r="L8" s="223"/>
-      <c r="M8" s="224"/>
+      <c r="A8" s="228"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="230"/>
     </row>
     <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="247" t="s">
+      <c r="A9" s="218" t="s">
         <v>266</v>
       </c>
-      <c r="B9" s="248"/>
-      <c r="C9" s="248"/>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
-      <c r="M9" s="249"/>
+      <c r="B9" s="219"/>
+      <c r="C9" s="219"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="219"/>
+      <c r="H9" s="219"/>
+      <c r="I9" s="219"/>
+      <c r="J9" s="219"/>
+      <c r="K9" s="219"/>
+      <c r="L9" s="219"/>
+      <c r="M9" s="220"/>
     </row>
     <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="233" t="s">
+      <c r="A10" s="239" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="234"/>
-      <c r="C10" s="234"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="234"/>
-      <c r="F10" s="234"/>
-      <c r="G10" s="234"/>
-      <c r="H10" s="234"/>
-      <c r="I10" s="234"/>
-      <c r="J10" s="234"/>
-      <c r="K10" s="234"/>
-      <c r="L10" s="234"/>
-      <c r="M10" s="235"/>
+      <c r="B10" s="240"/>
+      <c r="C10" s="240"/>
+      <c r="D10" s="240"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="240"/>
+      <c r="G10" s="240"/>
+      <c r="H10" s="240"/>
+      <c r="I10" s="240"/>
+      <c r="J10" s="240"/>
+      <c r="K10" s="240"/>
+      <c r="L10" s="240"/>
+      <c r="M10" s="241"/>
     </row>
     <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="236" t="s">
+      <c r="A11" s="242" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="237"/>
-      <c r="C11" s="237"/>
-      <c r="D11" s="237"/>
-      <c r="E11" s="237"/>
-      <c r="F11" s="237"/>
-      <c r="G11" s="237"/>
-      <c r="H11" s="237"/>
-      <c r="I11" s="237"/>
-      <c r="J11" s="237"/>
-      <c r="K11" s="237"/>
-      <c r="L11" s="237"/>
-      <c r="M11" s="238"/>
+      <c r="B11" s="243"/>
+      <c r="C11" s="243"/>
+      <c r="D11" s="243"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="243"/>
+      <c r="I11" s="243"/>
+      <c r="J11" s="243"/>
+      <c r="K11" s="243"/>
+      <c r="L11" s="243"/>
+      <c r="M11" s="244"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="225" t="s">
+      <c r="A12" s="231" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="227" t="s">
+      <c r="B12" s="233" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="227" t="s">
+      <c r="C12" s="233" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="227" t="s">
+      <c r="D12" s="233" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="229" t="s">
+      <c r="E12" s="235" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="227" t="s">
+      <c r="F12" s="233" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="231" t="s">
+      <c r="G12" s="237" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="229" t="s">
+      <c r="H12" s="235" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="229" t="s">
+      <c r="I12" s="235" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="229" t="s">
+      <c r="J12" s="235" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="240" t="s">
+      <c r="K12" s="246" t="s">
         <v>258</v>
       </c>
       <c r="L12" s="198" t="s">
         <v>140</v>
       </c>
-      <c r="M12" s="242" t="s">
+      <c r="M12" s="215" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="226"/>
-      <c r="B13" s="228"/>
-      <c r="C13" s="228"/>
-      <c r="D13" s="228"/>
-      <c r="E13" s="230"/>
-      <c r="F13" s="228"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="230"/>
-      <c r="I13" s="230"/>
-      <c r="J13" s="230"/>
-      <c r="K13" s="241"/>
+      <c r="A13" s="232"/>
+      <c r="B13" s="234"/>
+      <c r="C13" s="234"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="234"/>
+      <c r="G13" s="238"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="247"/>
       <c r="L13" s="199" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M13" s="243"/>
+      <c r="M13" s="216"/>
     </row>
     <row r="14" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="182">
@@ -8028,7 +8044,7 @@
         <v>191113.83</v>
       </c>
       <c r="F96" s="100">
-        <f>RESUMEN!D54/2+196846.93</f>
+        <f>RESUMEN!D55/2+196846.93</f>
         <v>469098.93</v>
       </c>
       <c r="G96" s="101">
@@ -8077,7 +8093,7 @@
         <v>449255.84</v>
       </c>
       <c r="F97" s="100">
-        <f>RESUMEN!D54/2+168836.84</f>
+        <f>RESUMEN!D55/2+168836.84</f>
         <v>441088.83999999997</v>
       </c>
       <c r="G97" s="101">
@@ -9103,87 +9119,90 @@
     </row>
     <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.35"/>
     <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="244" t="s">
+      <c r="B121" s="217" t="s">
         <v>106</v>
       </c>
-      <c r="C121" s="244"/>
-      <c r="D121" s="244"/>
-      <c r="E121" s="244"/>
-      <c r="F121" s="244"/>
-      <c r="G121" s="244"/>
-      <c r="H121" s="244"/>
-      <c r="I121" s="244"/>
-      <c r="J121" s="244"/>
-      <c r="K121" s="244"/>
-      <c r="L121" s="244"/>
+      <c r="C121" s="217"/>
+      <c r="D121" s="217"/>
+      <c r="E121" s="217"/>
+      <c r="F121" s="217"/>
+      <c r="G121" s="217"/>
+      <c r="H121" s="217"/>
+      <c r="I121" s="217"/>
+      <c r="J121" s="217"/>
+      <c r="K121" s="217"/>
+      <c r="L121" s="217"/>
     </row>
     <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B122" s="244"/>
-      <c r="C122" s="244"/>
-      <c r="D122" s="244"/>
-      <c r="E122" s="244"/>
-      <c r="F122" s="244"/>
-      <c r="G122" s="244"/>
-      <c r="H122" s="244"/>
-      <c r="I122" s="244"/>
-      <c r="J122" s="244"/>
-      <c r="K122" s="244"/>
-      <c r="L122" s="244"/>
+      <c r="B122" s="217"/>
+      <c r="C122" s="217"/>
+      <c r="D122" s="217"/>
+      <c r="E122" s="217"/>
+      <c r="F122" s="217"/>
+      <c r="G122" s="217"/>
+      <c r="H122" s="217"/>
+      <c r="I122" s="217"/>
+      <c r="J122" s="217"/>
+      <c r="K122" s="217"/>
+      <c r="L122" s="217"/>
     </row>
     <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B123" s="244"/>
-      <c r="C123" s="244"/>
-      <c r="D123" s="244"/>
-      <c r="E123" s="244"/>
-      <c r="F123" s="244"/>
-      <c r="G123" s="244"/>
-      <c r="H123" s="244"/>
-      <c r="I123" s="244"/>
-      <c r="J123" s="244"/>
-      <c r="K123" s="244"/>
-      <c r="L123" s="244"/>
+      <c r="B123" s="217"/>
+      <c r="C123" s="217"/>
+      <c r="D123" s="217"/>
+      <c r="E123" s="217"/>
+      <c r="F123" s="217"/>
+      <c r="G123" s="217"/>
+      <c r="H123" s="217"/>
+      <c r="I123" s="217"/>
+      <c r="J123" s="217"/>
+      <c r="K123" s="217"/>
+      <c r="L123" s="217"/>
     </row>
     <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="244"/>
-      <c r="C124" s="244"/>
-      <c r="D124" s="244"/>
-      <c r="E124" s="244"/>
-      <c r="F124" s="244"/>
-      <c r="G124" s="244"/>
-      <c r="H124" s="244"/>
-      <c r="I124" s="244"/>
-      <c r="J124" s="244"/>
-      <c r="K124" s="244"/>
-      <c r="L124" s="244"/>
+      <c r="B124" s="217"/>
+      <c r="C124" s="217"/>
+      <c r="D124" s="217"/>
+      <c r="E124" s="217"/>
+      <c r="F124" s="217"/>
+      <c r="G124" s="217"/>
+      <c r="H124" s="217"/>
+      <c r="I124" s="217"/>
+      <c r="J124" s="217"/>
+      <c r="K124" s="217"/>
+      <c r="L124" s="217"/>
     </row>
     <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="244"/>
-      <c r="C125" s="244"/>
-      <c r="D125" s="244"/>
-      <c r="E125" s="244"/>
-      <c r="F125" s="244"/>
-      <c r="G125" s="244"/>
-      <c r="H125" s="244"/>
-      <c r="I125" s="244"/>
-      <c r="J125" s="244"/>
-      <c r="K125" s="244"/>
-      <c r="L125" s="244"/>
+      <c r="B125" s="217"/>
+      <c r="C125" s="217"/>
+      <c r="D125" s="217"/>
+      <c r="E125" s="217"/>
+      <c r="F125" s="217"/>
+      <c r="G125" s="217"/>
+      <c r="H125" s="217"/>
+      <c r="I125" s="217"/>
+      <c r="J125" s="217"/>
+      <c r="K125" s="217"/>
+      <c r="L125" s="217"/>
     </row>
     <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="244"/>
-      <c r="C126" s="244"/>
-      <c r="D126" s="244"/>
-      <c r="E126" s="244"/>
-      <c r="F126" s="244"/>
-      <c r="G126" s="244"/>
-      <c r="H126" s="244"/>
-      <c r="I126" s="244"/>
-      <c r="J126" s="244"/>
-      <c r="K126" s="244"/>
-      <c r="L126" s="244"/>
+      <c r="B126" s="217"/>
+      <c r="C126" s="217"/>
+      <c r="D126" s="217"/>
+      <c r="E126" s="217"/>
+      <c r="F126" s="217"/>
+      <c r="G126" s="217"/>
+      <c r="H126" s="217"/>
+      <c r="I126" s="217"/>
+      <c r="J126" s="217"/>
+      <c r="K126" s="217"/>
+      <c r="L126" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="J12:J13"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="B121:L126"/>
     <mergeCell ref="A9:M9"/>
@@ -9200,9 +9219,6 @@
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="J12:J13"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9218,17 +9234,17 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="245" t="s">
+      <c r="B5" s="248" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="245"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
+      <c r="C5" s="248"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
       <c r="L5" s="82" t="s">
         <v>185</v>
       </c>
@@ -9394,24 +9410,24 @@
       <c r="C22" s="155"/>
     </row>
     <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="246" t="s">
+      <c r="B25" s="249" t="s">
         <v>193</v>
       </c>
-      <c r="C25" s="246"/>
-      <c r="D25" s="246"/>
-      <c r="E25" s="246"/>
-      <c r="F25" s="246"/>
-      <c r="G25" s="246"/>
-      <c r="H25" s="246"/>
-      <c r="I25" s="246"/>
-      <c r="J25" s="246"/>
-      <c r="K25" s="246"/>
-      <c r="L25" s="246"/>
-      <c r="M25" s="246"/>
-      <c r="N25" s="246"/>
-      <c r="O25" s="246"/>
-      <c r="P25" s="246"/>
-      <c r="Q25" s="246"/>
+      <c r="C25" s="249"/>
+      <c r="D25" s="249"/>
+      <c r="E25" s="249"/>
+      <c r="F25" s="249"/>
+      <c r="G25" s="249"/>
+      <c r="H25" s="249"/>
+      <c r="I25" s="249"/>
+      <c r="J25" s="249"/>
+      <c r="K25" s="249"/>
+      <c r="L25" s="249"/>
+      <c r="M25" s="249"/>
+      <c r="N25" s="249"/>
+      <c r="O25" s="249"/>
+      <c r="P25" s="249"/>
+      <c r="Q25" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -1,45 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\ITALIA\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B937B3D-42EE-4879-AD68-BBFFFDAB0796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3B1638-4DD7-49F1-A063-A82609A8678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="5" r:id="rId2"/>
     <sheet name="ANOTACIONES" sheetId="6" r:id="rId3"/>
+    <sheet name="7F SITUACION" sheetId="7" r:id="rId4"/>
+    <sheet name="SITUACION 6B" sheetId="8" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'7F SITUACION'!$C$4:$O$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$126</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$142</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'SITUACION 6B'!$C$2:$I$18</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="281">
   <si>
     <t>TOTAL</t>
   </si>
@@ -594,54 +585,10 @@
     <t>4 E COCHERA XHARDEZ MARIA EUGENIA</t>
   </si>
   <si>
-    <t>● alejandraaalejo@yahoo.com.ar para agregar a la cadena de italia
-● karinalanni16@gmail.com  para incorporar en la cadena de mails de italia del mes proximos
-● Agregar cadena de mails: marcela65bossetti@gmail.com - 
-             lucas_lc1@icloud.com
-borromeo22@hotmail.com
-altgenug@gmail.com</t>
-  </si>
-  <si>
     <t>AYALA GASTON</t>
   </si>
   <si>
     <t>Silvana Valeria Arredondo - Braian Brito</t>
-  </si>
-  <si>
-    <t>EL 12A Y 12 B TIENE GASTOS (QUE PAGARON ELLOS ) PENDIENTES QUE LES PONGAMOS COMO INGRESO DEL ASCENSOR. DEBEMOS AGREGARLE $272.252 A CADA UNO</t>
-  </si>
-  <si>
-    <t>marcela65bossetti@gmail.com
-             lucas_lc1@icloud.com
-borromeo22@hotmail.com
-altgenug@gmail.com karinalanni16@gmail.com alejandraaalejo@yahoo.com.ar</t>
-  </si>
-  <si>
-    <t>El 8vo e junto con las cocheras G y J habia abonado el  mes anterior 239.116,53 como un boludo. Nosotros le pusimos ese pago a la UF 53. Hay que quitarselo. El VO e y sus socheras debe abonar:</t>
-  </si>
-  <si>
-    <t>8vo E</t>
-  </si>
-  <si>
-    <t>Cochcera G</t>
-  </si>
-  <si>
-    <t>Cochera J</t>
-  </si>
-  <si>
-    <t>El 2C habia abonado el mes anterior $250.932,15 - Lo pusimos impago - Debe abonar $123.612,15 y los abono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El 8C deposito el 10/02 $120.000 </t>
-  </si>
-  <si>
-    <t>4D Transfirio $125.000 el 16/02</t>
-  </si>
-  <si>
-    <t>Buenos días, si, el pago no registrado corresponde a las expensas del mes de octubre 2025 cuya liquidación se recibió por mail el 2/11/2025 y fue enviado por la administración anterior. El 4-11-2025 se realizó el pago por $119452.71 que es el comprobante que les envié. Como el pago no se imputó, desde diciembre estoy recibiendo las expensas con esa deuda que no existe. Por favor le pido realizar la corrección correspondiente. En otro mail les voy a reenviar el mail de la liquidación en cuestión que me envió la administración anterior para que puedan corroborar el monto y la fecha que menciono. 
-Aguardo sus comentarios, 
-Saludos, 
-Julieta Nani</t>
   </si>
   <si>
     <t>VTO 13/03</t>
@@ -867,6 +814,78 @@
   </si>
   <si>
     <t>Seguro Sra. Gisela</t>
+  </si>
+  <si>
+    <t>En diciembre debia abonar</t>
+  </si>
+  <si>
+    <t>Abono</t>
+  </si>
+  <si>
+    <t>Deuda:</t>
+  </si>
+  <si>
+    <t>En enero debia abonar:</t>
+  </si>
+  <si>
+    <t>Expensas para abonar en enero</t>
+  </si>
+  <si>
+    <t>Expensas para abonar en Febrero</t>
+  </si>
+  <si>
+    <t>Total a abonar en febrero (expensas + deuda) - Descontamos punitorios</t>
+  </si>
+  <si>
+    <t>En febrero debia abonar:</t>
+  </si>
+  <si>
+    <t>Expensas para abonar en Marzo</t>
+  </si>
+  <si>
+    <t>Al 7F le hicimos su situacion detallada al pie de la letra debe abonar $371.016,53</t>
+  </si>
+  <si>
+    <t>Todo este problema con los números se origina en el mes de enero, cuando la unidad funcional 7°F no realizó ningún pago. En ese mismo período, otro propietario efectuó un pago con una terminacion de 53 centavos, lo que generó que el sistema de la administración imputara ese pago a la unidad funcional 7°F, cuando en realidad dicha unidad nunca abonó. Debido a que el inconveniente y la confusión se originan a partir de una situación ajena a la unidad funcional 7°F, la administración decidió no aplicar los punitorios correspondientes al momento de rehacer y corregir los cálculos.</t>
+  </si>
+  <si>
+    <t>Saldo inicio Diciembre</t>
+  </si>
+  <si>
+    <t>Deuda</t>
+  </si>
+  <si>
+    <t>Diciembre del año 2025</t>
+  </si>
+  <si>
+    <t>Punitorios</t>
+  </si>
+  <si>
+    <t>Expensas ordinarias (Gastos A)</t>
+  </si>
+  <si>
+    <t>Expensas extraordinarias (gastos B)</t>
+  </si>
+  <si>
+    <t>Total a abonar en Enero:</t>
+  </si>
+  <si>
+    <t>Enero del año 2026</t>
+  </si>
+  <si>
+    <t>Febrero del año 2026</t>
+  </si>
+  <si>
+    <t>SITUACION 6B</t>
+  </si>
+  <si>
+    <t>Total a abonar en Febrero:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total a abonar en Marzo: </t>
+  </si>
+  <si>
+    <t>*Aclaracion importante: la administracion nueva toma posesion de la liquidacion de expensas a partir de Diciembre del 2025. El monto pasado en dicho mes como Saldo de inicio ($598.682,42) parte de la informacion (de la ultima liquidacion) de la administracion antigua. Los intereses mensuales son del 3%.</t>
   </si>
 </sst>
 </file>
@@ -874,14 +893,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1140,19 +1159,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1620,9 +1639,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1643,8 +1662,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1655,10 +1674,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1668,52 +1687,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="15" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="15" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="15" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1724,24 +1743,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1750,27 +1769,27 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1781,20 +1800,20 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="2" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="11" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="11" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="3" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1821,60 +1840,57 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="13" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="13" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="19" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="13" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="23" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1882,70 +1898,112 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="15" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="15" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="13" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="13" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="14" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="14" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="13" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="13" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="15" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="13" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="19" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="11" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="15" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="19" fillId="7" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="13" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="19" fillId="7" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="11" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="19" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1953,37 +2011,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2046,12 +2098,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2076,7 +2122,7 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2085,15 +2131,89 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2455,31 +2575,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M143"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.54296875" customWidth="1"/>
-    <col min="2" max="2" width="24.6328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" customWidth="1"/>
-    <col min="5" max="5" width="16.6328125" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6328125" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="215" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="210"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="216"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>156</v>
@@ -2488,16 +2608,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="51.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="211" t="s">
+      <c r="B3" s="219" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
-      <c r="E3" s="212"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="219"/>
+      <c r="D3" s="219"/>
+      <c r="E3" s="220"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>103</v>
       </c>
@@ -2508,12 +2628,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2521,68 +2641,68 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="107" t="s">
         <v>142</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="213" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" s="213"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="213"/>
-      <c r="C9" s="213"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="213"/>
-      <c r="C10" s="213"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="214" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="221" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="221"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="221"/>
+      <c r="C9" s="221"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="221"/>
+      <c r="C10" s="221"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="222" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="214"/>
-      <c r="C13" s="214"/>
-      <c r="D13" s="214"/>
-      <c r="E13" s="214"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="214"/>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="214"/>
-      <c r="B15" s="214"/>
-      <c r="C15" s="214"/>
-      <c r="D15" s="214"/>
-      <c r="E15" s="214"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="214"/>
-      <c r="B16" s="214"/>
-      <c r="C16" s="214"/>
-      <c r="D16" s="214"/>
-      <c r="E16" s="214"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="222"/>
+      <c r="C13" s="222"/>
+      <c r="D13" s="222"/>
+      <c r="E13" s="222"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="222"/>
+      <c r="B14" s="222"/>
+      <c r="C14" s="222"/>
+      <c r="D14" s="222"/>
+      <c r="E14" s="222"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="222"/>
+      <c r="B15" s="222"/>
+      <c r="C15" s="222"/>
+      <c r="D15" s="222"/>
+      <c r="E15" s="222"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="222"/>
+      <c r="B16" s="222"/>
+      <c r="C16" s="222"/>
+      <c r="D16" s="222"/>
+      <c r="E16" s="222"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>107</v>
       </c>
@@ -2591,52 +2711,52 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>143</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
-      <c r="D21" s="157"/>
+      <c r="D21" s="154"/>
       <c r="E21" s="19"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="202" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="217" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="203"/>
+      <c r="B22" s="218"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="170">
+      <c r="D22" s="167">
         <v>1931623</v>
       </c>
       <c r="E22" s="47"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="202" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="217" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="203"/>
+      <c r="B23" s="218"/>
       <c r="C23" s="22"/>
-      <c r="D23" s="170">
+      <c r="D23" s="167">
         <v>-420128</v>
       </c>
       <c r="E23" s="24"/>
       <c r="H23" s="23"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="202" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="217" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="203"/>
+      <c r="B24" s="218"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="171">
+      <c r="D24" s="168">
         <v>0</v>
       </c>
       <c r="E24" s="24"/>
       <c r="H24" s="23"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
         <v>108</v>
       </c>
@@ -2648,18 +2768,18 @@
         <v>1511495</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="26"/>
       <c r="E26" s="108"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -2668,9 +2788,9 @@
       </c>
       <c r="E27" s="110"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -2681,7 +2801,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
         <v>108</v>
       </c>
@@ -2693,7 +2813,7 @@
         <v>153842.51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>144</v>
       </c>
@@ -2702,9 +2822,9 @@
       <c r="D30" s="26"/>
       <c r="E30" s="108"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B31" s="109"/>
       <c r="C31" s="109"/>
@@ -2712,10 +2832,10 @@
         <v>13757.84</v>
       </c>
       <c r="E31" s="118" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>160</v>
       </c>
@@ -2725,10 +2845,10 @@
         <v>1235711.01</v>
       </c>
       <c r="E32" s="118" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>146</v>
       </c>
@@ -2738,10 +2858,10 @@
         <v>225490.24</v>
       </c>
       <c r="E33" s="118" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>148</v>
       </c>
@@ -2755,7 +2875,7 @@
         <v>Debito 16/02</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>147</v>
       </c>
@@ -2769,7 +2889,7 @@
         <v>Debito 16/02</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>161</v>
       </c>
@@ -2778,7 +2898,7 @@
       <c r="D36" s="45"/>
       <c r="E36" s="118"/>
     </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
         <v>145</v>
       </c>
@@ -2790,7 +2910,7 @@
         <v>1584070.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>109</v>
       </c>
@@ -2799,46 +2919,46 @@
       <c r="D38" s="28"/>
       <c r="E38" s="29"/>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="205" t="s">
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="213" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="206"/>
+      <c r="B39" s="214"/>
       <c r="C39" s="32"/>
-      <c r="D39" s="172">
+      <c r="D39" s="169">
         <v>313739</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="205" t="s">
-        <v>264</v>
-      </c>
-      <c r="B40" s="206"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="213" t="s">
+        <v>253</v>
+      </c>
+      <c r="B40" s="214"/>
       <c r="C40" s="32"/>
-      <c r="D40" s="173">
+      <c r="D40" s="170">
         <v>214164</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="205" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="213" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="206"/>
+      <c r="B41" s="214"/>
       <c r="C41" s="32"/>
-      <c r="D41" s="173">
+      <c r="D41" s="170">
         <v>5204</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>110</v>
       </c>
@@ -2850,7 +2970,7 @@
         <v>533107</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
         <v>111</v>
       </c>
@@ -2859,27 +2979,27 @@
       <c r="D43" s="35"/>
       <c r="E43" s="36"/>
     </row>
-    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="37" t="s">
         <v>112</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="38">
         <v>542686.9</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
         <v>112</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="38">
@@ -2887,12 +3007,12 @@
       </c>
       <c r="E45" s="24"/>
     </row>
-    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
         <v>112</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C46" s="37"/>
       <c r="D46" s="38">
@@ -2900,7 +3020,7 @@
       </c>
       <c r="E46" s="24"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="37" t="s">
         <v>113</v>
       </c>
@@ -2910,23 +3030,23 @@
         <v>10111.620000000001</v>
       </c>
       <c r="E47" s="24" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="205" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="213" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="206"/>
+      <c r="B48" s="214"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38">
         <v>4813938.26</v>
       </c>
-      <c r="E48" s="158" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E48" s="155" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="40" t="s">
         <v>115</v>
       </c>
@@ -2935,7 +3055,7 @@
       <c r="D49" s="38"/>
       <c r="E49" s="24"/>
     </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="25" t="s">
         <v>116</v>
       </c>
@@ -2947,97 +3067,97 @@
         <v>5366736.7799999993</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="17"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
       <c r="D51" s="26"/>
       <c r="E51" s="43"/>
     </row>
-    <row r="52" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="202" t="s">
+    <row r="52" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="217" t="s">
         <v>178</v>
       </c>
-      <c r="B52" s="203"/>
+      <c r="B52" s="218"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38">
         <v>225000</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="202" t="s">
-        <v>201</v>
-      </c>
-      <c r="B53" s="203"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="217" t="s">
+        <v>190</v>
+      </c>
+      <c r="B53" s="218"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38">
         <v>500000</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="202" t="s">
-        <v>204</v>
-      </c>
-      <c r="B54" s="203"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="217" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="218"/>
       <c r="C54" s="37"/>
       <c r="D54" s="38">
         <v>1520000</v>
       </c>
       <c r="E54" s="151" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="202" t="s">
-        <v>233</v>
-      </c>
-      <c r="B55" s="203"/>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="217" t="s">
+        <v>222</v>
+      </c>
+      <c r="B55" s="218"/>
       <c r="C55" s="37"/>
       <c r="D55" s="38">
         <f>272252*2</f>
         <v>544504</v>
       </c>
       <c r="E55" s="151" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="202" t="s">
-        <v>219</v>
-      </c>
-      <c r="B56" s="203"/>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="217" t="s">
+        <v>208</v>
+      </c>
+      <c r="B56" s="218"/>
       <c r="C56" s="37"/>
       <c r="D56" s="38">
         <v>85000</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F56" s="63"/>
     </row>
-    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="202" t="s">
-        <v>238</v>
-      </c>
-      <c r="B57" s="203"/>
+    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="217" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" s="218"/>
       <c r="C57" s="37"/>
       <c r="D57" s="38">
         <v>120000</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="F57" s="63"/>
     </row>
-    <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="20" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="37"/>
@@ -3045,41 +3165,41 @@
         <v>35000</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F58" s="63"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="202" t="s">
-        <v>220</v>
-      </c>
-      <c r="B59" s="203"/>
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="217" t="s">
+        <v>209</v>
+      </c>
+      <c r="B59" s="218"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38">
         <v>6000</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F59" s="63"/>
     </row>
-    <row r="60" spans="1:6" ht="86" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="202" t="s">
-        <v>261</v>
-      </c>
-      <c r="B60" s="203"/>
+    <row r="60" spans="1:6" ht="85.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="217" t="s">
+        <v>250</v>
+      </c>
+      <c r="B60" s="218"/>
       <c r="C60" s="37"/>
       <c r="D60" s="38">
         <v>7000000</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F60" s="63"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="37"/>
@@ -3091,7 +3211,7 @@
       </c>
       <c r="F61" s="63"/>
     </row>
-    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="123" t="s">
         <v>179</v>
       </c>
@@ -3101,41 +3221,41 @@
         <v>150800</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F62" s="63"/>
     </row>
-    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="159" t="s">
-        <v>199</v>
-      </c>
-      <c r="B63" s="160"/>
+    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="156" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" s="157"/>
       <c r="C63" s="37"/>
       <c r="D63" s="38">
         <v>910000</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="F63" s="63"/>
     </row>
-    <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="202" t="s">
-        <v>217</v>
-      </c>
-      <c r="B64" s="203"/>
+    <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="217" t="s">
+        <v>206</v>
+      </c>
+      <c r="B64" s="218"/>
       <c r="C64" s="37"/>
       <c r="D64" s="38">
         <v>250000</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F64" s="63"/>
     </row>
-    <row r="65" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="123" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="37"/>
@@ -3143,38 +3263,38 @@
         <v>133300</v>
       </c>
       <c r="E65" s="47" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F65" s="63"/>
     </row>
-    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="202" t="s">
-        <v>210</v>
-      </c>
-      <c r="B66" s="203"/>
+    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="217" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="218"/>
       <c r="C66" s="37"/>
       <c r="D66" s="38">
         <v>105602.65</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F66" s="63"/>
     </row>
-    <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="202" t="s">
-        <v>195</v>
-      </c>
-      <c r="B67" s="203"/>
+    <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="217" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" s="218"/>
       <c r="C67" s="37"/>
       <c r="D67" s="38">
         <v>2022800</v>
       </c>
       <c r="E67" s="47" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="25" t="s">
         <v>0</v>
       </c>
@@ -3186,7 +3306,7 @@
         <v>13636006.65</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="17" t="s">
         <v>117</v>
       </c>
@@ -3195,57 +3315,57 @@
       <c r="D69" s="18"/>
       <c r="E69" s="19"/>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="202" t="s">
-        <v>203</v>
-      </c>
-      <c r="B70" s="203"/>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="217" t="s">
+        <v>192</v>
+      </c>
+      <c r="B70" s="218"/>
       <c r="C70" s="22"/>
-      <c r="D70" s="174">
+      <c r="D70" s="171">
         <v>650000</v>
       </c>
       <c r="E70" s="47"/>
     </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20" t="s">
         <v>177</v>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="22"/>
-      <c r="D71" s="175">
+      <c r="D71" s="172">
         <v>125000</v>
       </c>
       <c r="E71" s="47" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="202" t="s">
-        <v>232</v>
-      </c>
-      <c r="B72" s="203"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="217" t="s">
+        <v>221</v>
+      </c>
+      <c r="B72" s="218"/>
       <c r="C72" s="22"/>
-      <c r="D72" s="175">
+      <c r="D72" s="172">
         <v>62500</v>
       </c>
       <c r="E72" s="47" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="123" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="22"/>
-      <c r="D73" s="175">
+      <c r="D73" s="172">
         <v>45000</v>
       </c>
       <c r="E73" s="47" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="25" t="s">
         <v>108</v>
       </c>
@@ -3257,7 +3377,7 @@
         <v>882500</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
         <v>118</v>
       </c>
@@ -3266,7 +3386,7 @@
       <c r="D75" s="49"/>
       <c r="E75" s="33"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="37" t="s">
         <v>157</v>
       </c>
@@ -3277,9 +3397,9 @@
       </c>
       <c r="E76" s="50"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="37" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="B77" s="37"/>
       <c r="C77" s="37"/>
@@ -3289,30 +3409,30 @@
       </c>
       <c r="E77" s="51"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="37" t="s">
         <v>158</v>
       </c>
       <c r="B78" s="112"/>
       <c r="C78" s="112"/>
-      <c r="D78" s="176">
+      <c r="D78" s="173">
         <v>45000</v>
       </c>
       <c r="E78" s="51"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="37" t="s">
         <v>159</v>
       </c>
       <c r="B79" s="112"/>
       <c r="C79" s="112"/>
-      <c r="D79" s="176">
+      <c r="D79" s="173">
         <f>9386+1200+193960.95+3629+1284.98</f>
         <v>209460.93000000002</v>
       </c>
       <c r="E79" s="51"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="52" t="s">
         <v>108</v>
       </c>
@@ -3324,14 +3444,14 @@
         <v>334094.84000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="37"/>
       <c r="B81" s="37"/>
       <c r="C81" s="37"/>
       <c r="D81" s="55"/>
       <c r="E81" s="56"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="57" t="s">
         <v>119</v>
       </c>
@@ -3340,13 +3460,13 @@
       <c r="D82" s="58"/>
       <c r="E82" s="59"/>
     </row>
-    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="60"/>
       <c r="D83" s="61"/>
       <c r="E83" s="62"/>
       <c r="F83" s="63"/>
     </row>
-    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="64" t="s">
         <v>120</v>
       </c>
@@ -3360,16 +3480,16 @@
       <c r="F84" s="69"/>
       <c r="G84" s="63"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D85" s="61"/>
       <c r="E85" s="61"/>
     </row>
-    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D86" s="61"/>
       <c r="E86" s="61"/>
       <c r="H86" s="70"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>121</v>
       </c>
@@ -3378,50 +3498,50 @@
       <c r="D87" s="71"/>
       <c r="E87" s="72"/>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="30"/>
       <c r="B88" s="31"/>
       <c r="C88" s="37"/>
       <c r="D88" s="45"/>
       <c r="E88" s="73"/>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="202"/>
-      <c r="B89" s="203"/>
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="217"/>
+      <c r="B89" s="218"/>
       <c r="C89" s="37"/>
       <c r="D89" s="45"/>
       <c r="E89" s="73"/>
     </row>
-    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D90" s="55"/>
       <c r="E90" s="37"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="30"/>
       <c r="B91" s="74"/>
       <c r="C91" s="37"/>
       <c r="D91" s="45"/>
       <c r="E91" s="73"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="75" t="s">
         <v>152</v>
       </c>
       <c r="B92" s="76"/>
       <c r="C92" s="76"/>
-      <c r="D92" s="156"/>
+      <c r="D92" s="153"/>
       <c r="E92" s="111">
         <f>SUM(D88:D91)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D93" s="61"/>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="D94" s="61"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="57" t="s">
         <v>122</v>
       </c>
@@ -3430,10 +3550,10 @@
       <c r="D95" s="58"/>
       <c r="E95" s="119"/>
     </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D96" s="61"/>
     </row>
-    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="64" t="s">
         <v>123</v>
       </c>
@@ -3445,8 +3565,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="78" t="s">
         <v>124</v>
       </c>
@@ -3455,7 +3575,7 @@
         <v>24001853.77</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="78" t="s">
         <v>125</v>
       </c>
@@ -3464,7 +3584,7 @@
         <v>24001853.77</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="78" t="s">
         <v>126</v>
       </c>
@@ -3473,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="78" t="s">
         <v>127</v>
       </c>
@@ -3482,50 +3602,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="208" t="s">
-        <v>247</v>
-      </c>
-      <c r="B105" s="208"/>
-    </row>
-    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="208"/>
-      <c r="B106" s="208"/>
-    </row>
-    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="208"/>
-      <c r="B107" s="208"/>
-    </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="208" t="s">
-        <v>250</v>
-      </c>
-      <c r="B109" s="208"/>
-    </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="208"/>
-      <c r="B110" s="208"/>
-    </row>
-    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="208"/>
-      <c r="B111" s="208"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="207" t="s">
-        <v>265</v>
-      </c>
-      <c r="B114" s="207"/>
-    </row>
-    <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="207"/>
-      <c r="B115" s="207"/>
-    </row>
-    <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="225" t="s">
+        <v>236</v>
+      </c>
+      <c r="B105" s="225"/>
+    </row>
+    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="225"/>
+      <c r="B106" s="225"/>
+    </row>
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="225"/>
+      <c r="B107" s="225"/>
+    </row>
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="225" t="s">
+        <v>239</v>
+      </c>
+      <c r="B109" s="225"/>
+    </row>
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="225"/>
+      <c r="B110" s="225"/>
+    </row>
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="225"/>
+      <c r="B111" s="225"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="224" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="224"/>
+    </row>
+    <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="224"/>
+      <c r="B115" s="224"/>
+    </row>
+    <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116"/>
       <c r="B116" s="80"/>
       <c r="C116" s="81"/>
     </row>
-    <row r="117" spans="1:6" s="82" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" s="82" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="122" t="s">
         <v>173</v>
       </c>
@@ -3536,7 +3656,7 @@
       <c r="D117" s="84"/>
       <c r="E117" s="84"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="32" t="s">
         <v>151</v>
       </c>
@@ -3545,7 +3665,7 @@
         <v>-24001853.77</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="32" t="s">
         <v>128</v>
       </c>
@@ -3555,18 +3675,18 @@
       </c>
       <c r="F119" s="80"/>
     </row>
-    <row r="120" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="32" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B120" s="140">
         <v>-239116.53</v>
       </c>
       <c r="F120" s="80"/>
     </row>
-    <row r="121" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="32" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B121" s="141">
         <f>-119452</f>
@@ -3574,70 +3694,70 @@
       </c>
       <c r="F121" s="80"/>
     </row>
-    <row r="122" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="32" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B122" s="141">
         <v>-123612</v>
       </c>
       <c r="F122" s="80"/>
     </row>
-    <row r="123" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="32" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B123" s="141">
         <v>-168836.39</v>
       </c>
       <c r="F123" s="80"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="32" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B124" s="141">
         <v>-20871</v>
       </c>
       <c r="F124" s="80"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="32" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B125" s="141">
         <v>-3820</v>
       </c>
       <c r="F125" s="80"/>
     </row>
-    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="32" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B126" s="141">
         <v>-7274</v>
       </c>
       <c r="F126" s="80"/>
     </row>
-    <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="32" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="B127" s="139">
         <v>-7528</v>
       </c>
       <c r="F127" s="80"/>
     </row>
-    <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="32" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="B128" s="139">
         <v>-50000</v>
       </c>
       <c r="F128" s="80"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="32" t="s">
         <v>2</v>
       </c>
@@ -3647,70 +3767,70 @@
       </c>
       <c r="F129" s="80"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="32" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B130" s="86">
         <v>300000</v>
       </c>
       <c r="F130" s="80"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="32" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B131" s="86">
         <v>250000</v>
       </c>
       <c r="F131" s="80"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="32" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B132" s="86">
         <v>200000.42</v>
       </c>
       <c r="F132" s="80"/>
     </row>
-    <row r="133" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="B133" s="168">
+        <v>237</v>
+      </c>
+      <c r="B133" s="165">
         <v>-130000</v>
       </c>
       <c r="F133" s="80"/>
     </row>
-    <row r="134" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="B134" s="168">
+        <v>243</v>
+      </c>
+      <c r="B134" s="165">
         <v>-130000</v>
       </c>
       <c r="F134" s="80"/>
     </row>
-    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="B135" s="168">
+        <v>238</v>
+      </c>
+      <c r="B135" s="165">
         <v>-130000</v>
       </c>
       <c r="F135" s="80"/>
     </row>
-    <row r="136" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" s="87" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B136" s="152">
         <v>123300</v>
       </c>
       <c r="F136" s="80"/>
     </row>
-    <row r="137" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="88" t="s">
         <v>174</v>
       </c>
@@ -3722,22 +3842,22 @@
       <c r="E137" s="63"/>
       <c r="F137" s="63"/>
     </row>
-    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A139" s="204" t="s">
+    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="223" t="s">
         <v>129</v>
       </c>
-      <c r="B139" s="204"/>
-      <c r="C139" s="204"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A140" s="204"/>
-      <c r="B140" s="204"/>
-      <c r="C140" s="204"/>
-    </row>
-    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B139" s="223"/>
+      <c r="C139" s="223"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A140" s="223"/>
+      <c r="B140" s="223"/>
+      <c r="C140" s="223"/>
+    </row>
+    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="90" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B141" s="150">
         <v>195940.3</v>
@@ -3745,7 +3865,7 @@
       <c r="C141" s="91"/>
       <c r="D141" s="69"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="92" t="s">
         <v>0</v>
       </c>
@@ -3755,24 +3875,11 @@
       </c>
       <c r="C142" s="94"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M143" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A139:C140"/>
@@ -3789,6 +3896,19 @@
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A105:B107"/>
     <mergeCell ref="A109:B111"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3799,52 +3919,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:O126"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.36328125" customWidth="1"/>
-    <col min="2" max="2" width="25.54296875" customWidth="1"/>
-    <col min="3" max="3" width="8.984375E-2" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" customWidth="1"/>
-    <col min="6" max="6" width="12.36328125" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="9.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.453125" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" customWidth="1"/>
-    <col min="13" max="13" width="14.36328125" customWidth="1"/>
-    <col min="14" max="14" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="124"/>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
-      <c r="D1" s="221"/>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
+      <c r="I1" s="234"/>
+      <c r="J1" s="234"/>
+      <c r="K1" s="234"/>
+      <c r="L1" s="234"/>
       <c r="M1" s="126"/>
     </row>
-    <row r="2" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="127"/>
       <c r="B2" s="128"/>
       <c r="C2" s="129"/>
       <c r="D2" s="129" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="245">
+      <c r="E2" s="256">
         <v>3000000</v>
       </c>
-      <c r="F2" s="245"/>
+      <c r="F2" s="256"/>
       <c r="G2" s="129"/>
       <c r="H2" s="129"/>
       <c r="I2" s="129" t="s">
@@ -3858,7 +3978,7 @@
       <c r="M2" s="132"/>
       <c r="N2" s="96"/>
     </row>
-    <row r="3" spans="1:15" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="133"/>
       <c r="B3" s="134"/>
       <c r="C3" s="134"/>
@@ -3874,199 +3994,199 @@
       <c r="M3" s="137"/>
       <c r="N3" s="96"/>
     </row>
-    <row r="4" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="222" t="s">
+    <row r="4" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="235" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="224"/>
+      <c r="B4" s="236"/>
+      <c r="C4" s="236"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
+      <c r="M4" s="237"/>
       <c r="N4" s="96"/>
     </row>
-    <row r="5" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="225"/>
-      <c r="B5" s="226"/>
-      <c r="C5" s="226"/>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="227"/>
+    <row r="5" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="238"/>
+      <c r="B5" s="239"/>
+      <c r="C5" s="239"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="M5" s="240"/>
       <c r="N5" s="96"/>
     </row>
-    <row r="6" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="225"/>
-      <c r="B6" s="226"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="226"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="226"/>
-      <c r="M6" s="227"/>
+    <row r="6" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="238"/>
+      <c r="B6" s="239"/>
+      <c r="C6" s="239"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
+      <c r="F6" s="239"/>
+      <c r="G6" s="239"/>
+      <c r="H6" s="239"/>
+      <c r="I6" s="239"/>
+      <c r="J6" s="239"/>
+      <c r="K6" s="239"/>
+      <c r="L6" s="239"/>
+      <c r="M6" s="240"/>
       <c r="N6" s="96"/>
     </row>
-    <row r="7" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="225"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="227"/>
+    <row r="7" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="238"/>
+      <c r="B7" s="239"/>
+      <c r="C7" s="239"/>
+      <c r="D7" s="239"/>
+      <c r="E7" s="239"/>
+      <c r="F7" s="239"/>
+      <c r="G7" s="239"/>
+      <c r="H7" s="239"/>
+      <c r="I7" s="239"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="240"/>
       <c r="N7" s="96"/>
     </row>
-    <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="228"/>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="230"/>
-    </row>
-    <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="218" t="s">
-        <v>266</v>
-      </c>
-      <c r="B9" s="219"/>
-      <c r="C9" s="219"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="219"/>
-      <c r="F9" s="219"/>
-      <c r="G9" s="219"/>
-      <c r="H9" s="219"/>
-      <c r="I9" s="219"/>
-      <c r="J9" s="219"/>
-      <c r="K9" s="219"/>
-      <c r="L9" s="219"/>
-      <c r="M9" s="220"/>
-    </row>
-    <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="239" t="s">
+    <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="241"/>
+      <c r="B8" s="242"/>
+      <c r="C8" s="242"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="242"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="242"/>
+      <c r="K8" s="242"/>
+      <c r="L8" s="242"/>
+      <c r="M8" s="243"/>
+    </row>
+    <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="231" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="232"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
+      <c r="M9" s="233"/>
+    </row>
+    <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="250" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="240"/>
-      <c r="C10" s="240"/>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
-      <c r="M10" s="241"/>
-    </row>
-    <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="242" t="s">
+      <c r="B10" s="251"/>
+      <c r="C10" s="251"/>
+      <c r="D10" s="251"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="251"/>
+      <c r="H10" s="251"/>
+      <c r="I10" s="251"/>
+      <c r="J10" s="251"/>
+      <c r="K10" s="251"/>
+      <c r="L10" s="251"/>
+      <c r="M10" s="252"/>
+    </row>
+    <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="253" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="243"/>
-      <c r="C11" s="243"/>
-      <c r="D11" s="243"/>
-      <c r="E11" s="243"/>
-      <c r="F11" s="243"/>
-      <c r="G11" s="243"/>
-      <c r="H11" s="243"/>
-      <c r="I11" s="243"/>
-      <c r="J11" s="243"/>
-      <c r="K11" s="243"/>
-      <c r="L11" s="243"/>
-      <c r="M11" s="244"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="231" t="s">
+      <c r="B11" s="254"/>
+      <c r="C11" s="254"/>
+      <c r="D11" s="254"/>
+      <c r="E11" s="254"/>
+      <c r="F11" s="254"/>
+      <c r="G11" s="254"/>
+      <c r="H11" s="254"/>
+      <c r="I11" s="254"/>
+      <c r="J11" s="254"/>
+      <c r="K11" s="254"/>
+      <c r="L11" s="254"/>
+      <c r="M11" s="255"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="244" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="233" t="s">
+      <c r="B12" s="246" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="233" t="s">
+      <c r="C12" s="246" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="233" t="s">
+      <c r="D12" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="235" t="s">
+      <c r="E12" s="226" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="233" t="s">
+      <c r="F12" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="237" t="s">
+      <c r="G12" s="248" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="235" t="s">
+      <c r="H12" s="226" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="235" t="s">
+      <c r="I12" s="226" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="235" t="s">
+      <c r="J12" s="226" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="246" t="s">
-        <v>258</v>
-      </c>
-      <c r="L12" s="198" t="s">
+      <c r="K12" s="257" t="s">
+        <v>247</v>
+      </c>
+      <c r="L12" s="195" t="s">
         <v>140</v>
       </c>
-      <c r="M12" s="215" t="s">
+      <c r="M12" s="228" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="232"/>
-      <c r="B13" s="234"/>
-      <c r="C13" s="234"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="236"/>
-      <c r="F13" s="234"/>
-      <c r="G13" s="238"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="247"/>
-      <c r="L13" s="199" t="str">
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="245"/>
+      <c r="B13" s="247"/>
+      <c r="C13" s="247"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="227"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="227"/>
+      <c r="I13" s="227"/>
+      <c r="J13" s="227"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="196" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M13" s="216"/>
-    </row>
-    <row r="14" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="182">
+      <c r="M13" s="229"/>
+    </row>
+    <row r="14" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="179">
         <v>1</v>
       </c>
       <c r="B14" s="97" t="s">
@@ -4091,11 +4211,11 @@
         <f>IF(G14&gt;0,G14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="177">
+      <c r="I14" s="174">
         <f t="shared" ref="I14:I45" si="1">J$2*D14/100</f>
         <v>165422.36250000002</v>
       </c>
-      <c r="J14" s="177">
+      <c r="J14" s="174">
         <f t="shared" ref="J14:J45" si="2">E$2*D14/100</f>
         <v>41100.000000000007</v>
       </c>
@@ -4104,7 +4224,7 @@
         <f>ROUND(SUM(G14:K14),0) + N14</f>
         <v>206522.01</v>
       </c>
-      <c r="M14" s="193">
+      <c r="M14" s="190">
         <f t="shared" ref="M14:M34" si="3">ROUND(L14*3%,0) + L14</f>
         <v>212718.01</v>
       </c>
@@ -4112,8 +4232,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="182">
+    <row r="15" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="179">
         <v>2</v>
       </c>
       <c r="B15" s="97" t="s">
@@ -4137,11 +4257,11 @@
         <f t="shared" ref="H15:H78" si="4">IF(G15&gt;0,G15*3%,0)</f>
         <v>74472.870599999995</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="174">
         <f t="shared" si="1"/>
         <v>142480.57500000001</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="174">
         <f t="shared" si="2"/>
         <v>35400</v>
       </c>
@@ -4150,7 +4270,7 @@
         <f t="shared" ref="L15:L78" si="5">ROUND(SUM(G15:K15),0) + N15</f>
         <v>2734782.02</v>
       </c>
-      <c r="M15" s="193">
+      <c r="M15" s="190">
         <f t="shared" si="3"/>
         <v>2816825.02</v>
       </c>
@@ -4159,11 +4279,11 @@
         <v>0.02</v>
       </c>
       <c r="O15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="179">
         <v>3</v>
       </c>
       <c r="B16" s="97" t="s">
@@ -4188,11 +4308,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I16" s="177">
+      <c r="I16" s="174">
         <f t="shared" si="1"/>
         <v>89352.225000000006</v>
       </c>
-      <c r="J16" s="177">
+      <c r="J16" s="174">
         <f t="shared" si="2"/>
         <v>22200</v>
       </c>
@@ -4201,7 +4321,7 @@
         <f t="shared" si="5"/>
         <v>111552.03</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="190">
         <f t="shared" si="3"/>
         <v>114899.03</v>
       </c>
@@ -4210,11 +4330,11 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="183">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="180">
         <v>4</v>
       </c>
-      <c r="B17" s="169" t="s">
+      <c r="B17" s="166" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="121"/>
@@ -4236,11 +4356,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I17" s="178">
+      <c r="I17" s="175">
         <f t="shared" si="1"/>
         <v>177496.98749999999</v>
       </c>
-      <c r="J17" s="178">
+      <c r="J17" s="175">
         <f t="shared" si="2"/>
         <v>44100</v>
       </c>
@@ -4249,7 +4369,7 @@
         <f t="shared" si="5"/>
         <v>221597.04</v>
       </c>
-      <c r="M17" s="194">
+      <c r="M17" s="191">
         <f t="shared" si="3"/>
         <v>228245.04</v>
       </c>
@@ -4258,8 +4378,8 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="182">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="179">
         <v>5</v>
       </c>
       <c r="B18" s="97" t="s">
@@ -4283,11 +4403,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I18" s="177">
+      <c r="I18" s="174">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J18" s="177">
+      <c r="J18" s="174">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -4296,7 +4416,7 @@
         <f t="shared" si="5"/>
         <v>163923.04999999999</v>
       </c>
-      <c r="M18" s="193">
+      <c r="M18" s="190">
         <f t="shared" si="3"/>
         <v>168841.05</v>
       </c>
@@ -4305,8 +4425,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="182">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="179">
         <v>6</v>
       </c>
       <c r="B19" s="97" t="s">
@@ -4331,11 +4451,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I19" s="177">
+      <c r="I19" s="174">
         <f t="shared" si="1"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J19" s="177">
+      <c r="J19" s="174">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
@@ -4344,7 +4464,7 @@
         <f t="shared" si="5"/>
         <v>203507.06</v>
       </c>
-      <c r="M19" s="193">
+      <c r="M19" s="190">
         <f t="shared" si="3"/>
         <v>209612.06</v>
       </c>
@@ -4353,8 +4473,8 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="182">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="179">
         <v>7</v>
       </c>
       <c r="B20" s="97" t="s">
@@ -4379,11 +4499,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I20" s="177">
+      <c r="I20" s="174">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J20" s="177">
+      <c r="J20" s="174">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -4392,7 +4512,7 @@
         <f t="shared" si="5"/>
         <v>168836.07</v>
       </c>
-      <c r="M20" s="193">
+      <c r="M20" s="190">
         <f t="shared" si="3"/>
         <v>173901.07</v>
       </c>
@@ -4401,8 +4521,8 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="182">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="179">
         <v>8</v>
       </c>
       <c r="B21" s="97" t="s">
@@ -4427,11 +4547,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I21" s="177">
+      <c r="I21" s="174">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J21" s="177">
+      <c r="J21" s="174">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -4440,7 +4560,7 @@
         <f t="shared" si="5"/>
         <v>123612.08</v>
       </c>
-      <c r="M21" s="193">
+      <c r="M21" s="190">
         <f t="shared" si="3"/>
         <v>127320.08</v>
       </c>
@@ -4449,8 +4569,8 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="182">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="179">
         <v>9</v>
       </c>
       <c r="B22" s="97" t="s">
@@ -4474,11 +4594,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I22" s="177">
+      <c r="I22" s="174">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J22" s="177">
+      <c r="J22" s="174">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -4487,7 +4607,7 @@
         <f t="shared" si="5"/>
         <v>120015.09</v>
       </c>
-      <c r="M22" s="193">
+      <c r="M22" s="190">
         <f t="shared" si="3"/>
         <v>123615.09</v>
       </c>
@@ -4496,8 +4616,8 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="182">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="179">
         <v>10</v>
       </c>
       <c r="B23" s="97" t="s">
@@ -4522,11 +4642,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I23" s="177">
+      <c r="I23" s="174">
         <f t="shared" si="1"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J23" s="177">
+      <c r="J23" s="174">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
@@ -4535,7 +4655,7 @@
         <f t="shared" si="5"/>
         <v>202000.1</v>
       </c>
-      <c r="M23" s="193">
+      <c r="M23" s="190">
         <f t="shared" si="3"/>
         <v>208060.1</v>
       </c>
@@ -4544,8 +4664,8 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="182">
+    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="179">
         <v>11</v>
       </c>
       <c r="B24" s="97" t="s">
@@ -4570,11 +4690,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I24" s="177">
+      <c r="I24" s="174">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J24" s="177">
+      <c r="J24" s="174">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -4583,7 +4703,7 @@
         <f t="shared" si="5"/>
         <v>168836.11</v>
       </c>
-      <c r="M24" s="193">
+      <c r="M24" s="190">
         <f t="shared" si="3"/>
         <v>173901.11</v>
       </c>
@@ -4592,8 +4712,8 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="182">
+    <row r="25" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="179">
         <v>12</v>
       </c>
       <c r="B25" s="97" t="s">
@@ -4617,11 +4737,11 @@
         <f t="shared" si="4"/>
         <v>98401.0236</v>
       </c>
-      <c r="I25" s="177">
+      <c r="I25" s="174">
         <f t="shared" si="1"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J25" s="177">
+      <c r="J25" s="174">
         <f t="shared" si="2"/>
         <v>35100</v>
       </c>
@@ -4630,7 +4750,7 @@
         <f t="shared" si="5"/>
         <v>3554808.12</v>
       </c>
-      <c r="M25" s="193">
+      <c r="M25" s="190">
         <f t="shared" si="3"/>
         <v>3661452.12</v>
       </c>
@@ -4639,8 +4759,8 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="182">
+    <row r="26" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="179">
         <v>13</v>
       </c>
       <c r="B26" s="97" t="s">
@@ -4665,11 +4785,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I26" s="177">
+      <c r="I26" s="174">
         <f t="shared" si="1"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J26" s="177">
+      <c r="J26" s="174">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
@@ -4678,7 +4798,7 @@
         <f t="shared" si="5"/>
         <v>203507.13</v>
       </c>
-      <c r="M26" s="193">
+      <c r="M26" s="190">
         <f t="shared" si="3"/>
         <v>209612.13</v>
       </c>
@@ -4687,8 +4807,8 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="182">
+    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="179">
         <v>14</v>
       </c>
       <c r="B27" s="97" t="s">
@@ -4713,11 +4833,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I27" s="177">
+      <c r="I27" s="174">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J27" s="177">
+      <c r="J27" s="174">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -4726,7 +4846,7 @@
         <f t="shared" si="5"/>
         <v>168836.14</v>
       </c>
-      <c r="M27" s="193">
+      <c r="M27" s="190">
         <f t="shared" si="3"/>
         <v>173901.14</v>
       </c>
@@ -4735,8 +4855,8 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="184">
+    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="181">
         <v>15</v>
       </c>
       <c r="B28" s="142" t="s">
@@ -4761,11 +4881,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I28" s="177">
+      <c r="I28" s="174">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J28" s="177">
+      <c r="J28" s="174">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -4774,7 +4894,7 @@
         <f t="shared" si="5"/>
         <v>123612.15</v>
       </c>
-      <c r="M28" s="193">
+      <c r="M28" s="190">
         <f t="shared" si="3"/>
         <v>127320.15</v>
       </c>
@@ -4783,8 +4903,8 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="182">
+    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="179">
         <v>16</v>
       </c>
       <c r="B29" s="97" t="s">
@@ -4808,11 +4928,11 @@
         <f t="shared" si="4"/>
         <v>10755.900000000001</v>
       </c>
-      <c r="I29" s="177">
+      <c r="I29" s="174">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J29" s="177">
+      <c r="J29" s="174">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -4821,7 +4941,7 @@
         <f t="shared" si="5"/>
         <v>492898.16</v>
       </c>
-      <c r="M29" s="193">
+      <c r="M29" s="190">
         <f t="shared" si="3"/>
         <v>507685.16</v>
       </c>
@@ -4830,8 +4950,8 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="182">
+    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="179">
         <v>17</v>
       </c>
       <c r="B30" s="97" t="s">
@@ -4856,11 +4976,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="177">
+      <c r="I30" s="174">
         <f t="shared" si="1"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J30" s="177">
+      <c r="J30" s="174">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
@@ -4869,7 +4989,7 @@
         <f t="shared" si="5"/>
         <v>202000.17</v>
       </c>
-      <c r="M30" s="193">
+      <c r="M30" s="190">
         <f t="shared" si="3"/>
         <v>208060.17</v>
       </c>
@@ -4878,8 +4998,8 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="184">
+    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="181">
         <v>18</v>
       </c>
       <c r="B31" s="142" t="s">
@@ -4903,11 +5023,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I31" s="179">
+      <c r="I31" s="176">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J31" s="179">
+      <c r="J31" s="176">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -4916,7 +5036,7 @@
         <f t="shared" si="5"/>
         <v>163771.18</v>
       </c>
-      <c r="M31" s="195">
+      <c r="M31" s="192">
         <f t="shared" si="3"/>
         <v>168684.18</v>
       </c>
@@ -4925,8 +5045,8 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="182">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="179">
         <v>19</v>
       </c>
       <c r="B32" s="97" t="s">
@@ -4951,11 +5071,11 @@
         <f t="shared" si="4"/>
         <v>0.03</v>
       </c>
-      <c r="I32" s="177">
+      <c r="I32" s="174">
         <f t="shared" si="1"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J32" s="177">
+      <c r="J32" s="174">
         <f t="shared" si="2"/>
         <v>35100</v>
       </c>
@@ -4964,7 +5084,7 @@
         <f t="shared" si="5"/>
         <v>176374.19</v>
       </c>
-      <c r="M32" s="193">
+      <c r="M32" s="190">
         <f t="shared" si="3"/>
         <v>181665.19</v>
       </c>
@@ -4976,43 +5096,43 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="185">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="182">
         <v>20</v>
       </c>
-      <c r="B33" s="180" t="s">
+      <c r="B33" s="177" t="s">
         <v>22</v>
       </c>
-      <c r="C33" s="162"/>
-      <c r="D33" s="163">
+      <c r="C33" s="159"/>
+      <c r="D33" s="160">
         <v>1.35</v>
       </c>
-      <c r="E33" s="164">
+      <c r="E33" s="161">
         <v>203507.20000000001</v>
       </c>
-      <c r="F33" s="164"/>
-      <c r="G33" s="165">
+      <c r="F33" s="161"/>
+      <c r="G33" s="162">
         <f t="shared" si="0"/>
         <v>203507.20000000001</v>
       </c>
-      <c r="H33" s="165">
+      <c r="H33" s="162">
         <f t="shared" si="4"/>
         <v>6105.2160000000003</v>
       </c>
-      <c r="I33" s="181">
+      <c r="I33" s="178">
         <f t="shared" si="1"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J33" s="181">
+      <c r="J33" s="178">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
-      <c r="K33" s="166"/>
-      <c r="L33" s="167">
+      <c r="K33" s="163"/>
+      <c r="L33" s="164">
         <f t="shared" si="5"/>
         <v>413120.2</v>
       </c>
-      <c r="M33" s="196">
+      <c r="M33" s="193">
         <f t="shared" si="3"/>
         <v>425514.2</v>
       </c>
@@ -5024,8 +5144,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="184">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="181">
         <v>21</v>
       </c>
       <c r="B34" s="149" t="s">
@@ -5050,11 +5170,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I34" s="179">
+      <c r="I34" s="176">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J34" s="179">
+      <c r="J34" s="176">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -5063,7 +5183,7 @@
         <f t="shared" si="5"/>
         <v>168836.21</v>
       </c>
-      <c r="M34" s="195">
+      <c r="M34" s="192">
         <f t="shared" si="3"/>
         <v>173901.21</v>
       </c>
@@ -5072,8 +5192,8 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="182">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="179">
         <f>A34+1</f>
         <v>22</v>
       </c>
@@ -5098,11 +5218,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I35" s="177">
+      <c r="I35" s="174">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J35" s="177">
+      <c r="J35" s="174">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -5111,7 +5231,7 @@
         <f t="shared" si="5"/>
         <v>119904.22</v>
       </c>
-      <c r="M35" s="193">
+      <c r="M35" s="190">
         <f t="shared" ref="M35:M98" si="8">ROUND(L35*3%,0) + L35</f>
         <v>123501.22</v>
       </c>
@@ -5120,8 +5240,8 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A36" s="182">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="179">
         <f t="shared" ref="A36:A99" si="9">A35+1</f>
         <v>23</v>
       </c>
@@ -5147,11 +5267,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I36" s="177">
+      <c r="I36" s="174">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J36" s="177">
+      <c r="J36" s="174">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -5160,7 +5280,7 @@
         <f t="shared" si="5"/>
         <v>123612.23</v>
       </c>
-      <c r="M36" s="193">
+      <c r="M36" s="190">
         <f t="shared" si="8"/>
         <v>127320.23</v>
       </c>
@@ -5169,8 +5289,8 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="182">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="179">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
@@ -5196,11 +5316,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I37" s="177">
+      <c r="I37" s="174">
         <f t="shared" si="1"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J37" s="177">
+      <c r="J37" s="174">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
@@ -5209,7 +5329,7 @@
         <f t="shared" si="5"/>
         <v>202000.24</v>
       </c>
-      <c r="M37" s="193">
+      <c r="M37" s="190">
         <f t="shared" si="8"/>
         <v>208060.24</v>
       </c>
@@ -5218,8 +5338,8 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="182">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="179">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
@@ -5242,11 +5362,11 @@
         <f t="shared" si="4"/>
         <v>4519.4775</v>
       </c>
-      <c r="I38" s="177">
+      <c r="I38" s="174">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J38" s="177">
+      <c r="J38" s="174">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -5255,7 +5375,7 @@
         <f t="shared" si="5"/>
         <v>324005.25</v>
       </c>
-      <c r="M38" s="193">
+      <c r="M38" s="190">
         <f t="shared" si="8"/>
         <v>333725.25</v>
       </c>
@@ -5264,8 +5384,8 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="182">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="179">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
@@ -5291,11 +5411,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I39" s="177">
+      <c r="I39" s="174">
         <f t="shared" si="1"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J39" s="177">
+      <c r="J39" s="174">
         <f t="shared" si="2"/>
         <v>35100</v>
       </c>
@@ -5304,7 +5424,7 @@
         <f t="shared" si="5"/>
         <v>176373.26</v>
       </c>
-      <c r="M39" s="193">
+      <c r="M39" s="190">
         <f t="shared" si="8"/>
         <v>181664.26</v>
       </c>
@@ -5313,8 +5433,8 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="182">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="179">
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
@@ -5340,11 +5460,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="177">
+      <c r="I40" s="174">
         <f t="shared" si="1"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J40" s="177">
+      <c r="J40" s="174">
         <f t="shared" si="2"/>
         <v>40500.000000000007</v>
       </c>
@@ -5353,7 +5473,7 @@
         <f t="shared" si="5"/>
         <v>203507.27</v>
       </c>
-      <c r="M40" s="193">
+      <c r="M40" s="190">
         <f t="shared" si="8"/>
         <v>209612.27</v>
       </c>
@@ -5362,8 +5482,8 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="182">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="179">
         <f t="shared" si="9"/>
         <v>28</v>
       </c>
@@ -5388,11 +5508,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I41" s="177">
+      <c r="I41" s="174">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J41" s="177">
+      <c r="J41" s="174">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -5401,7 +5521,7 @@
         <f t="shared" si="5"/>
         <v>163923.28</v>
       </c>
-      <c r="M41" s="193">
+      <c r="M41" s="190">
         <f t="shared" si="8"/>
         <v>168841.28</v>
       </c>
@@ -5410,8 +5530,8 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A42" s="183">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="180">
         <f t="shared" si="9"/>
         <v>29</v>
       </c>
@@ -5434,11 +5554,11 @@
         <f t="shared" si="4"/>
         <v>3505.2986999999998</v>
       </c>
-      <c r="I42" s="178">
+      <c r="I42" s="175">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J42" s="178">
+      <c r="J42" s="175">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -5447,7 +5567,7 @@
         <f t="shared" si="5"/>
         <v>243961.29</v>
       </c>
-      <c r="M42" s="194">
+      <c r="M42" s="191">
         <f t="shared" si="8"/>
         <v>251280.29</v>
       </c>
@@ -5459,8 +5579,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A43" s="184">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="181">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
@@ -5485,11 +5605,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I43" s="177">
+      <c r="I43" s="174">
         <f t="shared" si="1"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J43" s="177">
+      <c r="J43" s="174">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
@@ -5498,7 +5618,7 @@
         <f t="shared" si="5"/>
         <v>119289.3</v>
       </c>
-      <c r="M43" s="193">
+      <c r="M43" s="190">
         <f t="shared" si="8"/>
         <v>122868.3</v>
       </c>
@@ -5507,8 +5627,8 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="182">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="179">
         <f t="shared" si="9"/>
         <v>31</v>
       </c>
@@ -5533,11 +5653,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I44" s="177">
+      <c r="I44" s="174">
         <f t="shared" si="1"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J44" s="177">
+      <c r="J44" s="174">
         <f t="shared" si="2"/>
         <v>40200.000000000007</v>
       </c>
@@ -5546,7 +5666,7 @@
         <f t="shared" si="5"/>
         <v>195940.31</v>
       </c>
-      <c r="M44" s="193">
+      <c r="M44" s="190">
         <f t="shared" si="8"/>
         <v>201818.31</v>
       </c>
@@ -5555,8 +5675,8 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A45" s="182">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="179">
         <f t="shared" si="9"/>
         <v>32</v>
       </c>
@@ -5579,11 +5699,11 @@
         <f t="shared" si="4"/>
         <v>4761.1895999999997</v>
       </c>
-      <c r="I45" s="177">
+      <c r="I45" s="174">
         <f t="shared" si="1"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J45" s="177">
+      <c r="J45" s="174">
         <f t="shared" si="2"/>
         <v>33600.000000000007</v>
       </c>
@@ -5592,7 +5712,7 @@
         <f t="shared" si="5"/>
         <v>332303.32</v>
       </c>
-      <c r="M45" s="193">
+      <c r="M45" s="190">
         <f t="shared" si="8"/>
         <v>342272.32</v>
       </c>
@@ -5601,44 +5721,44 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="185">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="182">
         <f t="shared" si="9"/>
         <v>33</v>
       </c>
-      <c r="B46" s="161" t="s">
+      <c r="B46" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="162"/>
-      <c r="D46" s="163">
+      <c r="C46" s="159"/>
+      <c r="D46" s="160">
         <v>1.17</v>
       </c>
-      <c r="E46" s="164">
+      <c r="E46" s="161">
         <v>176373.11249999999</v>
       </c>
-      <c r="F46" s="164"/>
-      <c r="G46" s="165">
+      <c r="F46" s="161"/>
+      <c r="G46" s="162">
         <f t="shared" si="0"/>
         <v>176373.11249999999</v>
       </c>
-      <c r="H46" s="165">
+      <c r="H46" s="162">
         <f t="shared" si="4"/>
         <v>5291.1933749999998</v>
       </c>
-      <c r="I46" s="181">
+      <c r="I46" s="178">
         <f t="shared" ref="I46:I77" si="10">J$2*D46/100</f>
         <v>141273.11249999999</v>
       </c>
-      <c r="J46" s="181">
+      <c r="J46" s="178">
         <f t="shared" ref="J46:J77" si="11">E$2*D46/100</f>
         <v>35100</v>
       </c>
-      <c r="K46" s="166"/>
-      <c r="L46" s="167">
+      <c r="K46" s="163"/>
+      <c r="L46" s="164">
         <f t="shared" si="5"/>
         <v>358037.33</v>
       </c>
-      <c r="M46" s="196">
+      <c r="M46" s="193">
         <f t="shared" si="8"/>
         <v>368778.33</v>
       </c>
@@ -5647,8 +5767,8 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A47" s="182">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="179">
         <f t="shared" si="9"/>
         <v>34</v>
       </c>
@@ -5674,11 +5794,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I47" s="177">
+      <c r="I47" s="174">
         <f t="shared" si="10"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J47" s="177">
+      <c r="J47" s="174">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
@@ -5687,7 +5807,7 @@
         <f t="shared" si="5"/>
         <v>203507.34</v>
       </c>
-      <c r="M47" s="193">
+      <c r="M47" s="190">
         <f t="shared" si="8"/>
         <v>209612.34</v>
       </c>
@@ -5696,8 +5816,8 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="183">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="180">
         <f t="shared" si="9"/>
         <v>35</v>
       </c>
@@ -5722,11 +5842,11 @@
         <f t="shared" si="4"/>
         <v>4252.9004999999988</v>
       </c>
-      <c r="I48" s="178">
+      <c r="I48" s="175">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J48" s="178">
+      <c r="J48" s="175">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -5735,7 +5855,7 @@
         <f t="shared" si="5"/>
         <v>314852.34999999998</v>
       </c>
-      <c r="M48" s="194">
+      <c r="M48" s="191">
         <f t="shared" si="8"/>
         <v>324298.34999999998</v>
       </c>
@@ -5747,8 +5867,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A49" s="182">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="179">
         <f t="shared" si="9"/>
         <v>36</v>
       </c>
@@ -5774,11 +5894,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I49" s="177">
+      <c r="I49" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J49" s="177">
+      <c r="J49" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -5787,7 +5907,7 @@
         <f t="shared" si="5"/>
         <v>123612.36</v>
       </c>
-      <c r="M49" s="193">
+      <c r="M49" s="190">
         <f t="shared" si="8"/>
         <v>127320.36</v>
       </c>
@@ -5799,8 +5919,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A50" s="182">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="179">
         <f t="shared" si="9"/>
         <v>37</v>
       </c>
@@ -5826,11 +5946,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I50" s="177">
+      <c r="I50" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J50" s="177">
+      <c r="J50" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -5839,7 +5959,7 @@
         <f t="shared" si="5"/>
         <v>123612.37</v>
       </c>
-      <c r="M50" s="193">
+      <c r="M50" s="190">
         <f t="shared" si="8"/>
         <v>127320.37</v>
       </c>
@@ -5848,8 +5968,8 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A51" s="182">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="179">
         <f t="shared" si="9"/>
         <v>38</v>
       </c>
@@ -5872,11 +5992,11 @@
         <f t="shared" si="4"/>
         <v>5878.2114000000001</v>
       </c>
-      <c r="I51" s="177">
+      <c r="I51" s="174">
         <f t="shared" si="10"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J51" s="177">
+      <c r="J51" s="174">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
@@ -5885,7 +6005,7 @@
         <f t="shared" si="5"/>
         <v>403819.38</v>
       </c>
-      <c r="M51" s="193">
+      <c r="M51" s="190">
         <f t="shared" si="8"/>
         <v>415934.38</v>
       </c>
@@ -5894,8 +6014,8 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A52" s="182">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="179">
         <f t="shared" si="9"/>
         <v>39</v>
       </c>
@@ -5921,11 +6041,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I52" s="177">
+      <c r="I52" s="174">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J52" s="177">
+      <c r="J52" s="174">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -5934,7 +6054,7 @@
         <f t="shared" si="5"/>
         <v>168835.39</v>
       </c>
-      <c r="M52" s="193">
+      <c r="M52" s="190">
         <f t="shared" si="8"/>
         <v>173900.39</v>
       </c>
@@ -5943,8 +6063,8 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A53" s="182">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="179">
         <f t="shared" si="9"/>
         <v>40</v>
       </c>
@@ -5967,11 +6087,11 @@
         <f t="shared" si="4"/>
         <v>10741.152</v>
       </c>
-      <c r="I53" s="177">
+      <c r="I53" s="174">
         <f t="shared" si="10"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J53" s="177">
+      <c r="J53" s="174">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
@@ -5980,7 +6100,7 @@
         <f t="shared" si="5"/>
         <v>545153.4</v>
       </c>
-      <c r="M53" s="193">
+      <c r="M53" s="190">
         <f t="shared" si="8"/>
         <v>561508.4</v>
       </c>
@@ -5989,8 +6109,8 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A54" s="182">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="179">
         <f t="shared" si="9"/>
         <v>41</v>
       </c>
@@ -6015,11 +6135,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I54" s="177">
+      <c r="I54" s="174">
         <f t="shared" si="10"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J54" s="177">
+      <c r="J54" s="174">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
@@ -6028,7 +6148,7 @@
         <f t="shared" si="5"/>
         <v>197402.41</v>
       </c>
-      <c r="M54" s="193">
+      <c r="M54" s="190">
         <f t="shared" si="8"/>
         <v>203324.41</v>
       </c>
@@ -6037,44 +6157,44 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" s="185">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="182">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
-      <c r="B55" s="161" t="s">
+      <c r="B55" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="162"/>
-      <c r="D55" s="163">
+      <c r="C55" s="159"/>
+      <c r="D55" s="160">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E55" s="164">
+      <c r="E55" s="161">
         <v>818744.42</v>
       </c>
-      <c r="F55" s="164"/>
-      <c r="G55" s="165">
+      <c r="F55" s="161"/>
+      <c r="G55" s="162">
         <f t="shared" si="0"/>
         <v>818744.42</v>
       </c>
-      <c r="H55" s="165">
+      <c r="H55" s="162">
         <f t="shared" si="4"/>
         <v>24562.332600000002</v>
       </c>
-      <c r="I55" s="181">
+      <c r="I55" s="178">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J55" s="181">
+      <c r="J55" s="178">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K55" s="166"/>
-      <c r="L55" s="167">
+      <c r="K55" s="163"/>
+      <c r="L55" s="164">
         <f t="shared" si="5"/>
         <v>1012143.42</v>
       </c>
-      <c r="M55" s="196">
+      <c r="M55" s="193">
         <f t="shared" si="8"/>
         <v>1042507.42</v>
       </c>
@@ -6083,8 +6203,8 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A56" s="182">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="179">
         <f t="shared" si="9"/>
         <v>43</v>
       </c>
@@ -6109,11 +6229,11 @@
         <f t="shared" si="4"/>
         <v>50544.342899999996</v>
       </c>
-      <c r="I56" s="177">
+      <c r="I56" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J56" s="177">
+      <c r="J56" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -6122,7 +6242,7 @@
         <f t="shared" si="5"/>
         <v>1858968.43</v>
       </c>
-      <c r="M56" s="193">
+      <c r="M56" s="190">
         <f t="shared" si="8"/>
         <v>1914737.43</v>
       </c>
@@ -6131,8 +6251,8 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" s="182">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="179">
         <f t="shared" si="9"/>
         <v>44</v>
       </c>
@@ -6155,11 +6275,11 @@
         <f t="shared" si="4"/>
         <v>7528.0032000000001</v>
       </c>
-      <c r="I57" s="177">
+      <c r="I57" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J57" s="177">
+      <c r="J57" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -6168,7 +6288,7 @@
         <f t="shared" si="5"/>
         <v>382073.44</v>
       </c>
-      <c r="M57" s="193">
+      <c r="M57" s="190">
         <f t="shared" si="8"/>
         <v>393535.44</v>
       </c>
@@ -6177,8 +6297,8 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A58" s="182">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="179">
         <f t="shared" si="9"/>
         <v>45</v>
       </c>
@@ -6204,11 +6324,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I58" s="177">
+      <c r="I58" s="174">
         <f t="shared" si="10"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J58" s="177">
+      <c r="J58" s="174">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
@@ -6217,7 +6337,7 @@
         <f t="shared" si="5"/>
         <v>202000.45</v>
       </c>
-      <c r="M58" s="193">
+      <c r="M58" s="190">
         <f t="shared" si="8"/>
         <v>208060.45</v>
       </c>
@@ -6226,8 +6346,8 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A59" s="182">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="179">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
@@ -6252,11 +6372,11 @@
         <f t="shared" si="4"/>
         <v>1237.7537999999997</v>
       </c>
-      <c r="I59" s="177">
+      <c r="I59" s="174">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J59" s="177">
+      <c r="J59" s="174">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -6265,7 +6385,7 @@
         <f t="shared" si="5"/>
         <v>211332.46</v>
       </c>
-      <c r="M59" s="193">
+      <c r="M59" s="190">
         <f t="shared" si="8"/>
         <v>217672.46</v>
       </c>
@@ -6277,8 +6397,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A60" s="183">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="180">
         <f t="shared" si="9"/>
         <v>47</v>
       </c>
@@ -6303,11 +6423,11 @@
         <f t="shared" si="4"/>
         <v>12239.318999999998</v>
       </c>
-      <c r="I60" s="178">
+      <c r="I60" s="175">
         <f t="shared" si="10"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J60" s="178">
+      <c r="J60" s="175">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
@@ -6316,7 +6436,7 @@
         <f t="shared" si="5"/>
         <v>596590.47</v>
       </c>
-      <c r="M60" s="194">
+      <c r="M60" s="191">
         <f t="shared" si="8"/>
         <v>614488.47</v>
       </c>
@@ -6325,11 +6445,11 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="O60" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="184">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="181">
         <f t="shared" si="9"/>
         <v>48</v>
       </c>
@@ -6355,11 +6475,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I61" s="179">
+      <c r="I61" s="176">
         <f t="shared" si="10"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J61" s="179">
+      <c r="J61" s="176">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
@@ -6368,7 +6488,7 @@
         <f t="shared" si="5"/>
         <v>203507.48</v>
       </c>
-      <c r="M61" s="195">
+      <c r="M61" s="192">
         <f t="shared" si="8"/>
         <v>209612.48</v>
       </c>
@@ -6380,8 +6500,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A62" s="182">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="179">
         <f t="shared" si="9"/>
         <v>49</v>
       </c>
@@ -6406,11 +6526,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I62" s="177">
+      <c r="I62" s="174">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J62" s="177">
+      <c r="J62" s="174">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -6419,7 +6539,7 @@
         <f t="shared" si="5"/>
         <v>163923.49</v>
       </c>
-      <c r="M62" s="193">
+      <c r="M62" s="190">
         <f t="shared" si="8"/>
         <v>168841.49</v>
       </c>
@@ -6428,8 +6548,8 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A63" s="182">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="179">
         <f t="shared" si="9"/>
         <v>50</v>
       </c>
@@ -6455,11 +6575,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I63" s="177">
+      <c r="I63" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J63" s="177">
+      <c r="J63" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -6468,7 +6588,7 @@
         <f t="shared" si="5"/>
         <v>123612.5</v>
       </c>
-      <c r="M63" s="193">
+      <c r="M63" s="190">
         <f t="shared" si="8"/>
         <v>127320.5</v>
       </c>
@@ -6477,8 +6597,8 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A64" s="182">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="179">
         <f t="shared" si="9"/>
         <v>51</v>
       </c>
@@ -6503,11 +6623,11 @@
         <f t="shared" si="4"/>
         <v>3804.1800000000003</v>
       </c>
-      <c r="I64" s="177">
+      <c r="I64" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J64" s="177">
+      <c r="J64" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -6516,7 +6636,7 @@
         <f t="shared" si="5"/>
         <v>254222.51</v>
       </c>
-      <c r="M64" s="193">
+      <c r="M64" s="190">
         <f t="shared" si="8"/>
         <v>261849.51</v>
       </c>
@@ -6525,8 +6645,8 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A65" s="182">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="179">
         <f t="shared" si="9"/>
         <v>52</v>
       </c>
@@ -6552,11 +6672,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I65" s="177">
+      <c r="I65" s="174">
         <f t="shared" si="10"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J65" s="177">
+      <c r="J65" s="174">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
@@ -6565,7 +6685,7 @@
         <f t="shared" si="5"/>
         <v>202000.52</v>
       </c>
-      <c r="M65" s="193">
+      <c r="M65" s="190">
         <f t="shared" si="8"/>
         <v>208060.52</v>
       </c>
@@ -6574,12 +6694,12 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A66" s="184">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="205">
         <f t="shared" si="9"/>
         <v>53</v>
       </c>
-      <c r="B66" s="149" t="s">
+      <c r="B66" s="206" t="s">
         <v>54</v>
       </c>
       <c r="C66" s="148"/>
@@ -6600,11 +6720,11 @@
         <f t="shared" si="4"/>
         <v>6065.43</v>
       </c>
-      <c r="I66" s="177">
+      <c r="I66" s="174">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J66" s="177">
+      <c r="J66" s="174">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -6613,7 +6733,7 @@
         <f t="shared" si="5"/>
         <v>377082.53</v>
       </c>
-      <c r="M66" s="193">
+      <c r="M66" s="190">
         <f t="shared" si="8"/>
         <v>388394.53</v>
       </c>
@@ -6622,8 +6742,8 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A67" s="182">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="179">
         <f t="shared" si="9"/>
         <v>54</v>
       </c>
@@ -6648,11 +6768,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I67" s="177">
+      <c r="I67" s="174">
         <f t="shared" si="10"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J67" s="177">
+      <c r="J67" s="174">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
@@ -6661,7 +6781,7 @@
         <f t="shared" si="5"/>
         <v>171241.54</v>
       </c>
-      <c r="M67" s="193">
+      <c r="M67" s="190">
         <f t="shared" si="8"/>
         <v>176378.54</v>
       </c>
@@ -6670,8 +6790,8 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A68" s="182">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="179">
         <f t="shared" si="9"/>
         <v>55</v>
       </c>
@@ -6696,11 +6816,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I68" s="177">
+      <c r="I68" s="174">
         <f t="shared" si="10"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J68" s="177">
+      <c r="J68" s="174">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
@@ -6709,7 +6829,7 @@
         <f t="shared" si="5"/>
         <v>197585.55</v>
       </c>
-      <c r="M68" s="193">
+      <c r="M68" s="190">
         <f t="shared" si="8"/>
         <v>203513.55</v>
       </c>
@@ -6718,8 +6838,8 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A69" s="182">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="179">
         <f t="shared" si="9"/>
         <v>56</v>
       </c>
@@ -6744,11 +6864,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I69" s="177">
+      <c r="I69" s="174">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J69" s="177">
+      <c r="J69" s="174">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -6757,7 +6877,7 @@
         <f t="shared" si="5"/>
         <v>163771.56</v>
       </c>
-      <c r="M69" s="193">
+      <c r="M69" s="190">
         <f t="shared" si="8"/>
         <v>168684.56</v>
       </c>
@@ -6766,8 +6886,8 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A70" s="184">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="181">
         <f t="shared" si="9"/>
         <v>57</v>
       </c>
@@ -6792,11 +6912,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I70" s="177">
+      <c r="I70" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J70" s="177">
+      <c r="J70" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -6805,7 +6925,7 @@
         <f t="shared" si="5"/>
         <v>123510.57</v>
       </c>
-      <c r="M70" s="193">
+      <c r="M70" s="190">
         <f t="shared" si="8"/>
         <v>127215.57</v>
       </c>
@@ -6814,8 +6934,8 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A71" s="182">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="179">
         <f t="shared" si="9"/>
         <v>58</v>
       </c>
@@ -6841,11 +6961,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I71" s="177">
+      <c r="I71" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J71" s="177">
+      <c r="J71" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -6854,7 +6974,7 @@
         <f t="shared" si="5"/>
         <v>123612.58</v>
       </c>
-      <c r="M71" s="193">
+      <c r="M71" s="190">
         <f t="shared" si="8"/>
         <v>127320.58</v>
       </c>
@@ -6863,8 +6983,8 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A72" s="184">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="181">
         <f t="shared" si="9"/>
         <v>59</v>
       </c>
@@ -6890,11 +7010,11 @@
         <f t="shared" si="4"/>
         <v>1.2300000000977888E-2</v>
       </c>
-      <c r="I72" s="179">
+      <c r="I72" s="176">
         <f t="shared" si="10"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J72" s="179">
+      <c r="J72" s="176">
         <f t="shared" si="11"/>
         <v>40200.000000000007</v>
       </c>
@@ -6903,7 +7023,7 @@
         <f t="shared" si="5"/>
         <v>202000.59</v>
       </c>
-      <c r="M72" s="195">
+      <c r="M72" s="192">
         <f t="shared" si="8"/>
         <v>208060.59</v>
       </c>
@@ -6912,8 +7032,8 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A73" s="182">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="179">
         <f t="shared" si="9"/>
         <v>60</v>
       </c>
@@ -6938,11 +7058,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I73" s="177">
+      <c r="I73" s="174">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J73" s="177">
+      <c r="J73" s="174">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -6951,7 +7071,7 @@
         <f t="shared" si="5"/>
         <v>163923.6</v>
       </c>
-      <c r="M73" s="193">
+      <c r="M73" s="190">
         <f t="shared" si="8"/>
         <v>168841.60000000001</v>
       </c>
@@ -6960,8 +7080,8 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A74" s="182">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="179">
         <f t="shared" si="9"/>
         <v>61</v>
       </c>
@@ -6987,11 +7107,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I74" s="177">
+      <c r="I74" s="174">
         <f t="shared" si="10"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J74" s="177">
+      <c r="J74" s="174">
         <f t="shared" si="11"/>
         <v>35100</v>
       </c>
@@ -7000,7 +7120,7 @@
         <f t="shared" si="5"/>
         <v>176373.61</v>
       </c>
-      <c r="M74" s="193">
+      <c r="M74" s="190">
         <f t="shared" si="8"/>
         <v>181664.61</v>
       </c>
@@ -7009,8 +7129,8 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A75" s="182">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="179">
         <f t="shared" si="9"/>
         <v>62</v>
       </c>
@@ -7035,11 +7155,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I75" s="177">
+      <c r="I75" s="174">
         <f t="shared" si="10"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J75" s="177">
+      <c r="J75" s="174">
         <f t="shared" si="11"/>
         <v>40500.000000000007</v>
       </c>
@@ -7048,7 +7168,7 @@
         <f t="shared" si="5"/>
         <v>197584.62</v>
       </c>
-      <c r="M75" s="193">
+      <c r="M75" s="190">
         <f t="shared" si="8"/>
         <v>203512.62</v>
       </c>
@@ -7057,8 +7177,8 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A76" s="182">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="179">
         <f t="shared" si="9"/>
         <v>63</v>
       </c>
@@ -7084,11 +7204,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I76" s="177">
+      <c r="I76" s="174">
         <f t="shared" si="10"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J76" s="177">
+      <c r="J76" s="174">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
@@ -7097,7 +7217,7 @@
         <f t="shared" si="5"/>
         <v>168836.63</v>
       </c>
-      <c r="M76" s="193">
+      <c r="M76" s="190">
         <f t="shared" si="8"/>
         <v>173901.63</v>
       </c>
@@ -7106,8 +7226,8 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A77" s="182">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="179">
         <f t="shared" si="9"/>
         <v>64</v>
       </c>
@@ -7133,11 +7253,11 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I77" s="177">
+      <c r="I77" s="174">
         <f t="shared" si="10"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J77" s="177">
+      <c r="J77" s="174">
         <f t="shared" si="11"/>
         <v>24600</v>
       </c>
@@ -7148,7 +7268,7 @@
         <f t="shared" si="5"/>
         <v>173612.64</v>
       </c>
-      <c r="M77" s="193">
+      <c r="M77" s="190">
         <f t="shared" si="8"/>
         <v>178820.64</v>
       </c>
@@ -7157,8 +7277,8 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A78" s="183">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="180">
         <f t="shared" si="9"/>
         <v>65</v>
       </c>
@@ -7172,7 +7292,7 @@
       <c r="E78" s="115">
         <v>880370.65</v>
       </c>
-      <c r="F78" s="201">
+      <c r="F78" s="198">
         <v>99011.93</v>
       </c>
       <c r="G78" s="116">
@@ -7183,11 +7303,11 @@
         <f t="shared" si="4"/>
         <v>23440.761599999998</v>
       </c>
-      <c r="I78" s="178">
+      <c r="I78" s="175">
         <f t="shared" ref="I78:I109" si="15">J$2*D78/100</f>
         <v>99011.925000000003</v>
       </c>
-      <c r="J78" s="178">
+      <c r="J78" s="175">
         <f t="shared" ref="J78:J109" si="16">E$2*D78/100</f>
         <v>24600</v>
       </c>
@@ -7196,7 +7316,7 @@
         <f t="shared" si="5"/>
         <v>928411.65</v>
       </c>
-      <c r="M78" s="194">
+      <c r="M78" s="191">
         <f t="shared" si="8"/>
         <v>956263.65</v>
       </c>
@@ -7205,11 +7325,11 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="O78" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A79" s="182">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="179">
         <f t="shared" si="9"/>
         <v>66</v>
       </c>
@@ -7234,11 +7354,11 @@
         <f t="shared" ref="H79:H116" si="17">IF(G79&gt;0,G79*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="I79" s="177">
+      <c r="I79" s="174">
         <f t="shared" si="15"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J79" s="177">
+      <c r="J79" s="174">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
@@ -7247,7 +7367,7 @@
         <f t="shared" ref="L79:L116" si="18">ROUND(SUM(G79:K79),0) + N79</f>
         <v>196122.66</v>
       </c>
-      <c r="M79" s="193">
+      <c r="M79" s="190">
         <f t="shared" si="8"/>
         <v>202006.66</v>
       </c>
@@ -7256,8 +7376,8 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A80" s="182">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="179">
         <f t="shared" si="9"/>
         <v>67</v>
       </c>
@@ -7282,11 +7402,11 @@
         <f t="shared" si="17"/>
         <v>5038.6499999999987</v>
       </c>
-      <c r="I80" s="177">
+      <c r="I80" s="174">
         <f t="shared" si="15"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J80" s="177">
+      <c r="J80" s="174">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
@@ -7295,7 +7415,7 @@
         <f t="shared" si="18"/>
         <v>341829.67</v>
       </c>
-      <c r="M80" s="193">
+      <c r="M80" s="190">
         <f t="shared" si="8"/>
         <v>352084.67</v>
       </c>
@@ -7304,8 +7424,8 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A81" s="182">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="179">
         <f t="shared" si="9"/>
         <v>68</v>
       </c>
@@ -7330,11 +7450,11 @@
         <f t="shared" si="17"/>
         <v>161132.42039999997</v>
       </c>
-      <c r="I81" s="177">
+      <c r="I81" s="174">
         <f t="shared" si="15"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J81" s="177">
+      <c r="J81" s="174">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
@@ -7343,7 +7463,7 @@
         <f t="shared" si="18"/>
         <v>5708586.6799999997</v>
       </c>
-      <c r="M81" s="193">
+      <c r="M81" s="190">
         <f t="shared" si="8"/>
         <v>5879844.6799999997</v>
       </c>
@@ -7352,8 +7472,8 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A82" s="182">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="179">
         <f t="shared" si="9"/>
         <v>69</v>
       </c>
@@ -7378,11 +7498,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I82" s="177">
+      <c r="I82" s="174">
         <f t="shared" si="15"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J82" s="177">
+      <c r="J82" s="174">
         <f t="shared" si="16"/>
         <v>40500.000000000007</v>
       </c>
@@ -7391,7 +7511,7 @@
         <f t="shared" si="18"/>
         <v>197585.69</v>
       </c>
-      <c r="M82" s="193">
+      <c r="M82" s="190">
         <f t="shared" si="8"/>
         <v>203513.69</v>
       </c>
@@ -7400,8 +7520,8 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A83" s="183">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="180">
         <f t="shared" si="9"/>
         <v>70</v>
       </c>
@@ -7424,11 +7544,11 @@
         <f t="shared" si="17"/>
         <v>4284.1109999999999</v>
       </c>
-      <c r="I83" s="178">
+      <c r="I83" s="175">
         <f t="shared" si="15"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J83" s="178">
+      <c r="J83" s="175">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
@@ -7437,7 +7557,7 @@
         <f t="shared" si="18"/>
         <v>315924.7</v>
       </c>
-      <c r="M83" s="194">
+      <c r="M83" s="191">
         <f t="shared" si="8"/>
         <v>325402.7</v>
       </c>
@@ -7446,11 +7566,11 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="O83" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A84" s="184">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="181">
         <f t="shared" si="9"/>
         <v>71</v>
       </c>
@@ -7476,11 +7596,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I84" s="177">
+      <c r="I84" s="174">
         <f t="shared" si="15"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J84" s="177">
+      <c r="J84" s="174">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
@@ -7489,7 +7609,7 @@
         <f t="shared" si="18"/>
         <v>123612.71</v>
       </c>
-      <c r="M84" s="193">
+      <c r="M84" s="190">
         <f t="shared" si="8"/>
         <v>127320.71</v>
       </c>
@@ -7498,8 +7618,8 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A85" s="182">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" s="179">
         <f t="shared" si="9"/>
         <v>72</v>
       </c>
@@ -7525,11 +7645,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I85" s="177">
+      <c r="I85" s="174">
         <f t="shared" si="15"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J85" s="177">
+      <c r="J85" s="174">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
@@ -7538,7 +7658,7 @@
         <f t="shared" si="18"/>
         <v>123612.72</v>
       </c>
-      <c r="M85" s="193">
+      <c r="M85" s="190">
         <f t="shared" si="8"/>
         <v>127320.72</v>
       </c>
@@ -7547,8 +7667,8 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A86" s="182">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="179">
         <f t="shared" si="9"/>
         <v>73</v>
       </c>
@@ -7571,11 +7691,11 @@
         <f t="shared" si="17"/>
         <v>6060.0218999999997</v>
       </c>
-      <c r="I86" s="177">
+      <c r="I86" s="174">
         <f t="shared" si="15"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J86" s="177">
+      <c r="J86" s="174">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
@@ -7584,7 +7704,7 @@
         <f t="shared" si="18"/>
         <v>410061.73</v>
       </c>
-      <c r="M86" s="193">
+      <c r="M86" s="190">
         <f t="shared" si="8"/>
         <v>422363.73</v>
       </c>
@@ -7593,8 +7713,8 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A87" s="182">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="179">
         <f t="shared" si="9"/>
         <v>74</v>
       </c>
@@ -7617,11 +7737,11 @@
         <f t="shared" si="17"/>
         <v>4602.3821999999991</v>
       </c>
-      <c r="I87" s="177">
+      <c r="I87" s="174">
         <f t="shared" si="15"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J87" s="177">
+      <c r="J87" s="174">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
@@ -7630,7 +7750,7 @@
         <f t="shared" si="18"/>
         <v>326851.74</v>
       </c>
-      <c r="M87" s="193">
+      <c r="M87" s="190">
         <f t="shared" si="8"/>
         <v>336657.74</v>
       </c>
@@ -7639,8 +7759,8 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A88" s="182">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" s="179">
         <f t="shared" si="9"/>
         <v>75</v>
       </c>
@@ -7666,11 +7786,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I88" s="177">
+      <c r="I88" s="174">
         <f t="shared" si="15"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J88" s="177">
+      <c r="J88" s="174">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
@@ -7679,7 +7799,7 @@
         <f t="shared" si="18"/>
         <v>176373.75</v>
       </c>
-      <c r="M88" s="193">
+      <c r="M88" s="190">
         <f t="shared" si="8"/>
         <v>181664.75</v>
       </c>
@@ -7688,8 +7808,8 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A89" s="182">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" s="179">
         <f t="shared" si="9"/>
         <v>76</v>
       </c>
@@ -7715,11 +7835,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I89" s="177">
+      <c r="I89" s="174">
         <f t="shared" si="15"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J89" s="177">
+      <c r="J89" s="174">
         <f t="shared" si="16"/>
         <v>40500.000000000007</v>
       </c>
@@ -7728,7 +7848,7 @@
         <f t="shared" si="18"/>
         <v>203507.76</v>
       </c>
-      <c r="M89" s="193">
+      <c r="M89" s="190">
         <f t="shared" si="8"/>
         <v>209612.76</v>
       </c>
@@ -7737,8 +7857,8 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A90" s="182">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" s="179">
         <f t="shared" si="9"/>
         <v>77</v>
       </c>
@@ -7763,11 +7883,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I90" s="177">
+      <c r="I90" s="174">
         <f t="shared" si="15"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J90" s="177">
+      <c r="J90" s="174">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
@@ -7776,7 +7896,7 @@
         <f t="shared" si="18"/>
         <v>163923.76999999999</v>
       </c>
-      <c r="M90" s="193">
+      <c r="M90" s="190">
         <f t="shared" si="8"/>
         <v>168841.77</v>
       </c>
@@ -7785,44 +7905,44 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A91" s="185">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91" s="182">
         <f t="shared" si="9"/>
         <v>78</v>
       </c>
-      <c r="B91" s="161" t="s">
+      <c r="B91" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="C91" s="162"/>
-      <c r="D91" s="163">
+      <c r="C91" s="159"/>
+      <c r="D91" s="160">
         <v>0.82</v>
       </c>
-      <c r="E91" s="164">
+      <c r="E91" s="161">
         <v>123611.925</v>
       </c>
-      <c r="F91" s="164"/>
-      <c r="G91" s="165">
+      <c r="F91" s="161"/>
+      <c r="G91" s="162">
         <f t="shared" si="14"/>
         <v>123611.925</v>
       </c>
-      <c r="H91" s="165">
+      <c r="H91" s="162">
         <f t="shared" si="17"/>
         <v>3708.3577500000001</v>
       </c>
-      <c r="I91" s="181">
+      <c r="I91" s="178">
         <f t="shared" si="15"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J91" s="181">
+      <c r="J91" s="178">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
-      <c r="K91" s="166"/>
-      <c r="L91" s="167">
+      <c r="K91" s="163"/>
+      <c r="L91" s="164">
         <f t="shared" si="18"/>
         <v>250932.78</v>
       </c>
-      <c r="M91" s="196">
+      <c r="M91" s="193">
         <f t="shared" si="8"/>
         <v>258460.78</v>
       </c>
@@ -7831,8 +7951,8 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A92" s="182">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92" s="179">
         <f t="shared" si="9"/>
         <v>79</v>
       </c>
@@ -7858,11 +7978,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I92" s="177">
+      <c r="I92" s="174">
         <f t="shared" si="15"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J92" s="177">
+      <c r="J92" s="174">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
@@ -7871,7 +7991,7 @@
         <f t="shared" si="18"/>
         <v>123612.79</v>
       </c>
-      <c r="M92" s="193">
+      <c r="M92" s="190">
         <f t="shared" si="8"/>
         <v>127320.79</v>
       </c>
@@ -7880,8 +8000,8 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A93" s="182">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93" s="179">
         <f t="shared" si="9"/>
         <v>80</v>
       </c>
@@ -7906,11 +8026,11 @@
         <f t="shared" si="17"/>
         <v>5689.83</v>
       </c>
-      <c r="I93" s="177">
+      <c r="I93" s="174">
         <f t="shared" si="15"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J93" s="177">
+      <c r="J93" s="174">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
@@ -7919,7 +8039,7 @@
         <f t="shared" si="18"/>
         <v>397351.8</v>
       </c>
-      <c r="M93" s="193">
+      <c r="M93" s="190">
         <f t="shared" si="8"/>
         <v>409272.8</v>
       </c>
@@ -7928,8 +8048,8 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A94" s="183">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94" s="180">
         <f t="shared" si="9"/>
         <v>81</v>
       </c>
@@ -7954,11 +8074,11 @@
         <f t="shared" si="17"/>
         <v>11661.774300000001</v>
       </c>
-      <c r="I94" s="178">
+      <c r="I94" s="175">
         <f t="shared" si="15"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J94" s="178">
+      <c r="J94" s="175">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
@@ -7967,7 +8087,7 @@
         <f t="shared" si="18"/>
         <v>569223.81000000006</v>
       </c>
-      <c r="M94" s="194">
+      <c r="M94" s="191">
         <f t="shared" si="8"/>
         <v>586300.81000000006</v>
       </c>
@@ -7976,11 +8096,11 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="O94" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A95" s="182">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A95" s="179">
         <f t="shared" si="9"/>
         <v>82</v>
       </c>
@@ -8006,11 +8126,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I95" s="177">
+      <c r="I95" s="174">
         <f t="shared" si="15"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J95" s="177">
+      <c r="J95" s="174">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
@@ -8019,7 +8139,7 @@
         <f t="shared" si="18"/>
         <v>176373.82</v>
       </c>
-      <c r="M95" s="193">
+      <c r="M95" s="190">
         <f t="shared" si="8"/>
         <v>181664.82</v>
       </c>
@@ -8028,8 +8148,8 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A96" s="184">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96" s="181">
         <f t="shared" si="9"/>
         <v>83</v>
       </c>
@@ -8055,11 +8175,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I96" s="177">
+      <c r="I96" s="174">
         <f t="shared" si="15"/>
         <v>163007.43750000003</v>
       </c>
-      <c r="J96" s="177">
+      <c r="J96" s="174">
         <f t="shared" si="16"/>
         <v>40500.000000000007</v>
       </c>
@@ -8068,7 +8188,7 @@
         <f t="shared" si="18"/>
         <v>-74477.17</v>
       </c>
-      <c r="M96" s="193">
+      <c r="M96" s="190">
         <f t="shared" si="8"/>
         <v>-76711.17</v>
       </c>
@@ -8077,8 +8197,8 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A97" s="184">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" s="181">
         <f t="shared" si="9"/>
         <v>84</v>
       </c>
@@ -8104,11 +8224,11 @@
         <f t="shared" si="17"/>
         <v>245.01000000000172</v>
       </c>
-      <c r="I97" s="177">
+      <c r="I97" s="174">
         <f t="shared" si="15"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J97" s="177">
+      <c r="J97" s="174">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
@@ -8117,7 +8237,7 @@
         <f t="shared" si="18"/>
         <v>177248.84</v>
       </c>
-      <c r="M97" s="193">
+      <c r="M97" s="190">
         <f t="shared" si="8"/>
         <v>182565.84</v>
       </c>
@@ -8126,8 +8246,8 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A98" s="182">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" s="179">
         <f t="shared" si="9"/>
         <v>85</v>
       </c>
@@ -8153,11 +8273,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I98" s="177">
+      <c r="I98" s="174">
         <f t="shared" si="15"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J98" s="177">
+      <c r="J98" s="174">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
@@ -8166,7 +8286,7 @@
         <f t="shared" si="18"/>
         <v>123612.85</v>
       </c>
-      <c r="M98" s="193">
+      <c r="M98" s="190">
         <f t="shared" si="8"/>
         <v>127320.85</v>
       </c>
@@ -8175,8 +8295,8 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A99" s="182">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" s="179">
         <f t="shared" si="9"/>
         <v>86</v>
       </c>
@@ -8202,11 +8322,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I99" s="177">
+      <c r="I99" s="174">
         <f t="shared" si="15"/>
         <v>99011.925000000003</v>
       </c>
-      <c r="J99" s="177">
+      <c r="J99" s="174">
         <f t="shared" si="16"/>
         <v>24600</v>
       </c>
@@ -8215,7 +8335,7 @@
         <f t="shared" si="18"/>
         <v>123612.86</v>
       </c>
-      <c r="M99" s="193">
+      <c r="M99" s="190">
         <f t="shared" ref="M99:M116" si="21">ROUND(L99*3%,0) + L99</f>
         <v>127320.86</v>
       </c>
@@ -8224,8 +8344,8 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A100" s="182">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" s="179">
         <f t="shared" ref="A100:A116" si="22">A99+1</f>
         <v>87</v>
       </c>
@@ -8250,11 +8370,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I100" s="177">
+      <c r="I100" s="174">
         <f t="shared" si="15"/>
         <v>161799.97500000001</v>
       </c>
-      <c r="J100" s="177">
+      <c r="J100" s="174">
         <f t="shared" si="16"/>
         <v>40200.000000000007</v>
       </c>
@@ -8263,7 +8383,7 @@
         <f t="shared" si="18"/>
         <v>196122.87</v>
       </c>
-      <c r="M100" s="193">
+      <c r="M100" s="190">
         <f t="shared" si="21"/>
         <v>202006.87</v>
       </c>
@@ -8272,8 +8392,8 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A101" s="182">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" s="179">
         <f t="shared" si="22"/>
         <v>88</v>
       </c>
@@ -8299,11 +8419,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I101" s="177">
+      <c r="I101" s="174">
         <f t="shared" si="15"/>
         <v>135235.80000000002</v>
       </c>
-      <c r="J101" s="177">
+      <c r="J101" s="174">
         <f t="shared" si="16"/>
         <v>33600.000000000007</v>
       </c>
@@ -8312,7 +8432,7 @@
         <f t="shared" si="18"/>
         <v>168836.88</v>
       </c>
-      <c r="M101" s="193">
+      <c r="M101" s="190">
         <f t="shared" si="21"/>
         <v>173901.88</v>
       </c>
@@ -8321,8 +8441,8 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A102" s="182">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" s="179">
         <f t="shared" si="22"/>
         <v>89</v>
       </c>
@@ -8348,11 +8468,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I102" s="177">
+      <c r="I102" s="174">
         <f t="shared" si="15"/>
         <v>141273.11249999999</v>
       </c>
-      <c r="J102" s="177">
+      <c r="J102" s="174">
         <f t="shared" si="16"/>
         <v>35100</v>
       </c>
@@ -8361,7 +8481,7 @@
         <f t="shared" si="18"/>
         <v>176373.89</v>
       </c>
-      <c r="M102" s="193">
+      <c r="M102" s="190">
         <f t="shared" si="21"/>
         <v>181664.89</v>
       </c>
@@ -8370,8 +8490,8 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A103" s="182">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" s="179">
         <f t="shared" si="22"/>
         <v>90</v>
       </c>
@@ -8396,11 +8516,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I103" s="177">
+      <c r="I103" s="174">
         <f t="shared" si="15"/>
         <v>12074.625</v>
       </c>
-      <c r="J103" s="177">
+      <c r="J103" s="174">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
@@ -8409,7 +8529,7 @@
         <f t="shared" si="18"/>
         <v>14636.9</v>
       </c>
-      <c r="M103" s="193">
+      <c r="M103" s="190">
         <f t="shared" si="21"/>
         <v>15075.9</v>
       </c>
@@ -8418,8 +8538,8 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A104" s="182">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" s="179">
         <f t="shared" si="22"/>
         <v>91</v>
       </c>
@@ -8444,11 +8564,11 @@
         <f t="shared" si="17"/>
         <v>466.2</v>
       </c>
-      <c r="I104" s="177">
+      <c r="I104" s="174">
         <f t="shared" si="15"/>
         <v>12074.625</v>
       </c>
-      <c r="J104" s="177">
+      <c r="J104" s="174">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
@@ -8457,7 +8577,7 @@
         <f t="shared" si="18"/>
         <v>31081.91</v>
       </c>
-      <c r="M104" s="193">
+      <c r="M104" s="190">
         <f t="shared" si="21"/>
         <v>32013.91</v>
       </c>
@@ -8466,8 +8586,8 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A105" s="182">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" s="179">
         <f t="shared" si="22"/>
         <v>92</v>
       </c>
@@ -8493,11 +8613,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I105" s="177">
+      <c r="I105" s="174">
         <f t="shared" si="15"/>
         <v>12074.625</v>
       </c>
-      <c r="J105" s="177">
+      <c r="J105" s="174">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
@@ -8506,7 +8626,7 @@
         <f t="shared" si="18"/>
         <v>15075.92</v>
       </c>
-      <c r="M105" s="193">
+      <c r="M105" s="190">
         <f t="shared" si="21"/>
         <v>15527.92</v>
       </c>
@@ -8515,8 +8635,8 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A106" s="184">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" s="181">
         <f t="shared" si="22"/>
         <v>93</v>
       </c>
@@ -8542,11 +8662,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I106" s="179">
+      <c r="I106" s="176">
         <f t="shared" si="15"/>
         <v>12074.625</v>
       </c>
-      <c r="J106" s="179">
+      <c r="J106" s="176">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
@@ -8555,7 +8675,7 @@
         <f t="shared" si="18"/>
         <v>15075.93</v>
       </c>
-      <c r="M106" s="195">
+      <c r="M106" s="192">
         <f t="shared" si="21"/>
         <v>15527.93</v>
       </c>
@@ -8564,8 +8684,8 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A107" s="184">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" s="181">
         <f t="shared" si="22"/>
         <v>94</v>
       </c>
@@ -8591,11 +8711,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I107" s="179">
+      <c r="I107" s="176">
         <f>J$2*D107/100</f>
         <v>12074.625</v>
       </c>
-      <c r="J107" s="179">
+      <c r="J107" s="176">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
@@ -8604,7 +8724,7 @@
         <f t="shared" si="18"/>
         <v>15075.94</v>
       </c>
-      <c r="M107" s="195">
+      <c r="M107" s="192">
         <f t="shared" si="21"/>
         <v>15527.94</v>
       </c>
@@ -8613,8 +8733,8 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="184">
+    <row r="108" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="181">
         <f t="shared" si="22"/>
         <v>95</v>
       </c>
@@ -8639,11 +8759,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I108" s="179">
+      <c r="I108" s="176">
         <f t="shared" si="15"/>
         <v>12074.625</v>
       </c>
-      <c r="J108" s="179">
+      <c r="J108" s="176">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
@@ -8652,7 +8772,7 @@
         <f t="shared" si="18"/>
         <v>14623.95</v>
       </c>
-      <c r="M108" s="195">
+      <c r="M108" s="192">
         <f t="shared" si="21"/>
         <v>15062.95</v>
       </c>
@@ -8661,8 +8781,8 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A109" s="184">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A109" s="181">
         <f t="shared" si="22"/>
         <v>96</v>
       </c>
@@ -8688,11 +8808,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I109" s="179">
+      <c r="I109" s="176">
         <f t="shared" si="15"/>
         <v>12074.625</v>
       </c>
-      <c r="J109" s="179">
+      <c r="J109" s="176">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
@@ -8701,7 +8821,7 @@
         <f t="shared" si="18"/>
         <v>15075.96</v>
       </c>
-      <c r="M109" s="195">
+      <c r="M109" s="192">
         <f t="shared" si="21"/>
         <v>15527.96</v>
       </c>
@@ -8713,8 +8833,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A110" s="184">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A110" s="181">
         <f t="shared" si="22"/>
         <v>97</v>
       </c>
@@ -8740,11 +8860,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I110" s="179">
+      <c r="I110" s="176">
         <f t="shared" ref="I110:I116" si="23">J$2*D110/100</f>
         <v>12074.625</v>
       </c>
-      <c r="J110" s="179">
+      <c r="J110" s="176">
         <f t="shared" ref="J110:J116" si="24">E$2*D110/100</f>
         <v>3000</v>
       </c>
@@ -8753,7 +8873,7 @@
         <f t="shared" si="18"/>
         <v>15075.97</v>
       </c>
-      <c r="M110" s="195">
+      <c r="M110" s="192">
         <f t="shared" si="21"/>
         <v>15527.97</v>
       </c>
@@ -8762,8 +8882,8 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A111" s="184">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A111" s="181">
         <f t="shared" si="22"/>
         <v>98</v>
       </c>
@@ -8789,11 +8909,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I111" s="179">
+      <c r="I111" s="176">
         <f t="shared" si="23"/>
         <v>12074.625</v>
       </c>
-      <c r="J111" s="179">
+      <c r="J111" s="176">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
@@ -8802,7 +8922,7 @@
         <f t="shared" si="18"/>
         <v>15075.98</v>
       </c>
-      <c r="M111" s="195">
+      <c r="M111" s="192">
         <f t="shared" si="21"/>
         <v>15527.98</v>
       </c>
@@ -8811,8 +8931,8 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A112" s="184">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A112" s="181">
         <f t="shared" si="22"/>
         <v>99</v>
       </c>
@@ -8837,11 +8957,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I112" s="179">
+      <c r="I112" s="176">
         <f t="shared" si="23"/>
         <v>12074.625</v>
       </c>
-      <c r="J112" s="179">
+      <c r="J112" s="176">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
@@ -8850,7 +8970,7 @@
         <f t="shared" si="18"/>
         <v>14636.99</v>
       </c>
-      <c r="M112" s="195">
+      <c r="M112" s="192">
         <f t="shared" si="21"/>
         <v>15075.99</v>
       </c>
@@ -8859,8 +8979,8 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A113" s="184">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A113" s="181">
         <f t="shared" si="22"/>
         <v>100</v>
       </c>
@@ -8886,11 +9006,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I113" s="179">
+      <c r="I113" s="176">
         <f t="shared" si="23"/>
         <v>12074.625</v>
       </c>
-      <c r="J113" s="179">
+      <c r="J113" s="176">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
@@ -8899,7 +9019,7 @@
         <f t="shared" si="18"/>
         <v>15076</v>
       </c>
-      <c r="M113" s="195">
+      <c r="M113" s="192">
         <f t="shared" si="21"/>
         <v>15528</v>
       </c>
@@ -8908,8 +9028,8 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A114" s="184">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A114" s="181">
         <f t="shared" si="22"/>
         <v>101</v>
       </c>
@@ -8935,11 +9055,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I114" s="179">
+      <c r="I114" s="176">
         <f t="shared" si="23"/>
         <v>12074.625</v>
       </c>
-      <c r="J114" s="179">
+      <c r="J114" s="176">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
@@ -8948,7 +9068,7 @@
         <f t="shared" si="18"/>
         <v>15076.01</v>
       </c>
-      <c r="M114" s="195">
+      <c r="M114" s="192">
         <f t="shared" si="21"/>
         <v>15528.01</v>
       </c>
@@ -8957,8 +9077,8 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A115" s="184">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A115" s="181">
         <f t="shared" si="22"/>
         <v>102</v>
       </c>
@@ -8984,11 +9104,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I115" s="179">
+      <c r="I115" s="176">
         <f t="shared" si="23"/>
         <v>12074.625</v>
       </c>
-      <c r="J115" s="179">
+      <c r="J115" s="176">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
@@ -8997,7 +9117,7 @@
         <f t="shared" si="18"/>
         <v>15076.02</v>
       </c>
-      <c r="M115" s="195">
+      <c r="M115" s="192">
         <f t="shared" si="21"/>
         <v>15528.02</v>
       </c>
@@ -9006,8 +9126,8 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A116" s="184">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A116" s="181">
         <f t="shared" si="22"/>
         <v>103</v>
       </c>
@@ -9033,11 +9153,11 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="I116" s="179">
+      <c r="I116" s="176">
         <f t="shared" si="23"/>
         <v>12074.625</v>
       </c>
-      <c r="J116" s="179">
+      <c r="J116" s="176">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
@@ -9046,7 +9166,7 @@
         <f t="shared" si="18"/>
         <v>15076.03</v>
       </c>
-      <c r="M116" s="195">
+      <c r="M116" s="192">
         <f t="shared" si="21"/>
         <v>15528.03</v>
       </c>
@@ -9055,8 +9175,8 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A117" s="184"/>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A117" s="181"/>
       <c r="B117" s="142"/>
       <c r="C117" s="148"/>
       <c r="D117" s="144"/>
@@ -9064,142 +9184,143 @@
       <c r="F117" s="100"/>
       <c r="G117" s="145"/>
       <c r="H117" s="145"/>
-      <c r="I117" s="179"/>
-      <c r="J117" s="179"/>
+      <c r="I117" s="176"/>
+      <c r="J117" s="176"/>
       <c r="K117" s="146"/>
       <c r="L117" s="147"/>
-      <c r="M117" s="195"/>
+      <c r="M117" s="192"/>
       <c r="N117" s="63"/>
     </row>
-    <row r="118" spans="1:14" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="186"/>
-      <c r="B118" s="187"/>
-      <c r="C118" s="187"/>
-      <c r="D118" s="188">
+    <row r="118" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="183"/>
+      <c r="B118" s="184"/>
+      <c r="C118" s="184"/>
+      <c r="D118" s="185">
         <f t="shared" ref="D118:M118" si="25">SUM(D14:D117)</f>
         <v>100.15999999999993</v>
       </c>
-      <c r="E118" s="189">
+      <c r="E118" s="186">
         <f t="shared" si="25"/>
         <v>32859172.487500001</v>
       </c>
-      <c r="F118" s="190">
+      <c r="F118" s="187">
         <f>SUM(F14:F117)</f>
         <v>14531886.810000001</v>
       </c>
-      <c r="G118" s="190">
+      <c r="G118" s="187">
         <f t="shared" si="25"/>
         <v>18327285.677499998</v>
       </c>
-      <c r="H118" s="190">
+      <c r="H118" s="187">
         <f t="shared" si="25"/>
         <v>560995.356225</v>
       </c>
-      <c r="I118" s="191">
+      <c r="I118" s="188">
         <f t="shared" si="25"/>
         <v>12093944.400000006</v>
       </c>
-      <c r="J118" s="190">
+      <c r="J118" s="187">
         <f t="shared" si="25"/>
         <v>3004800</v>
       </c>
-      <c r="K118" s="192"/>
-      <c r="L118" s="200">
+      <c r="K118" s="189"/>
+      <c r="L118" s="197">
         <f t="shared" si="25"/>
         <v>34037080.560000002</v>
       </c>
-      <c r="M118" s="197">
+      <c r="M118" s="194">
         <f t="shared" si="25"/>
         <v>35058186.560000002</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="106"/>
       <c r="C119" s="106"/>
     </row>
-    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="217" t="s">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="230" t="s">
         <v>106</v>
       </c>
-      <c r="C121" s="217"/>
-      <c r="D121" s="217"/>
-      <c r="E121" s="217"/>
-      <c r="F121" s="217"/>
-      <c r="G121" s="217"/>
-      <c r="H121" s="217"/>
-      <c r="I121" s="217"/>
-      <c r="J121" s="217"/>
-      <c r="K121" s="217"/>
-      <c r="L121" s="217"/>
-    </row>
-    <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B122" s="217"/>
-      <c r="C122" s="217"/>
-      <c r="D122" s="217"/>
-      <c r="E122" s="217"/>
-      <c r="F122" s="217"/>
-      <c r="G122" s="217"/>
-      <c r="H122" s="217"/>
-      <c r="I122" s="217"/>
-      <c r="J122" s="217"/>
-      <c r="K122" s="217"/>
-      <c r="L122" s="217"/>
-    </row>
-    <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B123" s="217"/>
-      <c r="C123" s="217"/>
-      <c r="D123" s="217"/>
-      <c r="E123" s="217"/>
-      <c r="F123" s="217"/>
-      <c r="G123" s="217"/>
-      <c r="H123" s="217"/>
-      <c r="I123" s="217"/>
-      <c r="J123" s="217"/>
-      <c r="K123" s="217"/>
-      <c r="L123" s="217"/>
-    </row>
-    <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="217"/>
-      <c r="C124" s="217"/>
-      <c r="D124" s="217"/>
-      <c r="E124" s="217"/>
-      <c r="F124" s="217"/>
-      <c r="G124" s="217"/>
-      <c r="H124" s="217"/>
-      <c r="I124" s="217"/>
-      <c r="J124" s="217"/>
-      <c r="K124" s="217"/>
-      <c r="L124" s="217"/>
-    </row>
-    <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="217"/>
-      <c r="C125" s="217"/>
-      <c r="D125" s="217"/>
-      <c r="E125" s="217"/>
-      <c r="F125" s="217"/>
-      <c r="G125" s="217"/>
-      <c r="H125" s="217"/>
-      <c r="I125" s="217"/>
-      <c r="J125" s="217"/>
-      <c r="K125" s="217"/>
-      <c r="L125" s="217"/>
-    </row>
-    <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="217"/>
-      <c r="C126" s="217"/>
-      <c r="D126" s="217"/>
-      <c r="E126" s="217"/>
-      <c r="F126" s="217"/>
-      <c r="G126" s="217"/>
-      <c r="H126" s="217"/>
-      <c r="I126" s="217"/>
-      <c r="J126" s="217"/>
-      <c r="K126" s="217"/>
-      <c r="L126" s="217"/>
+      <c r="C121" s="230"/>
+      <c r="D121" s="230"/>
+      <c r="E121" s="230"/>
+      <c r="F121" s="230"/>
+      <c r="G121" s="230"/>
+      <c r="H121" s="230"/>
+      <c r="I121" s="230"/>
+      <c r="J121" s="230"/>
+      <c r="K121" s="230"/>
+      <c r="L121" s="230"/>
+    </row>
+    <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="230"/>
+      <c r="C122" s="230"/>
+      <c r="D122" s="230"/>
+      <c r="E122" s="230"/>
+      <c r="F122" s="230"/>
+      <c r="G122" s="230"/>
+      <c r="H122" s="230"/>
+      <c r="I122" s="230"/>
+      <c r="J122" s="230"/>
+      <c r="K122" s="230"/>
+      <c r="L122" s="230"/>
+    </row>
+    <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="230"/>
+      <c r="C123" s="230"/>
+      <c r="D123" s="230"/>
+      <c r="E123" s="230"/>
+      <c r="F123" s="230"/>
+      <c r="G123" s="230"/>
+      <c r="H123" s="230"/>
+      <c r="I123" s="230"/>
+      <c r="J123" s="230"/>
+      <c r="K123" s="230"/>
+      <c r="L123" s="230"/>
+    </row>
+    <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="230"/>
+      <c r="C124" s="230"/>
+      <c r="D124" s="230"/>
+      <c r="E124" s="230"/>
+      <c r="F124" s="230"/>
+      <c r="G124" s="230"/>
+      <c r="H124" s="230"/>
+      <c r="I124" s="230"/>
+      <c r="J124" s="230"/>
+      <c r="K124" s="230"/>
+      <c r="L124" s="230"/>
+    </row>
+    <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="230"/>
+      <c r="C125" s="230"/>
+      <c r="D125" s="230"/>
+      <c r="E125" s="230"/>
+      <c r="F125" s="230"/>
+      <c r="G125" s="230"/>
+      <c r="H125" s="230"/>
+      <c r="I125" s="230"/>
+      <c r="J125" s="230"/>
+      <c r="K125" s="230"/>
+      <c r="L125" s="230"/>
+    </row>
+    <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="230"/>
+      <c r="C126" s="230"/>
+      <c r="D126" s="230"/>
+      <c r="E126" s="230"/>
+      <c r="F126" s="230"/>
+      <c r="G126" s="230"/>
+      <c r="H126" s="230"/>
+      <c r="I126" s="230"/>
+      <c r="J126" s="230"/>
+      <c r="K126" s="230"/>
+      <c r="L126" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="J12:J13"/>
@@ -9218,7 +9339,6 @@
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A11:M11"/>
-    <mergeCell ref="E2:F2"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9227,213 +9347,546 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="B5:Q25"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="C4:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="248" t="s">
-        <v>184</v>
-      </c>
-      <c r="C5" s="248"/>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="L5" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="M5" s="82" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B8" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="153" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="153"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="153"/>
-      <c r="L12" s="153"/>
-      <c r="M12" s="153"/>
-      <c r="N12" s="153"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="153" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="154">
-        <v>194996.59</v>
-      </c>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="153"/>
-      <c r="G13" s="153"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="153"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="153"/>
-      <c r="L13" s="153"/>
-      <c r="M13" s="153"/>
-      <c r="N13" s="153"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B14" s="153" t="s">
-        <v>188</v>
-      </c>
-      <c r="C14" s="154">
-        <v>15075.93</v>
-      </c>
-      <c r="D14" s="153"/>
-      <c r="E14" s="153"/>
-      <c r="F14" s="153"/>
-      <c r="G14" s="153"/>
-      <c r="H14" s="153"/>
-      <c r="I14" s="153"/>
-      <c r="J14" s="153"/>
-      <c r="K14" s="153"/>
-      <c r="L14" s="153"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="153"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="153" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="154">
-        <v>15076.01</v>
-      </c>
-      <c r="D15" s="153"/>
-      <c r="E15" s="153"/>
-      <c r="F15" s="153"/>
-      <c r="G15" s="153"/>
-      <c r="H15" s="153"/>
-      <c r="I15" s="153"/>
-      <c r="J15" s="153"/>
-      <c r="K15" s="153"/>
-      <c r="L15" s="153"/>
-      <c r="M15" s="153"/>
-      <c r="N15" s="153"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="153"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="153"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="153"/>
-      <c r="G16" s="153"/>
-      <c r="H16" s="153"/>
-      <c r="I16" s="153"/>
-      <c r="J16" s="153"/>
-      <c r="K16" s="153"/>
-      <c r="L16" s="153"/>
-      <c r="M16" s="153"/>
-      <c r="N16" s="153"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B19" s="23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B22" s="155" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" s="155"/>
-    </row>
-    <row r="25" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="249" t="s">
-        <v>193</v>
-      </c>
-      <c r="C25" s="249"/>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="249"/>
-      <c r="I25" s="249"/>
-      <c r="J25" s="249"/>
-      <c r="K25" s="249"/>
-      <c r="L25" s="249"/>
-      <c r="M25" s="249"/>
-      <c r="N25" s="249"/>
-      <c r="O25" s="249"/>
-      <c r="P25" s="249"/>
-      <c r="Q25" s="249"/>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C4" s="204" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4895585-CAB1-4A86-BA25-20A34A9B436A}">
+  <dimension ref="C4:O21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" customWidth="1"/>
+    <col min="13" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C4" s="259" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" s="259"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="199" t="s">
+        <v>258</v>
+      </c>
+      <c r="H4" t="s">
+        <v>259</v>
+      </c>
+      <c r="J4" s="261" t="s">
+        <v>261</v>
+      </c>
+      <c r="K4" s="261"/>
+    </row>
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C5" s="260">
+        <v>168835.53000000003</v>
+      </c>
+      <c r="D5" s="260"/>
+      <c r="E5" s="202"/>
+      <c r="F5" s="200">
+        <f>C5</f>
+        <v>168835.53000000003</v>
+      </c>
+      <c r="H5" s="80">
+        <v>0</v>
+      </c>
+      <c r="J5" s="262">
+        <f>F5</f>
+        <v>168835.53000000003</v>
+      </c>
+      <c r="K5" s="262"/>
+    </row>
+    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="M7" s="265" t="s">
+        <v>263</v>
+      </c>
+      <c r="N7" s="265"/>
+      <c r="O7" s="265"/>
+    </row>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F8" s="199" t="s">
+        <v>258</v>
+      </c>
+      <c r="H8" t="s">
+        <v>259</v>
+      </c>
+      <c r="J8" s="261" t="s">
+        <v>262</v>
+      </c>
+      <c r="K8" s="261"/>
+      <c r="M8" s="265"/>
+      <c r="N8" s="265"/>
+      <c r="O8" s="265"/>
+    </row>
+    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C9" s="260">
+        <v>168836.53</v>
+      </c>
+      <c r="D9" s="260"/>
+      <c r="F9" s="80">
+        <v>0</v>
+      </c>
+      <c r="H9" s="80">
+        <f>C9-F9</f>
+        <v>168836.53</v>
+      </c>
+      <c r="J9" s="260">
+        <f>33600+135235.8</f>
+        <v>168835.8</v>
+      </c>
+      <c r="K9" s="260"/>
+      <c r="M9" s="264">
+        <v>300737.53000000003</v>
+      </c>
+      <c r="N9" s="264"/>
+      <c r="O9" s="264"/>
+    </row>
+    <row r="10" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="202"/>
+      <c r="D10" s="202"/>
+      <c r="F10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="J10" s="202"/>
+      <c r="K10" s="202"/>
+      <c r="M10" s="203"/>
+      <c r="N10" s="203"/>
+      <c r="O10" s="203"/>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="M11" s="269" t="s">
+        <v>263</v>
+      </c>
+      <c r="N11" s="270"/>
+      <c r="O11" s="271"/>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F12" s="199" t="s">
+        <v>258</v>
+      </c>
+      <c r="H12" t="s">
+        <v>259</v>
+      </c>
+      <c r="J12" s="261" t="s">
+        <v>265</v>
+      </c>
+      <c r="K12" s="261"/>
+      <c r="M12" s="272"/>
+      <c r="N12" s="273"/>
+      <c r="O12" s="274"/>
+    </row>
+    <row r="13" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="260">
+        <f>M9</f>
+        <v>300737.53000000003</v>
+      </c>
+      <c r="D13" s="260"/>
+      <c r="F13" s="80">
+        <v>98556.53</v>
+      </c>
+      <c r="H13" s="80">
+        <f>C13-F13</f>
+        <v>202181.00000000003</v>
+      </c>
+      <c r="J13" s="260">
+        <f>33600+135235.8</f>
+        <v>168835.8</v>
+      </c>
+      <c r="K13" s="260"/>
+      <c r="M13" s="266">
+        <f>J13+H13-0.27</f>
+        <v>371016.53</v>
+      </c>
+      <c r="N13" s="267"/>
+      <c r="O13" s="268"/>
+    </row>
+    <row r="15" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C15" s="263" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="263"/>
+      <c r="E15" s="263"/>
+      <c r="F15" s="263"/>
+      <c r="G15" s="263"/>
+      <c r="H15" s="263"/>
+      <c r="I15" s="263"/>
+      <c r="J15" s="263"/>
+      <c r="K15" s="263"/>
+      <c r="L15" s="263"/>
+      <c r="M15" s="263"/>
+      <c r="N15" s="263"/>
+      <c r="O15" s="263"/>
+    </row>
+    <row r="16" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C16" s="263"/>
+      <c r="D16" s="263"/>
+      <c r="E16" s="263"/>
+      <c r="F16" s="263"/>
+      <c r="G16" s="263"/>
+      <c r="H16" s="263"/>
+      <c r="I16" s="263"/>
+      <c r="J16" s="263"/>
+      <c r="K16" s="263"/>
+      <c r="L16" s="263"/>
+      <c r="M16" s="263"/>
+      <c r="N16" s="263"/>
+      <c r="O16" s="263"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C17" s="263"/>
+      <c r="D17" s="263"/>
+      <c r="E17" s="263"/>
+      <c r="F17" s="263"/>
+      <c r="G17" s="263"/>
+      <c r="H17" s="263"/>
+      <c r="I17" s="263"/>
+      <c r="J17" s="263"/>
+      <c r="K17" s="263"/>
+      <c r="L17" s="263"/>
+      <c r="M17" s="263"/>
+      <c r="N17" s="263"/>
+      <c r="O17" s="263"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C18" s="263"/>
+      <c r="D18" s="263"/>
+      <c r="E18" s="263"/>
+      <c r="F18" s="263"/>
+      <c r="G18" s="263"/>
+      <c r="H18" s="263"/>
+      <c r="I18" s="263"/>
+      <c r="J18" s="263"/>
+      <c r="K18" s="263"/>
+      <c r="L18" s="263"/>
+      <c r="M18" s="263"/>
+      <c r="N18" s="263"/>
+      <c r="O18" s="263"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C19" s="263"/>
+      <c r="D19" s="263"/>
+      <c r="E19" s="263"/>
+      <c r="F19" s="263"/>
+      <c r="G19" s="263"/>
+      <c r="H19" s="263"/>
+      <c r="I19" s="263"/>
+      <c r="J19" s="263"/>
+      <c r="K19" s="263"/>
+      <c r="L19" s="263"/>
+      <c r="M19" s="263"/>
+      <c r="N19" s="263"/>
+      <c r="O19" s="263"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C20" s="263"/>
+      <c r="D20" s="263"/>
+      <c r="E20" s="263"/>
+      <c r="F20" s="263"/>
+      <c r="G20" s="263"/>
+      <c r="H20" s="263"/>
+      <c r="I20" s="263"/>
+      <c r="J20" s="263"/>
+      <c r="K20" s="263"/>
+      <c r="L20" s="263"/>
+      <c r="M20" s="263"/>
+      <c r="N20" s="263"/>
+      <c r="O20" s="263"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C21" s="263"/>
+      <c r="D21" s="263"/>
+      <c r="E21" s="263"/>
+      <c r="F21" s="263"/>
+      <c r="G21" s="263"/>
+      <c r="H21" s="263"/>
+      <c r="I21" s="263"/>
+      <c r="J21" s="263"/>
+      <c r="K21" s="263"/>
+      <c r="L21" s="263"/>
+      <c r="M21" s="263"/>
+      <c r="N21" s="263"/>
+      <c r="O21" s="263"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="C15:O21"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M7:O8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M11:O12"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J8:K8"/>
+  </mergeCells>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="3" scale="125" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DC61AA-F548-49A9-A9B8-49FB942F95D7}">
+  <dimension ref="C1:K18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="275" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="276"/>
+      <c r="E2" s="276"/>
+      <c r="F2" s="276"/>
+      <c r="G2" s="276"/>
+      <c r="H2" s="276"/>
+      <c r="I2" s="277"/>
+    </row>
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C3" s="207" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="D4" s="208" t="s">
+        <v>258</v>
+      </c>
+      <c r="E4" s="208" t="s">
+        <v>269</v>
+      </c>
+      <c r="F4" s="208" t="s">
+        <v>271</v>
+      </c>
+      <c r="G4" s="210" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" s="210" t="s">
+        <v>273</v>
+      </c>
+      <c r="I4" s="210" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C5" s="211">
+        <v>598682.42000000004</v>
+      </c>
+      <c r="D5" s="209">
+        <v>150000.42000000001</v>
+      </c>
+      <c r="E5" s="209">
+        <v>448682</v>
+      </c>
+      <c r="F5" s="209">
+        <v>13460.46</v>
+      </c>
+      <c r="G5" s="209">
+        <v>135235.80000000002</v>
+      </c>
+      <c r="H5" s="209">
+        <v>33600.000000000007</v>
+      </c>
+      <c r="I5" s="209">
+        <v>630978.42000000004</v>
+      </c>
+      <c r="K5" s="63">
+        <f>E5+F5+G5+H5</f>
+        <v>630978.26</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="207" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C8" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="208" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="208" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="208" t="s">
+        <v>271</v>
+      </c>
+      <c r="G8" s="210" t="s">
+        <v>272</v>
+      </c>
+      <c r="H8" s="210" t="s">
+        <v>273</v>
+      </c>
+      <c r="I8" s="210" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C9" s="211">
+        <v>630978.42000000004</v>
+      </c>
+      <c r="D9" s="209">
+        <v>0</v>
+      </c>
+      <c r="E9" s="209">
+        <v>630978.42000000004</v>
+      </c>
+      <c r="F9" s="209">
+        <v>18929.352600000002</v>
+      </c>
+      <c r="G9" s="209">
+        <v>135235.80000000002</v>
+      </c>
+      <c r="H9" s="209">
+        <v>33600.000000000007</v>
+      </c>
+      <c r="I9" s="209">
+        <v>818744.42</v>
+      </c>
+      <c r="K9" s="63">
+        <f>E9+F9+G9+H9</f>
+        <v>818743.57260000007</v>
+      </c>
+    </row>
+    <row r="11" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C11" s="207" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="3:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C12" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="208" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" s="208" t="s">
+        <v>269</v>
+      </c>
+      <c r="F12" s="208" t="s">
+        <v>271</v>
+      </c>
+      <c r="G12" s="210" t="s">
+        <v>272</v>
+      </c>
+      <c r="H12" s="210" t="s">
+        <v>273</v>
+      </c>
+      <c r="I12" s="210" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C13" s="211">
+        <f>I9</f>
+        <v>818744.42</v>
+      </c>
+      <c r="D13" s="209">
+        <v>0</v>
+      </c>
+      <c r="E13" s="209">
+        <v>818744.42</v>
+      </c>
+      <c r="F13" s="209"/>
+      <c r="G13" s="209">
+        <v>135235.80000000002</v>
+      </c>
+      <c r="H13" s="209">
+        <v>33600.000000000007</v>
+      </c>
+      <c r="I13" s="212">
+        <v>1012143.42</v>
+      </c>
+      <c r="K13" s="63">
+        <f>E13+F13+G13+H13</f>
+        <v>987580.22000000009</v>
+      </c>
+    </row>
+    <row r="14" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C15" s="278" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="279"/>
+      <c r="E15" s="279"/>
+      <c r="F15" s="279"/>
+      <c r="G15" s="279"/>
+      <c r="H15" s="279"/>
+      <c r="I15" s="280"/>
+    </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C16" s="281"/>
+      <c r="D16" s="282"/>
+      <c r="E16" s="282"/>
+      <c r="F16" s="282"/>
+      <c r="G16" s="282"/>
+      <c r="H16" s="282"/>
+      <c r="I16" s="283"/>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="281"/>
+      <c r="D17" s="282"/>
+      <c r="E17" s="282"/>
+      <c r="F17" s="282"/>
+      <c r="G17" s="282"/>
+      <c r="H17" s="282"/>
+      <c r="I17" s="283"/>
+    </row>
+    <row r="18" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="284"/>
+      <c r="D18" s="285"/>
+      <c r="E18" s="285"/>
+      <c r="F18" s="285"/>
+      <c r="G18" s="285"/>
+      <c r="H18" s="285"/>
+      <c r="I18" s="286"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B25:Q25"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="C15:I18"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3B1638-4DD7-49F1-A063-A82609A8678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168794AE-1FD1-4956-9C9D-50F8D1AF8593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'7F SITUACION'!$C$4:$O$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$126</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$142</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'SITUACION 6B'!$C$2:$I$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'SITUACION 6B'!$C$2:$I$21</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="282">
   <si>
     <t>TOTAL</t>
   </si>
@@ -886,6 +886,9 @@
   </si>
   <si>
     <t>*Aclaracion importante: la administracion nueva toma posesion de la liquidacion de expensas a partir de Diciembre del 2025. El monto pasado en dicho mes como Saldo de inicio ($598.682,42) parte de la informacion (de la ultima liquidacion) de la administracion antigua. Los intereses mensuales son del 3%.</t>
+  </si>
+  <si>
+    <t>En el mes de febrero se debia abonar en concepto de honorarios de la Sra. Abogada : $132.000, se abona $200.000,42 cubriendo honorarios mencionados y abonando el adelanto del plan de pago por $68.000</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1644,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1993,24 +1996,33 @@
     </xf>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2023,14 +2035,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2038,6 +2044,12 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2122,59 +2134,50 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2209,6 +2212,35 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2592,12 +2624,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="220" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="215"/>
-      <c r="D1" s="215"/>
-      <c r="E1" s="216"/>
+      <c r="C1" s="220"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="221"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2610,12 +2642,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="219" t="s">
+      <c r="B3" s="222" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="219"/>
-      <c r="D3" s="219"/>
-      <c r="E3" s="220"/>
+      <c r="C3" s="222"/>
+      <c r="D3" s="222"/>
+      <c r="E3" s="223"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2653,49 +2685,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="221" t="s">
+      <c r="B8" s="224" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="221"/>
+      <c r="C8" s="224"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="221"/>
-      <c r="C9" s="221"/>
+      <c r="B9" s="224"/>
+      <c r="C9" s="224"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="221"/>
-      <c r="C10" s="221"/>
+      <c r="B10" s="224"/>
+      <c r="C10" s="224"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="222" t="s">
+      <c r="A13" s="225" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="222"/>
-      <c r="C13" s="222"/>
-      <c r="D13" s="222"/>
-      <c r="E13" s="222"/>
+      <c r="B13" s="225"/>
+      <c r="C13" s="225"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="222"/>
-      <c r="B14" s="222"/>
-      <c r="C14" s="222"/>
-      <c r="D14" s="222"/>
-      <c r="E14" s="222"/>
+      <c r="A14" s="225"/>
+      <c r="B14" s="225"/>
+      <c r="C14" s="225"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="222"/>
-      <c r="B15" s="222"/>
-      <c r="C15" s="222"/>
-      <c r="D15" s="222"/>
-      <c r="E15" s="222"/>
+      <c r="A15" s="225"/>
+      <c r="B15" s="225"/>
+      <c r="C15" s="225"/>
+      <c r="D15" s="225"/>
+      <c r="E15" s="225"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="222"/>
-      <c r="B16" s="222"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
+      <c r="A16" s="225"/>
+      <c r="B16" s="225"/>
+      <c r="C16" s="225"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2721,10 +2753,10 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="217" t="s">
+      <c r="A22" s="213" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="218"/>
+      <c r="B22" s="214"/>
       <c r="C22" s="22"/>
       <c r="D22" s="167">
         <v>1931623</v>
@@ -2733,10 +2765,10 @@
       <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="217" t="s">
+      <c r="A23" s="213" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="218"/>
+      <c r="B23" s="214"/>
       <c r="C23" s="22"/>
       <c r="D23" s="167">
         <v>-420128</v>
@@ -2745,10 +2777,10 @@
       <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="217" t="s">
+      <c r="A24" s="213" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="218"/>
+      <c r="B24" s="214"/>
       <c r="C24" s="22"/>
       <c r="D24" s="168">
         <v>0</v>
@@ -2920,10 +2952,10 @@
       <c r="E38" s="29"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="213" t="s">
+      <c r="A39" s="216" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="214"/>
+      <c r="B39" s="217"/>
       <c r="C39" s="32"/>
       <c r="D39" s="169">
         <v>313739</v>
@@ -2933,10 +2965,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="213" t="s">
+      <c r="A40" s="216" t="s">
         <v>253</v>
       </c>
-      <c r="B40" s="214"/>
+      <c r="B40" s="217"/>
       <c r="C40" s="32"/>
       <c r="D40" s="170">
         <v>214164</v>
@@ -2946,10 +2978,10 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="213" t="s">
+      <c r="A41" s="216" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="214"/>
+      <c r="B41" s="217"/>
       <c r="C41" s="32"/>
       <c r="D41" s="170">
         <v>5204</v>
@@ -3034,10 +3066,10 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="213" t="s">
+      <c r="A48" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="214"/>
+      <c r="B48" s="217"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38">
         <v>4813938.26</v>
@@ -3075,10 +3107,10 @@
       <c r="E51" s="43"/>
     </row>
     <row r="52" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="217" t="s">
+      <c r="A52" s="213" t="s">
         <v>178</v>
       </c>
-      <c r="B52" s="218"/>
+      <c r="B52" s="214"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38">
         <v>225000</v>
@@ -3088,10 +3120,10 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="217" t="s">
+      <c r="A53" s="213" t="s">
         <v>190</v>
       </c>
-      <c r="B53" s="218"/>
+      <c r="B53" s="214"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38">
         <v>500000</v>
@@ -3101,10 +3133,10 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="217" t="s">
+      <c r="A54" s="213" t="s">
         <v>193</v>
       </c>
-      <c r="B54" s="218"/>
+      <c r="B54" s="214"/>
       <c r="C54" s="37"/>
       <c r="D54" s="38">
         <v>1520000</v>
@@ -3114,10 +3146,10 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="217" t="s">
+      <c r="A55" s="213" t="s">
         <v>222</v>
       </c>
-      <c r="B55" s="218"/>
+      <c r="B55" s="214"/>
       <c r="C55" s="37"/>
       <c r="D55" s="38">
         <f>272252*2</f>
@@ -3128,10 +3160,10 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="217" t="s">
+      <c r="A56" s="213" t="s">
         <v>208</v>
       </c>
-      <c r="B56" s="218"/>
+      <c r="B56" s="214"/>
       <c r="C56" s="37"/>
       <c r="D56" s="38">
         <v>85000</v>
@@ -3142,10 +3174,10 @@
       <c r="F56" s="63"/>
     </row>
     <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="217" t="s">
+      <c r="A57" s="213" t="s">
         <v>227</v>
       </c>
-      <c r="B57" s="218"/>
+      <c r="B57" s="214"/>
       <c r="C57" s="37"/>
       <c r="D57" s="38">
         <v>120000</v>
@@ -3170,10 +3202,10 @@
       <c r="F58" s="63"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="217" t="s">
+      <c r="A59" s="213" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="218"/>
+      <c r="B59" s="214"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38">
         <v>6000</v>
@@ -3184,10 +3216,10 @@
       <c r="F59" s="63"/>
     </row>
     <row r="60" spans="1:6" ht="85.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="217" t="s">
+      <c r="A60" s="213" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="218"/>
+      <c r="B60" s="214"/>
       <c r="C60" s="37"/>
       <c r="D60" s="38">
         <v>7000000</v>
@@ -3240,10 +3272,10 @@
       <c r="F63" s="63"/>
     </row>
     <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="217" t="s">
+      <c r="A64" s="213" t="s">
         <v>206</v>
       </c>
-      <c r="B64" s="218"/>
+      <c r="B64" s="214"/>
       <c r="C64" s="37"/>
       <c r="D64" s="38">
         <v>250000</v>
@@ -3268,10 +3300,10 @@
       <c r="F65" s="63"/>
     </row>
     <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="217" t="s">
+      <c r="A66" s="213" t="s">
         <v>199</v>
       </c>
-      <c r="B66" s="218"/>
+      <c r="B66" s="214"/>
       <c r="C66" s="37"/>
       <c r="D66" s="38">
         <v>105602.65</v>
@@ -3282,10 +3314,10 @@
       <c r="F66" s="63"/>
     </row>
     <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="217" t="s">
+      <c r="A67" s="213" t="s">
         <v>184</v>
       </c>
-      <c r="B67" s="218"/>
+      <c r="B67" s="214"/>
       <c r="C67" s="37"/>
       <c r="D67" s="38">
         <v>2022800</v>
@@ -3316,10 +3348,10 @@
       <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="217" t="s">
+      <c r="A70" s="213" t="s">
         <v>192</v>
       </c>
-      <c r="B70" s="218"/>
+      <c r="B70" s="214"/>
       <c r="C70" s="22"/>
       <c r="D70" s="171">
         <v>650000</v>
@@ -3340,10 +3372,10 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="217" t="s">
+      <c r="A72" s="213" t="s">
         <v>221</v>
       </c>
-      <c r="B72" s="218"/>
+      <c r="B72" s="214"/>
       <c r="C72" s="22"/>
       <c r="D72" s="172">
         <v>62500</v>
@@ -3506,8 +3538,8 @@
       <c r="E88" s="73"/>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="217"/>
-      <c r="B89" s="218"/>
+      <c r="A89" s="213"/>
+      <c r="B89" s="214"/>
       <c r="C89" s="37"/>
       <c r="D89" s="45"/>
       <c r="E89" s="73"/>
@@ -3603,42 +3635,42 @@
       </c>
     </row>
     <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="225" t="s">
+      <c r="A105" s="219" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="225"/>
+      <c r="B105" s="219"/>
     </row>
     <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="225"/>
-      <c r="B106" s="225"/>
+      <c r="A106" s="219"/>
+      <c r="B106" s="219"/>
     </row>
     <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="225"/>
-      <c r="B107" s="225"/>
+      <c r="A107" s="219"/>
+      <c r="B107" s="219"/>
     </row>
     <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="225" t="s">
+      <c r="A109" s="219" t="s">
         <v>239</v>
       </c>
-      <c r="B109" s="225"/>
+      <c r="B109" s="219"/>
     </row>
     <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="225"/>
-      <c r="B110" s="225"/>
+      <c r="A110" s="219"/>
+      <c r="B110" s="219"/>
     </row>
     <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="225"/>
-      <c r="B111" s="225"/>
+      <c r="A111" s="219"/>
+      <c r="B111" s="219"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="224" t="s">
+      <c r="A114" s="218" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="224"/>
+      <c r="B114" s="218"/>
     </row>
     <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="224"/>
-      <c r="B115" s="224"/>
+      <c r="A115" s="218"/>
+      <c r="B115" s="218"/>
     </row>
     <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116"/>
@@ -3844,16 +3876,16 @@
     </row>
     <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="223" t="s">
+      <c r="A139" s="215" t="s">
         <v>129</v>
       </c>
-      <c r="B139" s="223"/>
-      <c r="C139" s="223"/>
+      <c r="B139" s="215"/>
+      <c r="C139" s="215"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="223"/>
-      <c r="B140" s="223"/>
-      <c r="C140" s="223"/>
+      <c r="A140" s="215"/>
+      <c r="B140" s="215"/>
+      <c r="C140" s="215"/>
     </row>
     <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="90" t="s">
@@ -3880,6 +3912,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A139:C140"/>
@@ -3896,19 +3941,6 @@
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A105:B107"/>
     <mergeCell ref="A109:B111"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3943,15 +3975,15 @@
       <c r="A1" s="124"/>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
+      <c r="D1" s="237"/>
+      <c r="E1" s="237"/>
+      <c r="F1" s="237"/>
+      <c r="G1" s="237"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
+      <c r="K1" s="237"/>
+      <c r="L1" s="237"/>
       <c r="M1" s="126"/>
     </row>
     <row r="2" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3961,10 +3993,10 @@
       <c r="D2" s="129" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="256">
+      <c r="E2" s="226">
         <v>3000000</v>
       </c>
-      <c r="F2" s="256"/>
+      <c r="F2" s="226"/>
       <c r="G2" s="129"/>
       <c r="H2" s="129"/>
       <c r="I2" s="129" t="s">
@@ -3995,195 +4027,195 @@
       <c r="N3" s="96"/>
     </row>
     <row r="4" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="235" t="s">
+      <c r="A4" s="238" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="236"/>
-      <c r="C4" s="236"/>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="236"/>
-      <c r="I4" s="236"/>
-      <c r="J4" s="236"/>
-      <c r="K4" s="236"/>
-      <c r="L4" s="236"/>
-      <c r="M4" s="237"/>
+      <c r="B4" s="239"/>
+      <c r="C4" s="239"/>
+      <c r="D4" s="239"/>
+      <c r="E4" s="239"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
+      <c r="H4" s="239"/>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="M4" s="240"/>
       <c r="N4" s="96"/>
     </row>
     <row r="5" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="238"/>
-      <c r="B5" s="239"/>
-      <c r="C5" s="239"/>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239"/>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="M5" s="240"/>
+      <c r="A5" s="241"/>
+      <c r="B5" s="242"/>
+      <c r="C5" s="242"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242"/>
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
+      <c r="M5" s="243"/>
       <c r="N5" s="96"/>
     </row>
     <row r="6" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="238"/>
-      <c r="B6" s="239"/>
-      <c r="C6" s="239"/>
-      <c r="D6" s="239"/>
-      <c r="E6" s="239"/>
-      <c r="F6" s="239"/>
-      <c r="G6" s="239"/>
-      <c r="H6" s="239"/>
-      <c r="I6" s="239"/>
-      <c r="J6" s="239"/>
-      <c r="K6" s="239"/>
-      <c r="L6" s="239"/>
-      <c r="M6" s="240"/>
+      <c r="A6" s="241"/>
+      <c r="B6" s="242"/>
+      <c r="C6" s="242"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="242"/>
+      <c r="F6" s="242"/>
+      <c r="G6" s="242"/>
+      <c r="H6" s="242"/>
+      <c r="I6" s="242"/>
+      <c r="J6" s="242"/>
+      <c r="K6" s="242"/>
+      <c r="L6" s="242"/>
+      <c r="M6" s="243"/>
       <c r="N6" s="96"/>
     </row>
     <row r="7" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="238"/>
-      <c r="B7" s="239"/>
-      <c r="C7" s="239"/>
-      <c r="D7" s="239"/>
-      <c r="E7" s="239"/>
-      <c r="F7" s="239"/>
-      <c r="G7" s="239"/>
-      <c r="H7" s="239"/>
-      <c r="I7" s="239"/>
-      <c r="J7" s="239"/>
-      <c r="K7" s="239"/>
-      <c r="L7" s="239"/>
-      <c r="M7" s="240"/>
+      <c r="A7" s="241"/>
+      <c r="B7" s="242"/>
+      <c r="C7" s="242"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="242"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
+      <c r="H7" s="242"/>
+      <c r="I7" s="242"/>
+      <c r="J7" s="242"/>
+      <c r="K7" s="242"/>
+      <c r="L7" s="242"/>
+      <c r="M7" s="243"/>
       <c r="N7" s="96"/>
     </row>
     <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="241"/>
-      <c r="B8" s="242"/>
-      <c r="C8" s="242"/>
-      <c r="D8" s="242"/>
-      <c r="E8" s="242"/>
-      <c r="F8" s="242"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="242"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="242"/>
-      <c r="K8" s="242"/>
-      <c r="L8" s="242"/>
-      <c r="M8" s="243"/>
+      <c r="A8" s="244"/>
+      <c r="B8" s="245"/>
+      <c r="C8" s="245"/>
+      <c r="D8" s="245"/>
+      <c r="E8" s="245"/>
+      <c r="F8" s="245"/>
+      <c r="G8" s="245"/>
+      <c r="H8" s="245"/>
+      <c r="I8" s="245"/>
+      <c r="J8" s="245"/>
+      <c r="K8" s="245"/>
+      <c r="L8" s="245"/>
+      <c r="M8" s="246"/>
     </row>
     <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="231" t="s">
+      <c r="A9" s="234" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="232"/>
-      <c r="E9" s="232"/>
-      <c r="F9" s="232"/>
-      <c r="G9" s="232"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="232"/>
-      <c r="J9" s="232"/>
-      <c r="K9" s="232"/>
-      <c r="L9" s="232"/>
-      <c r="M9" s="233"/>
+      <c r="B9" s="235"/>
+      <c r="C9" s="235"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
+      <c r="M9" s="236"/>
     </row>
     <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="250" t="s">
+      <c r="A10" s="253" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="251"/>
-      <c r="C10" s="251"/>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="251"/>
-      <c r="L10" s="251"/>
-      <c r="M10" s="252"/>
+      <c r="B10" s="254"/>
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="254"/>
+      <c r="I10" s="254"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="254"/>
+      <c r="L10" s="254"/>
+      <c r="M10" s="255"/>
     </row>
     <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="253" t="s">
+      <c r="A11" s="256" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="254"/>
-      <c r="C11" s="254"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="254"/>
-      <c r="G11" s="254"/>
-      <c r="H11" s="254"/>
-      <c r="I11" s="254"/>
-      <c r="J11" s="254"/>
-      <c r="K11" s="254"/>
-      <c r="L11" s="254"/>
-      <c r="M11" s="255"/>
+      <c r="B11" s="257"/>
+      <c r="C11" s="257"/>
+      <c r="D11" s="257"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="257"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="257"/>
+      <c r="J11" s="257"/>
+      <c r="K11" s="257"/>
+      <c r="L11" s="257"/>
+      <c r="M11" s="258"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="244" t="s">
+      <c r="A12" s="247" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="246" t="s">
+      <c r="B12" s="249" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="246" t="s">
+      <c r="C12" s="249" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="246" t="s">
+      <c r="D12" s="249" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="226" t="s">
+      <c r="E12" s="227" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="246" t="s">
+      <c r="F12" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="248" t="s">
+      <c r="G12" s="251" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="226" t="s">
+      <c r="H12" s="227" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="226" t="s">
+      <c r="I12" s="227" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="226" t="s">
+      <c r="J12" s="227" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="257" t="s">
+      <c r="K12" s="229" t="s">
         <v>247</v>
       </c>
       <c r="L12" s="195" t="s">
         <v>140</v>
       </c>
-      <c r="M12" s="228" t="s">
+      <c r="M12" s="231" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="245"/>
-      <c r="B13" s="247"/>
-      <c r="C13" s="247"/>
-      <c r="D13" s="247"/>
-      <c r="E13" s="227"/>
-      <c r="F13" s="247"/>
-      <c r="G13" s="249"/>
-      <c r="H13" s="227"/>
-      <c r="I13" s="227"/>
-      <c r="J13" s="227"/>
-      <c r="K13" s="258"/>
+      <c r="A13" s="248"/>
+      <c r="B13" s="250"/>
+      <c r="C13" s="250"/>
+      <c r="D13" s="250"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="250"/>
+      <c r="G13" s="252"/>
+      <c r="H13" s="228"/>
+      <c r="I13" s="228"/>
+      <c r="J13" s="228"/>
+      <c r="K13" s="230"/>
       <c r="L13" s="196" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M13" s="229"/>
+      <c r="M13" s="232"/>
     </row>
     <row r="14" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="179">
@@ -9239,92 +9271,87 @@
     </row>
     <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="230" t="s">
+      <c r="B121" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="C121" s="230"/>
-      <c r="D121" s="230"/>
-      <c r="E121" s="230"/>
-      <c r="F121" s="230"/>
-      <c r="G121" s="230"/>
-      <c r="H121" s="230"/>
-      <c r="I121" s="230"/>
-      <c r="J121" s="230"/>
-      <c r="K121" s="230"/>
-      <c r="L121" s="230"/>
+      <c r="C121" s="233"/>
+      <c r="D121" s="233"/>
+      <c r="E121" s="233"/>
+      <c r="F121" s="233"/>
+      <c r="G121" s="233"/>
+      <c r="H121" s="233"/>
+      <c r="I121" s="233"/>
+      <c r="J121" s="233"/>
+      <c r="K121" s="233"/>
+      <c r="L121" s="233"/>
     </row>
     <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="230"/>
-      <c r="C122" s="230"/>
-      <c r="D122" s="230"/>
-      <c r="E122" s="230"/>
-      <c r="F122" s="230"/>
-      <c r="G122" s="230"/>
-      <c r="H122" s="230"/>
-      <c r="I122" s="230"/>
-      <c r="J122" s="230"/>
-      <c r="K122" s="230"/>
-      <c r="L122" s="230"/>
+      <c r="B122" s="233"/>
+      <c r="C122" s="233"/>
+      <c r="D122" s="233"/>
+      <c r="E122" s="233"/>
+      <c r="F122" s="233"/>
+      <c r="G122" s="233"/>
+      <c r="H122" s="233"/>
+      <c r="I122" s="233"/>
+      <c r="J122" s="233"/>
+      <c r="K122" s="233"/>
+      <c r="L122" s="233"/>
     </row>
     <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="230"/>
-      <c r="C123" s="230"/>
-      <c r="D123" s="230"/>
-      <c r="E123" s="230"/>
-      <c r="F123" s="230"/>
-      <c r="G123" s="230"/>
-      <c r="H123" s="230"/>
-      <c r="I123" s="230"/>
-      <c r="J123" s="230"/>
-      <c r="K123" s="230"/>
-      <c r="L123" s="230"/>
+      <c r="B123" s="233"/>
+      <c r="C123" s="233"/>
+      <c r="D123" s="233"/>
+      <c r="E123" s="233"/>
+      <c r="F123" s="233"/>
+      <c r="G123" s="233"/>
+      <c r="H123" s="233"/>
+      <c r="I123" s="233"/>
+      <c r="J123" s="233"/>
+      <c r="K123" s="233"/>
+      <c r="L123" s="233"/>
     </row>
     <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="230"/>
-      <c r="C124" s="230"/>
-      <c r="D124" s="230"/>
-      <c r="E124" s="230"/>
-      <c r="F124" s="230"/>
-      <c r="G124" s="230"/>
-      <c r="H124" s="230"/>
-      <c r="I124" s="230"/>
-      <c r="J124" s="230"/>
-      <c r="K124" s="230"/>
-      <c r="L124" s="230"/>
+      <c r="B124" s="233"/>
+      <c r="C124" s="233"/>
+      <c r="D124" s="233"/>
+      <c r="E124" s="233"/>
+      <c r="F124" s="233"/>
+      <c r="G124" s="233"/>
+      <c r="H124" s="233"/>
+      <c r="I124" s="233"/>
+      <c r="J124" s="233"/>
+      <c r="K124" s="233"/>
+      <c r="L124" s="233"/>
     </row>
     <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="230"/>
-      <c r="C125" s="230"/>
-      <c r="D125" s="230"/>
-      <c r="E125" s="230"/>
-      <c r="F125" s="230"/>
-      <c r="G125" s="230"/>
-      <c r="H125" s="230"/>
-      <c r="I125" s="230"/>
-      <c r="J125" s="230"/>
-      <c r="K125" s="230"/>
-      <c r="L125" s="230"/>
+      <c r="B125" s="233"/>
+      <c r="C125" s="233"/>
+      <c r="D125" s="233"/>
+      <c r="E125" s="233"/>
+      <c r="F125" s="233"/>
+      <c r="G125" s="233"/>
+      <c r="H125" s="233"/>
+      <c r="I125" s="233"/>
+      <c r="J125" s="233"/>
+      <c r="K125" s="233"/>
+      <c r="L125" s="233"/>
     </row>
     <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="230"/>
-      <c r="C126" s="230"/>
-      <c r="D126" s="230"/>
-      <c r="E126" s="230"/>
-      <c r="F126" s="230"/>
-      <c r="G126" s="230"/>
-      <c r="H126" s="230"/>
-      <c r="I126" s="230"/>
-      <c r="J126" s="230"/>
-      <c r="K126" s="230"/>
-      <c r="L126" s="230"/>
+      <c r="B126" s="233"/>
+      <c r="C126" s="233"/>
+      <c r="D126" s="233"/>
+      <c r="E126" s="233"/>
+      <c r="F126" s="233"/>
+      <c r="G126" s="233"/>
+      <c r="H126" s="233"/>
+      <c r="I126" s="233"/>
+      <c r="J126" s="233"/>
+      <c r="K126" s="233"/>
+      <c r="L126" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
     <mergeCell ref="B121:L126"/>
     <mergeCell ref="A9:M9"/>
     <mergeCell ref="D1:L1"/>
@@ -9339,6 +9366,11 @@
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A11:M11"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9379,10 +9411,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C4" s="259" t="s">
+      <c r="C4" s="273" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="259"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="201"/>
       <c r="F4" s="199" t="s">
         <v>258</v>
@@ -9390,16 +9422,16 @@
       <c r="H4" t="s">
         <v>259</v>
       </c>
-      <c r="J4" s="261" t="s">
+      <c r="J4" s="263" t="s">
         <v>261</v>
       </c>
-      <c r="K4" s="261"/>
+      <c r="K4" s="263"/>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C5" s="260">
+      <c r="C5" s="262">
         <v>168835.53000000003</v>
       </c>
-      <c r="D5" s="260"/>
+      <c r="D5" s="262"/>
       <c r="E5" s="202"/>
       <c r="F5" s="200">
         <f>C5</f>
@@ -9408,18 +9440,18 @@
       <c r="H5" s="80">
         <v>0</v>
       </c>
-      <c r="J5" s="262">
+      <c r="J5" s="274">
         <f>F5</f>
         <v>168835.53000000003</v>
       </c>
-      <c r="K5" s="262"/>
+      <c r="K5" s="274"/>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M7" s="265" t="s">
+      <c r="M7" s="261" t="s">
         <v>263</v>
       </c>
-      <c r="N7" s="265"/>
-      <c r="O7" s="265"/>
+      <c r="N7" s="261"/>
+      <c r="O7" s="261"/>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
@@ -9431,19 +9463,19 @@
       <c r="H8" t="s">
         <v>259</v>
       </c>
-      <c r="J8" s="261" t="s">
+      <c r="J8" s="263" t="s">
         <v>262</v>
       </c>
-      <c r="K8" s="261"/>
-      <c r="M8" s="265"/>
-      <c r="N8" s="265"/>
-      <c r="O8" s="265"/>
+      <c r="K8" s="263"/>
+      <c r="M8" s="261"/>
+      <c r="N8" s="261"/>
+      <c r="O8" s="261"/>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C9" s="260">
+      <c r="C9" s="262">
         <v>168836.53</v>
       </c>
-      <c r="D9" s="260"/>
+      <c r="D9" s="262"/>
       <c r="F9" s="80">
         <v>0</v>
       </c>
@@ -9451,16 +9483,16 @@
         <f>C9-F9</f>
         <v>168836.53</v>
       </c>
-      <c r="J9" s="260">
+      <c r="J9" s="262">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K9" s="260"/>
-      <c r="M9" s="264">
+      <c r="K9" s="262"/>
+      <c r="M9" s="260">
         <v>300737.53000000003</v>
       </c>
-      <c r="N9" s="264"/>
-      <c r="O9" s="264"/>
+      <c r="N9" s="260"/>
+      <c r="O9" s="260"/>
     </row>
     <row r="10" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="202"/>
@@ -9474,11 +9506,11 @@
       <c r="O10" s="203"/>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M11" s="269" t="s">
+      <c r="M11" s="267" t="s">
         <v>263</v>
       </c>
-      <c r="N11" s="270"/>
-      <c r="O11" s="271"/>
+      <c r="N11" s="268"/>
+      <c r="O11" s="269"/>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
@@ -9490,20 +9522,20 @@
       <c r="H12" t="s">
         <v>259</v>
       </c>
-      <c r="J12" s="261" t="s">
+      <c r="J12" s="263" t="s">
         <v>265</v>
       </c>
-      <c r="K12" s="261"/>
-      <c r="M12" s="272"/>
-      <c r="N12" s="273"/>
-      <c r="O12" s="274"/>
+      <c r="K12" s="263"/>
+      <c r="M12" s="270"/>
+      <c r="N12" s="271"/>
+      <c r="O12" s="272"/>
     </row>
     <row r="13" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="260">
+      <c r="C13" s="262">
         <f>M9</f>
         <v>300737.53000000003</v>
       </c>
-      <c r="D13" s="260"/>
+      <c r="D13" s="262"/>
       <c r="F13" s="80">
         <v>98556.53</v>
       </c>
@@ -9511,127 +9543,132 @@
         <f>C13-F13</f>
         <v>202181.00000000003</v>
       </c>
-      <c r="J13" s="260">
+      <c r="J13" s="262">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K13" s="260"/>
-      <c r="M13" s="266">
+      <c r="K13" s="262"/>
+      <c r="M13" s="264">
         <f>J13+H13-0.27</f>
         <v>371016.53</v>
       </c>
-      <c r="N13" s="267"/>
-      <c r="O13" s="268"/>
+      <c r="N13" s="265"/>
+      <c r="O13" s="266"/>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C15" s="263" t="s">
+      <c r="C15" s="259" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="263"/>
-      <c r="E15" s="263"/>
-      <c r="F15" s="263"/>
-      <c r="G15" s="263"/>
-      <c r="H15" s="263"/>
-      <c r="I15" s="263"/>
-      <c r="J15" s="263"/>
-      <c r="K15" s="263"/>
-      <c r="L15" s="263"/>
-      <c r="M15" s="263"/>
-      <c r="N15" s="263"/>
-      <c r="O15" s="263"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="259"/>
+      <c r="F15" s="259"/>
+      <c r="G15" s="259"/>
+      <c r="H15" s="259"/>
+      <c r="I15" s="259"/>
+      <c r="J15" s="259"/>
+      <c r="K15" s="259"/>
+      <c r="L15" s="259"/>
+      <c r="M15" s="259"/>
+      <c r="N15" s="259"/>
+      <c r="O15" s="259"/>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C16" s="263"/>
-      <c r="D16" s="263"/>
-      <c r="E16" s="263"/>
-      <c r="F16" s="263"/>
-      <c r="G16" s="263"/>
-      <c r="H16" s="263"/>
-      <c r="I16" s="263"/>
-      <c r="J16" s="263"/>
-      <c r="K16" s="263"/>
-      <c r="L16" s="263"/>
-      <c r="M16" s="263"/>
-      <c r="N16" s="263"/>
-      <c r="O16" s="263"/>
+      <c r="C16" s="259"/>
+      <c r="D16" s="259"/>
+      <c r="E16" s="259"/>
+      <c r="F16" s="259"/>
+      <c r="G16" s="259"/>
+      <c r="H16" s="259"/>
+      <c r="I16" s="259"/>
+      <c r="J16" s="259"/>
+      <c r="K16" s="259"/>
+      <c r="L16" s="259"/>
+      <c r="M16" s="259"/>
+      <c r="N16" s="259"/>
+      <c r="O16" s="259"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C17" s="263"/>
-      <c r="D17" s="263"/>
-      <c r="E17" s="263"/>
-      <c r="F17" s="263"/>
-      <c r="G17" s="263"/>
-      <c r="H17" s="263"/>
-      <c r="I17" s="263"/>
-      <c r="J17" s="263"/>
-      <c r="K17" s="263"/>
-      <c r="L17" s="263"/>
-      <c r="M17" s="263"/>
-      <c r="N17" s="263"/>
-      <c r="O17" s="263"/>
+      <c r="C17" s="259"/>
+      <c r="D17" s="259"/>
+      <c r="E17" s="259"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
+      <c r="J17" s="259"/>
+      <c r="K17" s="259"/>
+      <c r="L17" s="259"/>
+      <c r="M17" s="259"/>
+      <c r="N17" s="259"/>
+      <c r="O17" s="259"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C18" s="263"/>
-      <c r="D18" s="263"/>
-      <c r="E18" s="263"/>
-      <c r="F18" s="263"/>
-      <c r="G18" s="263"/>
-      <c r="H18" s="263"/>
-      <c r="I18" s="263"/>
-      <c r="J18" s="263"/>
-      <c r="K18" s="263"/>
-      <c r="L18" s="263"/>
-      <c r="M18" s="263"/>
-      <c r="N18" s="263"/>
-      <c r="O18" s="263"/>
+      <c r="C18" s="259"/>
+      <c r="D18" s="259"/>
+      <c r="E18" s="259"/>
+      <c r="F18" s="259"/>
+      <c r="G18" s="259"/>
+      <c r="H18" s="259"/>
+      <c r="I18" s="259"/>
+      <c r="J18" s="259"/>
+      <c r="K18" s="259"/>
+      <c r="L18" s="259"/>
+      <c r="M18" s="259"/>
+      <c r="N18" s="259"/>
+      <c r="O18" s="259"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C19" s="263"/>
-      <c r="D19" s="263"/>
-      <c r="E19" s="263"/>
-      <c r="F19" s="263"/>
-      <c r="G19" s="263"/>
-      <c r="H19" s="263"/>
-      <c r="I19" s="263"/>
-      <c r="J19" s="263"/>
-      <c r="K19" s="263"/>
-      <c r="L19" s="263"/>
-      <c r="M19" s="263"/>
-      <c r="N19" s="263"/>
-      <c r="O19" s="263"/>
+      <c r="C19" s="259"/>
+      <c r="D19" s="259"/>
+      <c r="E19" s="259"/>
+      <c r="F19" s="259"/>
+      <c r="G19" s="259"/>
+      <c r="H19" s="259"/>
+      <c r="I19" s="259"/>
+      <c r="J19" s="259"/>
+      <c r="K19" s="259"/>
+      <c r="L19" s="259"/>
+      <c r="M19" s="259"/>
+      <c r="N19" s="259"/>
+      <c r="O19" s="259"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C20" s="263"/>
-      <c r="D20" s="263"/>
-      <c r="E20" s="263"/>
-      <c r="F20" s="263"/>
-      <c r="G20" s="263"/>
-      <c r="H20" s="263"/>
-      <c r="I20" s="263"/>
-      <c r="J20" s="263"/>
-      <c r="K20" s="263"/>
-      <c r="L20" s="263"/>
-      <c r="M20" s="263"/>
-      <c r="N20" s="263"/>
-      <c r="O20" s="263"/>
+      <c r="C20" s="259"/>
+      <c r="D20" s="259"/>
+      <c r="E20" s="259"/>
+      <c r="F20" s="259"/>
+      <c r="G20" s="259"/>
+      <c r="H20" s="259"/>
+      <c r="I20" s="259"/>
+      <c r="J20" s="259"/>
+      <c r="K20" s="259"/>
+      <c r="L20" s="259"/>
+      <c r="M20" s="259"/>
+      <c r="N20" s="259"/>
+      <c r="O20" s="259"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="263"/>
-      <c r="D21" s="263"/>
-      <c r="E21" s="263"/>
-      <c r="F21" s="263"/>
-      <c r="G21" s="263"/>
-      <c r="H21" s="263"/>
-      <c r="I21" s="263"/>
-      <c r="J21" s="263"/>
-      <c r="K21" s="263"/>
-      <c r="L21" s="263"/>
-      <c r="M21" s="263"/>
-      <c r="N21" s="263"/>
-      <c r="O21" s="263"/>
+      <c r="C21" s="259"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="259"/>
+      <c r="F21" s="259"/>
+      <c r="G21" s="259"/>
+      <c r="H21" s="259"/>
+      <c r="I21" s="259"/>
+      <c r="J21" s="259"/>
+      <c r="K21" s="259"/>
+      <c r="L21" s="259"/>
+      <c r="M21" s="259"/>
+      <c r="N21" s="259"/>
+      <c r="O21" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="C15:O21"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="M7:O8"/>
@@ -9642,11 +9679,6 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M11:O12"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="125" orientation="landscape" r:id="rId1"/>
@@ -9655,12 +9687,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DC61AA-F548-49A9-A9B8-49FB942F95D7}">
-  <dimension ref="C1:K18"/>
+  <dimension ref="C1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.21875" customWidth="1"/>
     <col min="11" max="11" width="15.33203125" customWidth="1"/>
@@ -9827,7 +9857,9 @@
       <c r="E13" s="209">
         <v>818744.42</v>
       </c>
-      <c r="F13" s="209"/>
+      <c r="F13" s="209">
+        <v>0</v>
+      </c>
       <c r="G13" s="209">
         <v>135235.80000000002</v>
       </c>
@@ -9842,49 +9874,90 @@
         <v>987580.22000000009</v>
       </c>
     </row>
-    <row r="14" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="287"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="288"/>
+      <c r="K14" s="63"/>
+    </row>
     <row r="15" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C15" s="278" t="s">
+      <c r="C15" s="289" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="290"/>
+      <c r="E15" s="290"/>
+      <c r="F15" s="290"/>
+      <c r="G15" s="290"/>
+      <c r="H15" s="290"/>
+      <c r="I15" s="291"/>
+      <c r="K15" s="63"/>
+    </row>
+    <row r="16" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C16" s="292"/>
+      <c r="D16" s="293"/>
+      <c r="E16" s="293"/>
+      <c r="F16" s="293"/>
+      <c r="G16" s="293"/>
+      <c r="H16" s="293"/>
+      <c r="I16" s="294"/>
+      <c r="K16" s="63"/>
+    </row>
+    <row r="17" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="295"/>
+      <c r="D17" s="296"/>
+      <c r="E17" s="296"/>
+      <c r="F17" s="296"/>
+      <c r="G17" s="296"/>
+      <c r="H17" s="296"/>
+      <c r="I17" s="297"/>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="278" t="s">
         <v>280</v>
       </c>
-      <c r="D15" s="279"/>
-      <c r="E15" s="279"/>
-      <c r="F15" s="279"/>
-      <c r="G15" s="279"/>
-      <c r="H15" s="279"/>
-      <c r="I15" s="280"/>
-    </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C16" s="281"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="282"/>
-      <c r="H16" s="282"/>
-      <c r="I16" s="283"/>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="281"/>
-      <c r="D17" s="282"/>
-      <c r="E17" s="282"/>
-      <c r="F17" s="282"/>
-      <c r="G17" s="282"/>
-      <c r="H17" s="282"/>
-      <c r="I17" s="283"/>
-    </row>
-    <row r="18" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="284"/>
-      <c r="D18" s="285"/>
-      <c r="E18" s="285"/>
-      <c r="F18" s="285"/>
-      <c r="G18" s="285"/>
-      <c r="H18" s="285"/>
-      <c r="I18" s="286"/>
+      <c r="D18" s="279"/>
+      <c r="E18" s="279"/>
+      <c r="F18" s="279"/>
+      <c r="G18" s="279"/>
+      <c r="H18" s="279"/>
+      <c r="I18" s="280"/>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="281"/>
+      <c r="D19" s="282"/>
+      <c r="E19" s="282"/>
+      <c r="F19" s="282"/>
+      <c r="G19" s="282"/>
+      <c r="H19" s="282"/>
+      <c r="I19" s="283"/>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="281"/>
+      <c r="D20" s="282"/>
+      <c r="E20" s="282"/>
+      <c r="F20" s="282"/>
+      <c r="G20" s="282"/>
+      <c r="H20" s="282"/>
+      <c r="I20" s="283"/>
+    </row>
+    <row r="21" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="284"/>
+      <c r="D21" s="285"/>
+      <c r="E21" s="285"/>
+      <c r="F21" s="285"/>
+      <c r="G21" s="285"/>
+      <c r="H21" s="285"/>
+      <c r="I21" s="286"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C2:I2"/>
-    <mergeCell ref="C15:I18"/>
+    <mergeCell ref="C18:I21"/>
+    <mergeCell ref="C15:I17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168794AE-1FD1-4956-9C9D-50F8D1AF8593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4F7661-4BA4-47B2-95DB-79898E2D4F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'7F SITUACION'!$C$4:$O$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$126</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$142</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'SITUACION 6B'!$C$2:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'SITUACION 6B'!$D$4:$N$13</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="276">
   <si>
     <t>TOTAL</t>
   </si>
@@ -849,46 +849,28 @@
     <t>Todo este problema con los números se origina en el mes de enero, cuando la unidad funcional 7°F no realizó ningún pago. En ese mismo período, otro propietario efectuó un pago con una terminacion de 53 centavos, lo que generó que el sistema de la administración imputara ese pago a la unidad funcional 7°F, cuando en realidad dicha unidad nunca abonó. Debido a que el inconveniente y la confusión se originan a partir de una situación ajena a la unidad funcional 7°F, la administración decidió no aplicar los punitorios correspondientes al momento de rehacer y corregir los cálculos.</t>
   </si>
   <si>
-    <t>Saldo inicio Diciembre</t>
-  </si>
-  <si>
-    <t>Deuda</t>
-  </si>
-  <si>
-    <t>Diciembre del año 2025</t>
-  </si>
-  <si>
-    <t>Punitorios</t>
-  </si>
-  <si>
-    <t>Expensas ordinarias (Gastos A)</t>
-  </si>
-  <si>
-    <t>Expensas extraordinarias (gastos B)</t>
-  </si>
-  <si>
-    <t>Total a abonar en Enero:</t>
-  </si>
-  <si>
-    <t>Enero del año 2026</t>
-  </si>
-  <si>
-    <t>Febrero del año 2026</t>
-  </si>
-  <si>
-    <t>SITUACION 6B</t>
-  </si>
-  <si>
-    <t>Total a abonar en Febrero:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total a abonar en Marzo: </t>
-  </si>
-  <si>
-    <t>*Aclaracion importante: la administracion nueva toma posesion de la liquidacion de expensas a partir de Diciembre del 2025. El monto pasado en dicho mes como Saldo de inicio ($598.682,42) parte de la informacion (de la ultima liquidacion) de la administracion antigua. Los intereses mensuales son del 3%.</t>
-  </si>
-  <si>
-    <t>En el mes de febrero se debia abonar en concepto de honorarios de la Sra. Abogada : $132.000, se abona $200.000,42 cubriendo honorarios mencionados y abonando el adelanto del plan de pago por $68.000</t>
+    <t>Deuda a Financiar</t>
+  </si>
+  <si>
+    <t>Ingreso de convenio</t>
+  </si>
+  <si>
+    <t>Saldo</t>
+  </si>
+  <si>
+    <t>Gastos A Febrero</t>
+  </si>
+  <si>
+    <t>Gastos B Febrero</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>En el mes de febrero se abonaron $200.000,42 pesos que correspondieron $132.000 en concepto de honorarios de la Sra. Abogada y el restante ($68.000 en concepto de adelanto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El saldo total sera abonado mediante 24 cuotas de $33.000 </t>
   </si>
 </sst>
 </file>
@@ -1644,7 +1626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1986,64 +1968,132 @@
     <xf numFmtId="0" fontId="19" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2056,84 +2106,14 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2143,10 +2123,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2174,74 +2150,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2624,12 +2539,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="220" t="s">
+      <c r="B1" s="209" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="220"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="221"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="210"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2642,12 +2557,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="222" t="s">
+      <c r="B3" s="213" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="223"/>
+      <c r="C3" s="213"/>
+      <c r="D3" s="213"/>
+      <c r="E3" s="214"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2685,49 +2600,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="224" t="s">
+      <c r="B8" s="215" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="224"/>
+      <c r="C8" s="215"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="224"/>
-      <c r="C9" s="224"/>
+      <c r="B9" s="215"/>
+      <c r="C9" s="215"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="224"/>
-      <c r="C10" s="224"/>
+      <c r="B10" s="215"/>
+      <c r="C10" s="215"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="225" t="s">
+      <c r="A13" s="216" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="225"/>
-      <c r="C13" s="225"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="225"/>
+      <c r="B13" s="216"/>
+      <c r="C13" s="216"/>
+      <c r="D13" s="216"/>
+      <c r="E13" s="216"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="225"/>
-      <c r="B14" s="225"/>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
+      <c r="A14" s="216"/>
+      <c r="B14" s="216"/>
+      <c r="C14" s="216"/>
+      <c r="D14" s="216"/>
+      <c r="E14" s="216"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="225"/>
-      <c r="B15" s="225"/>
-      <c r="C15" s="225"/>
-      <c r="D15" s="225"/>
-      <c r="E15" s="225"/>
+      <c r="A15" s="216"/>
+      <c r="B15" s="216"/>
+      <c r="C15" s="216"/>
+      <c r="D15" s="216"/>
+      <c r="E15" s="216"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="225"/>
-      <c r="B16" s="225"/>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
+      <c r="A16" s="216"/>
+      <c r="B16" s="216"/>
+      <c r="C16" s="216"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2753,10 +2668,10 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="213" t="s">
+      <c r="A22" s="211" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="214"/>
+      <c r="B22" s="212"/>
       <c r="C22" s="22"/>
       <c r="D22" s="167">
         <v>1931623</v>
@@ -2765,10 +2680,10 @@
       <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="213" t="s">
+      <c r="A23" s="211" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="214"/>
+      <c r="B23" s="212"/>
       <c r="C23" s="22"/>
       <c r="D23" s="167">
         <v>-420128</v>
@@ -2777,10 +2692,10 @@
       <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="213" t="s">
+      <c r="A24" s="211" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="214"/>
+      <c r="B24" s="212"/>
       <c r="C24" s="22"/>
       <c r="D24" s="168">
         <v>0</v>
@@ -2952,10 +2867,10 @@
       <c r="E38" s="29"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="216" t="s">
+      <c r="A39" s="207" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="217"/>
+      <c r="B39" s="208"/>
       <c r="C39" s="32"/>
       <c r="D39" s="169">
         <v>313739</v>
@@ -2965,10 +2880,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="216" t="s">
+      <c r="A40" s="207" t="s">
         <v>253</v>
       </c>
-      <c r="B40" s="217"/>
+      <c r="B40" s="208"/>
       <c r="C40" s="32"/>
       <c r="D40" s="170">
         <v>214164</v>
@@ -2978,10 +2893,10 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="216" t="s">
+      <c r="A41" s="207" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="217"/>
+      <c r="B41" s="208"/>
       <c r="C41" s="32"/>
       <c r="D41" s="170">
         <v>5204</v>
@@ -3066,10 +2981,10 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="216" t="s">
+      <c r="A48" s="207" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="217"/>
+      <c r="B48" s="208"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38">
         <v>4813938.26</v>
@@ -3107,10 +3022,10 @@
       <c r="E51" s="43"/>
     </row>
     <row r="52" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="213" t="s">
+      <c r="A52" s="211" t="s">
         <v>178</v>
       </c>
-      <c r="B52" s="214"/>
+      <c r="B52" s="212"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38">
         <v>225000</v>
@@ -3120,10 +3035,10 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="213" t="s">
+      <c r="A53" s="211" t="s">
         <v>190</v>
       </c>
-      <c r="B53" s="214"/>
+      <c r="B53" s="212"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38">
         <v>500000</v>
@@ -3133,10 +3048,10 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="213" t="s">
+      <c r="A54" s="211" t="s">
         <v>193</v>
       </c>
-      <c r="B54" s="214"/>
+      <c r="B54" s="212"/>
       <c r="C54" s="37"/>
       <c r="D54" s="38">
         <v>1520000</v>
@@ -3146,10 +3061,10 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="213" t="s">
+      <c r="A55" s="211" t="s">
         <v>222</v>
       </c>
-      <c r="B55" s="214"/>
+      <c r="B55" s="212"/>
       <c r="C55" s="37"/>
       <c r="D55" s="38">
         <f>272252*2</f>
@@ -3160,10 +3075,10 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="213" t="s">
+      <c r="A56" s="211" t="s">
         <v>208</v>
       </c>
-      <c r="B56" s="214"/>
+      <c r="B56" s="212"/>
       <c r="C56" s="37"/>
       <c r="D56" s="38">
         <v>85000</v>
@@ -3174,10 +3089,10 @@
       <c r="F56" s="63"/>
     </row>
     <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="213" t="s">
+      <c r="A57" s="211" t="s">
         <v>227</v>
       </c>
-      <c r="B57" s="214"/>
+      <c r="B57" s="212"/>
       <c r="C57" s="37"/>
       <c r="D57" s="38">
         <v>120000</v>
@@ -3202,10 +3117,10 @@
       <c r="F58" s="63"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="213" t="s">
+      <c r="A59" s="211" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="214"/>
+      <c r="B59" s="212"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38">
         <v>6000</v>
@@ -3216,10 +3131,10 @@
       <c r="F59" s="63"/>
     </row>
     <row r="60" spans="1:6" ht="85.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="213" t="s">
+      <c r="A60" s="211" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="214"/>
+      <c r="B60" s="212"/>
       <c r="C60" s="37"/>
       <c r="D60" s="38">
         <v>7000000</v>
@@ -3272,10 +3187,10 @@
       <c r="F63" s="63"/>
     </row>
     <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="213" t="s">
+      <c r="A64" s="211" t="s">
         <v>206</v>
       </c>
-      <c r="B64" s="214"/>
+      <c r="B64" s="212"/>
       <c r="C64" s="37"/>
       <c r="D64" s="38">
         <v>250000</v>
@@ -3300,10 +3215,10 @@
       <c r="F65" s="63"/>
     </row>
     <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="213" t="s">
+      <c r="A66" s="211" t="s">
         <v>199</v>
       </c>
-      <c r="B66" s="214"/>
+      <c r="B66" s="212"/>
       <c r="C66" s="37"/>
       <c r="D66" s="38">
         <v>105602.65</v>
@@ -3314,10 +3229,10 @@
       <c r="F66" s="63"/>
     </row>
     <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="213" t="s">
+      <c r="A67" s="211" t="s">
         <v>184</v>
       </c>
-      <c r="B67" s="214"/>
+      <c r="B67" s="212"/>
       <c r="C67" s="37"/>
       <c r="D67" s="38">
         <v>2022800</v>
@@ -3348,10 +3263,10 @@
       <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="213" t="s">
+      <c r="A70" s="211" t="s">
         <v>192</v>
       </c>
-      <c r="B70" s="214"/>
+      <c r="B70" s="212"/>
       <c r="C70" s="22"/>
       <c r="D70" s="171">
         <v>650000</v>
@@ -3372,10 +3287,10 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="213" t="s">
+      <c r="A72" s="211" t="s">
         <v>221</v>
       </c>
-      <c r="B72" s="214"/>
+      <c r="B72" s="212"/>
       <c r="C72" s="22"/>
       <c r="D72" s="172">
         <v>62500</v>
@@ -3538,8 +3453,8 @@
       <c r="E88" s="73"/>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="213"/>
-      <c r="B89" s="214"/>
+      <c r="A89" s="211"/>
+      <c r="B89" s="212"/>
       <c r="C89" s="37"/>
       <c r="D89" s="45"/>
       <c r="E89" s="73"/>
@@ -3876,16 +3791,16 @@
     </row>
     <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="215" t="s">
+      <c r="A139" s="217" t="s">
         <v>129</v>
       </c>
-      <c r="B139" s="215"/>
-      <c r="C139" s="215"/>
+      <c r="B139" s="217"/>
+      <c r="C139" s="217"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="215"/>
-      <c r="B140" s="215"/>
-      <c r="C140" s="215"/>
+      <c r="A140" s="217"/>
+      <c r="B140" s="217"/>
+      <c r="C140" s="217"/>
     </row>
     <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="90" t="s">
@@ -3912,19 +3827,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A139:C140"/>
@@ -3941,6 +3843,19 @@
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A105:B107"/>
     <mergeCell ref="A109:B111"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3975,15 +3890,15 @@
       <c r="A1" s="124"/>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
-      <c r="D1" s="237"/>
-      <c r="E1" s="237"/>
-      <c r="F1" s="237"/>
-      <c r="G1" s="237"/>
-      <c r="H1" s="237"/>
-      <c r="I1" s="237"/>
-      <c r="J1" s="237"/>
-      <c r="K1" s="237"/>
-      <c r="L1" s="237"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
       <c r="M1" s="126"/>
     </row>
     <row r="2" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3993,10 +3908,10 @@
       <c r="D2" s="129" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="226">
+      <c r="E2" s="248">
         <v>3000000</v>
       </c>
-      <c r="F2" s="226"/>
+      <c r="F2" s="248"/>
       <c r="G2" s="129"/>
       <c r="H2" s="129"/>
       <c r="I2" s="129" t="s">
@@ -4027,195 +3942,195 @@
       <c r="N3" s="96"/>
     </row>
     <row r="4" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="238" t="s">
+      <c r="A4" s="225" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="239"/>
-      <c r="C4" s="239"/>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="M4" s="240"/>
+      <c r="B4" s="226"/>
+      <c r="C4" s="226"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="226"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="226"/>
+      <c r="K4" s="226"/>
+      <c r="L4" s="226"/>
+      <c r="M4" s="227"/>
       <c r="N4" s="96"/>
     </row>
     <row r="5" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="241"/>
-      <c r="B5" s="242"/>
-      <c r="C5" s="242"/>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
-      <c r="M5" s="243"/>
+      <c r="A5" s="228"/>
+      <c r="B5" s="229"/>
+      <c r="C5" s="229"/>
+      <c r="D5" s="229"/>
+      <c r="E5" s="229"/>
+      <c r="F5" s="229"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="229"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
+      <c r="L5" s="229"/>
+      <c r="M5" s="230"/>
       <c r="N5" s="96"/>
     </row>
     <row r="6" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="241"/>
-      <c r="B6" s="242"/>
-      <c r="C6" s="242"/>
-      <c r="D6" s="242"/>
-      <c r="E6" s="242"/>
-      <c r="F6" s="242"/>
-      <c r="G6" s="242"/>
-      <c r="H6" s="242"/>
-      <c r="I6" s="242"/>
-      <c r="J6" s="242"/>
-      <c r="K6" s="242"/>
-      <c r="L6" s="242"/>
-      <c r="M6" s="243"/>
+      <c r="A6" s="228"/>
+      <c r="B6" s="229"/>
+      <c r="C6" s="229"/>
+      <c r="D6" s="229"/>
+      <c r="E6" s="229"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="229"/>
+      <c r="H6" s="229"/>
+      <c r="I6" s="229"/>
+      <c r="J6" s="229"/>
+      <c r="K6" s="229"/>
+      <c r="L6" s="229"/>
+      <c r="M6" s="230"/>
       <c r="N6" s="96"/>
     </row>
     <row r="7" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="241"/>
-      <c r="B7" s="242"/>
-      <c r="C7" s="242"/>
-      <c r="D7" s="242"/>
-      <c r="E7" s="242"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="242"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="242"/>
-      <c r="K7" s="242"/>
-      <c r="L7" s="242"/>
-      <c r="M7" s="243"/>
+      <c r="A7" s="228"/>
+      <c r="B7" s="229"/>
+      <c r="C7" s="229"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="229"/>
+      <c r="H7" s="229"/>
+      <c r="I7" s="229"/>
+      <c r="J7" s="229"/>
+      <c r="K7" s="229"/>
+      <c r="L7" s="229"/>
+      <c r="M7" s="230"/>
       <c r="N7" s="96"/>
     </row>
     <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="244"/>
-      <c r="B8" s="245"/>
-      <c r="C8" s="245"/>
-      <c r="D8" s="245"/>
-      <c r="E8" s="245"/>
-      <c r="F8" s="245"/>
-      <c r="G8" s="245"/>
-      <c r="H8" s="245"/>
-      <c r="I8" s="245"/>
-      <c r="J8" s="245"/>
-      <c r="K8" s="245"/>
-      <c r="L8" s="245"/>
-      <c r="M8" s="246"/>
+      <c r="A8" s="231"/>
+      <c r="B8" s="232"/>
+      <c r="C8" s="232"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="232"/>
+      <c r="G8" s="232"/>
+      <c r="H8" s="232"/>
+      <c r="I8" s="232"/>
+      <c r="J8" s="232"/>
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="233"/>
     </row>
     <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="234" t="s">
+      <c r="A9" s="221" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="235"/>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="236"/>
+      <c r="B9" s="222"/>
+      <c r="C9" s="222"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="222"/>
+      <c r="K9" s="222"/>
+      <c r="L9" s="222"/>
+      <c r="M9" s="223"/>
     </row>
     <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="253" t="s">
+      <c r="A10" s="242" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="254"/>
-      <c r="C10" s="254"/>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="254"/>
-      <c r="G10" s="254"/>
-      <c r="H10" s="254"/>
-      <c r="I10" s="254"/>
-      <c r="J10" s="254"/>
-      <c r="K10" s="254"/>
-      <c r="L10" s="254"/>
-      <c r="M10" s="255"/>
+      <c r="B10" s="243"/>
+      <c r="C10" s="243"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="243"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="243"/>
+      <c r="M10" s="244"/>
     </row>
     <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="256" t="s">
+      <c r="A11" s="245" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="257"/>
-      <c r="C11" s="257"/>
-      <c r="D11" s="257"/>
-      <c r="E11" s="257"/>
-      <c r="F11" s="257"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
-      <c r="M11" s="258"/>
+      <c r="B11" s="246"/>
+      <c r="C11" s="246"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
+      <c r="M11" s="247"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="247" t="s">
+      <c r="A12" s="234" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="249" t="s">
+      <c r="B12" s="236" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="249" t="s">
+      <c r="C12" s="236" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="249" t="s">
+      <c r="D12" s="236" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="227" t="s">
+      <c r="E12" s="238" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="249" t="s">
+      <c r="F12" s="236" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="251" t="s">
+      <c r="G12" s="240" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="227" t="s">
+      <c r="H12" s="238" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="227" t="s">
+      <c r="I12" s="238" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="227" t="s">
+      <c r="J12" s="238" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="229" t="s">
+      <c r="K12" s="249" t="s">
         <v>247</v>
       </c>
       <c r="L12" s="195" t="s">
         <v>140</v>
       </c>
-      <c r="M12" s="231" t="s">
+      <c r="M12" s="251" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="248"/>
-      <c r="B13" s="250"/>
-      <c r="C13" s="250"/>
-      <c r="D13" s="250"/>
-      <c r="E13" s="228"/>
-      <c r="F13" s="250"/>
-      <c r="G13" s="252"/>
-      <c r="H13" s="228"/>
-      <c r="I13" s="228"/>
-      <c r="J13" s="228"/>
-      <c r="K13" s="230"/>
+      <c r="A13" s="235"/>
+      <c r="B13" s="237"/>
+      <c r="C13" s="237"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="237"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="239"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="250"/>
       <c r="L13" s="196" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M13" s="232"/>
+      <c r="M13" s="252"/>
     </row>
     <row r="14" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="179">
@@ -9271,87 +9186,90 @@
     </row>
     <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="233" t="s">
+      <c r="B121" s="220" t="s">
         <v>106</v>
       </c>
-      <c r="C121" s="233"/>
-      <c r="D121" s="233"/>
-      <c r="E121" s="233"/>
-      <c r="F121" s="233"/>
-      <c r="G121" s="233"/>
-      <c r="H121" s="233"/>
-      <c r="I121" s="233"/>
-      <c r="J121" s="233"/>
-      <c r="K121" s="233"/>
-      <c r="L121" s="233"/>
+      <c r="C121" s="220"/>
+      <c r="D121" s="220"/>
+      <c r="E121" s="220"/>
+      <c r="F121" s="220"/>
+      <c r="G121" s="220"/>
+      <c r="H121" s="220"/>
+      <c r="I121" s="220"/>
+      <c r="J121" s="220"/>
+      <c r="K121" s="220"/>
+      <c r="L121" s="220"/>
     </row>
     <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="233"/>
-      <c r="C122" s="233"/>
-      <c r="D122" s="233"/>
-      <c r="E122" s="233"/>
-      <c r="F122" s="233"/>
-      <c r="G122" s="233"/>
-      <c r="H122" s="233"/>
-      <c r="I122" s="233"/>
-      <c r="J122" s="233"/>
-      <c r="K122" s="233"/>
-      <c r="L122" s="233"/>
+      <c r="B122" s="220"/>
+      <c r="C122" s="220"/>
+      <c r="D122" s="220"/>
+      <c r="E122" s="220"/>
+      <c r="F122" s="220"/>
+      <c r="G122" s="220"/>
+      <c r="H122" s="220"/>
+      <c r="I122" s="220"/>
+      <c r="J122" s="220"/>
+      <c r="K122" s="220"/>
+      <c r="L122" s="220"/>
     </row>
     <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="233"/>
-      <c r="C123" s="233"/>
-      <c r="D123" s="233"/>
-      <c r="E123" s="233"/>
-      <c r="F123" s="233"/>
-      <c r="G123" s="233"/>
-      <c r="H123" s="233"/>
-      <c r="I123" s="233"/>
-      <c r="J123" s="233"/>
-      <c r="K123" s="233"/>
-      <c r="L123" s="233"/>
+      <c r="B123" s="220"/>
+      <c r="C123" s="220"/>
+      <c r="D123" s="220"/>
+      <c r="E123" s="220"/>
+      <c r="F123" s="220"/>
+      <c r="G123" s="220"/>
+      <c r="H123" s="220"/>
+      <c r="I123" s="220"/>
+      <c r="J123" s="220"/>
+      <c r="K123" s="220"/>
+      <c r="L123" s="220"/>
     </row>
     <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="233"/>
-      <c r="C124" s="233"/>
-      <c r="D124" s="233"/>
-      <c r="E124" s="233"/>
-      <c r="F124" s="233"/>
-      <c r="G124" s="233"/>
-      <c r="H124" s="233"/>
-      <c r="I124" s="233"/>
-      <c r="J124" s="233"/>
-      <c r="K124" s="233"/>
-      <c r="L124" s="233"/>
+      <c r="B124" s="220"/>
+      <c r="C124" s="220"/>
+      <c r="D124" s="220"/>
+      <c r="E124" s="220"/>
+      <c r="F124" s="220"/>
+      <c r="G124" s="220"/>
+      <c r="H124" s="220"/>
+      <c r="I124" s="220"/>
+      <c r="J124" s="220"/>
+      <c r="K124" s="220"/>
+      <c r="L124" s="220"/>
     </row>
     <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="233"/>
-      <c r="C125" s="233"/>
-      <c r="D125" s="233"/>
-      <c r="E125" s="233"/>
-      <c r="F125" s="233"/>
-      <c r="G125" s="233"/>
-      <c r="H125" s="233"/>
-      <c r="I125" s="233"/>
-      <c r="J125" s="233"/>
-      <c r="K125" s="233"/>
-      <c r="L125" s="233"/>
+      <c r="B125" s="220"/>
+      <c r="C125" s="220"/>
+      <c r="D125" s="220"/>
+      <c r="E125" s="220"/>
+      <c r="F125" s="220"/>
+      <c r="G125" s="220"/>
+      <c r="H125" s="220"/>
+      <c r="I125" s="220"/>
+      <c r="J125" s="220"/>
+      <c r="K125" s="220"/>
+      <c r="L125" s="220"/>
     </row>
     <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="233"/>
-      <c r="C126" s="233"/>
-      <c r="D126" s="233"/>
-      <c r="E126" s="233"/>
-      <c r="F126" s="233"/>
-      <c r="G126" s="233"/>
-      <c r="H126" s="233"/>
-      <c r="I126" s="233"/>
-      <c r="J126" s="233"/>
-      <c r="K126" s="233"/>
-      <c r="L126" s="233"/>
+      <c r="B126" s="220"/>
+      <c r="C126" s="220"/>
+      <c r="D126" s="220"/>
+      <c r="E126" s="220"/>
+      <c r="F126" s="220"/>
+      <c r="G126" s="220"/>
+      <c r="H126" s="220"/>
+      <c r="I126" s="220"/>
+      <c r="J126" s="220"/>
+      <c r="K126" s="220"/>
+      <c r="L126" s="220"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
     <mergeCell ref="B121:L126"/>
     <mergeCell ref="A9:M9"/>
     <mergeCell ref="D1:L1"/>
@@ -9368,9 +9286,6 @@
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I12:I13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9411,10 +9326,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C4" s="273" t="s">
+      <c r="C4" s="253" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="273"/>
+      <c r="D4" s="253"/>
       <c r="E4" s="201"/>
       <c r="F4" s="199" t="s">
         <v>258</v>
@@ -9422,16 +9337,16 @@
       <c r="H4" t="s">
         <v>259</v>
       </c>
-      <c r="J4" s="263" t="s">
+      <c r="J4" s="255" t="s">
         <v>261</v>
       </c>
-      <c r="K4" s="263"/>
+      <c r="K4" s="255"/>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C5" s="262">
+      <c r="C5" s="254">
         <v>168835.53000000003</v>
       </c>
-      <c r="D5" s="262"/>
+      <c r="D5" s="254"/>
       <c r="E5" s="202"/>
       <c r="F5" s="200">
         <f>C5</f>
@@ -9440,18 +9355,18 @@
       <c r="H5" s="80">
         <v>0</v>
       </c>
-      <c r="J5" s="274">
+      <c r="J5" s="256">
         <f>F5</f>
         <v>168835.53000000003</v>
       </c>
-      <c r="K5" s="274"/>
+      <c r="K5" s="256"/>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M7" s="261" t="s">
+      <c r="M7" s="259" t="s">
         <v>263</v>
       </c>
-      <c r="N7" s="261"/>
-      <c r="O7" s="261"/>
+      <c r="N7" s="259"/>
+      <c r="O7" s="259"/>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
@@ -9463,19 +9378,19 @@
       <c r="H8" t="s">
         <v>259</v>
       </c>
-      <c r="J8" s="263" t="s">
+      <c r="J8" s="255" t="s">
         <v>262</v>
       </c>
-      <c r="K8" s="263"/>
-      <c r="M8" s="261"/>
-      <c r="N8" s="261"/>
-      <c r="O8" s="261"/>
+      <c r="K8" s="255"/>
+      <c r="M8" s="259"/>
+      <c r="N8" s="259"/>
+      <c r="O8" s="259"/>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C9" s="262">
+      <c r="C9" s="254">
         <v>168836.53</v>
       </c>
-      <c r="D9" s="262"/>
+      <c r="D9" s="254"/>
       <c r="F9" s="80">
         <v>0</v>
       </c>
@@ -9483,16 +9398,16 @@
         <f>C9-F9</f>
         <v>168836.53</v>
       </c>
-      <c r="J9" s="262">
+      <c r="J9" s="254">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K9" s="262"/>
-      <c r="M9" s="260">
+      <c r="K9" s="254"/>
+      <c r="M9" s="258">
         <v>300737.53000000003</v>
       </c>
-      <c r="N9" s="260"/>
-      <c r="O9" s="260"/>
+      <c r="N9" s="258"/>
+      <c r="O9" s="258"/>
     </row>
     <row r="10" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="202"/>
@@ -9506,11 +9421,11 @@
       <c r="O10" s="203"/>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M11" s="267" t="s">
+      <c r="M11" s="263" t="s">
         <v>263</v>
       </c>
-      <c r="N11" s="268"/>
-      <c r="O11" s="269"/>
+      <c r="N11" s="264"/>
+      <c r="O11" s="265"/>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
@@ -9522,20 +9437,20 @@
       <c r="H12" t="s">
         <v>259</v>
       </c>
-      <c r="J12" s="263" t="s">
+      <c r="J12" s="255" t="s">
         <v>265</v>
       </c>
-      <c r="K12" s="263"/>
-      <c r="M12" s="270"/>
-      <c r="N12" s="271"/>
-      <c r="O12" s="272"/>
+      <c r="K12" s="255"/>
+      <c r="M12" s="266"/>
+      <c r="N12" s="267"/>
+      <c r="O12" s="268"/>
     </row>
     <row r="13" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="262">
+      <c r="C13" s="254">
         <f>M9</f>
         <v>300737.53000000003</v>
       </c>
-      <c r="D13" s="262"/>
+      <c r="D13" s="254"/>
       <c r="F13" s="80">
         <v>98556.53</v>
       </c>
@@ -9543,132 +9458,127 @@
         <f>C13-F13</f>
         <v>202181.00000000003</v>
       </c>
-      <c r="J13" s="262">
+      <c r="J13" s="254">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K13" s="262"/>
-      <c r="M13" s="264">
+      <c r="K13" s="254"/>
+      <c r="M13" s="260">
         <f>J13+H13-0.27</f>
         <v>371016.53</v>
       </c>
-      <c r="N13" s="265"/>
-      <c r="O13" s="266"/>
+      <c r="N13" s="261"/>
+      <c r="O13" s="262"/>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C15" s="259" t="s">
+      <c r="C15" s="257" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="259"/>
-      <c r="E15" s="259"/>
-      <c r="F15" s="259"/>
-      <c r="G15" s="259"/>
-      <c r="H15" s="259"/>
-      <c r="I15" s="259"/>
-      <c r="J15" s="259"/>
-      <c r="K15" s="259"/>
-      <c r="L15" s="259"/>
-      <c r="M15" s="259"/>
-      <c r="N15" s="259"/>
-      <c r="O15" s="259"/>
+      <c r="D15" s="257"/>
+      <c r="E15" s="257"/>
+      <c r="F15" s="257"/>
+      <c r="G15" s="257"/>
+      <c r="H15" s="257"/>
+      <c r="I15" s="257"/>
+      <c r="J15" s="257"/>
+      <c r="K15" s="257"/>
+      <c r="L15" s="257"/>
+      <c r="M15" s="257"/>
+      <c r="N15" s="257"/>
+      <c r="O15" s="257"/>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C16" s="259"/>
-      <c r="D16" s="259"/>
-      <c r="E16" s="259"/>
-      <c r="F16" s="259"/>
-      <c r="G16" s="259"/>
-      <c r="H16" s="259"/>
-      <c r="I16" s="259"/>
-      <c r="J16" s="259"/>
-      <c r="K16" s="259"/>
-      <c r="L16" s="259"/>
-      <c r="M16" s="259"/>
-      <c r="N16" s="259"/>
-      <c r="O16" s="259"/>
+      <c r="C16" s="257"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="257"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="257"/>
+      <c r="J16" s="257"/>
+      <c r="K16" s="257"/>
+      <c r="L16" s="257"/>
+      <c r="M16" s="257"/>
+      <c r="N16" s="257"/>
+      <c r="O16" s="257"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C17" s="259"/>
-      <c r="D17" s="259"/>
-      <c r="E17" s="259"/>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
-      <c r="J17" s="259"/>
-      <c r="K17" s="259"/>
-      <c r="L17" s="259"/>
-      <c r="M17" s="259"/>
-      <c r="N17" s="259"/>
-      <c r="O17" s="259"/>
+      <c r="C17" s="257"/>
+      <c r="D17" s="257"/>
+      <c r="E17" s="257"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
+      <c r="J17" s="257"/>
+      <c r="K17" s="257"/>
+      <c r="L17" s="257"/>
+      <c r="M17" s="257"/>
+      <c r="N17" s="257"/>
+      <c r="O17" s="257"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C18" s="259"/>
-      <c r="D18" s="259"/>
-      <c r="E18" s="259"/>
-      <c r="F18" s="259"/>
-      <c r="G18" s="259"/>
-      <c r="H18" s="259"/>
-      <c r="I18" s="259"/>
-      <c r="J18" s="259"/>
-      <c r="K18" s="259"/>
-      <c r="L18" s="259"/>
-      <c r="M18" s="259"/>
-      <c r="N18" s="259"/>
-      <c r="O18" s="259"/>
+      <c r="C18" s="257"/>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="257"/>
+      <c r="J18" s="257"/>
+      <c r="K18" s="257"/>
+      <c r="L18" s="257"/>
+      <c r="M18" s="257"/>
+      <c r="N18" s="257"/>
+      <c r="O18" s="257"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C19" s="259"/>
-      <c r="D19" s="259"/>
-      <c r="E19" s="259"/>
-      <c r="F19" s="259"/>
-      <c r="G19" s="259"/>
-      <c r="H19" s="259"/>
-      <c r="I19" s="259"/>
-      <c r="J19" s="259"/>
-      <c r="K19" s="259"/>
-      <c r="L19" s="259"/>
-      <c r="M19" s="259"/>
-      <c r="N19" s="259"/>
-      <c r="O19" s="259"/>
+      <c r="C19" s="257"/>
+      <c r="D19" s="257"/>
+      <c r="E19" s="257"/>
+      <c r="F19" s="257"/>
+      <c r="G19" s="257"/>
+      <c r="H19" s="257"/>
+      <c r="I19" s="257"/>
+      <c r="J19" s="257"/>
+      <c r="K19" s="257"/>
+      <c r="L19" s="257"/>
+      <c r="M19" s="257"/>
+      <c r="N19" s="257"/>
+      <c r="O19" s="257"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C20" s="259"/>
-      <c r="D20" s="259"/>
-      <c r="E20" s="259"/>
-      <c r="F20" s="259"/>
-      <c r="G20" s="259"/>
-      <c r="H20" s="259"/>
-      <c r="I20" s="259"/>
-      <c r="J20" s="259"/>
-      <c r="K20" s="259"/>
-      <c r="L20" s="259"/>
-      <c r="M20" s="259"/>
-      <c r="N20" s="259"/>
-      <c r="O20" s="259"/>
+      <c r="C20" s="257"/>
+      <c r="D20" s="257"/>
+      <c r="E20" s="257"/>
+      <c r="F20" s="257"/>
+      <c r="G20" s="257"/>
+      <c r="H20" s="257"/>
+      <c r="I20" s="257"/>
+      <c r="J20" s="257"/>
+      <c r="K20" s="257"/>
+      <c r="L20" s="257"/>
+      <c r="M20" s="257"/>
+      <c r="N20" s="257"/>
+      <c r="O20" s="257"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="259"/>
-      <c r="D21" s="259"/>
-      <c r="E21" s="259"/>
-      <c r="F21" s="259"/>
-      <c r="G21" s="259"/>
-      <c r="H21" s="259"/>
-      <c r="I21" s="259"/>
-      <c r="J21" s="259"/>
-      <c r="K21" s="259"/>
-      <c r="L21" s="259"/>
-      <c r="M21" s="259"/>
-      <c r="N21" s="259"/>
-      <c r="O21" s="259"/>
+      <c r="C21" s="257"/>
+      <c r="D21" s="257"/>
+      <c r="E21" s="257"/>
+      <c r="F21" s="257"/>
+      <c r="G21" s="257"/>
+      <c r="H21" s="257"/>
+      <c r="I21" s="257"/>
+      <c r="J21" s="257"/>
+      <c r="K21" s="257"/>
+      <c r="L21" s="257"/>
+      <c r="M21" s="257"/>
+      <c r="N21" s="257"/>
+      <c r="O21" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J8:K8"/>
     <mergeCell ref="C15:O21"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="M7:O8"/>
@@ -9679,6 +9589,11 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M11:O12"/>
     <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="125" orientation="landscape" r:id="rId1"/>
@@ -9687,7 +9602,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DC61AA-F548-49A9-A9B8-49FB942F95D7}">
-  <dimension ref="C1:K21"/>
+  <dimension ref="D4:N13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -9696,270 +9611,107 @@
     <col min="11" max="11" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="275" t="s">
-        <v>277</v>
-      </c>
-      <c r="D2" s="276"/>
-      <c r="E2" s="276"/>
-      <c r="F2" s="276"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="276"/>
-      <c r="I2" s="277"/>
-    </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C3" s="207" t="s">
+    <row r="4" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F4" s="80">
+        <v>843306.42</v>
+      </c>
+      <c r="G4" s="271" t="s">
+        <v>274</v>
+      </c>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="M4" s="271"/>
+      <c r="N4" s="271"/>
+    </row>
+    <row r="5" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="270">
+        <v>-68000</v>
+      </c>
+      <c r="G5" s="271"/>
+      <c r="H5" s="271"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="M5" s="271"/>
+      <c r="N5" s="271"/>
+    </row>
+    <row r="6" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="4" spans="3:11" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" s="208" t="s">
-        <v>258</v>
-      </c>
-      <c r="E4" s="208" t="s">
-        <v>269</v>
-      </c>
-      <c r="F4" s="208" t="s">
+      <c r="F6" s="63">
+        <f>F4+F5</f>
+        <v>775306.42</v>
+      </c>
+      <c r="G6" s="271"/>
+      <c r="H6" s="271"/>
+      <c r="I6" s="271"/>
+      <c r="J6" s="271"/>
+      <c r="K6" s="271"/>
+      <c r="L6" s="271"/>
+      <c r="M6" s="271"/>
+      <c r="N6" s="271"/>
+    </row>
+    <row r="7" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="G7" s="271"/>
+      <c r="H7" s="271"/>
+      <c r="I7" s="271"/>
+      <c r="J7" s="271"/>
+      <c r="K7" s="271"/>
+      <c r="L7" s="271"/>
+      <c r="M7" s="271"/>
+      <c r="N7" s="271"/>
+    </row>
+    <row r="8" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
         <v>271</v>
       </c>
-      <c r="G4" s="210" t="s">
+      <c r="F8" s="80">
+        <v>135235.80000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
         <v>272</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="F9" s="80">
+        <v>33600.000000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D11" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="I4" s="210" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C5" s="211">
-        <v>598682.42000000004</v>
-      </c>
-      <c r="D5" s="209">
-        <v>150000.42000000001</v>
-      </c>
-      <c r="E5" s="209">
-        <v>448682</v>
-      </c>
-      <c r="F5" s="209">
-        <v>13460.46</v>
-      </c>
-      <c r="G5" s="209">
-        <v>135235.80000000002</v>
-      </c>
-      <c r="H5" s="209">
-        <v>33600.000000000007</v>
-      </c>
-      <c r="I5" s="209">
-        <v>630978.42000000004</v>
-      </c>
-      <c r="K5" s="63">
-        <f>E5+F5+G5+H5</f>
-        <v>630978.26</v>
-      </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C7" s="207" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="269">
+        <f>F6+F8+F9</f>
+        <v>944142.22000000009</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="D13" s="272" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="8" spans="3:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C8" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="208" t="s">
-        <v>258</v>
-      </c>
-      <c r="E8" s="208" t="s">
-        <v>269</v>
-      </c>
-      <c r="F8" s="208" t="s">
-        <v>271</v>
-      </c>
-      <c r="G8" s="210" t="s">
-        <v>272</v>
-      </c>
-      <c r="H8" s="210" t="s">
-        <v>273</v>
-      </c>
-      <c r="I8" s="210" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C9" s="211">
-        <v>630978.42000000004</v>
-      </c>
-      <c r="D9" s="209">
-        <v>0</v>
-      </c>
-      <c r="E9" s="209">
-        <v>630978.42000000004</v>
-      </c>
-      <c r="F9" s="209">
-        <v>18929.352600000002</v>
-      </c>
-      <c r="G9" s="209">
-        <v>135235.80000000002</v>
-      </c>
-      <c r="H9" s="209">
-        <v>33600.000000000007</v>
-      </c>
-      <c r="I9" s="209">
-        <v>818744.42</v>
-      </c>
-      <c r="K9" s="63">
-        <f>E9+F9+G9+H9</f>
-        <v>818743.57260000007</v>
-      </c>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C11" s="207" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12" spans="3:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C12" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="D12" s="208" t="s">
-        <v>258</v>
-      </c>
-      <c r="E12" s="208" t="s">
-        <v>269</v>
-      </c>
-      <c r="F12" s="208" t="s">
-        <v>271</v>
-      </c>
-      <c r="G12" s="210" t="s">
-        <v>272</v>
-      </c>
-      <c r="H12" s="210" t="s">
-        <v>273</v>
-      </c>
-      <c r="I12" s="210" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C13" s="211">
-        <f>I9</f>
-        <v>818744.42</v>
-      </c>
-      <c r="D13" s="209">
-        <v>0</v>
-      </c>
-      <c r="E13" s="209">
-        <v>818744.42</v>
-      </c>
-      <c r="F13" s="209">
-        <v>0</v>
-      </c>
-      <c r="G13" s="209">
-        <v>135235.80000000002</v>
-      </c>
-      <c r="H13" s="209">
-        <v>33600.000000000007</v>
-      </c>
-      <c r="I13" s="212">
-        <v>1012143.42</v>
-      </c>
-      <c r="K13" s="63">
-        <f>E13+F13+G13+H13</f>
-        <v>987580.22000000009</v>
-      </c>
-    </row>
-    <row r="14" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="287"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="288"/>
-      <c r="K14" s="63"/>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C15" s="289" t="s">
-        <v>281</v>
-      </c>
-      <c r="D15" s="290"/>
-      <c r="E15" s="290"/>
-      <c r="F15" s="290"/>
-      <c r="G15" s="290"/>
-      <c r="H15" s="290"/>
-      <c r="I15" s="291"/>
-      <c r="K15" s="63"/>
-    </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C16" s="292"/>
-      <c r="D16" s="293"/>
-      <c r="E16" s="293"/>
-      <c r="F16" s="293"/>
-      <c r="G16" s="293"/>
-      <c r="H16" s="293"/>
-      <c r="I16" s="294"/>
-      <c r="K16" s="63"/>
-    </row>
-    <row r="17" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="295"/>
-      <c r="D17" s="296"/>
-      <c r="E17" s="296"/>
-      <c r="F17" s="296"/>
-      <c r="G17" s="296"/>
-      <c r="H17" s="296"/>
-      <c r="I17" s="297"/>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="278" t="s">
-        <v>280</v>
-      </c>
-      <c r="D18" s="279"/>
-      <c r="E18" s="279"/>
-      <c r="F18" s="279"/>
-      <c r="G18" s="279"/>
-      <c r="H18" s="279"/>
-      <c r="I18" s="280"/>
-    </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="281"/>
-      <c r="D19" s="282"/>
-      <c r="E19" s="282"/>
-      <c r="F19" s="282"/>
-      <c r="G19" s="282"/>
-      <c r="H19" s="282"/>
-      <c r="I19" s="283"/>
-    </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="281"/>
-      <c r="D20" s="282"/>
-      <c r="E20" s="282"/>
-      <c r="F20" s="282"/>
-      <c r="G20" s="282"/>
-      <c r="H20" s="282"/>
-      <c r="I20" s="283"/>
-    </row>
-    <row r="21" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="284"/>
-      <c r="D21" s="285"/>
-      <c r="E21" s="285"/>
-      <c r="F21" s="285"/>
-      <c r="G21" s="285"/>
-      <c r="H21" s="285"/>
-      <c r="I21" s="286"/>
+      <c r="E13" s="272"/>
+      <c r="F13" s="272"/>
+      <c r="G13" s="272"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="C18:I21"/>
-    <mergeCell ref="C15:I17"/>
+  <mergeCells count="2">
+    <mergeCell ref="G4:N7"/>
+    <mergeCell ref="D13:G13"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="110" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4F7661-4BA4-47B2-95DB-79898E2D4F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29022F05-9C42-490B-A2C2-386EF01AFF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="279">
   <si>
     <t>TOTAL</t>
   </si>
@@ -871,6 +871,15 @@
   </si>
   <si>
     <t xml:space="preserve">El saldo total sera abonado mediante 24 cuotas de $33.000 </t>
+  </si>
+  <si>
+    <t>Al 7D le debemos poner el deposito no identificado de enero de $110,000 este mes debe abonar $123.612,51</t>
+  </si>
+  <si>
+    <t>El 3C tiene nuevo propietario,  Marotta Pablo, agregarlo a la cadena de mails pabloeze.marotta@gmail.com</t>
+  </si>
+  <si>
+    <t>8C deposito $132.520 el 12/03</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1078,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1160,6 +1169,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF74FA84"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="37">
     <border>
@@ -1626,7 +1647,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="273">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1968,6 +1989,19 @@
     <xf numFmtId="0" fontId="19" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2007,6 +2041,93 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2018,93 +2139,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2150,13 +2184,21 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2165,6 +2207,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF74FA84"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2539,12 +2586,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="216" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="210"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="216"/>
+      <c r="E1" s="217"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2557,12 +2604,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="220" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="213"/>
-      <c r="D3" s="213"/>
-      <c r="E3" s="214"/>
+      <c r="C3" s="220"/>
+      <c r="D3" s="220"/>
+      <c r="E3" s="221"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2600,49 +2647,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="215" t="s">
+      <c r="B8" s="222" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="215"/>
+      <c r="C8" s="222"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="215"/>
-      <c r="C9" s="215"/>
+      <c r="B9" s="222"/>
+      <c r="C9" s="222"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="215"/>
-      <c r="C10" s="215"/>
+      <c r="B10" s="222"/>
+      <c r="C10" s="222"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="223" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="216"/>
-      <c r="C13" s="216"/>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
+      <c r="B13" s="223"/>
+      <c r="C13" s="223"/>
+      <c r="D13" s="223"/>
+      <c r="E13" s="223"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="216"/>
-      <c r="B14" s="216"/>
-      <c r="C14" s="216"/>
-      <c r="D14" s="216"/>
-      <c r="E14" s="216"/>
+      <c r="A14" s="223"/>
+      <c r="B14" s="223"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="223"/>
+      <c r="E14" s="223"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="216"/>
-      <c r="B15" s="216"/>
-      <c r="C15" s="216"/>
-      <c r="D15" s="216"/>
-      <c r="E15" s="216"/>
+      <c r="A15" s="223"/>
+      <c r="B15" s="223"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="223"/>
+      <c r="E15" s="223"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="216"/>
-      <c r="B16" s="216"/>
-      <c r="C16" s="216"/>
-      <c r="D16" s="216"/>
-      <c r="E16" s="216"/>
+      <c r="A16" s="223"/>
+      <c r="B16" s="223"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2668,10 +2715,10 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="211" t="s">
+      <c r="A22" s="218" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="212"/>
+      <c r="B22" s="219"/>
       <c r="C22" s="22"/>
       <c r="D22" s="167">
         <v>1931623</v>
@@ -2680,10 +2727,10 @@
       <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="211" t="s">
+      <c r="A23" s="218" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="212"/>
+      <c r="B23" s="219"/>
       <c r="C23" s="22"/>
       <c r="D23" s="167">
         <v>-420128</v>
@@ -2692,10 +2739,10 @@
       <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="211" t="s">
+      <c r="A24" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="212"/>
+      <c r="B24" s="219"/>
       <c r="C24" s="22"/>
       <c r="D24" s="168">
         <v>0</v>
@@ -2867,10 +2914,10 @@
       <c r="E38" s="29"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="207" t="s">
+      <c r="A39" s="214" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="208"/>
+      <c r="B39" s="215"/>
       <c r="C39" s="32"/>
       <c r="D39" s="169">
         <v>313739</v>
@@ -2880,10 +2927,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="207" t="s">
+      <c r="A40" s="214" t="s">
         <v>253</v>
       </c>
-      <c r="B40" s="208"/>
+      <c r="B40" s="215"/>
       <c r="C40" s="32"/>
       <c r="D40" s="170">
         <v>214164</v>
@@ -2893,10 +2940,10 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="207" t="s">
+      <c r="A41" s="214" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="208"/>
+      <c r="B41" s="215"/>
       <c r="C41" s="32"/>
       <c r="D41" s="170">
         <v>5204</v>
@@ -2981,10 +3028,10 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="207" t="s">
+      <c r="A48" s="214" t="s">
         <v>114</v>
       </c>
-      <c r="B48" s="208"/>
+      <c r="B48" s="215"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38">
         <v>4813938.26</v>
@@ -3022,10 +3069,10 @@
       <c r="E51" s="43"/>
     </row>
     <row r="52" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="211" t="s">
+      <c r="A52" s="218" t="s">
         <v>178</v>
       </c>
-      <c r="B52" s="212"/>
+      <c r="B52" s="219"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38">
         <v>225000</v>
@@ -3035,10 +3082,10 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="211" t="s">
+      <c r="A53" s="218" t="s">
         <v>190</v>
       </c>
-      <c r="B53" s="212"/>
+      <c r="B53" s="219"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38">
         <v>500000</v>
@@ -3048,10 +3095,10 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="211" t="s">
+      <c r="A54" s="218" t="s">
         <v>193</v>
       </c>
-      <c r="B54" s="212"/>
+      <c r="B54" s="219"/>
       <c r="C54" s="37"/>
       <c r="D54" s="38">
         <v>1520000</v>
@@ -3061,10 +3108,10 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="211" t="s">
+      <c r="A55" s="218" t="s">
         <v>222</v>
       </c>
-      <c r="B55" s="212"/>
+      <c r="B55" s="219"/>
       <c r="C55" s="37"/>
       <c r="D55" s="38">
         <f>272252*2</f>
@@ -3075,10 +3122,10 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="211" t="s">
+      <c r="A56" s="218" t="s">
         <v>208</v>
       </c>
-      <c r="B56" s="212"/>
+      <c r="B56" s="219"/>
       <c r="C56" s="37"/>
       <c r="D56" s="38">
         <v>85000</v>
@@ -3089,10 +3136,10 @@
       <c r="F56" s="63"/>
     </row>
     <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="211" t="s">
+      <c r="A57" s="218" t="s">
         <v>227</v>
       </c>
-      <c r="B57" s="212"/>
+      <c r="B57" s="219"/>
       <c r="C57" s="37"/>
       <c r="D57" s="38">
         <v>120000</v>
@@ -3117,10 +3164,10 @@
       <c r="F58" s="63"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="211" t="s">
+      <c r="A59" s="218" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="212"/>
+      <c r="B59" s="219"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38">
         <v>6000</v>
@@ -3131,10 +3178,10 @@
       <c r="F59" s="63"/>
     </row>
     <row r="60" spans="1:6" ht="85.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="211" t="s">
+      <c r="A60" s="218" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="212"/>
+      <c r="B60" s="219"/>
       <c r="C60" s="37"/>
       <c r="D60" s="38">
         <v>7000000</v>
@@ -3187,10 +3234,10 @@
       <c r="F63" s="63"/>
     </row>
     <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="211" t="s">
+      <c r="A64" s="218" t="s">
         <v>206</v>
       </c>
-      <c r="B64" s="212"/>
+      <c r="B64" s="219"/>
       <c r="C64" s="37"/>
       <c r="D64" s="38">
         <v>250000</v>
@@ -3215,10 +3262,10 @@
       <c r="F65" s="63"/>
     </row>
     <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="211" t="s">
+      <c r="A66" s="218" t="s">
         <v>199</v>
       </c>
-      <c r="B66" s="212"/>
+      <c r="B66" s="219"/>
       <c r="C66" s="37"/>
       <c r="D66" s="38">
         <v>105602.65</v>
@@ -3229,10 +3276,10 @@
       <c r="F66" s="63"/>
     </row>
     <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="211" t="s">
+      <c r="A67" s="218" t="s">
         <v>184</v>
       </c>
-      <c r="B67" s="212"/>
+      <c r="B67" s="219"/>
       <c r="C67" s="37"/>
       <c r="D67" s="38">
         <v>2022800</v>
@@ -3263,10 +3310,10 @@
       <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="211" t="s">
+      <c r="A70" s="218" t="s">
         <v>192</v>
       </c>
-      <c r="B70" s="212"/>
+      <c r="B70" s="219"/>
       <c r="C70" s="22"/>
       <c r="D70" s="171">
         <v>650000</v>
@@ -3287,10 +3334,10 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="211" t="s">
+      <c r="A72" s="218" t="s">
         <v>221</v>
       </c>
-      <c r="B72" s="212"/>
+      <c r="B72" s="219"/>
       <c r="C72" s="22"/>
       <c r="D72" s="172">
         <v>62500</v>
@@ -3453,8 +3500,8 @@
       <c r="E88" s="73"/>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="211"/>
-      <c r="B89" s="212"/>
+      <c r="A89" s="218"/>
+      <c r="B89" s="219"/>
       <c r="C89" s="37"/>
       <c r="D89" s="45"/>
       <c r="E89" s="73"/>
@@ -3550,42 +3597,42 @@
       </c>
     </row>
     <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="219" t="s">
+      <c r="A105" s="226" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="219"/>
+      <c r="B105" s="226"/>
     </row>
     <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="219"/>
-      <c r="B106" s="219"/>
+      <c r="A106" s="226"/>
+      <c r="B106" s="226"/>
     </row>
     <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="219"/>
-      <c r="B107" s="219"/>
+      <c r="A107" s="226"/>
+      <c r="B107" s="226"/>
     </row>
     <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="219" t="s">
+      <c r="A109" s="226" t="s">
         <v>239</v>
       </c>
-      <c r="B109" s="219"/>
+      <c r="B109" s="226"/>
     </row>
     <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="219"/>
-      <c r="B110" s="219"/>
+      <c r="A110" s="226"/>
+      <c r="B110" s="226"/>
     </row>
     <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="219"/>
-      <c r="B111" s="219"/>
+      <c r="A111" s="226"/>
+      <c r="B111" s="226"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="218" t="s">
+      <c r="A114" s="225" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="218"/>
+      <c r="B114" s="225"/>
     </row>
     <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="218"/>
-      <c r="B115" s="218"/>
+      <c r="A115" s="225"/>
+      <c r="B115" s="225"/>
     </row>
     <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116"/>
@@ -3791,16 +3838,16 @@
     </row>
     <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="217" t="s">
+      <c r="A139" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="B139" s="217"/>
-      <c r="C139" s="217"/>
+      <c r="B139" s="224"/>
+      <c r="C139" s="224"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="217"/>
-      <c r="B140" s="217"/>
-      <c r="C140" s="217"/>
+      <c r="A140" s="224"/>
+      <c r="B140" s="224"/>
+      <c r="C140" s="224"/>
     </row>
     <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="90" t="s">
@@ -3890,15 +3937,15 @@
       <c r="A1" s="124"/>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="224"/>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
       <c r="M1" s="126"/>
     </row>
     <row r="2" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3908,10 +3955,10 @@
       <c r="D2" s="129" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="248">
+      <c r="E2" s="251">
         <v>3000000</v>
       </c>
-      <c r="F2" s="248"/>
+      <c r="F2" s="251"/>
       <c r="G2" s="129"/>
       <c r="H2" s="129"/>
       <c r="I2" s="129" t="s">
@@ -3942,195 +3989,195 @@
       <c r="N3" s="96"/>
     </row>
     <row r="4" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="225" t="s">
+      <c r="A4" s="228" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="226"/>
-      <c r="C4" s="226"/>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
-      <c r="I4" s="226"/>
-      <c r="J4" s="226"/>
-      <c r="K4" s="226"/>
-      <c r="L4" s="226"/>
-      <c r="M4" s="227"/>
+      <c r="B4" s="229"/>
+      <c r="C4" s="229"/>
+      <c r="D4" s="229"/>
+      <c r="E4" s="229"/>
+      <c r="F4" s="229"/>
+      <c r="G4" s="229"/>
+      <c r="H4" s="229"/>
+      <c r="I4" s="229"/>
+      <c r="J4" s="229"/>
+      <c r="K4" s="229"/>
+      <c r="L4" s="229"/>
+      <c r="M4" s="230"/>
       <c r="N4" s="96"/>
     </row>
     <row r="5" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="228"/>
-      <c r="B5" s="229"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
-      <c r="M5" s="230"/>
+      <c r="A5" s="231"/>
+      <c r="B5" s="232"/>
+      <c r="C5" s="232"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
+      <c r="G5" s="232"/>
+      <c r="H5" s="232"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="232"/>
+      <c r="M5" s="233"/>
       <c r="N5" s="96"/>
     </row>
     <row r="6" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="228"/>
-      <c r="B6" s="229"/>
-      <c r="C6" s="229"/>
-      <c r="D6" s="229"/>
-      <c r="E6" s="229"/>
-      <c r="F6" s="229"/>
-      <c r="G6" s="229"/>
-      <c r="H6" s="229"/>
-      <c r="I6" s="229"/>
-      <c r="J6" s="229"/>
-      <c r="K6" s="229"/>
-      <c r="L6" s="229"/>
-      <c r="M6" s="230"/>
+      <c r="A6" s="231"/>
+      <c r="B6" s="232"/>
+      <c r="C6" s="232"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="232"/>
+      <c r="I6" s="232"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="232"/>
+      <c r="L6" s="232"/>
+      <c r="M6" s="233"/>
       <c r="N6" s="96"/>
     </row>
     <row r="7" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="228"/>
-      <c r="B7" s="229"/>
-      <c r="C7" s="229"/>
-      <c r="D7" s="229"/>
-      <c r="E7" s="229"/>
-      <c r="F7" s="229"/>
-      <c r="G7" s="229"/>
-      <c r="H7" s="229"/>
-      <c r="I7" s="229"/>
-      <c r="J7" s="229"/>
-      <c r="K7" s="229"/>
-      <c r="L7" s="229"/>
-      <c r="M7" s="230"/>
+      <c r="A7" s="231"/>
+      <c r="B7" s="232"/>
+      <c r="C7" s="232"/>
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="232"/>
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="232"/>
+      <c r="M7" s="233"/>
       <c r="N7" s="96"/>
     </row>
     <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="231"/>
-      <c r="B8" s="232"/>
-      <c r="C8" s="232"/>
-      <c r="D8" s="232"/>
-      <c r="E8" s="232"/>
-      <c r="F8" s="232"/>
-      <c r="G8" s="232"/>
-      <c r="H8" s="232"/>
-      <c r="I8" s="232"/>
-      <c r="J8" s="232"/>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="233"/>
+      <c r="A8" s="234"/>
+      <c r="B8" s="235"/>
+      <c r="C8" s="235"/>
+      <c r="D8" s="235"/>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="235"/>
+      <c r="L8" s="235"/>
+      <c r="M8" s="236"/>
     </row>
     <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="221" t="s">
+      <c r="A9" s="257" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="222"/>
-      <c r="C9" s="222"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="222"/>
-      <c r="K9" s="222"/>
-      <c r="L9" s="222"/>
-      <c r="M9" s="223"/>
+      <c r="B9" s="258"/>
+      <c r="C9" s="258"/>
+      <c r="D9" s="258"/>
+      <c r="E9" s="258"/>
+      <c r="F9" s="258"/>
+      <c r="G9" s="258"/>
+      <c r="H9" s="258"/>
+      <c r="I9" s="258"/>
+      <c r="J9" s="258"/>
+      <c r="K9" s="258"/>
+      <c r="L9" s="258"/>
+      <c r="M9" s="259"/>
     </row>
     <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="242" t="s">
+      <c r="A10" s="245" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="243"/>
-      <c r="C10" s="243"/>
-      <c r="D10" s="243"/>
-      <c r="E10" s="243"/>
-      <c r="F10" s="243"/>
-      <c r="G10" s="243"/>
-      <c r="H10" s="243"/>
-      <c r="I10" s="243"/>
-      <c r="J10" s="243"/>
-      <c r="K10" s="243"/>
-      <c r="L10" s="243"/>
-      <c r="M10" s="244"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
+      <c r="M10" s="247"/>
     </row>
     <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="245" t="s">
+      <c r="A11" s="248" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="246"/>
-      <c r="C11" s="246"/>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="246"/>
-      <c r="L11" s="246"/>
-      <c r="M11" s="247"/>
+      <c r="B11" s="249"/>
+      <c r="C11" s="249"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
+      <c r="M11" s="250"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="234" t="s">
+      <c r="A12" s="237" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="236" t="s">
+      <c r="B12" s="239" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="236" t="s">
+      <c r="C12" s="239" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="236" t="s">
+      <c r="D12" s="239" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="238" t="s">
+      <c r="E12" s="241" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="236" t="s">
+      <c r="F12" s="239" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="240" t="s">
+      <c r="G12" s="243" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="238" t="s">
+      <c r="H12" s="241" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="238" t="s">
+      <c r="I12" s="241" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="238" t="s">
+      <c r="J12" s="241" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="249" t="s">
+      <c r="K12" s="252" t="s">
         <v>247</v>
       </c>
       <c r="L12" s="195" t="s">
         <v>140</v>
       </c>
-      <c r="M12" s="251" t="s">
+      <c r="M12" s="254" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="235"/>
-      <c r="B13" s="237"/>
-      <c r="C13" s="237"/>
-      <c r="D13" s="237"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="237"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="239"/>
-      <c r="I13" s="239"/>
-      <c r="J13" s="239"/>
-      <c r="K13" s="250"/>
+      <c r="A13" s="238"/>
+      <c r="B13" s="240"/>
+      <c r="C13" s="240"/>
+      <c r="D13" s="240"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="240"/>
+      <c r="G13" s="244"/>
+      <c r="H13" s="242"/>
+      <c r="I13" s="242"/>
+      <c r="J13" s="242"/>
+      <c r="K13" s="253"/>
       <c r="L13" s="196" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M13" s="252"/>
+      <c r="M13" s="255"/>
     </row>
     <row r="14" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="179">
@@ -5140,11 +5187,11 @@
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="179">
+      <c r="A35" s="278">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="105" t="s">
+      <c r="B35" s="279" t="s">
         <v>24</v>
       </c>
       <c r="C35" s="104"/>
@@ -6545,15 +6592,15 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" s="179">
+      <c r="A64" s="209">
         <f t="shared" si="9"/>
         <v>51</v>
       </c>
-      <c r="B64" s="105" t="s">
+      <c r="B64" s="210" t="s">
         <v>52</v>
       </c>
-      <c r="C64" s="104"/>
-      <c r="D64" s="98">
+      <c r="C64" s="211"/>
+      <c r="D64" s="212">
         <v>0.82</v>
       </c>
       <c r="E64" s="99">
@@ -6834,11 +6881,11 @@
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="181">
+      <c r="A70" s="282">
         <f t="shared" si="9"/>
         <v>57</v>
       </c>
-      <c r="B70" s="149" t="s">
+      <c r="B70" s="283" t="s">
         <v>58</v>
       </c>
       <c r="C70" s="104"/>
@@ -9186,89 +9233,87 @@
     </row>
     <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="220" t="s">
+      <c r="B121" s="256" t="s">
         <v>106</v>
       </c>
-      <c r="C121" s="220"/>
-      <c r="D121" s="220"/>
-      <c r="E121" s="220"/>
-      <c r="F121" s="220"/>
-      <c r="G121" s="220"/>
-      <c r="H121" s="220"/>
-      <c r="I121" s="220"/>
-      <c r="J121" s="220"/>
-      <c r="K121" s="220"/>
-      <c r="L121" s="220"/>
+      <c r="C121" s="256"/>
+      <c r="D121" s="256"/>
+      <c r="E121" s="256"/>
+      <c r="F121" s="256"/>
+      <c r="G121" s="256"/>
+      <c r="H121" s="256"/>
+      <c r="I121" s="256"/>
+      <c r="J121" s="256"/>
+      <c r="K121" s="256"/>
+      <c r="L121" s="256"/>
     </row>
     <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="220"/>
-      <c r="C122" s="220"/>
-      <c r="D122" s="220"/>
-      <c r="E122" s="220"/>
-      <c r="F122" s="220"/>
-      <c r="G122" s="220"/>
-      <c r="H122" s="220"/>
-      <c r="I122" s="220"/>
-      <c r="J122" s="220"/>
-      <c r="K122" s="220"/>
-      <c r="L122" s="220"/>
+      <c r="B122" s="256"/>
+      <c r="C122" s="256"/>
+      <c r="D122" s="256"/>
+      <c r="E122" s="256"/>
+      <c r="F122" s="256"/>
+      <c r="G122" s="256"/>
+      <c r="H122" s="256"/>
+      <c r="I122" s="256"/>
+      <c r="J122" s="256"/>
+      <c r="K122" s="256"/>
+      <c r="L122" s="256"/>
     </row>
     <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="220"/>
-      <c r="C123" s="220"/>
-      <c r="D123" s="220"/>
-      <c r="E123" s="220"/>
-      <c r="F123" s="220"/>
-      <c r="G123" s="220"/>
-      <c r="H123" s="220"/>
-      <c r="I123" s="220"/>
-      <c r="J123" s="220"/>
-      <c r="K123" s="220"/>
-      <c r="L123" s="220"/>
+      <c r="B123" s="256"/>
+      <c r="C123" s="256"/>
+      <c r="D123" s="256"/>
+      <c r="E123" s="256"/>
+      <c r="F123" s="256"/>
+      <c r="G123" s="256"/>
+      <c r="H123" s="256"/>
+      <c r="I123" s="256"/>
+      <c r="J123" s="256"/>
+      <c r="K123" s="256"/>
+      <c r="L123" s="256"/>
     </row>
     <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="220"/>
-      <c r="C124" s="220"/>
-      <c r="D124" s="220"/>
-      <c r="E124" s="220"/>
-      <c r="F124" s="220"/>
-      <c r="G124" s="220"/>
-      <c r="H124" s="220"/>
-      <c r="I124" s="220"/>
-      <c r="J124" s="220"/>
-      <c r="K124" s="220"/>
-      <c r="L124" s="220"/>
+      <c r="B124" s="256"/>
+      <c r="C124" s="256"/>
+      <c r="D124" s="256"/>
+      <c r="E124" s="256"/>
+      <c r="F124" s="256"/>
+      <c r="G124" s="256"/>
+      <c r="H124" s="256"/>
+      <c r="I124" s="256"/>
+      <c r="J124" s="256"/>
+      <c r="K124" s="256"/>
+      <c r="L124" s="256"/>
     </row>
     <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="220"/>
-      <c r="C125" s="220"/>
-      <c r="D125" s="220"/>
-      <c r="E125" s="220"/>
-      <c r="F125" s="220"/>
-      <c r="G125" s="220"/>
-      <c r="H125" s="220"/>
-      <c r="I125" s="220"/>
-      <c r="J125" s="220"/>
-      <c r="K125" s="220"/>
-      <c r="L125" s="220"/>
+      <c r="B125" s="256"/>
+      <c r="C125" s="256"/>
+      <c r="D125" s="256"/>
+      <c r="E125" s="256"/>
+      <c r="F125" s="256"/>
+      <c r="G125" s="256"/>
+      <c r="H125" s="256"/>
+      <c r="I125" s="256"/>
+      <c r="J125" s="256"/>
+      <c r="K125" s="256"/>
+      <c r="L125" s="256"/>
     </row>
     <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="220"/>
-      <c r="C126" s="220"/>
-      <c r="D126" s="220"/>
-      <c r="E126" s="220"/>
-      <c r="F126" s="220"/>
-      <c r="G126" s="220"/>
-      <c r="H126" s="220"/>
-      <c r="I126" s="220"/>
-      <c r="J126" s="220"/>
-      <c r="K126" s="220"/>
-      <c r="L126" s="220"/>
+      <c r="B126" s="256"/>
+      <c r="C126" s="256"/>
+      <c r="D126" s="256"/>
+      <c r="E126" s="256"/>
+      <c r="F126" s="256"/>
+      <c r="G126" s="256"/>
+      <c r="H126" s="256"/>
+      <c r="I126" s="256"/>
+      <c r="J126" s="256"/>
+      <c r="K126" s="256"/>
+      <c r="L126" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="J12:J13"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="B121:L126"/>
     <mergeCell ref="A9:M9"/>
@@ -9286,6 +9331,8 @@
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I12:I13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="J12:J13"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9306,6 +9353,21 @@
       </c>
     </row>
     <row r="5" spans="3:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C7" s="213" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C10" s="280" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C12" s="281" t="s">
+        <v>278</v>
+      </c>
+    </row>
     <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9326,10 +9388,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C4" s="253" t="s">
+      <c r="C4" s="260" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="253"/>
+      <c r="D4" s="260"/>
       <c r="E4" s="201"/>
       <c r="F4" s="199" t="s">
         <v>258</v>
@@ -9337,16 +9399,16 @@
       <c r="H4" t="s">
         <v>259</v>
       </c>
-      <c r="J4" s="255" t="s">
+      <c r="J4" s="262" t="s">
         <v>261</v>
       </c>
-      <c r="K4" s="255"/>
+      <c r="K4" s="262"/>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C5" s="254">
+      <c r="C5" s="261">
         <v>168835.53000000003</v>
       </c>
-      <c r="D5" s="254"/>
+      <c r="D5" s="261"/>
       <c r="E5" s="202"/>
       <c r="F5" s="200">
         <f>C5</f>
@@ -9355,18 +9417,18 @@
       <c r="H5" s="80">
         <v>0</v>
       </c>
-      <c r="J5" s="256">
+      <c r="J5" s="263">
         <f>F5</f>
         <v>168835.53000000003</v>
       </c>
-      <c r="K5" s="256"/>
+      <c r="K5" s="263"/>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M7" s="259" t="s">
+      <c r="M7" s="266" t="s">
         <v>263</v>
       </c>
-      <c r="N7" s="259"/>
-      <c r="O7" s="259"/>
+      <c r="N7" s="266"/>
+      <c r="O7" s="266"/>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
@@ -9378,19 +9440,19 @@
       <c r="H8" t="s">
         <v>259</v>
       </c>
-      <c r="J8" s="255" t="s">
+      <c r="J8" s="262" t="s">
         <v>262</v>
       </c>
-      <c r="K8" s="255"/>
-      <c r="M8" s="259"/>
-      <c r="N8" s="259"/>
-      <c r="O8" s="259"/>
+      <c r="K8" s="262"/>
+      <c r="M8" s="266"/>
+      <c r="N8" s="266"/>
+      <c r="O8" s="266"/>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C9" s="254">
+      <c r="C9" s="261">
         <v>168836.53</v>
       </c>
-      <c r="D9" s="254"/>
+      <c r="D9" s="261"/>
       <c r="F9" s="80">
         <v>0</v>
       </c>
@@ -9398,16 +9460,16 @@
         <f>C9-F9</f>
         <v>168836.53</v>
       </c>
-      <c r="J9" s="254">
+      <c r="J9" s="261">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K9" s="254"/>
-      <c r="M9" s="258">
+      <c r="K9" s="261"/>
+      <c r="M9" s="265">
         <v>300737.53000000003</v>
       </c>
-      <c r="N9" s="258"/>
-      <c r="O9" s="258"/>
+      <c r="N9" s="265"/>
+      <c r="O9" s="265"/>
     </row>
     <row r="10" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="202"/>
@@ -9421,11 +9483,11 @@
       <c r="O10" s="203"/>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M11" s="263" t="s">
+      <c r="M11" s="270" t="s">
         <v>263</v>
       </c>
-      <c r="N11" s="264"/>
-      <c r="O11" s="265"/>
+      <c r="N11" s="271"/>
+      <c r="O11" s="272"/>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
@@ -9437,20 +9499,20 @@
       <c r="H12" t="s">
         <v>259</v>
       </c>
-      <c r="J12" s="255" t="s">
+      <c r="J12" s="262" t="s">
         <v>265</v>
       </c>
-      <c r="K12" s="255"/>
-      <c r="M12" s="266"/>
-      <c r="N12" s="267"/>
-      <c r="O12" s="268"/>
+      <c r="K12" s="262"/>
+      <c r="M12" s="273"/>
+      <c r="N12" s="274"/>
+      <c r="O12" s="275"/>
     </row>
     <row r="13" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="254">
+      <c r="C13" s="261">
         <f>M9</f>
         <v>300737.53000000003</v>
       </c>
-      <c r="D13" s="254"/>
+      <c r="D13" s="261"/>
       <c r="F13" s="80">
         <v>98556.53</v>
       </c>
@@ -9458,124 +9520,124 @@
         <f>C13-F13</f>
         <v>202181.00000000003</v>
       </c>
-      <c r="J13" s="254">
+      <c r="J13" s="261">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K13" s="254"/>
-      <c r="M13" s="260">
+      <c r="K13" s="261"/>
+      <c r="M13" s="267">
         <f>J13+H13-0.27</f>
         <v>371016.53</v>
       </c>
-      <c r="N13" s="261"/>
-      <c r="O13" s="262"/>
+      <c r="N13" s="268"/>
+      <c r="O13" s="269"/>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C15" s="257" t="s">
+      <c r="C15" s="264" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="257"/>
-      <c r="E15" s="257"/>
-      <c r="F15" s="257"/>
-      <c r="G15" s="257"/>
-      <c r="H15" s="257"/>
-      <c r="I15" s="257"/>
-      <c r="J15" s="257"/>
-      <c r="K15" s="257"/>
-      <c r="L15" s="257"/>
-      <c r="M15" s="257"/>
-      <c r="N15" s="257"/>
-      <c r="O15" s="257"/>
+      <c r="D15" s="264"/>
+      <c r="E15" s="264"/>
+      <c r="F15" s="264"/>
+      <c r="G15" s="264"/>
+      <c r="H15" s="264"/>
+      <c r="I15" s="264"/>
+      <c r="J15" s="264"/>
+      <c r="K15" s="264"/>
+      <c r="L15" s="264"/>
+      <c r="M15" s="264"/>
+      <c r="N15" s="264"/>
+      <c r="O15" s="264"/>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C16" s="257"/>
-      <c r="D16" s="257"/>
-      <c r="E16" s="257"/>
-      <c r="F16" s="257"/>
-      <c r="G16" s="257"/>
-      <c r="H16" s="257"/>
-      <c r="I16" s="257"/>
-      <c r="J16" s="257"/>
-      <c r="K16" s="257"/>
-      <c r="L16" s="257"/>
-      <c r="M16" s="257"/>
-      <c r="N16" s="257"/>
-      <c r="O16" s="257"/>
+      <c r="C16" s="264"/>
+      <c r="D16" s="264"/>
+      <c r="E16" s="264"/>
+      <c r="F16" s="264"/>
+      <c r="G16" s="264"/>
+      <c r="H16" s="264"/>
+      <c r="I16" s="264"/>
+      <c r="J16" s="264"/>
+      <c r="K16" s="264"/>
+      <c r="L16" s="264"/>
+      <c r="M16" s="264"/>
+      <c r="N16" s="264"/>
+      <c r="O16" s="264"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C17" s="257"/>
-      <c r="D17" s="257"/>
-      <c r="E17" s="257"/>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
-      <c r="J17" s="257"/>
-      <c r="K17" s="257"/>
-      <c r="L17" s="257"/>
-      <c r="M17" s="257"/>
-      <c r="N17" s="257"/>
-      <c r="O17" s="257"/>
+      <c r="C17" s="264"/>
+      <c r="D17" s="264"/>
+      <c r="E17" s="264"/>
+      <c r="F17" s="264"/>
+      <c r="G17" s="264"/>
+      <c r="H17" s="264"/>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
+      <c r="O17" s="264"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C18" s="257"/>
-      <c r="D18" s="257"/>
-      <c r="E18" s="257"/>
-      <c r="F18" s="257"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="257"/>
-      <c r="J18" s="257"/>
-      <c r="K18" s="257"/>
-      <c r="L18" s="257"/>
-      <c r="M18" s="257"/>
-      <c r="N18" s="257"/>
-      <c r="O18" s="257"/>
+      <c r="C18" s="264"/>
+      <c r="D18" s="264"/>
+      <c r="E18" s="264"/>
+      <c r="F18" s="264"/>
+      <c r="G18" s="264"/>
+      <c r="H18" s="264"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
+      <c r="M18" s="264"/>
+      <c r="N18" s="264"/>
+      <c r="O18" s="264"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C19" s="257"/>
-      <c r="D19" s="257"/>
-      <c r="E19" s="257"/>
-      <c r="F19" s="257"/>
-      <c r="G19" s="257"/>
-      <c r="H19" s="257"/>
-      <c r="I19" s="257"/>
-      <c r="J19" s="257"/>
-      <c r="K19" s="257"/>
-      <c r="L19" s="257"/>
-      <c r="M19" s="257"/>
-      <c r="N19" s="257"/>
-      <c r="O19" s="257"/>
+      <c r="C19" s="264"/>
+      <c r="D19" s="264"/>
+      <c r="E19" s="264"/>
+      <c r="F19" s="264"/>
+      <c r="G19" s="264"/>
+      <c r="H19" s="264"/>
+      <c r="I19" s="264"/>
+      <c r="J19" s="264"/>
+      <c r="K19" s="264"/>
+      <c r="L19" s="264"/>
+      <c r="M19" s="264"/>
+      <c r="N19" s="264"/>
+      <c r="O19" s="264"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C20" s="257"/>
-      <c r="D20" s="257"/>
-      <c r="E20" s="257"/>
-      <c r="F20" s="257"/>
-      <c r="G20" s="257"/>
-      <c r="H20" s="257"/>
-      <c r="I20" s="257"/>
-      <c r="J20" s="257"/>
-      <c r="K20" s="257"/>
-      <c r="L20" s="257"/>
-      <c r="M20" s="257"/>
-      <c r="N20" s="257"/>
-      <c r="O20" s="257"/>
+      <c r="C20" s="264"/>
+      <c r="D20" s="264"/>
+      <c r="E20" s="264"/>
+      <c r="F20" s="264"/>
+      <c r="G20" s="264"/>
+      <c r="H20" s="264"/>
+      <c r="I20" s="264"/>
+      <c r="J20" s="264"/>
+      <c r="K20" s="264"/>
+      <c r="L20" s="264"/>
+      <c r="M20" s="264"/>
+      <c r="N20" s="264"/>
+      <c r="O20" s="264"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="257"/>
-      <c r="D21" s="257"/>
-      <c r="E21" s="257"/>
-      <c r="F21" s="257"/>
-      <c r="G21" s="257"/>
-      <c r="H21" s="257"/>
-      <c r="I21" s="257"/>
-      <c r="J21" s="257"/>
-      <c r="K21" s="257"/>
-      <c r="L21" s="257"/>
-      <c r="M21" s="257"/>
-      <c r="N21" s="257"/>
-      <c r="O21" s="257"/>
+      <c r="C21" s="264"/>
+      <c r="D21" s="264"/>
+      <c r="E21" s="264"/>
+      <c r="F21" s="264"/>
+      <c r="G21" s="264"/>
+      <c r="H21" s="264"/>
+      <c r="I21" s="264"/>
+      <c r="J21" s="264"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
+      <c r="M21" s="264"/>
+      <c r="N21" s="264"/>
+      <c r="O21" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -9618,32 +9680,32 @@
       <c r="F4" s="80">
         <v>843306.42</v>
       </c>
-      <c r="G4" s="271" t="s">
+      <c r="G4" s="276" t="s">
         <v>274</v>
       </c>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
-      <c r="M4" s="271"/>
-      <c r="N4" s="271"/>
+      <c r="H4" s="276"/>
+      <c r="I4" s="276"/>
+      <c r="J4" s="276"/>
+      <c r="K4" s="276"/>
+      <c r="L4" s="276"/>
+      <c r="M4" s="276"/>
+      <c r="N4" s="276"/>
     </row>
     <row r="5" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>269</v>
       </c>
-      <c r="F5" s="270">
+      <c r="F5" s="208">
         <v>-68000</v>
       </c>
-      <c r="G5" s="271"/>
-      <c r="H5" s="271"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
-      <c r="M5" s="271"/>
-      <c r="N5" s="271"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="276"/>
+      <c r="I5" s="276"/>
+      <c r="J5" s="276"/>
+      <c r="K5" s="276"/>
+      <c r="L5" s="276"/>
+      <c r="M5" s="276"/>
+      <c r="N5" s="276"/>
     </row>
     <row r="6" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
@@ -9653,24 +9715,24 @@
         <f>F4+F5</f>
         <v>775306.42</v>
       </c>
-      <c r="G6" s="271"/>
-      <c r="H6" s="271"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="271"/>
-      <c r="L6" s="271"/>
-      <c r="M6" s="271"/>
-      <c r="N6" s="271"/>
+      <c r="G6" s="276"/>
+      <c r="H6" s="276"/>
+      <c r="I6" s="276"/>
+      <c r="J6" s="276"/>
+      <c r="K6" s="276"/>
+      <c r="L6" s="276"/>
+      <c r="M6" s="276"/>
+      <c r="N6" s="276"/>
     </row>
     <row r="7" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="G7" s="271"/>
-      <c r="H7" s="271"/>
-      <c r="I7" s="271"/>
-      <c r="J7" s="271"/>
-      <c r="K7" s="271"/>
-      <c r="L7" s="271"/>
-      <c r="M7" s="271"/>
-      <c r="N7" s="271"/>
+      <c r="G7" s="276"/>
+      <c r="H7" s="276"/>
+      <c r="I7" s="276"/>
+      <c r="J7" s="276"/>
+      <c r="K7" s="276"/>
+      <c r="L7" s="276"/>
+      <c r="M7" s="276"/>
+      <c r="N7" s="276"/>
     </row>
     <row r="8" spans="4:14" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
@@ -9693,18 +9755,18 @@
         <v>273</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="269">
+      <c r="F11" s="207">
         <f>F6+F8+F9</f>
         <v>944142.22000000009</v>
       </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D13" s="272" t="s">
+      <c r="D13" s="277" t="s">
         <v>275</v>
       </c>
-      <c r="E13" s="272"/>
-      <c r="F13" s="272"/>
-      <c r="G13" s="272"/>
+      <c r="E13" s="277"/>
+      <c r="F13" s="277"/>
+      <c r="G13" s="277"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29022F05-9C42-490B-A2C2-386EF01AFF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1E17A2-F5BD-44AD-9D40-E8A2AA7355C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -26,6 +26,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'SITUACION 6B'!$D$4:$N$13</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -102,9 +107,6 @@
   </si>
   <si>
     <t>3 B WASZNIEWSKI G.</t>
-  </si>
-  <si>
-    <t>3 C DESTEFANO ABUD</t>
   </si>
   <si>
     <t xml:space="preserve">3 D GARCIA MANUELA </t>
@@ -880,6 +882,9 @@
   </si>
   <si>
     <t>8C deposito $132.520 el 12/03</t>
+  </si>
+  <si>
+    <t>3 C MAROTTA PABLO</t>
   </si>
 </sst>
 </file>
@@ -2002,194 +2007,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2199,6 +2016,194 @@
     <xf numFmtId="0" fontId="19" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2282,9 +2287,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2322,9 +2327,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2357,9 +2362,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2392,9 +2414,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2569,156 +2608,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M143"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="216" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="216"/>
-      <c r="D1" s="216"/>
-      <c r="E1" s="217"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="227" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="228"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="220" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="220"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="221"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="229" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="229"/>
+      <c r="D3" s="229"/>
+      <c r="E3" s="230"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="107" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="222" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="222"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="222"/>
-      <c r="C9" s="222"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="222"/>
-      <c r="C10" s="222"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="223" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="231" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="231"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="231"/>
+      <c r="C9" s="231"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="232" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="232"/>
+      <c r="C13" s="232"/>
+      <c r="D13" s="232"/>
+      <c r="E13" s="232"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="232"/>
+      <c r="B14" s="232"/>
+      <c r="C14" s="232"/>
+      <c r="D14" s="232"/>
+      <c r="E14" s="232"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="232"/>
+      <c r="B15" s="232"/>
+      <c r="C15" s="232"/>
+      <c r="D15" s="232"/>
+      <c r="E15" s="232"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="232"/>
+      <c r="B16" s="232"/>
+      <c r="C16" s="232"/>
+      <c r="D16" s="232"/>
+      <c r="E16" s="232"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>106</v>
-      </c>
-      <c r="B13" s="223"/>
-      <c r="C13" s="223"/>
-      <c r="D13" s="223"/>
-      <c r="E13" s="223"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="223"/>
-      <c r="B14" s="223"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="223"/>
-      <c r="B15" s="223"/>
-      <c r="C15" s="223"/>
-      <c r="D15" s="223"/>
-      <c r="E15" s="223"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="223"/>
-      <c r="B16" s="223"/>
-      <c r="C16" s="223"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>107</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="154"/>
       <c r="E21" s="19"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="218" t="s">
-        <v>175</v>
-      </c>
-      <c r="B22" s="219"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="220" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="221"/>
       <c r="C22" s="22"/>
       <c r="D22" s="167">
         <v>1931623</v>
@@ -2726,11 +2765,11 @@
       <c r="E22" s="47"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="218" t="s">
-        <v>176</v>
-      </c>
-      <c r="B23" s="219"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="220" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="221"/>
       <c r="C23" s="22"/>
       <c r="D23" s="167">
         <v>-420128</v>
@@ -2738,11 +2777,11 @@
       <c r="E23" s="24"/>
       <c r="H23" s="23"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="218" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="220" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="219"/>
+      <c r="B24" s="221"/>
       <c r="C24" s="22"/>
       <c r="D24" s="168">
         <v>0</v>
@@ -2750,9 +2789,9 @@
       <c r="E24" s="24"/>
       <c r="H24" s="23"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -2762,18 +2801,18 @@
         <v>1511495</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="26"/>
       <c r="E26" s="108"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -2782,9 +2821,9 @@
       </c>
       <c r="E27" s="110"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -2792,12 +2831,12 @@
         <v>5842.51</v>
       </c>
       <c r="E28" s="118" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -2807,18 +2846,18 @@
         <v>153842.51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
       <c r="D30" s="26"/>
       <c r="E30" s="108"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B31" s="109"/>
       <c r="C31" s="109"/>
@@ -2826,12 +2865,12 @@
         <v>13757.84</v>
       </c>
       <c r="E31" s="118" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B32" s="109"/>
       <c r="C32" s="109"/>
@@ -2839,12 +2878,12 @@
         <v>1235711.01</v>
       </c>
       <c r="E32" s="118" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B33" s="109"/>
       <c r="C33" s="109"/>
@@ -2852,12 +2891,12 @@
         <v>225490.24</v>
       </c>
       <c r="E33" s="118" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="109"/>
       <c r="C34" s="109"/>
@@ -2869,9 +2908,9 @@
         <v>Debito 16/02</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B35" s="109"/>
       <c r="C35" s="109"/>
@@ -2883,18 +2922,18 @@
         <v>Debito 16/02</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B36" s="109"/>
       <c r="C36" s="109"/>
       <c r="D36" s="45"/>
       <c r="E36" s="118"/>
     </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -2904,57 +2943,57 @@
         <v>1584070.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
       <c r="D38" s="28"/>
       <c r="E38" s="29"/>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="214" t="s">
-        <v>149</v>
-      </c>
-      <c r="B39" s="215"/>
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="223" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" s="224"/>
       <c r="C39" s="32"/>
       <c r="D39" s="169">
         <v>313739</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="214" t="s">
-        <v>253</v>
-      </c>
-      <c r="B40" s="215"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="223" t="s">
+        <v>252</v>
+      </c>
+      <c r="B40" s="224"/>
       <c r="C40" s="32"/>
       <c r="D40" s="170">
         <v>214164</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="214" t="s">
-        <v>150</v>
-      </c>
-      <c r="B41" s="215"/>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="223" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="224"/>
       <c r="C41" s="32"/>
       <c r="D41" s="170">
         <v>5204</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B42" s="25"/>
       <c r="C42" s="25"/>
@@ -2964,36 +3003,36 @@
         <v>533107</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
       <c r="D43" s="35"/>
       <c r="E43" s="36"/>
     </row>
-    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="38">
         <v>542686.9</v>
       </c>
       <c r="E44" s="24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="37" t="s">
         <v>219</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="B45" s="37" t="s">
-        <v>220</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="38">
@@ -3001,12 +3040,12 @@
       </c>
       <c r="E45" s="24"/>
     </row>
-    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C46" s="37"/>
       <c r="D46" s="38">
@@ -3014,9 +3053,9 @@
       </c>
       <c r="E46" s="24"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B47" s="39"/>
       <c r="C47" s="37"/>
@@ -3024,34 +3063,34 @@
         <v>10111.620000000001</v>
       </c>
       <c r="E47" s="24" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="214" t="s">
-        <v>114</v>
-      </c>
-      <c r="B48" s="215"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="223" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="224"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38">
         <v>4813938.26</v>
       </c>
       <c r="E48" s="155" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B49" s="31"/>
       <c r="C49" s="37"/>
       <c r="D49" s="38"/>
       <c r="E49" s="24"/>
     </row>
-    <row r="50" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B50" s="25"/>
       <c r="C50" s="25"/>
@@ -3061,97 +3100,97 @@
         <v>5366736.7799999993</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
       <c r="D51" s="26"/>
       <c r="E51" s="43"/>
     </row>
-    <row r="52" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="218" t="s">
-        <v>178</v>
-      </c>
-      <c r="B52" s="219"/>
+    <row r="52" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="220" t="s">
+        <v>177</v>
+      </c>
+      <c r="B52" s="221"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38">
         <v>225000</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="218" t="s">
-        <v>190</v>
-      </c>
-      <c r="B53" s="219"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="220" t="s">
+        <v>189</v>
+      </c>
+      <c r="B53" s="221"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38">
         <v>500000</v>
       </c>
       <c r="E53" s="44" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="218" t="s">
-        <v>193</v>
-      </c>
-      <c r="B54" s="219"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="220" t="s">
+        <v>192</v>
+      </c>
+      <c r="B54" s="221"/>
       <c r="C54" s="37"/>
       <c r="D54" s="38">
         <v>1520000</v>
       </c>
       <c r="E54" s="151" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="218" t="s">
-        <v>222</v>
-      </c>
-      <c r="B55" s="219"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="220" t="s">
+        <v>221</v>
+      </c>
+      <c r="B55" s="221"/>
       <c r="C55" s="37"/>
       <c r="D55" s="38">
         <f>272252*2</f>
         <v>544504</v>
       </c>
       <c r="E55" s="151" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="218" t="s">
-        <v>208</v>
-      </c>
-      <c r="B56" s="219"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="220" t="s">
+        <v>207</v>
+      </c>
+      <c r="B56" s="221"/>
       <c r="C56" s="37"/>
       <c r="D56" s="38">
         <v>85000</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F56" s="63"/>
     </row>
-    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="218" t="s">
-        <v>227</v>
-      </c>
-      <c r="B57" s="219"/>
+    <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="220" t="s">
+        <v>226</v>
+      </c>
+      <c r="B57" s="221"/>
       <c r="C57" s="37"/>
       <c r="D57" s="38">
         <v>120000</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F57" s="63"/>
     </row>
-    <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="37"/>
@@ -3159,41 +3198,41 @@
         <v>35000</v>
       </c>
       <c r="E58" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="63"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="218" t="s">
-        <v>209</v>
-      </c>
-      <c r="B59" s="219"/>
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="220" t="s">
+        <v>208</v>
+      </c>
+      <c r="B59" s="221"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38">
         <v>6000</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" s="63"/>
     </row>
-    <row r="60" spans="1:6" ht="85.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="218" t="s">
-        <v>250</v>
-      </c>
-      <c r="B60" s="219"/>
+    <row r="60" spans="1:6" ht="85.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="220" t="s">
+        <v>249</v>
+      </c>
+      <c r="B60" s="221"/>
       <c r="C60" s="37"/>
       <c r="D60" s="38">
         <v>7000000</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="63"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="37"/>
@@ -3201,13 +3240,13 @@
         <v>28000</v>
       </c>
       <c r="E61" s="44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F61" s="63"/>
     </row>
-    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="123" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="37"/>
@@ -3215,13 +3254,13 @@
         <v>150800</v>
       </c>
       <c r="E62" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F62" s="63"/>
     </row>
-    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="156" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B63" s="157"/>
       <c r="C63" s="37"/>
@@ -3229,27 +3268,27 @@
         <v>910000</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F63" s="63"/>
     </row>
-    <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="218" t="s">
-        <v>206</v>
-      </c>
-      <c r="B64" s="219"/>
+    <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="220" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" s="221"/>
       <c r="C64" s="37"/>
       <c r="D64" s="38">
         <v>250000</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F64" s="63"/>
     </row>
-    <row r="65" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="123" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="37"/>
@@ -3257,38 +3296,38 @@
         <v>133300</v>
       </c>
       <c r="E65" s="47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F65" s="63"/>
     </row>
-    <row r="66" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="218" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" s="219"/>
+    <row r="66" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="220" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66" s="221"/>
       <c r="C66" s="37"/>
       <c r="D66" s="38">
         <v>105602.65</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F66" s="63"/>
     </row>
-    <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="218" t="s">
-        <v>184</v>
-      </c>
-      <c r="B67" s="219"/>
+    <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="220" t="s">
+        <v>183</v>
+      </c>
+      <c r="B67" s="221"/>
       <c r="C67" s="37"/>
       <c r="D67" s="38">
         <v>2022800</v>
       </c>
       <c r="E67" s="47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
         <v>0</v>
       </c>
@@ -3300,29 +3339,29 @@
         <v>13636006.65</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
       <c r="D69" s="18"/>
       <c r="E69" s="19"/>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="218" t="s">
-        <v>192</v>
-      </c>
-      <c r="B70" s="219"/>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="220" t="s">
+        <v>191</v>
+      </c>
+      <c r="B70" s="221"/>
       <c r="C70" s="22"/>
       <c r="D70" s="171">
         <v>650000</v>
       </c>
       <c r="E70" s="47"/>
     </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="22"/>
@@ -3330,25 +3369,25 @@
         <v>125000</v>
       </c>
       <c r="E71" s="47" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="218" t="s">
-        <v>221</v>
-      </c>
-      <c r="B72" s="219"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="220" t="s">
+        <v>220</v>
+      </c>
+      <c r="B72" s="221"/>
       <c r="C72" s="22"/>
       <c r="D72" s="172">
         <v>62500</v>
       </c>
       <c r="E72" s="47" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="123" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="22"/>
@@ -3356,12 +3395,12 @@
         <v>45000</v>
       </c>
       <c r="E73" s="47" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" s="25"/>
       <c r="C74" s="25"/>
@@ -3371,18 +3410,18 @@
         <v>882500</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B75" s="48"/>
       <c r="C75" s="25"/>
       <c r="D75" s="49"/>
       <c r="E75" s="33"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B76" s="37"/>
       <c r="C76" s="37"/>
@@ -3391,9 +3430,9 @@
       </c>
       <c r="E76" s="50"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="37" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="37"/>
       <c r="C77" s="37"/>
@@ -3403,9 +3442,9 @@
       </c>
       <c r="E77" s="51"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B78" s="112"/>
       <c r="C78" s="112"/>
@@ -3414,9 +3453,9 @@
       </c>
       <c r="E78" s="51"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B79" s="112"/>
       <c r="C79" s="112"/>
@@ -3426,9 +3465,9 @@
       </c>
       <c r="E79" s="51"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" s="52"/>
       <c r="C80" s="52"/>
@@ -3438,31 +3477,31 @@
         <v>334094.84000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="37"/>
       <c r="B81" s="37"/>
       <c r="C81" s="37"/>
       <c r="D81" s="55"/>
       <c r="E81" s="56"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B82" s="57"/>
       <c r="C82" s="57"/>
       <c r="D82" s="58"/>
       <c r="E82" s="59"/>
     </row>
-    <row r="83" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="60"/>
       <c r="D83" s="61"/>
       <c r="E83" s="62"/>
       <c r="F83" s="63"/>
     </row>
-    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B84" s="65"/>
       <c r="C84" s="66"/>
@@ -3474,52 +3513,52 @@
       <c r="F84" s="69"/>
       <c r="G84" s="63"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D85" s="61"/>
       <c r="E85" s="61"/>
     </row>
-    <row r="86" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D86" s="61"/>
       <c r="E86" s="61"/>
       <c r="H86" s="70"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B87" s="13"/>
       <c r="C87" s="14"/>
       <c r="D87" s="71"/>
       <c r="E87" s="72"/>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="30"/>
       <c r="B88" s="31"/>
       <c r="C88" s="37"/>
       <c r="D88" s="45"/>
       <c r="E88" s="73"/>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="218"/>
-      <c r="B89" s="219"/>
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="220"/>
+      <c r="B89" s="221"/>
       <c r="C89" s="37"/>
       <c r="D89" s="45"/>
       <c r="E89" s="73"/>
     </row>
-    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="55"/>
       <c r="E90" s="37"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="30"/>
       <c r="B91" s="74"/>
       <c r="C91" s="37"/>
       <c r="D91" s="45"/>
       <c r="E91" s="73"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="75" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B92" s="76"/>
       <c r="C92" s="76"/>
@@ -3529,27 +3568,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="61"/>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="D94" s="61"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B95" s="57"/>
       <c r="C95" s="57"/>
       <c r="D95" s="58"/>
       <c r="E95" s="119"/>
     </row>
-    <row r="96" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D96" s="61"/>
     </row>
-    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B97" s="65"/>
       <c r="C97" s="66"/>
@@ -3559,89 +3598,89 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="78" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B99" s="79">
         <f>E84</f>
         <v>24001853.77</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100" s="79">
         <f>E84-E82</f>
         <v>24001853.77</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="78" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B101" s="79">
         <f>E97-E95</f>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B102" s="79">
         <f>E97</f>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="226" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B105" s="226"/>
     </row>
-    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="226"/>
       <c r="B106" s="226"/>
     </row>
-    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="226"/>
       <c r="B107" s="226"/>
     </row>
-    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="226" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B109" s="226"/>
     </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="226"/>
       <c r="B110" s="226"/>
     </row>
-    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="226"/>
       <c r="B111" s="226"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="225" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B114" s="225"/>
     </row>
-    <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="225"/>
       <c r="B115" s="225"/>
     </row>
-    <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="B116" s="80"/>
       <c r="C116" s="81"/>
     </row>
-    <row r="117" spans="1:6" s="82" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" s="82" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="122" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B117" s="83">
         <v>10597369.743745035</v>
@@ -3650,18 +3689,18 @@
       <c r="D117" s="84"/>
       <c r="E117" s="84"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B118" s="85">
         <f>-B100-B101</f>
         <v>-24001853.77</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B119" s="85">
         <f>B142</f>
@@ -3669,18 +3708,18 @@
       </c>
       <c r="F119" s="80"/>
     </row>
-    <row r="120" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B120" s="140">
         <v>-239116.53</v>
       </c>
       <c r="F120" s="80"/>
     </row>
-    <row r="121" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B121" s="141">
         <f>-119452</f>
@@ -3688,70 +3727,70 @@
       </c>
       <c r="F121" s="80"/>
     </row>
-    <row r="122" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B122" s="141">
         <v>-123612</v>
       </c>
       <c r="F122" s="80"/>
     </row>
-    <row r="123" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B123" s="141">
         <v>-168836.39</v>
       </c>
       <c r="F123" s="80"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B124" s="141">
         <v>-20871</v>
       </c>
       <c r="F124" s="80"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B125" s="141">
         <v>-3820</v>
       </c>
       <c r="F125" s="80"/>
     </row>
-    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B126" s="141">
         <v>-7274</v>
       </c>
       <c r="F126" s="80"/>
     </row>
-    <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B127" s="139">
         <v>-7528</v>
       </c>
       <c r="F127" s="80"/>
     </row>
-    <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="32" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B128" s="139">
         <v>-50000</v>
       </c>
       <c r="F128" s="80"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="32" t="s">
         <v>2</v>
       </c>
@@ -3761,72 +3800,72 @@
       </c>
       <c r="F129" s="80"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B130" s="86">
         <v>300000</v>
       </c>
       <c r="F130" s="80"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="32" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B131" s="86">
         <v>250000</v>
       </c>
       <c r="F131" s="80"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B132" s="86">
         <v>200000.42</v>
       </c>
       <c r="F132" s="80"/>
     </row>
-    <row r="133" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B133" s="165">
         <v>-130000</v>
       </c>
       <c r="F133" s="80"/>
     </row>
-    <row r="134" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B134" s="165">
         <v>-130000</v>
       </c>
       <c r="F134" s="80"/>
     </row>
-    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B135" s="165">
         <v>-130000</v>
       </c>
       <c r="F135" s="80"/>
     </row>
-    <row r="136" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="87" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B136" s="152">
         <v>123300</v>
       </c>
       <c r="F136" s="80"/>
     </row>
-    <row r="137" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="88" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B137" s="89">
         <f>SUM(B117:C136)</f>
@@ -3836,22 +3875,22 @@
       <c r="E137" s="63"/>
       <c r="F137" s="63"/>
     </row>
-    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="224" t="s">
-        <v>129</v>
-      </c>
-      <c r="B139" s="224"/>
-      <c r="C139" s="224"/>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="224"/>
-      <c r="B140" s="224"/>
-      <c r="C140" s="224"/>
-    </row>
-    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="222" t="s">
+        <v>128</v>
+      </c>
+      <c r="B139" s="222"/>
+      <c r="C139" s="222"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="222"/>
+      <c r="B140" s="222"/>
+      <c r="C140" s="222"/>
+    </row>
+    <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="90" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B141" s="150">
         <v>195940.3</v>
@@ -3859,7 +3898,7 @@
       <c r="C141" s="91"/>
       <c r="D141" s="69"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="92" t="s">
         <v>0</v>
       </c>
@@ -3869,11 +3908,24 @@
       </c>
       <c r="C142" s="94"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M143" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A139:C140"/>
@@ -3890,19 +3942,6 @@
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A105:B107"/>
     <mergeCell ref="A109:B111"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3913,56 +3952,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:O126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="124"/>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="239"/>
+      <c r="J1" s="239"/>
+      <c r="K1" s="239"/>
+      <c r="L1" s="239"/>
       <c r="M1" s="126"/>
     </row>
-    <row r="2" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="127"/>
       <c r="B2" s="128"/>
       <c r="C2" s="129"/>
       <c r="D2" s="129" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" s="251">
+        <v>129</v>
+      </c>
+      <c r="E2" s="263">
         <v>3000000</v>
       </c>
-      <c r="F2" s="251"/>
+      <c r="F2" s="263"/>
       <c r="G2" s="129"/>
       <c r="H2" s="129"/>
       <c r="I2" s="129" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J2" s="130">
         <v>12074625</v>
@@ -3972,7 +4011,7 @@
       <c r="M2" s="132"/>
       <c r="N2" s="96"/>
     </row>
-    <row r="3" spans="1:15" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="133"/>
       <c r="B3" s="134"/>
       <c r="C3" s="134"/>
@@ -3988,198 +4027,198 @@
       <c r="M3" s="137"/>
       <c r="N3" s="96"/>
     </row>
-    <row r="4" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="228" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="229"/>
-      <c r="C4" s="229"/>
-      <c r="D4" s="229"/>
-      <c r="E4" s="229"/>
-      <c r="F4" s="229"/>
-      <c r="G4" s="229"/>
-      <c r="H4" s="229"/>
-      <c r="I4" s="229"/>
-      <c r="J4" s="229"/>
-      <c r="K4" s="229"/>
-      <c r="L4" s="229"/>
-      <c r="M4" s="230"/>
+    <row r="4" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="240" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="241"/>
+      <c r="C4" s="241"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="M4" s="242"/>
       <c r="N4" s="96"/>
     </row>
-    <row r="5" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="231"/>
-      <c r="B5" s="232"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="232"/>
-      <c r="L5" s="232"/>
-      <c r="M5" s="233"/>
+    <row r="5" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="243"/>
+      <c r="B5" s="244"/>
+      <c r="C5" s="244"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="244"/>
+      <c r="H5" s="244"/>
+      <c r="I5" s="244"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="244"/>
+      <c r="L5" s="244"/>
+      <c r="M5" s="245"/>
       <c r="N5" s="96"/>
     </row>
-    <row r="6" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="231"/>
-      <c r="B6" s="232"/>
-      <c r="C6" s="232"/>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-      <c r="G6" s="232"/>
-      <c r="H6" s="232"/>
-      <c r="I6" s="232"/>
-      <c r="J6" s="232"/>
-      <c r="K6" s="232"/>
-      <c r="L6" s="232"/>
-      <c r="M6" s="233"/>
+    <row r="6" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="243"/>
+      <c r="B6" s="244"/>
+      <c r="C6" s="244"/>
+      <c r="D6" s="244"/>
+      <c r="E6" s="244"/>
+      <c r="F6" s="244"/>
+      <c r="G6" s="244"/>
+      <c r="H6" s="244"/>
+      <c r="I6" s="244"/>
+      <c r="J6" s="244"/>
+      <c r="K6" s="244"/>
+      <c r="L6" s="244"/>
+      <c r="M6" s="245"/>
       <c r="N6" s="96"/>
     </row>
-    <row r="7" spans="1:15" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="231"/>
-      <c r="B7" s="232"/>
-      <c r="C7" s="232"/>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="232"/>
-      <c r="H7" s="232"/>
-      <c r="I7" s="232"/>
-      <c r="J7" s="232"/>
-      <c r="K7" s="232"/>
-      <c r="L7" s="232"/>
-      <c r="M7" s="233"/>
+    <row r="7" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="243"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="244"/>
+      <c r="D7" s="244"/>
+      <c r="E7" s="244"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
+      <c r="H7" s="244"/>
+      <c r="I7" s="244"/>
+      <c r="J7" s="244"/>
+      <c r="K7" s="244"/>
+      <c r="L7" s="244"/>
+      <c r="M7" s="245"/>
       <c r="N7" s="96"/>
     </row>
-    <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="234"/>
-      <c r="B8" s="235"/>
-      <c r="C8" s="235"/>
-      <c r="D8" s="235"/>
-      <c r="E8" s="235"/>
-      <c r="F8" s="235"/>
-      <c r="G8" s="235"/>
-      <c r="H8" s="235"/>
-      <c r="I8" s="235"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="235"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="236"/>
-    </row>
-    <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="257" t="s">
-        <v>255</v>
-      </c>
-      <c r="B9" s="258"/>
-      <c r="C9" s="258"/>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
-      <c r="M9" s="259"/>
-    </row>
-    <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="245" t="s">
+    <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="246"/>
+      <c r="B8" s="247"/>
+      <c r="C8" s="247"/>
+      <c r="D8" s="247"/>
+      <c r="E8" s="247"/>
+      <c r="F8" s="247"/>
+      <c r="G8" s="247"/>
+      <c r="H8" s="247"/>
+      <c r="I8" s="247"/>
+      <c r="J8" s="247"/>
+      <c r="K8" s="247"/>
+      <c r="L8" s="247"/>
+      <c r="M8" s="248"/>
+    </row>
+    <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="236" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="237"/>
+      <c r="C9" s="237"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="237"/>
+      <c r="F9" s="237"/>
+      <c r="G9" s="237"/>
+      <c r="H9" s="237"/>
+      <c r="I9" s="237"/>
+      <c r="J9" s="237"/>
+      <c r="K9" s="237"/>
+      <c r="L9" s="237"/>
+      <c r="M9" s="238"/>
+    </row>
+    <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="257" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="258"/>
+      <c r="C10" s="258"/>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
+      <c r="M10" s="259"/>
+    </row>
+    <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="260" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="246"/>
-      <c r="C10" s="246"/>
-      <c r="D10" s="246"/>
-      <c r="E10" s="246"/>
-      <c r="F10" s="246"/>
-      <c r="G10" s="246"/>
-      <c r="H10" s="246"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="246"/>
-      <c r="K10" s="246"/>
-      <c r="L10" s="246"/>
-      <c r="M10" s="247"/>
-    </row>
-    <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="248" t="s">
-        <v>170</v>
-      </c>
-      <c r="B11" s="249"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
-      <c r="M11" s="250"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="237" t="s">
+      <c r="B11" s="261"/>
+      <c r="C11" s="261"/>
+      <c r="D11" s="261"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="261"/>
+      <c r="G11" s="261"/>
+      <c r="H11" s="261"/>
+      <c r="I11" s="261"/>
+      <c r="J11" s="261"/>
+      <c r="K11" s="261"/>
+      <c r="L11" s="261"/>
+      <c r="M11" s="262"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="249" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="251" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="239" t="s">
+      <c r="C12" s="251" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="239" t="s">
+      <c r="D12" s="251" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="239" t="s">
+      <c r="E12" s="253" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="241" t="s">
+      <c r="F12" s="251" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="239" t="s">
+      <c r="G12" s="255" t="s">
         <v>137</v>
       </c>
-      <c r="G12" s="243" t="s">
+      <c r="H12" s="253" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="241" t="s">
+      <c r="I12" s="253" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" s="253" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="264" t="s">
+        <v>246</v>
+      </c>
+      <c r="L12" s="195" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="241" t="s">
-        <v>131</v>
-      </c>
-      <c r="J12" s="241" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="252" t="s">
-        <v>247</v>
-      </c>
-      <c r="L12" s="195" t="s">
+      <c r="M12" s="233" t="s">
         <v>140</v>
       </c>
-      <c r="M12" s="254" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="238"/>
-      <c r="B13" s="240"/>
-      <c r="C13" s="240"/>
-      <c r="D13" s="240"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="240"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="242"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="253"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="250"/>
+      <c r="B13" s="252"/>
+      <c r="C13" s="252"/>
+      <c r="D13" s="252"/>
+      <c r="E13" s="254"/>
+      <c r="F13" s="252"/>
+      <c r="G13" s="256"/>
+      <c r="H13" s="254"/>
+      <c r="I13" s="254"/>
+      <c r="J13" s="254"/>
+      <c r="K13" s="265"/>
       <c r="L13" s="196" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M13" s="255"/>
-    </row>
-    <row r="14" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="234"/>
+    </row>
+    <row r="14" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="179">
         <v>1</v>
       </c>
@@ -4226,7 +4265,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="179">
         <v>2</v>
       </c>
@@ -4273,10 +4312,10 @@
         <v>0.02</v>
       </c>
       <c r="O15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="179">
         <v>3</v>
       </c>
@@ -4324,7 +4363,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="180">
         <v>4</v>
       </c>
@@ -4372,7 +4411,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="179">
         <v>5</v>
       </c>
@@ -4419,7 +4458,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="179">
         <v>6</v>
       </c>
@@ -4467,7 +4506,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="179">
         <v>7</v>
       </c>
@@ -4515,7 +4554,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="179">
         <v>8</v>
       </c>
@@ -4563,7 +4602,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="179">
         <v>9</v>
       </c>
@@ -4610,7 +4649,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="179">
         <v>10</v>
       </c>
@@ -4658,7 +4697,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="179">
         <v>11</v>
       </c>
@@ -4706,7 +4745,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="179">
         <v>12</v>
       </c>
@@ -4753,7 +4792,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="179">
         <v>13</v>
       </c>
@@ -4801,7 +4840,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="179">
         <v>14</v>
       </c>
@@ -4849,7 +4888,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="181">
         <v>15</v>
       </c>
@@ -4897,7 +4936,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="179">
         <v>16</v>
       </c>
@@ -4944,7 +4983,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="179">
         <v>17</v>
       </c>
@@ -4992,7 +5031,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="181">
         <v>18</v>
       </c>
@@ -5039,7 +5078,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="179">
         <v>19</v>
       </c>
@@ -5087,10 +5126,10 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="O32" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="182">
         <v>20</v>
       </c>
@@ -5135,10 +5174,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="O33" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="181">
         <v>21</v>
       </c>
@@ -5186,13 +5225,13 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="278">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="214">
         <f>A34+1</f>
         <v>22</v>
       </c>
-      <c r="B35" s="279" t="s">
-        <v>24</v>
+      <c r="B35" s="215" t="s">
+        <v>278</v>
       </c>
       <c r="C35" s="104"/>
       <c r="D35" s="98">
@@ -5234,13 +5273,13 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="179">
         <f t="shared" ref="A36:A99" si="9">A35+1</f>
         <v>23</v>
       </c>
       <c r="B36" s="105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36" s="104"/>
       <c r="D36" s="98">
@@ -5283,13 +5322,13 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="179">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="B37" s="105" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37" s="104"/>
       <c r="D37" s="98">
@@ -5332,13 +5371,13 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="179">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="B38" s="105" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C38" s="104"/>
       <c r="D38" s="98">
@@ -5378,13 +5417,13 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="179">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="B39" s="105" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="104"/>
       <c r="D39" s="98">
@@ -5427,13 +5466,13 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="179">
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="B40" s="105" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" s="104"/>
       <c r="D40" s="98">
@@ -5476,13 +5515,13 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="179">
         <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="B41" s="105" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" s="104"/>
       <c r="D41" s="98">
@@ -5524,13 +5563,13 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="180">
         <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="B42" s="120" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" s="121"/>
       <c r="D42" s="114">
@@ -5570,16 +5609,16 @@
         <v>0.29000000000000009</v>
       </c>
       <c r="O42" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="181">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="B43" s="149" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" s="104"/>
       <c r="D43" s="98">
@@ -5621,13 +5660,13 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="179">
         <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="B44" s="105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C44" s="104"/>
       <c r="D44" s="98">
@@ -5669,13 +5708,13 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="179">
         <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="B45" s="105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" s="104"/>
       <c r="D45" s="98">
@@ -5715,13 +5754,13 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="182">
         <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="B46" s="158" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" s="159"/>
       <c r="D46" s="160">
@@ -5761,13 +5800,13 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="179">
         <f t="shared" si="9"/>
         <v>34</v>
       </c>
       <c r="B47" s="105" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C47" s="104"/>
       <c r="D47" s="98">
@@ -5810,13 +5849,13 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="180">
         <f t="shared" si="9"/>
         <v>35</v>
       </c>
       <c r="B48" s="120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" s="121"/>
       <c r="D48" s="114">
@@ -5858,16 +5897,16 @@
         <v>0.35000000000000014</v>
       </c>
       <c r="O48" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="179">
         <f t="shared" si="9"/>
         <v>36</v>
       </c>
       <c r="B49" s="105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49" s="104"/>
       <c r="D49" s="98">
@@ -5910,16 +5949,16 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="O49" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="179">
         <f t="shared" si="9"/>
         <v>37</v>
       </c>
       <c r="B50" s="105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" s="104"/>
       <c r="D50" s="98">
@@ -5962,13 +6001,13 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="179">
         <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="B51" s="105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" s="104"/>
       <c r="D51" s="98">
@@ -6008,13 +6047,13 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="179">
         <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="B52" s="105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C52" s="104"/>
       <c r="D52" s="98">
@@ -6057,13 +6096,13 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="179">
         <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="B53" s="105" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="104"/>
       <c r="D53" s="98">
@@ -6103,13 +6142,13 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="179">
         <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="B54" s="105" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" s="104"/>
       <c r="D54" s="98">
@@ -6151,13 +6190,13 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="182">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="B55" s="158" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C55" s="159"/>
       <c r="D55" s="160">
@@ -6197,13 +6236,13 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="179">
         <f t="shared" si="9"/>
         <v>43</v>
       </c>
       <c r="B56" s="105" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C56" s="104"/>
       <c r="D56" s="98">
@@ -6245,13 +6284,13 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="179">
         <f t="shared" si="9"/>
         <v>44</v>
       </c>
       <c r="B57" s="105" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C57" s="104"/>
       <c r="D57" s="98">
@@ -6291,13 +6330,13 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="179">
         <f t="shared" si="9"/>
         <v>45</v>
       </c>
       <c r="B58" s="105" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C58" s="104"/>
       <c r="D58" s="98">
@@ -6340,13 +6379,13 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="179">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
       <c r="B59" s="105" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C59" s="104"/>
       <c r="D59" s="98">
@@ -6388,16 +6427,16 @@
         <v>0.46000000000000024</v>
       </c>
       <c r="O59" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="180">
         <f t="shared" si="9"/>
         <v>47</v>
       </c>
       <c r="B60" s="120" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="121"/>
       <c r="D60" s="114">
@@ -6439,16 +6478,16 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="O60" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="181">
         <f t="shared" si="9"/>
         <v>48</v>
       </c>
       <c r="B61" s="149" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="148"/>
       <c r="D61" s="144">
@@ -6491,16 +6530,16 @@
         <v>0.48000000000000026</v>
       </c>
       <c r="O61" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="179">
         <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="B62" s="105" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62" s="104"/>
       <c r="D62" s="98">
@@ -6542,13 +6581,13 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="179">
         <f t="shared" si="9"/>
         <v>50</v>
       </c>
       <c r="B63" s="105" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C63" s="104"/>
       <c r="D63" s="98">
@@ -6591,13 +6630,13 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="209">
         <f t="shared" si="9"/>
         <v>51</v>
       </c>
       <c r="B64" s="210" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C64" s="211"/>
       <c r="D64" s="212">
@@ -6639,13 +6678,13 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="179">
         <f t="shared" si="9"/>
         <v>52</v>
       </c>
       <c r="B65" s="105" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C65" s="104"/>
       <c r="D65" s="98">
@@ -6688,13 +6727,13 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="205">
         <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="B66" s="206" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C66" s="148"/>
       <c r="D66" s="144">
@@ -6736,13 +6775,13 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="179">
         <f t="shared" si="9"/>
         <v>54</v>
       </c>
       <c r="B67" s="105" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C67" s="104"/>
       <c r="D67" s="98">
@@ -6784,13 +6823,13 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="179">
         <f t="shared" si="9"/>
         <v>55</v>
       </c>
       <c r="B68" s="105" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C68" s="104"/>
       <c r="D68" s="98">
@@ -6832,13 +6871,13 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="179">
         <f t="shared" si="9"/>
         <v>56</v>
       </c>
       <c r="B69" s="105" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C69" s="104"/>
       <c r="D69" s="98">
@@ -6880,13 +6919,13 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="282">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="218">
         <f t="shared" si="9"/>
         <v>57</v>
       </c>
-      <c r="B70" s="283" t="s">
-        <v>58</v>
+      <c r="B70" s="219" t="s">
+        <v>57</v>
       </c>
       <c r="C70" s="104"/>
       <c r="D70" s="98">
@@ -6928,13 +6967,13 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="179">
         <f t="shared" si="9"/>
         <v>58</v>
       </c>
       <c r="B71" s="105" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C71" s="104"/>
       <c r="D71" s="98">
@@ -6977,13 +7016,13 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="181">
         <f t="shared" si="9"/>
         <v>59</v>
       </c>
       <c r="B72" s="149" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C72" s="148"/>
       <c r="D72" s="144">
@@ -7026,13 +7065,13 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="179">
         <f t="shared" si="9"/>
         <v>60</v>
       </c>
       <c r="B73" s="105" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C73" s="104"/>
       <c r="D73" s="98">
@@ -7074,13 +7113,13 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="179">
         <f t="shared" si="9"/>
         <v>61</v>
       </c>
       <c r="B74" s="105" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C74" s="104"/>
       <c r="D74" s="98">
@@ -7123,13 +7162,13 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="179">
         <f t="shared" si="9"/>
         <v>62</v>
       </c>
       <c r="B75" s="105" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C75" s="104"/>
       <c r="D75" s="98">
@@ -7171,13 +7210,13 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="179">
         <f t="shared" si="9"/>
         <v>63</v>
       </c>
       <c r="B76" s="105" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C76" s="104"/>
       <c r="D76" s="98">
@@ -7220,13 +7259,13 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="179">
         <f t="shared" si="9"/>
         <v>64</v>
       </c>
       <c r="B77" s="105" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C77" s="104"/>
       <c r="D77" s="98">
@@ -7271,13 +7310,13 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="180">
         <f t="shared" si="9"/>
         <v>65</v>
       </c>
       <c r="B78" s="120" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C78" s="121"/>
       <c r="D78" s="114">
@@ -7319,16 +7358,16 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="O78" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="179">
         <f t="shared" si="9"/>
         <v>66</v>
       </c>
       <c r="B79" s="105" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C79" s="104"/>
       <c r="D79" s="98">
@@ -7370,13 +7409,13 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="179">
         <f t="shared" si="9"/>
         <v>67</v>
       </c>
       <c r="B80" s="105" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C80" s="104"/>
       <c r="D80" s="98">
@@ -7418,13 +7457,13 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="179">
         <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="B81" s="105" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C81" s="104"/>
       <c r="D81" s="98">
@@ -7466,13 +7505,13 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="179">
         <f t="shared" si="9"/>
         <v>69</v>
       </c>
       <c r="B82" s="105" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C82" s="104"/>
       <c r="D82" s="98">
@@ -7514,13 +7553,13 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="180">
         <f t="shared" si="9"/>
         <v>70</v>
       </c>
       <c r="B83" s="120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C83" s="121"/>
       <c r="D83" s="114">
@@ -7560,16 +7599,16 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="O83" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="181">
         <f t="shared" si="9"/>
         <v>71</v>
       </c>
       <c r="B84" s="149" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C84" s="104"/>
       <c r="D84" s="98">
@@ -7612,13 +7651,13 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="179">
         <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="B85" s="105" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C85" s="104"/>
       <c r="D85" s="98">
@@ -7661,13 +7700,13 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="179">
         <f t="shared" si="9"/>
         <v>73</v>
       </c>
       <c r="B86" s="105" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C86" s="104"/>
       <c r="D86" s="98">
@@ -7707,13 +7746,13 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="179">
         <f t="shared" si="9"/>
         <v>74</v>
       </c>
       <c r="B87" s="105" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C87" s="104"/>
       <c r="D87" s="98">
@@ -7753,13 +7792,13 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="179">
         <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="B88" s="105" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C88" s="104"/>
       <c r="D88" s="98">
@@ -7802,13 +7841,13 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="179">
         <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="B89" s="105" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C89" s="104"/>
       <c r="D89" s="98">
@@ -7851,13 +7890,13 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="179">
         <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="B90" s="105" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C90" s="104"/>
       <c r="D90" s="98">
@@ -7899,13 +7938,13 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="182">
         <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="B91" s="158" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C91" s="159"/>
       <c r="D91" s="160">
@@ -7945,13 +7984,13 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="179">
         <f t="shared" si="9"/>
         <v>79</v>
       </c>
       <c r="B92" s="105" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C92" s="104"/>
       <c r="D92" s="98">
@@ -7994,13 +8033,13 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="179">
         <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="B93" s="105" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C93" s="104"/>
       <c r="D93" s="98">
@@ -8042,13 +8081,13 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="180">
         <f t="shared" si="9"/>
         <v>81</v>
       </c>
       <c r="B94" s="120" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C94" s="121"/>
       <c r="D94" s="114">
@@ -8090,16 +8129,16 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="O94" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="179">
         <f t="shared" si="9"/>
         <v>82</v>
       </c>
       <c r="B95" s="105" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C95" s="104"/>
       <c r="D95" s="98">
@@ -8142,13 +8181,13 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="181">
         <f t="shared" si="9"/>
         <v>83</v>
       </c>
       <c r="B96" s="149" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C96" s="148"/>
       <c r="D96" s="144">
@@ -8191,13 +8230,13 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="181">
         <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="B97" s="149" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C97" s="148"/>
       <c r="D97" s="144">
@@ -8240,13 +8279,13 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="179">
         <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="B98" s="105" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C98" s="104"/>
       <c r="D98" s="98">
@@ -8289,13 +8328,13 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="179">
         <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="B99" s="105" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C99" s="104"/>
       <c r="D99" s="98">
@@ -8338,13 +8377,13 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="179">
         <f t="shared" ref="A100:A116" si="22">A99+1</f>
         <v>87</v>
       </c>
       <c r="B100" s="105" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C100" s="104"/>
       <c r="D100" s="98">
@@ -8386,13 +8425,13 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="179">
         <f t="shared" si="22"/>
         <v>88</v>
       </c>
       <c r="B101" s="105" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C101" s="104"/>
       <c r="D101" s="98">
@@ -8435,13 +8474,13 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="179">
         <f t="shared" si="22"/>
         <v>89</v>
       </c>
       <c r="B102" s="105" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C102" s="104"/>
       <c r="D102" s="98">
@@ -8484,13 +8523,13 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="179">
         <f t="shared" si="22"/>
         <v>90</v>
       </c>
       <c r="B103" s="105" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C103" s="104"/>
       <c r="D103" s="98">
@@ -8532,13 +8571,13 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="179">
         <f t="shared" si="22"/>
         <v>91</v>
       </c>
       <c r="B104" s="105" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C104" s="104"/>
       <c r="D104" s="98">
@@ -8580,13 +8619,13 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="179">
         <f t="shared" si="22"/>
         <v>92</v>
       </c>
       <c r="B105" s="105" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C105" s="104"/>
       <c r="D105" s="98">
@@ -8629,13 +8668,13 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="181">
         <f t="shared" si="22"/>
         <v>93</v>
       </c>
       <c r="B106" s="149" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C106" s="148"/>
       <c r="D106" s="144">
@@ -8678,13 +8717,13 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="181">
         <f t="shared" si="22"/>
         <v>94</v>
       </c>
       <c r="B107" s="149" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C107" s="148"/>
       <c r="D107" s="144">
@@ -8727,13 +8766,13 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="181">
         <f t="shared" si="22"/>
         <v>95</v>
       </c>
       <c r="B108" s="149" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C108" s="148"/>
       <c r="D108" s="144">
@@ -8775,13 +8814,13 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="181">
         <f t="shared" si="22"/>
         <v>96</v>
       </c>
       <c r="B109" s="149" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C109" s="148"/>
       <c r="D109" s="144">
@@ -8824,16 +8863,16 @@
         <v>0.96000000000000063</v>
       </c>
       <c r="O109" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="181">
         <f t="shared" si="22"/>
         <v>97</v>
       </c>
       <c r="B110" s="149" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C110" s="148"/>
       <c r="D110" s="144">
@@ -8876,13 +8915,13 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="181">
         <f t="shared" si="22"/>
         <v>98</v>
       </c>
       <c r="B111" s="149" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C111" s="148"/>
       <c r="D111" s="144">
@@ -8925,13 +8964,13 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="181">
         <f t="shared" si="22"/>
         <v>99</v>
       </c>
       <c r="B112" s="149" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C112" s="148"/>
       <c r="D112" s="144">
@@ -8973,13 +9012,13 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="181">
         <f t="shared" si="22"/>
         <v>100</v>
       </c>
       <c r="B113" s="149" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C113" s="148"/>
       <c r="D113" s="144">
@@ -9022,13 +9061,13 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="181">
         <f t="shared" si="22"/>
         <v>101</v>
       </c>
       <c r="B114" s="142" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C114" s="148"/>
       <c r="D114" s="144">
@@ -9071,13 +9110,13 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="181">
         <f t="shared" si="22"/>
         <v>102</v>
       </c>
       <c r="B115" s="142" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C115" s="148"/>
       <c r="D115" s="144">
@@ -9120,13 +9159,13 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A116" s="181">
         <f t="shared" si="22"/>
         <v>103</v>
       </c>
       <c r="B116" s="149" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C116" s="148"/>
       <c r="D116" s="144">
@@ -9169,7 +9208,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="181"/>
       <c r="B117" s="142"/>
       <c r="C117" s="148"/>
@@ -9185,7 +9224,7 @@
       <c r="M117" s="192"/>
       <c r="N117" s="63"/>
     </row>
-    <row r="118" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="183"/>
       <c r="B118" s="184"/>
       <c r="C118" s="184"/>
@@ -9227,93 +9266,96 @@
         <v>35058186.560000002</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="106"/>
       <c r="C119" s="106"/>
     </row>
-    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="256" t="s">
-        <v>106</v>
-      </c>
-      <c r="C121" s="256"/>
-      <c r="D121" s="256"/>
-      <c r="E121" s="256"/>
-      <c r="F121" s="256"/>
-      <c r="G121" s="256"/>
-      <c r="H121" s="256"/>
-      <c r="I121" s="256"/>
-      <c r="J121" s="256"/>
-      <c r="K121" s="256"/>
-      <c r="L121" s="256"/>
-    </row>
-    <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="256"/>
-      <c r="C122" s="256"/>
-      <c r="D122" s="256"/>
-      <c r="E122" s="256"/>
-      <c r="F122" s="256"/>
-      <c r="G122" s="256"/>
-      <c r="H122" s="256"/>
-      <c r="I122" s="256"/>
-      <c r="J122" s="256"/>
-      <c r="K122" s="256"/>
-      <c r="L122" s="256"/>
-    </row>
-    <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="256"/>
-      <c r="C123" s="256"/>
-      <c r="D123" s="256"/>
-      <c r="E123" s="256"/>
-      <c r="F123" s="256"/>
-      <c r="G123" s="256"/>
-      <c r="H123" s="256"/>
-      <c r="I123" s="256"/>
-      <c r="J123" s="256"/>
-      <c r="K123" s="256"/>
-      <c r="L123" s="256"/>
-    </row>
-    <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="256"/>
-      <c r="C124" s="256"/>
-      <c r="D124" s="256"/>
-      <c r="E124" s="256"/>
-      <c r="F124" s="256"/>
-      <c r="G124" s="256"/>
-      <c r="H124" s="256"/>
-      <c r="I124" s="256"/>
-      <c r="J124" s="256"/>
-      <c r="K124" s="256"/>
-      <c r="L124" s="256"/>
-    </row>
-    <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="256"/>
-      <c r="C125" s="256"/>
-      <c r="D125" s="256"/>
-      <c r="E125" s="256"/>
-      <c r="F125" s="256"/>
-      <c r="G125" s="256"/>
-      <c r="H125" s="256"/>
-      <c r="I125" s="256"/>
-      <c r="J125" s="256"/>
-      <c r="K125" s="256"/>
-      <c r="L125" s="256"/>
-    </row>
-    <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="256"/>
-      <c r="C126" s="256"/>
-      <c r="D126" s="256"/>
-      <c r="E126" s="256"/>
-      <c r="F126" s="256"/>
-      <c r="G126" s="256"/>
-      <c r="H126" s="256"/>
-      <c r="I126" s="256"/>
-      <c r="J126" s="256"/>
-      <c r="K126" s="256"/>
-      <c r="L126" s="256"/>
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="235" t="s">
+        <v>105</v>
+      </c>
+      <c r="C121" s="235"/>
+      <c r="D121" s="235"/>
+      <c r="E121" s="235"/>
+      <c r="F121" s="235"/>
+      <c r="G121" s="235"/>
+      <c r="H121" s="235"/>
+      <c r="I121" s="235"/>
+      <c r="J121" s="235"/>
+      <c r="K121" s="235"/>
+      <c r="L121" s="235"/>
+    </row>
+    <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="235"/>
+      <c r="C122" s="235"/>
+      <c r="D122" s="235"/>
+      <c r="E122" s="235"/>
+      <c r="F122" s="235"/>
+      <c r="G122" s="235"/>
+      <c r="H122" s="235"/>
+      <c r="I122" s="235"/>
+      <c r="J122" s="235"/>
+      <c r="K122" s="235"/>
+      <c r="L122" s="235"/>
+    </row>
+    <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="235"/>
+      <c r="C123" s="235"/>
+      <c r="D123" s="235"/>
+      <c r="E123" s="235"/>
+      <c r="F123" s="235"/>
+      <c r="G123" s="235"/>
+      <c r="H123" s="235"/>
+      <c r="I123" s="235"/>
+      <c r="J123" s="235"/>
+      <c r="K123" s="235"/>
+      <c r="L123" s="235"/>
+    </row>
+    <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="235"/>
+      <c r="C124" s="235"/>
+      <c r="D124" s="235"/>
+      <c r="E124" s="235"/>
+      <c r="F124" s="235"/>
+      <c r="G124" s="235"/>
+      <c r="H124" s="235"/>
+      <c r="I124" s="235"/>
+      <c r="J124" s="235"/>
+      <c r="K124" s="235"/>
+      <c r="L124" s="235"/>
+    </row>
+    <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="235"/>
+      <c r="C125" s="235"/>
+      <c r="D125" s="235"/>
+      <c r="E125" s="235"/>
+      <c r="F125" s="235"/>
+      <c r="G125" s="235"/>
+      <c r="H125" s="235"/>
+      <c r="I125" s="235"/>
+      <c r="J125" s="235"/>
+      <c r="K125" s="235"/>
+      <c r="L125" s="235"/>
+    </row>
+    <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="235"/>
+      <c r="C126" s="235"/>
+      <c r="D126" s="235"/>
+      <c r="E126" s="235"/>
+      <c r="F126" s="235"/>
+      <c r="G126" s="235"/>
+      <c r="H126" s="235"/>
+      <c r="I126" s="235"/>
+      <c r="J126" s="235"/>
+      <c r="K126" s="235"/>
+      <c r="L126" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="J12:J13"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="B121:L126"/>
     <mergeCell ref="A9:M9"/>
@@ -9330,9 +9372,6 @@
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="J12:J13"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9342,33 +9381,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C4:C25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" s="204" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="5" spans="3:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" s="213" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="216" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C10" s="280" t="s">
+    <row r="12" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="217" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="12" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C12" s="281" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9377,38 +9416,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4895585-CAB1-4A86-BA25-20A34A9B436A}">
   <dimension ref="C4:O21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" customWidth="1"/>
-    <col min="13" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C4" s="260" t="s">
-        <v>257</v>
-      </c>
-      <c r="D4" s="260"/>
+    <row r="4" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C4" s="280" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="280"/>
       <c r="E4" s="201"/>
       <c r="F4" s="199" t="s">
+        <v>257</v>
+      </c>
+      <c r="H4" t="s">
         <v>258</v>
       </c>
-      <c r="H4" t="s">
-        <v>259</v>
-      </c>
-      <c r="J4" s="262" t="s">
-        <v>261</v>
-      </c>
-      <c r="K4" s="262"/>
-    </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C5" s="261">
+      <c r="J4" s="270" t="s">
+        <v>260</v>
+      </c>
+      <c r="K4" s="270"/>
+    </row>
+    <row r="5" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C5" s="269">
         <v>168835.53000000003</v>
       </c>
-      <c r="D5" s="261"/>
+      <c r="D5" s="269"/>
       <c r="E5" s="202"/>
       <c r="F5" s="200">
         <f>C5</f>
@@ -9417,42 +9456,42 @@
       <c r="H5" s="80">
         <v>0</v>
       </c>
-      <c r="J5" s="263">
+      <c r="J5" s="281">
         <f>F5</f>
         <v>168835.53000000003</v>
       </c>
-      <c r="K5" s="263"/>
-    </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M7" s="266" t="s">
-        <v>263</v>
-      </c>
-      <c r="N7" s="266"/>
-      <c r="O7" s="266"/>
-    </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="K5" s="281"/>
+    </row>
+    <row r="7" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="M7" s="268" t="s">
+        <v>262</v>
+      </c>
+      <c r="N7" s="268"/>
+      <c r="O7" s="268"/>
+    </row>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F8" s="199" t="s">
+        <v>257</v>
+      </c>
+      <c r="H8" t="s">
         <v>258</v>
       </c>
-      <c r="H8" t="s">
-        <v>259</v>
-      </c>
-      <c r="J8" s="262" t="s">
-        <v>262</v>
-      </c>
-      <c r="K8" s="262"/>
-      <c r="M8" s="266"/>
-      <c r="N8" s="266"/>
-      <c r="O8" s="266"/>
-    </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C9" s="261">
+      <c r="J8" s="270" t="s">
+        <v>261</v>
+      </c>
+      <c r="K8" s="270"/>
+      <c r="M8" s="268"/>
+      <c r="N8" s="268"/>
+      <c r="O8" s="268"/>
+    </row>
+    <row r="9" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="269">
         <v>168836.53</v>
       </c>
-      <c r="D9" s="261"/>
+      <c r="D9" s="269"/>
       <c r="F9" s="80">
         <v>0</v>
       </c>
@@ -9460,18 +9499,18 @@
         <f>C9-F9</f>
         <v>168836.53</v>
       </c>
-      <c r="J9" s="261">
+      <c r="J9" s="269">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K9" s="261"/>
-      <c r="M9" s="265">
+      <c r="K9" s="269"/>
+      <c r="M9" s="267">
         <v>300737.53000000003</v>
       </c>
-      <c r="N9" s="265"/>
-      <c r="O9" s="265"/>
-    </row>
-    <row r="10" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N9" s="267"/>
+      <c r="O9" s="267"/>
+    </row>
+    <row r="10" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="202"/>
       <c r="D10" s="202"/>
       <c r="F10" s="80"/>
@@ -9482,37 +9521,37 @@
       <c r="N10" s="203"/>
       <c r="O10" s="203"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="M11" s="270" t="s">
+    <row r="11" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="M11" s="274" t="s">
+        <v>262</v>
+      </c>
+      <c r="N11" s="275"/>
+      <c r="O11" s="276"/>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
         <v>263</v>
       </c>
-      <c r="N11" s="271"/>
-      <c r="O11" s="272"/>
-    </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
+      <c r="F12" s="199" t="s">
+        <v>257</v>
+      </c>
+      <c r="H12" t="s">
+        <v>258</v>
+      </c>
+      <c r="J12" s="270" t="s">
         <v>264</v>
       </c>
-      <c r="F12" s="199" t="s">
-        <v>258</v>
-      </c>
-      <c r="H12" t="s">
-        <v>259</v>
-      </c>
-      <c r="J12" s="262" t="s">
-        <v>265</v>
-      </c>
-      <c r="K12" s="262"/>
-      <c r="M12" s="273"/>
-      <c r="N12" s="274"/>
-      <c r="O12" s="275"/>
-    </row>
-    <row r="13" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="261">
+      <c r="K12" s="270"/>
+      <c r="M12" s="277"/>
+      <c r="N12" s="278"/>
+      <c r="O12" s="279"/>
+    </row>
+    <row r="13" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="269">
         <f>M9</f>
         <v>300737.53000000003</v>
       </c>
-      <c r="D13" s="261"/>
+      <c r="D13" s="269"/>
       <c r="F13" s="80">
         <v>98556.53</v>
       </c>
@@ -9520,127 +9559,132 @@
         <f>C13-F13</f>
         <v>202181.00000000003</v>
       </c>
-      <c r="J13" s="261">
+      <c r="J13" s="269">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K13" s="261"/>
-      <c r="M13" s="267">
+      <c r="K13" s="269"/>
+      <c r="M13" s="271">
         <f>J13+H13-0.27</f>
         <v>371016.53</v>
       </c>
-      <c r="N13" s="268"/>
-      <c r="O13" s="269"/>
-    </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C15" s="264" t="s">
-        <v>267</v>
-      </c>
-      <c r="D15" s="264"/>
-      <c r="E15" s="264"/>
-      <c r="F15" s="264"/>
-      <c r="G15" s="264"/>
-      <c r="H15" s="264"/>
-      <c r="I15" s="264"/>
-      <c r="J15" s="264"/>
-      <c r="K15" s="264"/>
-      <c r="L15" s="264"/>
-      <c r="M15" s="264"/>
-      <c r="N15" s="264"/>
-      <c r="O15" s="264"/>
-    </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C16" s="264"/>
-      <c r="D16" s="264"/>
-      <c r="E16" s="264"/>
-      <c r="F16" s="264"/>
-      <c r="G16" s="264"/>
-      <c r="H16" s="264"/>
-      <c r="I16" s="264"/>
-      <c r="J16" s="264"/>
-      <c r="K16" s="264"/>
-      <c r="L16" s="264"/>
-      <c r="M16" s="264"/>
-      <c r="N16" s="264"/>
-      <c r="O16" s="264"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C17" s="264"/>
-      <c r="D17" s="264"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
-      <c r="J17" s="264"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="264"/>
-      <c r="M17" s="264"/>
-      <c r="N17" s="264"/>
-      <c r="O17" s="264"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C18" s="264"/>
-      <c r="D18" s="264"/>
-      <c r="E18" s="264"/>
-      <c r="F18" s="264"/>
-      <c r="G18" s="264"/>
-      <c r="H18" s="264"/>
-      <c r="I18" s="264"/>
-      <c r="J18" s="264"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
-      <c r="M18" s="264"/>
-      <c r="N18" s="264"/>
-      <c r="O18" s="264"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C19" s="264"/>
-      <c r="D19" s="264"/>
-      <c r="E19" s="264"/>
-      <c r="F19" s="264"/>
-      <c r="G19" s="264"/>
-      <c r="H19" s="264"/>
-      <c r="I19" s="264"/>
-      <c r="J19" s="264"/>
-      <c r="K19" s="264"/>
-      <c r="L19" s="264"/>
-      <c r="M19" s="264"/>
-      <c r="N19" s="264"/>
-      <c r="O19" s="264"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C20" s="264"/>
-      <c r="D20" s="264"/>
-      <c r="E20" s="264"/>
-      <c r="F20" s="264"/>
-      <c r="G20" s="264"/>
-      <c r="H20" s="264"/>
-      <c r="I20" s="264"/>
-      <c r="J20" s="264"/>
-      <c r="K20" s="264"/>
-      <c r="L20" s="264"/>
-      <c r="M20" s="264"/>
-      <c r="N20" s="264"/>
-      <c r="O20" s="264"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="264"/>
-      <c r="D21" s="264"/>
-      <c r="E21" s="264"/>
-      <c r="F21" s="264"/>
-      <c r="G21" s="264"/>
-      <c r="H21" s="264"/>
-      <c r="I21" s="264"/>
-      <c r="J21" s="264"/>
-      <c r="K21" s="264"/>
-      <c r="L21" s="264"/>
-      <c r="M21" s="264"/>
-      <c r="N21" s="264"/>
-      <c r="O21" s="264"/>
+      <c r="N13" s="272"/>
+      <c r="O13" s="273"/>
+    </row>
+    <row r="15" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C15" s="266" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="266"/>
+      <c r="E15" s="266"/>
+      <c r="F15" s="266"/>
+      <c r="G15" s="266"/>
+      <c r="H15" s="266"/>
+      <c r="I15" s="266"/>
+      <c r="J15" s="266"/>
+      <c r="K15" s="266"/>
+      <c r="L15" s="266"/>
+      <c r="M15" s="266"/>
+      <c r="N15" s="266"/>
+      <c r="O15" s="266"/>
+    </row>
+    <row r="16" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C16" s="266"/>
+      <c r="D16" s="266"/>
+      <c r="E16" s="266"/>
+      <c r="F16" s="266"/>
+      <c r="G16" s="266"/>
+      <c r="H16" s="266"/>
+      <c r="I16" s="266"/>
+      <c r="J16" s="266"/>
+      <c r="K16" s="266"/>
+      <c r="L16" s="266"/>
+      <c r="M16" s="266"/>
+      <c r="N16" s="266"/>
+      <c r="O16" s="266"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C17" s="266"/>
+      <c r="D17" s="266"/>
+      <c r="E17" s="266"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
+      <c r="J17" s="266"/>
+      <c r="K17" s="266"/>
+      <c r="L17" s="266"/>
+      <c r="M17" s="266"/>
+      <c r="N17" s="266"/>
+      <c r="O17" s="266"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C18" s="266"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="266"/>
+      <c r="J18" s="266"/>
+      <c r="K18" s="266"/>
+      <c r="L18" s="266"/>
+      <c r="M18" s="266"/>
+      <c r="N18" s="266"/>
+      <c r="O18" s="266"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C19" s="266"/>
+      <c r="D19" s="266"/>
+      <c r="E19" s="266"/>
+      <c r="F19" s="266"/>
+      <c r="G19" s="266"/>
+      <c r="H19" s="266"/>
+      <c r="I19" s="266"/>
+      <c r="J19" s="266"/>
+      <c r="K19" s="266"/>
+      <c r="L19" s="266"/>
+      <c r="M19" s="266"/>
+      <c r="N19" s="266"/>
+      <c r="O19" s="266"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C20" s="266"/>
+      <c r="D20" s="266"/>
+      <c r="E20" s="266"/>
+      <c r="F20" s="266"/>
+      <c r="G20" s="266"/>
+      <c r="H20" s="266"/>
+      <c r="I20" s="266"/>
+      <c r="J20" s="266"/>
+      <c r="K20" s="266"/>
+      <c r="L20" s="266"/>
+      <c r="M20" s="266"/>
+      <c r="N20" s="266"/>
+      <c r="O20" s="266"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C21" s="266"/>
+      <c r="D21" s="266"/>
+      <c r="E21" s="266"/>
+      <c r="F21" s="266"/>
+      <c r="G21" s="266"/>
+      <c r="H21" s="266"/>
+      <c r="I21" s="266"/>
+      <c r="J21" s="266"/>
+      <c r="K21" s="266"/>
+      <c r="L21" s="266"/>
+      <c r="M21" s="266"/>
+      <c r="N21" s="266"/>
+      <c r="O21" s="266"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="C15:O21"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="M7:O8"/>
@@ -9651,11 +9695,6 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M11:O12"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="125" orientation="landscape" r:id="rId1"/>
@@ -9665,94 +9704,94 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0DC61AA-F548-49A9-A9B8-49FB942F95D7}">
   <dimension ref="D4:N13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" customWidth="1"/>
+    <col min="3" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F4" s="80">
         <v>843306.42</v>
       </c>
-      <c r="G4" s="276" t="s">
-        <v>274</v>
-      </c>
-      <c r="H4" s="276"/>
-      <c r="I4" s="276"/>
-      <c r="J4" s="276"/>
-      <c r="K4" s="276"/>
-      <c r="L4" s="276"/>
-      <c r="M4" s="276"/>
-      <c r="N4" s="276"/>
-    </row>
-    <row r="5" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="G4" s="282" t="s">
+        <v>273</v>
+      </c>
+      <c r="H4" s="282"/>
+      <c r="I4" s="282"/>
+      <c r="J4" s="282"/>
+      <c r="K4" s="282"/>
+      <c r="L4" s="282"/>
+      <c r="M4" s="282"/>
+      <c r="N4" s="282"/>
+    </row>
+    <row r="5" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F5" s="208">
         <v>-68000</v>
       </c>
-      <c r="G5" s="276"/>
-      <c r="H5" s="276"/>
-      <c r="I5" s="276"/>
-      <c r="J5" s="276"/>
-      <c r="K5" s="276"/>
-      <c r="L5" s="276"/>
-      <c r="M5" s="276"/>
-      <c r="N5" s="276"/>
-    </row>
-    <row r="6" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="G5" s="282"/>
+      <c r="H5" s="282"/>
+      <c r="I5" s="282"/>
+      <c r="J5" s="282"/>
+      <c r="K5" s="282"/>
+      <c r="L5" s="282"/>
+      <c r="M5" s="282"/>
+      <c r="N5" s="282"/>
+    </row>
+    <row r="6" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F6" s="63">
         <f>F4+F5</f>
         <v>775306.42</v>
       </c>
-      <c r="G6" s="276"/>
-      <c r="H6" s="276"/>
-      <c r="I6" s="276"/>
-      <c r="J6" s="276"/>
-      <c r="K6" s="276"/>
-      <c r="L6" s="276"/>
-      <c r="M6" s="276"/>
-      <c r="N6" s="276"/>
-    </row>
-    <row r="7" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="G7" s="276"/>
-      <c r="H7" s="276"/>
-      <c r="I7" s="276"/>
-      <c r="J7" s="276"/>
-      <c r="K7" s="276"/>
-      <c r="L7" s="276"/>
-      <c r="M7" s="276"/>
-      <c r="N7" s="276"/>
-    </row>
-    <row r="8" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="G6" s="282"/>
+      <c r="H6" s="282"/>
+      <c r="I6" s="282"/>
+      <c r="J6" s="282"/>
+      <c r="K6" s="282"/>
+      <c r="L6" s="282"/>
+      <c r="M6" s="282"/>
+      <c r="N6" s="282"/>
+    </row>
+    <row r="7" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="G7" s="282"/>
+      <c r="H7" s="282"/>
+      <c r="I7" s="282"/>
+      <c r="J7" s="282"/>
+      <c r="K7" s="282"/>
+      <c r="L7" s="282"/>
+      <c r="M7" s="282"/>
+      <c r="N7" s="282"/>
+    </row>
+    <row r="8" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F8" s="80">
         <v>135235.80000000002</v>
       </c>
     </row>
-    <row r="9" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F9" s="80">
         <v>33600.000000000007</v>
       </c>
     </row>
-    <row r="11" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D11" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="207">
@@ -9760,13 +9799,13 @@
         <v>944142.22000000009</v>
       </c>
     </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D13" s="277" t="s">
-        <v>275</v>
-      </c>
-      <c r="E13" s="277"/>
-      <c r="F13" s="277"/>
-      <c r="G13" s="277"/>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D13" s="283" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" s="283"/>
+      <c r="F13" s="283"/>
+      <c r="G13" s="283"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
+++ b/2026/ITALIA/Febrero/Febrero ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1E17A2-F5BD-44AD-9D40-E8A2AA7355C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505C884E-3C61-47E1-BF72-D09CDEF01E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5460" yWindow="3270" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -2017,43 +2017,55 @@
     <xf numFmtId="0" fontId="19" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2116,12 +2128,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2149,12 +2155,14 @@
     <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2164,10 +2172,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2195,10 +2199,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2625,12 +2625,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="227" t="s">
+      <c r="B1" s="222" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="228"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="223"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -2643,12 +2643,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="229" t="s">
+      <c r="B3" s="226" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="229"/>
-      <c r="D3" s="229"/>
-      <c r="E3" s="230"/>
+      <c r="C3" s="226"/>
+      <c r="D3" s="226"/>
+      <c r="E3" s="227"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -2686,49 +2686,49 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="231" t="s">
+      <c r="B8" s="228" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="231"/>
+      <c r="C8" s="228"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="231"/>
-      <c r="C9" s="231"/>
+      <c r="B9" s="228"/>
+      <c r="C9" s="228"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="231"/>
-      <c r="C10" s="231"/>
+      <c r="B10" s="228"/>
+      <c r="C10" s="228"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="232" t="s">
+      <c r="A13" s="229" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="232"/>
-      <c r="C13" s="232"/>
-      <c r="D13" s="232"/>
-      <c r="E13" s="232"/>
+      <c r="B13" s="229"/>
+      <c r="C13" s="229"/>
+      <c r="D13" s="229"/>
+      <c r="E13" s="229"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="232"/>
-      <c r="B14" s="232"/>
-      <c r="C14" s="232"/>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
+      <c r="A14" s="229"/>
+      <c r="B14" s="229"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="232"/>
-      <c r="B15" s="232"/>
-      <c r="C15" s="232"/>
-      <c r="D15" s="232"/>
-      <c r="E15" s="232"/>
+      <c r="A15" s="229"/>
+      <c r="B15" s="229"/>
+      <c r="C15" s="229"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="229"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="232"/>
-      <c r="B16" s="232"/>
-      <c r="C16" s="232"/>
-      <c r="D16" s="232"/>
-      <c r="E16" s="232"/>
+      <c r="A16" s="229"/>
+      <c r="B16" s="229"/>
+      <c r="C16" s="229"/>
+      <c r="D16" s="229"/>
+      <c r="E16" s="229"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2754,10 +2754,10 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="220" t="s">
+      <c r="A22" s="224" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="221"/>
+      <c r="B22" s="225"/>
       <c r="C22" s="22"/>
       <c r="D22" s="167">
         <v>1931623</v>
@@ -2766,10 +2766,10 @@
       <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="220" t="s">
+      <c r="A23" s="224" t="s">
         <v>175</v>
       </c>
-      <c r="B23" s="221"/>
+      <c r="B23" s="225"/>
       <c r="C23" s="22"/>
       <c r="D23" s="167">
         <v>-420128</v>
@@ -2778,10 +2778,10 @@
       <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="220" t="s">
+      <c r="A24" s="224" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="221"/>
+      <c r="B24" s="225"/>
       <c r="C24" s="22"/>
       <c r="D24" s="168">
         <v>0</v>
@@ -2953,10 +2953,10 @@
       <c r="E38" s="29"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="223" t="s">
+      <c r="A39" s="220" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="224"/>
+      <c r="B39" s="221"/>
       <c r="C39" s="32"/>
       <c r="D39" s="169">
         <v>313739</v>
@@ -2966,10 +2966,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="223" t="s">
+      <c r="A40" s="220" t="s">
         <v>252</v>
       </c>
-      <c r="B40" s="224"/>
+      <c r="B40" s="221"/>
       <c r="C40" s="32"/>
       <c r="D40" s="170">
         <v>214164</v>
@@ -2979,10 +2979,10 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="223" t="s">
+      <c r="A41" s="220" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="224"/>
+      <c r="B41" s="221"/>
       <c r="C41" s="32"/>
       <c r="D41" s="170">
         <v>5204</v>
@@ -3067,10 +3067,10 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="223" t="s">
+      <c r="A48" s="220" t="s">
         <v>113</v>
       </c>
-      <c r="B48" s="224"/>
+      <c r="B48" s="221"/>
       <c r="C48" s="37"/>
       <c r="D48" s="38">
         <v>4813938.26</v>
@@ -3108,10 +3108,10 @@
       <c r="E51" s="43"/>
     </row>
     <row r="52" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="220" t="s">
+      <c r="A52" s="224" t="s">
         <v>177</v>
       </c>
-      <c r="B52" s="221"/>
+      <c r="B52" s="225"/>
       <c r="C52" s="37"/>
       <c r="D52" s="38">
         <v>225000</v>
@@ -3121,10 +3121,10 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="220" t="s">
+      <c r="A53" s="224" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="221"/>
+      <c r="B53" s="225"/>
       <c r="C53" s="37"/>
       <c r="D53" s="38">
         <v>500000</v>
@@ -3134,10 +3134,10 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="220" t="s">
+      <c r="A54" s="224" t="s">
         <v>192</v>
       </c>
-      <c r="B54" s="221"/>
+      <c r="B54" s="225"/>
       <c r="C54" s="37"/>
       <c r="D54" s="38">
         <v>1520000</v>
@@ -3147,10 +3147,10 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="220" t="s">
+      <c r="A55" s="224" t="s">
         <v>221</v>
       </c>
-      <c r="B55" s="221"/>
+      <c r="B55" s="225"/>
       <c r="C55" s="37"/>
       <c r="D55" s="38">
         <f>272252*2</f>
@@ -3161,10 +3161,10 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="220" t="s">
+      <c r="A56" s="224" t="s">
         <v>207</v>
       </c>
-      <c r="B56" s="221"/>
+      <c r="B56" s="225"/>
       <c r="C56" s="37"/>
       <c r="D56" s="38">
         <v>85000</v>
@@ -3175,10 +3175,10 @@
       <c r="F56" s="63"/>
     </row>
     <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="220" t="s">
+      <c r="A57" s="224" t="s">
         <v>226</v>
       </c>
-      <c r="B57" s="221"/>
+      <c r="B57" s="225"/>
       <c r="C57" s="37"/>
       <c r="D57" s="38">
         <v>120000</v>
@@ -3203,10 +3203,10 @@
       <c r="F58" s="63"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="220" t="s">
+      <c r="A59" s="224" t="s">
         <v>208</v>
       </c>
-      <c r="B59" s="221"/>
+      <c r="B59" s="225"/>
       <c r="C59" s="37"/>
       <c r="D59" s="38">
         <v>6000</v>
@@ -3217,10 +3217,10 @@
       <c r="F59" s="63"/>
     </row>
     <row r="60" spans="1:6" ht="85.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="220" t="s">
+      <c r="A60" s="224" t="s">
         <v>249</v>
       </c>
-      <c r="B60" s="221"/>
+      <c r="B60" s="225"/>
       <c r="C60" s="37"/>
       <c r="D60" s="38">
         <v>7000000</v>
@@ -3273,10 +3273,10 @@
       <c r="F63" s="63"/>
     </row>
     <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="220" t="s">
+      <c r="A64" s="224" t="s">
         <v>205</v>
       </c>
-      <c r="B64" s="221"/>
+      <c r="B64" s="225"/>
       <c r="C64" s="37"/>
       <c r="D64" s="38">
         <v>250000</v>
@@ -3301,10 +3301,10 @@
       <c r="F65" s="63"/>
     </row>
     <row r="66" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="220" t="s">
+      <c r="A66" s="224" t="s">
         <v>198</v>
       </c>
-      <c r="B66" s="221"/>
+      <c r="B66" s="225"/>
       <c r="C66" s="37"/>
       <c r="D66" s="38">
         <v>105602.65</v>
@@ -3315,10 +3315,10 @@
       <c r="F66" s="63"/>
     </row>
     <row r="67" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="220" t="s">
+      <c r="A67" s="224" t="s">
         <v>183</v>
       </c>
-      <c r="B67" s="221"/>
+      <c r="B67" s="225"/>
       <c r="C67" s="37"/>
       <c r="D67" s="38">
         <v>2022800</v>
@@ -3349,10 +3349,10 @@
       <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="220" t="s">
+      <c r="A70" s="224" t="s">
         <v>191</v>
       </c>
-      <c r="B70" s="221"/>
+      <c r="B70" s="225"/>
       <c r="C70" s="22"/>
       <c r="D70" s="171">
         <v>650000</v>
@@ -3373,10 +3373,10 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="220" t="s">
+      <c r="A72" s="224" t="s">
         <v>220</v>
       </c>
-      <c r="B72" s="221"/>
+      <c r="B72" s="225"/>
       <c r="C72" s="22"/>
       <c r="D72" s="172">
         <v>62500</v>
@@ -3539,8 +3539,8 @@
       <c r="E88" s="73"/>
     </row>
     <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="220"/>
-      <c r="B89" s="221"/>
+      <c r="A89" s="224"/>
+      <c r="B89" s="225"/>
       <c r="C89" s="37"/>
       <c r="D89" s="45"/>
       <c r="E89" s="73"/>
@@ -3636,42 +3636,42 @@
       </c>
     </row>
     <row r="105" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="226" t="s">
+      <c r="A105" s="232" t="s">
         <v>235</v>
       </c>
-      <c r="B105" s="226"/>
+      <c r="B105" s="232"/>
     </row>
     <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="226"/>
-      <c r="B106" s="226"/>
+      <c r="A106" s="232"/>
+      <c r="B106" s="232"/>
     </row>
     <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="226"/>
-      <c r="B107" s="226"/>
+      <c r="A107" s="232"/>
+      <c r="B107" s="232"/>
     </row>
     <row r="109" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="226" t="s">
+      <c r="A109" s="232" t="s">
         <v>238</v>
       </c>
-      <c r="B109" s="226"/>
+      <c r="B109" s="232"/>
     </row>
     <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="226"/>
-      <c r="B110" s="226"/>
+      <c r="A110" s="232"/>
+      <c r="B110" s="232"/>
     </row>
     <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="226"/>
-      <c r="B111" s="226"/>
+      <c r="A111" s="232"/>
+      <c r="B111" s="232"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="225" t="s">
+      <c r="A114" s="231" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="225"/>
+      <c r="B114" s="231"/>
     </row>
     <row r="115" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="225"/>
-      <c r="B115" s="225"/>
+      <c r="A115" s="231"/>
+      <c r="B115" s="231"/>
     </row>
     <row r="116" spans="1:6" s="82" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
@@ -3877,16 +3877,16 @@
     </row>
     <row r="138" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A139" s="222" t="s">
+      <c r="A139" s="230" t="s">
         <v>128</v>
       </c>
-      <c r="B139" s="222"/>
-      <c r="C139" s="222"/>
+      <c r="B139" s="230"/>
+      <c r="C139" s="230"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="222"/>
-      <c r="B140" s="222"/>
-      <c r="C140" s="222"/>
+      <c r="A140" s="230"/>
+      <c r="B140" s="230"/>
+      <c r="C140" s="230"/>
     </row>
     <row r="141" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="90" t="s">
@@ -3913,19 +3913,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A139:C140"/>
@@ -3942,6 +3929,19 @@
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A105:B107"/>
     <mergeCell ref="A109:B111"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3976,15 +3976,15 @@
       <c r="A1" s="124"/>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
+      <c r="F1" s="243"/>
+      <c r="G1" s="243"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="243"/>
+      <c r="J1" s="243"/>
+      <c r="K1" s="243"/>
+      <c r="L1" s="243"/>
       <c r="M1" s="126"/>
     </row>
     <row r="2" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3994,10 +3994,10 @@
       <c r="D2" s="129" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="263">
+      <c r="E2" s="265">
         <v>3000000</v>
       </c>
-      <c r="F2" s="263"/>
+      <c r="F2" s="265"/>
       <c r="G2" s="129"/>
       <c r="H2" s="129"/>
       <c r="I2" s="129" t="s">
@@ -4028,195 +4028,195 @@
       <c r="N3" s="96"/>
     </row>
     <row r="4" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="240" t="s">
+      <c r="A4" s="244" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="241"/>
-      <c r="C4" s="241"/>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="M4" s="242"/>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="M4" s="246"/>
       <c r="N4" s="96"/>
     </row>
     <row r="5" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="243"/>
-      <c r="B5" s="244"/>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="M5" s="245"/>
+      <c r="A5" s="247"/>
+      <c r="B5" s="248"/>
+      <c r="C5" s="248"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="M5" s="249"/>
       <c r="N5" s="96"/>
     </row>
     <row r="6" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="243"/>
-      <c r="B6" s="244"/>
-      <c r="C6" s="244"/>
-      <c r="D6" s="244"/>
-      <c r="E6" s="244"/>
-      <c r="F6" s="244"/>
-      <c r="G6" s="244"/>
-      <c r="H6" s="244"/>
-      <c r="I6" s="244"/>
-      <c r="J6" s="244"/>
-      <c r="K6" s="244"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="245"/>
+      <c r="A6" s="247"/>
+      <c r="B6" s="248"/>
+      <c r="C6" s="248"/>
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="248"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="248"/>
+      <c r="I6" s="248"/>
+      <c r="J6" s="248"/>
+      <c r="K6" s="248"/>
+      <c r="L6" s="248"/>
+      <c r="M6" s="249"/>
       <c r="N6" s="96"/>
     </row>
     <row r="7" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="243"/>
-      <c r="B7" s="244"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="244"/>
-      <c r="E7" s="244"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
-      <c r="H7" s="244"/>
-      <c r="I7" s="244"/>
-      <c r="J7" s="244"/>
-      <c r="K7" s="244"/>
-      <c r="L7" s="244"/>
-      <c r="M7" s="245"/>
+      <c r="A7" s="247"/>
+      <c r="B7" s="248"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="248"/>
+      <c r="K7" s="248"/>
+      <c r="L7" s="248"/>
+      <c r="M7" s="249"/>
       <c r="N7" s="96"/>
     </row>
     <row r="8" spans="1:15" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="246"/>
-      <c r="B8" s="247"/>
-      <c r="C8" s="247"/>
-      <c r="D8" s="247"/>
-      <c r="E8" s="247"/>
-      <c r="F8" s="247"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="247"/>
-      <c r="I8" s="247"/>
-      <c r="J8" s="247"/>
-      <c r="K8" s="247"/>
-      <c r="L8" s="247"/>
-      <c r="M8" s="248"/>
+      <c r="A8" s="250"/>
+      <c r="B8" s="251"/>
+      <c r="C8" s="251"/>
+      <c r="D8" s="251"/>
+      <c r="E8" s="251"/>
+      <c r="F8" s="251"/>
+      <c r="G8" s="251"/>
+      <c r="H8" s="251"/>
+      <c r="I8" s="251"/>
+      <c r="J8" s="251"/>
+      <c r="K8" s="251"/>
+      <c r="L8" s="251"/>
+      <c r="M8" s="252"/>
     </row>
     <row r="9" spans="1:15" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="236" t="s">
+      <c r="A9" s="240" t="s">
         <v>254</v>
       </c>
-      <c r="B9" s="237"/>
-      <c r="C9" s="237"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="237"/>
-      <c r="F9" s="237"/>
-      <c r="G9" s="237"/>
-      <c r="H9" s="237"/>
-      <c r="I9" s="237"/>
-      <c r="J9" s="237"/>
-      <c r="K9" s="237"/>
-      <c r="L9" s="237"/>
-      <c r="M9" s="238"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
+      <c r="M9" s="242"/>
     </row>
     <row r="10" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="257" t="s">
+      <c r="A10" s="259" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="258"/>
-      <c r="C10" s="258"/>
-      <c r="D10" s="258"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="258"/>
-      <c r="G10" s="258"/>
-      <c r="H10" s="258"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
-      <c r="M10" s="259"/>
+      <c r="B10" s="260"/>
+      <c r="C10" s="260"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="260"/>
+      <c r="J10" s="260"/>
+      <c r="K10" s="260"/>
+      <c r="L10" s="260"/>
+      <c r="M10" s="261"/>
     </row>
     <row r="11" spans="1:15" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="260" t="s">
+      <c r="A11" s="262" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="261"/>
-      <c r="C11" s="261"/>
-      <c r="D11" s="261"/>
-      <c r="E11" s="261"/>
-      <c r="F11" s="261"/>
-      <c r="G11" s="261"/>
-      <c r="H11" s="261"/>
-      <c r="I11" s="261"/>
-      <c r="J11" s="261"/>
-      <c r="K11" s="261"/>
-      <c r="L11" s="261"/>
-      <c r="M11" s="262"/>
+      <c r="B11" s="263"/>
+      <c r="C11" s="263"/>
+      <c r="D11" s="263"/>
+      <c r="E11" s="263"/>
+      <c r="F11" s="263"/>
+      <c r="G11" s="263"/>
+      <c r="H11" s="263"/>
+      <c r="I11" s="263"/>
+      <c r="J11" s="263"/>
+      <c r="K11" s="263"/>
+      <c r="L11" s="263"/>
+      <c r="M11" s="264"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="249" t="s">
+      <c r="A12" s="253" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="251" t="s">
+      <c r="B12" s="255" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="251" t="s">
+      <c r="C12" s="255" t="s">
         <v>133</v>
       </c>
-      <c r="D12" s="251" t="s">
+      <c r="D12" s="255" t="s">
         <v>134</v>
       </c>
-      <c r="E12" s="253" t="s">
+      <c r="E12" s="233" t="s">
         <v>135</v>
       </c>
-      <c r="F12" s="251" t="s">
+      <c r="F12" s="255" t="s">
         <v>136</v>
       </c>
-      <c r="G12" s="255" t="s">
+      <c r="G12" s="257" t="s">
         <v>137</v>
       </c>
-      <c r="H12" s="253" t="s">
+      <c r="H12" s="233" t="s">
         <v>138</v>
       </c>
-      <c r="I12" s="253" t="s">
+      <c r="I12" s="233" t="s">
         <v>130</v>
       </c>
-      <c r="J12" s="253" t="s">
+      <c r="J12" s="233" t="s">
         <v>129</v>
       </c>
-      <c r="K12" s="264" t="s">
+      <c r="K12" s="235" t="s">
         <v>246</v>
       </c>
       <c r="L12" s="195" t="s">
         <v>139</v>
       </c>
-      <c r="M12" s="233" t="s">
+      <c r="M12" s="237" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="250"/>
-      <c r="B13" s="252"/>
-      <c r="C13" s="252"/>
-      <c r="D13" s="252"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="252"/>
-      <c r="G13" s="256"/>
-      <c r="H13" s="254"/>
-      <c r="I13" s="254"/>
-      <c r="J13" s="254"/>
-      <c r="K13" s="265"/>
+      <c r="A13" s="254"/>
+      <c r="B13" s="256"/>
+      <c r="C13" s="256"/>
+      <c r="D13" s="256"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="256"/>
+      <c r="G13" s="258"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="234"/>
+      <c r="J13" s="234"/>
+      <c r="K13" s="236"/>
       <c r="L13" s="196" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="M13" s="234"/>
+      <c r="M13" s="238"/>
     </row>
     <row r="14" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="179">
@@ -9272,92 +9272,87 @@
     </row>
     <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="121" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="235" t="s">
+      <c r="B121" s="239" t="s">
         <v>105</v>
       </c>
-      <c r="C121" s="235"/>
-      <c r="D121" s="235"/>
-      <c r="E121" s="235"/>
-      <c r="F121" s="235"/>
-      <c r="G121" s="235"/>
-      <c r="H121" s="235"/>
-      <c r="I121" s="235"/>
-      <c r="J121" s="235"/>
-      <c r="K121" s="235"/>
-      <c r="L121" s="235"/>
+      <c r="C121" s="239"/>
+      <c r="D121" s="239"/>
+      <c r="E121" s="239"/>
+      <c r="F121" s="239"/>
+      <c r="G121" s="239"/>
+      <c r="H121" s="239"/>
+      <c r="I121" s="239"/>
+      <c r="J121" s="239"/>
+      <c r="K121" s="239"/>
+      <c r="L121" s="239"/>
     </row>
     <row r="122" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="235"/>
-      <c r="C122" s="235"/>
-      <c r="D122" s="235"/>
-      <c r="E122" s="235"/>
-      <c r="F122" s="235"/>
-      <c r="G122" s="235"/>
-      <c r="H122" s="235"/>
-      <c r="I122" s="235"/>
-      <c r="J122" s="235"/>
-      <c r="K122" s="235"/>
-      <c r="L122" s="235"/>
+      <c r="B122" s="239"/>
+      <c r="C122" s="239"/>
+      <c r="D122" s="239"/>
+      <c r="E122" s="239"/>
+      <c r="F122" s="239"/>
+      <c r="G122" s="239"/>
+      <c r="H122" s="239"/>
+      <c r="I122" s="239"/>
+      <c r="J122" s="239"/>
+      <c r="K122" s="239"/>
+      <c r="L122" s="239"/>
     </row>
     <row r="123" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="235"/>
-      <c r="C123" s="235"/>
-      <c r="D123" s="235"/>
-      <c r="E123" s="235"/>
-      <c r="F123" s="235"/>
-      <c r="G123" s="235"/>
-      <c r="H123" s="235"/>
-      <c r="I123" s="235"/>
-      <c r="J123" s="235"/>
-      <c r="K123" s="235"/>
-      <c r="L123" s="235"/>
+      <c r="B123" s="239"/>
+      <c r="C123" s="239"/>
+      <c r="D123" s="239"/>
+      <c r="E123" s="239"/>
+      <c r="F123" s="239"/>
+      <c r="G123" s="239"/>
+      <c r="H123" s="239"/>
+      <c r="I123" s="239"/>
+      <c r="J123" s="239"/>
+      <c r="K123" s="239"/>
+      <c r="L123" s="239"/>
     </row>
     <row r="124" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="235"/>
-      <c r="C124" s="235"/>
-      <c r="D124" s="235"/>
-      <c r="E124" s="235"/>
-      <c r="F124" s="235"/>
-      <c r="G124" s="235"/>
-      <c r="H124" s="235"/>
-      <c r="I124" s="235"/>
-      <c r="J124" s="235"/>
-      <c r="K124" s="235"/>
-      <c r="L124" s="235"/>
+      <c r="B124" s="239"/>
+      <c r="C124" s="239"/>
+      <c r="D124" s="239"/>
+      <c r="E124" s="239"/>
+      <c r="F124" s="239"/>
+      <c r="G124" s="239"/>
+      <c r="H124" s="239"/>
+      <c r="I124" s="239"/>
+      <c r="J124" s="239"/>
+      <c r="K124" s="239"/>
+      <c r="L124" s="239"/>
     </row>
     <row r="125" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="235"/>
-      <c r="C125" s="235"/>
-      <c r="D125" s="235"/>
-      <c r="E125" s="235"/>
-      <c r="F125" s="235"/>
-      <c r="G125" s="235"/>
-      <c r="H125" s="235"/>
-      <c r="I125" s="235"/>
-      <c r="J125" s="235"/>
-      <c r="K125" s="235"/>
-      <c r="L125" s="235"/>
+      <c r="B125" s="239"/>
+      <c r="C125" s="239"/>
+      <c r="D125" s="239"/>
+      <c r="E125" s="239"/>
+      <c r="F125" s="239"/>
+      <c r="G125" s="239"/>
+      <c r="H125" s="239"/>
+      <c r="I125" s="239"/>
+      <c r="J125" s="239"/>
+      <c r="K125" s="239"/>
+      <c r="L125" s="239"/>
     </row>
     <row r="126" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="235"/>
-      <c r="C126" s="235"/>
-      <c r="D126" s="235"/>
-      <c r="E126" s="235"/>
-      <c r="F126" s="235"/>
-      <c r="G126" s="235"/>
-      <c r="H126" s="235"/>
-      <c r="I126" s="235"/>
-      <c r="J126" s="235"/>
-      <c r="K126" s="235"/>
-      <c r="L126" s="235"/>
+      <c r="B126" s="239"/>
+      <c r="C126" s="239"/>
+      <c r="D126" s="239"/>
+      <c r="E126" s="239"/>
+      <c r="F126" s="239"/>
+      <c r="G126" s="239"/>
+      <c r="H126" s="239"/>
+      <c r="I126" s="239"/>
+      <c r="J126" s="239"/>
+      <c r="K126" s="239"/>
+      <c r="L126" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="B121:L126"/>
     <mergeCell ref="A9:M9"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="A4:M8"/>
@@ -9372,6 +9367,11 @@
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A11:M11"/>
     <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="B121:L126"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9427,10 +9427,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="280" t="s">
+      <c r="C4" s="266" t="s">
         <v>256</v>
       </c>
-      <c r="D4" s="280"/>
+      <c r="D4" s="266"/>
       <c r="E4" s="201"/>
       <c r="F4" s="199" t="s">
         <v>257</v>
@@ -9438,16 +9438,16 @@
       <c r="H4" t="s">
         <v>258</v>
       </c>
-      <c r="J4" s="270" t="s">
+      <c r="J4" s="268" t="s">
         <v>260</v>
       </c>
-      <c r="K4" s="270"/>
+      <c r="K4" s="268"/>
     </row>
     <row r="5" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C5" s="269">
+      <c r="C5" s="267">
         <v>168835.53000000003</v>
       </c>
-      <c r="D5" s="269"/>
+      <c r="D5" s="267"/>
       <c r="E5" s="202"/>
       <c r="F5" s="200">
         <f>C5</f>
@@ -9456,18 +9456,18 @@
       <c r="H5" s="80">
         <v>0</v>
       </c>
-      <c r="J5" s="281">
+      <c r="J5" s="269">
         <f>F5</f>
         <v>168835.53000000003</v>
       </c>
-      <c r="K5" s="281"/>
+      <c r="K5" s="269"/>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="M7" s="268" t="s">
+      <c r="M7" s="272" t="s">
         <v>262</v>
       </c>
-      <c r="N7" s="268"/>
-      <c r="O7" s="268"/>
+      <c r="N7" s="272"/>
+      <c r="O7" s="272"/>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
@@ -9479,19 +9479,19 @@
       <c r="H8" t="s">
         <v>258</v>
       </c>
-      <c r="J8" s="270" t="s">
+      <c r="J8" s="268" t="s">
         <v>261</v>
       </c>
-      <c r="K8" s="270"/>
-      <c r="M8" s="268"/>
-      <c r="N8" s="268"/>
-      <c r="O8" s="268"/>
+      <c r="K8" s="268"/>
+      <c r="M8" s="272"/>
+      <c r="N8" s="272"/>
+      <c r="O8" s="272"/>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="269">
+      <c r="C9" s="267">
         <v>168836.53</v>
       </c>
-      <c r="D9" s="269"/>
+      <c r="D9" s="267"/>
       <c r="F9" s="80">
         <v>0</v>
       </c>
@@ -9499,16 +9499,16 @@
         <f>C9-F9</f>
         <v>168836.53</v>
       </c>
-      <c r="J9" s="269">
+      <c r="J9" s="267">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K9" s="269"/>
-      <c r="M9" s="267">
+      <c r="K9" s="267"/>
+      <c r="M9" s="271">
         <v>300737.53000000003</v>
       </c>
-      <c r="N9" s="267"/>
-      <c r="O9" s="267"/>
+      <c r="N9" s="271"/>
+      <c r="O9" s="271"/>
     </row>
     <row r="10" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="202"/>
@@ -9522,11 +9522,11 @@
       <c r="O10" s="203"/>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="M11" s="274" t="s">
+      <c r="M11" s="276" t="s">
         <v>262</v>
       </c>
-      <c r="N11" s="275"/>
-      <c r="O11" s="276"/>
+      <c r="N11" s="277"/>
+      <c r="O11" s="278"/>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
@@ -9538,20 +9538,20 @@
       <c r="H12" t="s">
         <v>258</v>
       </c>
-      <c r="J12" s="270" t="s">
+      <c r="J12" s="268" t="s">
         <v>264</v>
       </c>
-      <c r="K12" s="270"/>
-      <c r="M12" s="277"/>
-      <c r="N12" s="278"/>
-      <c r="O12" s="279"/>
+      <c r="K12" s="268"/>
+      <c r="M12" s="279"/>
+      <c r="N12" s="280"/>
+      <c r="O12" s="281"/>
     </row>
     <row r="13" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="269">
+      <c r="C13" s="267">
         <f>M9</f>
         <v>300737.53000000003</v>
       </c>
-      <c r="D13" s="269"/>
+      <c r="D13" s="267"/>
       <c r="F13" s="80">
         <v>98556.53</v>
       </c>
@@ -9559,132 +9559,127 @@
         <f>C13-F13</f>
         <v>202181.00000000003</v>
       </c>
-      <c r="J13" s="269">
+      <c r="J13" s="267">
         <f>33600+135235.8</f>
         <v>168835.8</v>
       </c>
-      <c r="K13" s="269"/>
-      <c r="M13" s="271">
+      <c r="K13" s="267"/>
+      <c r="M13" s="273">
         <f>J13+H13-0.27</f>
         <v>371016.53</v>
       </c>
-      <c r="N13" s="272"/>
-      <c r="O13" s="273"/>
+      <c r="N13" s="274"/>
+      <c r="O13" s="275"/>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C15" s="266" t="s">
+      <c r="C15" s="270" t="s">
         <v>266</v>
       </c>
-      <c r="D15" s="266"/>
-      <c r="E15" s="266"/>
-      <c r="F15" s="266"/>
-      <c r="G15" s="266"/>
-      <c r="H15" s="266"/>
-      <c r="I15" s="266"/>
-      <c r="J15" s="266"/>
-      <c r="K15" s="266"/>
-      <c r="L15" s="266"/>
-      <c r="M15" s="266"/>
-      <c r="N15" s="266"/>
-      <c r="O15" s="266"/>
+      <c r="D15" s="270"/>
+      <c r="E15" s="270"/>
+      <c r="F15" s="270"/>
+      <c r="G15" s="270"/>
+      <c r="H15" s="270"/>
+      <c r="I15" s="270"/>
+      <c r="J15" s="270"/>
+      <c r="K15" s="270"/>
+      <c r="L15" s="270"/>
+      <c r="M15" s="270"/>
+      <c r="N15" s="270"/>
+      <c r="O15" s="270"/>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="266"/>
-      <c r="D16" s="266"/>
-      <c r="E16" s="266"/>
-      <c r="F16" s="266"/>
-      <c r="G16" s="266"/>
-      <c r="H16" s="266"/>
-      <c r="I16" s="266"/>
-      <c r="J16" s="266"/>
-      <c r="K16" s="266"/>
-      <c r="L16" s="266"/>
-      <c r="M16" s="266"/>
-      <c r="N16" s="266"/>
-      <c r="O16" s="266"/>
+      <c r="C16" s="270"/>
+      <c r="D16" s="270"/>
+      <c r="E16" s="270"/>
+      <c r="F16" s="270"/>
+      <c r="G16" s="270"/>
+      <c r="H16" s="270"/>
+      <c r="I16" s="270"/>
+      <c r="J16" s="270"/>
+      <c r="K16" s="270"/>
+      <c r="L16" s="270"/>
+      <c r="M16" s="270"/>
+      <c r="N16" s="270"/>
+      <c r="O16" s="270"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C17" s="266"/>
-      <c r="D17" s="266"/>
-      <c r="E17" s="266"/>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
-      <c r="J17" s="266"/>
-      <c r="K17" s="266"/>
-      <c r="L17" s="266"/>
-      <c r="M17" s="266"/>
-      <c r="N17" s="266"/>
-      <c r="O17" s="266"/>
+      <c r="C17" s="270"/>
+      <c r="D17" s="270"/>
+      <c r="E17" s="270"/>
+      <c r="F17" s="270"/>
+      <c r="G17" s="270"/>
+      <c r="H17" s="270"/>
+      <c r="I17" s="270"/>
+      <c r="J17" s="270"/>
+      <c r="K17" s="270"/>
+      <c r="L17" s="270"/>
+      <c r="M17" s="270"/>
+      <c r="N17" s="270"/>
+      <c r="O17" s="270"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C18" s="266"/>
-      <c r="D18" s="266"/>
-      <c r="E18" s="266"/>
-      <c r="F18" s="266"/>
-      <c r="G18" s="266"/>
-      <c r="H18" s="266"/>
-      <c r="I18" s="266"/>
-      <c r="J18" s="266"/>
-      <c r="K18" s="266"/>
-      <c r="L18" s="266"/>
-      <c r="M18" s="266"/>
-      <c r="N18" s="266"/>
-      <c r="O18" s="266"/>
+      <c r="C18" s="270"/>
+      <c r="D18" s="270"/>
+      <c r="E18" s="270"/>
+      <c r="F18" s="270"/>
+      <c r="G18" s="270"/>
+      <c r="H18" s="270"/>
+      <c r="I18" s="270"/>
+      <c r="J18" s="270"/>
+      <c r="K18" s="270"/>
+      <c r="L18" s="270"/>
+      <c r="M18" s="270"/>
+      <c r="N18" s="270"/>
+      <c r="O18" s="270"/>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C19" s="266"/>
-      <c r="D19" s="266"/>
-      <c r="E19" s="266"/>
-      <c r="F19" s="266"/>
-      <c r="G19" s="266"/>
-      <c r="H19" s="266"/>
-      <c r="I19" s="266"/>
-      <c r="J19" s="266"/>
-      <c r="K19" s="266"/>
-      <c r="L19" s="266"/>
-      <c r="M19" s="266"/>
-      <c r="N19" s="266"/>
-      <c r="O19" s="266"/>
+      <c r="C19" s="270"/>
+      <c r="D19" s="270"/>
+      <c r="E19" s="270"/>
+      <c r="F19" s="270"/>
+      <c r="G19" s="270"/>
+      <c r="H19" s="270"/>
+      <c r="I19" s="270"/>
+      <c r="J19" s="270"/>
+      <c r="K19" s="270"/>
+      <c r="L19" s="270"/>
+      <c r="M19" s="270"/>
+      <c r="N19" s="270"/>
+      <c r="O19" s="270"/>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C20" s="266"/>
-      <c r="D20" s="266"/>
-      <c r="E20" s="266"/>
-      <c r="F20" s="266"/>
-      <c r="G20" s="266"/>
-      <c r="H20" s="266"/>
-      <c r="I20" s="266"/>
-      <c r="J20" s="266"/>
-      <c r="K20" s="266"/>
-      <c r="L20" s="266"/>
-      <c r="M20" s="266"/>
-      <c r="N20" s="266"/>
-      <c r="O20" s="266"/>
+      <c r="C20" s="270"/>
+      <c r="D20" s="270"/>
+      <c r="E20" s="270"/>
+      <c r="F20" s="270"/>
+      <c r="G20" s="270"/>
+      <c r="H20" s="270"/>
+      <c r="I20" s="270"/>
+      <c r="J20" s="270"/>
+      <c r="K20" s="270"/>
+      <c r="L20" s="270"/>
+      <c r="M20" s="270"/>
+      <c r="N20" s="270"/>
+      <c r="O20" s="270"/>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="266"/>
-      <c r="D21" s="266"/>
-      <c r="E21" s="266"/>
-      <c r="F21" s="266"/>
-      <c r="G21" s="266"/>
-      <c r="H21" s="266"/>
-      <c r="I21" s="266"/>
-      <c r="J21" s="266"/>
-      <c r="K21" s="266"/>
-      <c r="L21" s="266"/>
-      <c r="M21" s="266"/>
-      <c r="N21" s="266"/>
-      <c r="O21" s="266"/>
+      <c r="C21" s="270"/>
+      <c r="D21" s="270"/>
+      <c r="E21" s="270"/>
+      <c r="F21" s="270"/>
+      <c r="G21" s="270"/>
+      <c r="H21" s="270"/>
+      <c r="I21" s="270"/>
+      <c r="J21" s="270"/>
+      <c r="K21" s="270"/>
+      <c r="L21" s="270"/>
+      <c r="M21" s="270"/>
+      <c r="N21" s="270"/>
+      <c r="O21" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J8:K8"/>
     <mergeCell ref="C15:O21"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="M7:O8"/>
@@ -9695,6 +9690,11 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M11:O12"/>
     <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J8:K8"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="125" orientation="landscape" r:id="rId1"/>
